--- a/testrail-import/Report-Suite_Technician-Utilization-Report_testrail-import.xlsx
+++ b/testrail-import/Report-Suite_Technician-Utilization-Report_testrail-import.xlsx
@@ -490,7 +490,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Technician Utilization appears in the reports navigation under the Performance group</t>
+          <t>Technician Utilization sits under Performance, below existing report links</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -517,18 +517,20 @@
         <is>
           <t>1. Open the reports navigation.
 2. Look under the Performance group.
-3. Click the entry labeled Technician Utilization.</t>
+3. Click the entry labeled Technician Utilization.
+4. Note where the entry sits relative to the report links that existed before this release.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
           <t>1. The report is listed under the Performance group, labeled "Technician Utilization".
-2. Clicking it opens the report.</t>
+2. Clicking it opens the report.
+3. The entry sits BELOW the previously existing report links (toward the bottom) — the new reports are added without moving or disturbing the existing entries.</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>specs/technician-utilization.md S1-R1</t>
+          <t>SV-8648 (specs/technician-utilization.md S1-R1 — nav placement tightened per kickoff video P3 05:11-05:19 [below existing items, additive not interruptive], user ruling 2026-07-28: video overrides spec (video newer, last-update-wins))</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr"/>
@@ -2889,7 +2891,7 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>The Location filter is the rightmost multi-select listing accessible locations, with All Locations acting as a select-all shortcut</t>
+          <t>The Location filter is the rightmost multi-select; All Locations = select-all</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
@@ -2917,19 +2919,21 @@
         <is>
           <t>1. Look at the rightmost control in the toolbar and read its label.
 2. Open it and read the listed options.
-3. Choose "All Locations", then uncheck one individual location.</t>
+3. Choose "All Locations", then uncheck one individual location.
+4. With every accessible location selected, look at how the report tells you which location the shown data belongs to.</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
           <t>1. The toolbar has a location filter labeled "Location" - a multi-select and the RIGHTMOST control.
 2. It lists the locations the signed-in user has access to, plus an "All Locations" option.
-3. "All Locations" acts as a select-all shortcut: choosing it selects every accessible location; unchecking one location leaves the remaining specific locations selected - the selection is always the concrete set of checked locations.</t>
+3. "All Locations" acts as a select-all shortcut: choosing it selects every accessible location; unchecking one location leaves the remaining specific locations selected - the selection is always the concrete set of checked locations.
+4. With all locations selected you can tell which location the shown data belongs to — a location label or marking is shown. (Exactly where and how it appears is confirmed in the build; this report pools each technician's hours into one row, so the marking may take a different form here.)</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>specs/technician-utilization.md S9-R1</t>
+          <t>SV-8656 (specs/technician-utilization.md S9-R1 — per-row location identifier in All-Locations view ADDED per kickoff video P10 40:58-41:20, user ruling 2026-07-28: video overrides spec (video newer, last-update-wins))</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr"/>
@@ -3082,7 +3086,7 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>A user with access to only one location still sees the Location filter with a single selectable location</t>
+          <t>The Location filter is hidden for a user with access to only one location</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
@@ -3108,18 +3112,19 @@
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>1. Look at the Location filter and open it.</t>
+          <t>1. Look for the Location filter in the toolbar.
+2. Then sign in as a user with access to two or more locations and look again.</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>1. The filter is still shown, with a single selectable location.
-2. Report behavior is unchanged from single-location use.</t>
+          <t>1. For the single-location user the Location filter is NOT shown at all — the report simply shows that one location's data.
+2. For the user with access to two or more locations the Location filter IS shown.</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>specs/technician-utilization.md S9-N1</t>
+          <t>SV-8656 (specs/technician-utilization.md S9-N1 — expectation FLIPPED by kickoff video P33 46:10-46:28, user ruling 2026-07-28: video overrides spec (video newer, last-update-wins))</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr"/>

--- a/testrail-import/Report-Suite_Technician-Utilization-Report_testrail-import.xlsx
+++ b/testrail-import/Report-Suite_Technician-Utilization-Report_testrail-import.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J60"/>
+  <dimension ref="A1:J58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
@@ -825,7 +825,7 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>The standard no-data message shows when no technician clocked time in scope</t>
+          <t>Standard no-data message when no time in scope or all technicians cleared</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
@@ -845,25 +845,27 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1. A date range exists in which no technician clocked any time at the selected location(s), or a selectable location has no clocked time for the range.</t>
+          <t>1. A date range exists in which no technician clocked any time at the selected location(s), or a selectable location has no clocked time for the range.
+2. For the cleared-filter check: the report can also be loaded with rows showing.</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
           <t>1. Select that empty date range (or the empty location) and let the report load.
-2. Read the message in the data area and look for the Summary row.</t>
+2. Read the message in the data area and look for the Summary row.
+3. Separately, with rows loaded, use "Clear all" in the Filter by Technician filter and re-read the data area and the Summary row.</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
           <t>1. Instead of rows, the data area shows exactly: "Empty bays, endless possibilities. Get Going!" (the application's standard reports no-data label).
 2. The Summary row is hidden.
-3. The same message is used whether the cause is genuinely no data or a cleared technician filter - this version does not use distinct copy for the two.</t>
+3. Clearing every technician shows the SAME message and hides the Summary row — this version does not use distinct copy for genuinely-no-data vs a cleared filter.</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>specs/technician-utilization.md S1-N2; S9-N2; §7</t>
+          <t>specs/technician-utilization.md S1-N2; S9-N2; S5-N1; S3-N1; §7</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr"/>
@@ -872,7 +874,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>Column headers appear in the fixed order ending with Est. Lost Labor</t>
+          <t>Headers in fixed order; Total, WO and Internal Hours show clocked hours (2 dp)</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
@@ -887,27 +889,35 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1. You are on the Technician Utilization report with rows loaded.</t>
+          <t>1. A technician with known clocked time in the range: some clocked to work orders and some to an internal, non-billable activity (e.g. shop cleanup or a staff meeting).
+2. Part of the internal time was clocked at a location with NO default labor rate configured (for the completeness check).</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>1. Read the column headers left to right.</t>
+          <t>1. Read the column headers left to right.
+2. Read the technician's Total Hours, WO Hours, and Internal Hours.
+3. Compare against the known clock records.
+4. Check the number format on a value over 100 hours.</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>1. The headers appear in exactly this order: Technician, Total Hours, WO Hours, Internal Hours, Utilization %, Est. Lost Labor.</t>
+          <t>1. The headers appear in exactly this order: Technician, Total Hours, WO Hours, Internal Hours, Utilization %, Est. Lost Labor.
+2. Total Hours = all time the technician was clocked in for the range.
+3. WO Hours = time clocked directly to work orders; Internal Hours = time clocked to internal, non-billable activities.
+4. Internal Hours includes ALL internal time - including hours at a location with no configured labor rate.
+5. Hours show two decimal places with NO thousands separator (e.g. "107.70"), rounded from the unrounded hours using round-half-up (a tie rounds away from zero - 0.005 → 0.01).</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>specs/technician-utilization.md S2-R1</t>
+          <t>specs/technician-utilization.md S2-R1; S2-R2; S2-R3; S2-R4; S2-R5; §3</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr"/>
@@ -916,7 +926,7 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>Total, WO, and Internal Hours show the range's clocked hours in two decimals with no thousands separator</t>
+          <t>Utilization % is WO hours over total hours computed from unrounded values, shown to one decimal with round-half-up</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
@@ -936,28 +946,24 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1. A technician with known clocked time in the range: some clocked to work orders and some to an internal, non-billable activity (e.g. shop cleanup or a staff meeting).
-2. Part of the internal time was clocked at a location with NO default labor rate configured (for the completeness check).</t>
+          <t>1. A technician whose unrounded WO and total hours produce a checkable percentage - ideally one landing on a rounding tie (e.g. computing to 66.65%).</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1. Read the technician's Total Hours, WO Hours, and Internal Hours.
-2. Compare against the known clock records.
-3. Check the number format on a value over 100 hours.</t>
+          <t>1. Compute the expected value by hand: work-order hours ÷ total clocked hours × 100, from the UNROUNDED hours.
+2. Read the technician's Utilization % and compare.</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>1. Total Hours = all time the technician was clocked in for the range.
-2. WO Hours = time clocked directly to work orders; Internal Hours = time clocked to internal, non-billable activities.
-3. Internal Hours includes ALL internal time - including hours at a location with no configured labor rate.
-4. Hours show two decimal places with NO thousands separator (e.g. "107.70"), rounded from the unrounded hours using round-half-up (a tie rounds away from zero - 0.005 → 0.01).</t>
+          <t>1. Utilization % = work-order hours as a percentage of total clocked hours, computed from the unrounded hours (not from the already-rounded displays).
+2. It shows one decimal place followed by a percent sign, rounded round-half-up (66.65% → 66.7%).</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>specs/technician-utilization.md S2-R2; S2-R3; S2-R4; S2-R5; §3</t>
+          <t>specs/technician-utilization.md S2-R6; S2-R7; §3</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr"/>
@@ -966,7 +972,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>Utilization % is WO hours over total hours computed from unrounded values, shown to one decimal with round-half-up</t>
+          <t>A technician with only internal hours shows 0.0% utilization, and utilization never exceeds 100%</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
@@ -981,398 +987,352 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>1. A technician whose unrounded WO and total hours produce a checkable percentage - ideally one landing on a rounding tie (e.g. computing to 66.65%).</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>1. Compute the expected value by hand: work-order hours ÷ total clocked hours × 100, from the UNROUNDED hours.
-2. Read the technician's Utilization % and compare.</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>1. Utilization % = work-order hours as a percentage of total clocked hours, computed from the unrounded hours (not from the already-rounded displays).
-2. It shows one decimal place followed by a percent sign, rounded round-half-up (66.65% → 66.7%).</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>specs/technician-utilization.md S2-R6; S2-R7; §3</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr"/>
-      <c r="J12" s="2" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>A technician with only internal hours shows 0.0% utilization, and utilization never exceeds 100%</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>TU — Hours &amp; Utilization</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
         <is>
           <t>1. A technician with internal hours but ZERO work-order hours in the range.
 2. Other technicians with mixed hours for the upper-bound check.</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="F12" s="2" t="inlineStr">
         <is>
           <t>1. Read the internal-only technician's Utilization %.
 2. Scan every row's Utilization %.</t>
         </is>
       </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>1. The internal-only technician shows "0.0%".
 2. No row shows more than 100% - work-order hours are always part of total clocked hours.
 3. The "—" (undefined, total = 0) state is unreachable on a rendered technician or day row, because only technicians with clocked time get rows.</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>specs/technician-utilization.md S2-E1; S2-R7; S2 context note</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr"/>
-      <c r="J13" s="2" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="2" t="inlineStr">
+      <c r="I12" s="2" t="inlineStr"/>
+      <c r="J12" s="2" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
         <is>
           <t>Est. Lost Labor values internal hours at each location's default labor rate, summed at full precision and rounded once</t>
         </is>
       </c>
-      <c r="B14" s="2" t="inlineStr">
+      <c r="B13" s="2" t="inlineStr">
         <is>
           <t>TU — Est. Lost Labor</t>
         </is>
       </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="E13" s="2" t="inlineStr">
         <is>
           <t>1. Location A has default labor rate $R1 and location B has a different default labor rate $R2.
 2. A technician clocked known internal hours at A and known internal hours at B in the range.
 3. Both locations are selected in the location filter.</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="F13" s="2" t="inlineStr">
         <is>
           <t>1. Compute by hand: (R1 × internal hours at A) + (R2 × internal hours at B), keeping full precision, rounding only the final total (round-half-up).
 2. Read the technician's Est. Lost Labor and compare.
 3. Repeat with only one location selected.</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="G13" s="2" t="inlineStr">
         <is>
           <t>1. Est. Lost Labor = the sum, per contributing location, of that location's default labor rate × the technician's internal hours clocked there - summed at full precision, with the technician's total rounded ONCE (round-half-up).
 2. In a single-location view it is simply that one location's rate × the technician's internal hours.
 3. The value shows as dollars with two decimals and commas between thousands (e.g. "$1,234.50").</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>specs/technician-utilization.md S2-R8; S2-R9; §3</t>
         </is>
       </c>
-      <c r="I14" s="2" t="inlineStr"/>
-      <c r="J14" s="2" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="2" t="inlineStr">
+      <c r="I13" s="2" t="inlineStr"/>
+      <c r="J13" s="2" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
         <is>
           <t>Est. Lost Labor is pinned far right and bold, and only its header carries the info icon with the exact tooltip text</t>
         </is>
       </c>
-      <c r="B15" s="2" t="inlineStr">
+      <c r="B14" s="2" t="inlineStr">
         <is>
           <t>TU — Est. Lost Labor</t>
         </is>
       </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="E14" s="2" t="inlineStr">
         <is>
           <t>1. You are on the Technician Utilization report with rows loaded.</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="F14" s="2" t="inlineStr">
         <is>
           <t>1. Look at the position and weight of the Est. Lost Labor column (header and cells).
 2. Hover the information icon on the Est. Lost Labor header and read the text; also reach it by keyboard focus and by tap on a touch device.
 3. Check every other column header for an information icon.</t>
         </is>
       </c>
-      <c r="G15" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>1. The Est. Lost Labor column is pinned to the far right; its cells are bold and its header is bold, matching.
 2. The information icon shows exactly: "Internal hours valued at each location's default labor rate" - on hover, on keyboard focus, and on tap; it is dismissible.
 3. NO column header other than Est. Lost Labor shows the information icon.</t>
         </is>
       </c>
-      <c r="H15" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>specs/technician-utilization.md S2-R10; S2-R11; S8-R4; S8-R6; S8-R7; S8-N1</t>
         </is>
       </c>
-      <c r="I15" s="2" t="inlineStr"/>
-      <c r="J15" s="2" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr"/>
+      <c r="J14" s="2" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
         <is>
           <t>Zero internal hours - or a configured $0.00 rate - shows $0.00, never an em-dash</t>
         </is>
       </c>
-      <c r="B16" s="2" t="inlineStr">
+      <c r="B15" s="2" t="inlineStr">
         <is>
           <t>TU — Est. Lost Labor</t>
         </is>
       </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="E15" s="2" t="inlineStr">
         <is>
           <t>1. Technician A has zero internal hours in the range (all time on work orders).
 2. Technician B has internal hours at a location whose default labor rate is configured as exactly $0.00.</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="F15" s="2" t="inlineStr">
         <is>
           <t>1. Read technician A's Est. Lost Labor.
 2. Read technician B's Est. Lost Labor.</t>
         </is>
       </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="G15" s="2" t="inlineStr">
         <is>
           <t>1. Technician A shows "$0.00" - there is nothing to value, regardless of whether the location has a rate configured.
 2. Technician B also shows "$0.00" - a configured rate of exactly $0.00 is a KNOWN rate that values the hours at $0.00, not "—".
 3. "$0.00" means 'the rate is known and there is nothing (or $0) to value' - a different state from "—" ('the rate is unknown').</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
+      <c r="H15" s="2" t="inlineStr">
         <is>
           <t>specs/technician-utilization.md S2-E2; §5 Assumptions; S2 context note</t>
         </is>
       </c>
-      <c r="I16" s="2" t="inlineStr"/>
-      <c r="J16" s="2" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="2" t="inlineStr">
+      <c r="I15" s="2" t="inlineStr"/>
+      <c r="J15" s="2" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
         <is>
           <t>Internal hours with no default labor rate at any contributing location show an em-dash with the correct assistive-technology label</t>
         </is>
       </c>
-      <c r="B17" s="2" t="inlineStr">
+      <c r="B16" s="2" t="inlineStr">
         <is>
           <t>TU — Est. Lost Labor</t>
         </is>
       </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="E16" s="2" t="inlineStr">
         <is>
           <t>1. A technician's in-range internal hours were all clocked at location(s) with NO default labor rate configured (rate absent, not $0.00).</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
+      <c r="F16" s="2" t="inlineStr">
         <is>
           <t>1. Read that technician's Est. Lost Labor.
 2. Inspect the cell with a screen reader or the accessibility tree.</t>
         </is>
       </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>1. Est. Lost Labor shows "—" (an em-dash), NOT "$0.00" - the rate is unknown, so the value cannot be computed.
 2. The "—" cell carries the assistive-technology label "No default labor rate configured" (distinguishing it from "$0.00", which reads as its dollar value).
 3. The technician's Internal Hours column still shows all the internal hours (they are counted even though they cannot be valued).</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>specs/technician-utilization.md S2-E3; S8-R11; S2-R4</t>
         </is>
       </c>
-      <c r="I17" s="2" t="inlineStr"/>
-      <c r="J17" s="2" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="2" t="inlineStr">
+      <c r="I16" s="2" t="inlineStr"/>
+      <c r="J16" s="2" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
         <is>
           <t>Internal hours split across rated and unrated locations show a partial dollar value with no indicator - expected, not a defect</t>
         </is>
       </c>
-      <c r="B18" s="2" t="inlineStr">
+      <c r="B17" s="2" t="inlineStr">
         <is>
           <t>TU — Est. Lost Labor</t>
         </is>
       </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="E17" s="2" t="inlineStr">
         <is>
           <t>1. A technician clocked internal hours at BOTH a location with a configured default labor rate and a location with NO rate, in the range.
 2. Both locations are selected.</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="F17" s="2" t="inlineStr">
         <is>
           <t>1. Read the technician's Internal Hours and Est. Lost Labor.
 2. Compare the dollar value against rate × (internal hours at the RATED location only).</t>
         </is>
       </c>
-      <c r="G18" s="2" t="inlineStr">
+      <c r="G17" s="2" t="inlineStr">
         <is>
           <t>1. Est. Lost Labor is the sum of the valued (rated-location) portions only - the unrated-location hours are excluded from the dollar amount.
 2. The amount shows as a normal "$X.XX" with NO partial-value indicator in this version - so the row's Est. Lost Labor values fewer hours than its Internal Hours column shows.
 3. This is a documented known limitation (a partial-value indicator is a possible follow-up) - expected behavior, not a defect.</t>
         </is>
       </c>
-      <c r="H18" s="2" t="inlineStr">
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>specs/technician-utilization.md S2-E4</t>
         </is>
       </c>
-      <c r="I18" s="2" t="inlineStr"/>
-      <c r="J18" s="2" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="2" t="inlineStr">
+      <c r="I17" s="2" t="inlineStr"/>
+      <c r="J17" s="2" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
         <is>
           <t>On load the rows are sorted by Technician A to Z with the ascending indicator and correct aria-sort exposure</t>
         </is>
       </c>
-      <c r="B19" s="2" t="inlineStr">
+      <c r="B18" s="2" t="inlineStr">
         <is>
           <t>TU — Sorting</t>
         </is>
       </c>
-      <c r="C19" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="E18" s="2" t="inlineStr">
         <is>
           <t>1. You are on the Technician Utilization report with several technician rows loaded.</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
+      <c r="F18" s="2" t="inlineStr">
         <is>
           <t>1. Let the report load without clicking any header and read the Technician column top to bottom.
 2. Look at the Technician header's sort indicator.
 3. Inspect the headers in the accessibility tree.</t>
         </is>
       </c>
-      <c r="G19" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr">
         <is>
           <t>1. The technician rows are sorted by Technician name, A to Z.
 2. The Technician header shows the ascending sort indicator.
 3. The active sort header exposes its state to assistive technology (aria-sort = ascending on the Technician header; none on the others).</t>
         </is>
       </c>
-      <c r="H19" s="2" t="inlineStr">
+      <c r="H18" s="2" t="inlineStr">
         <is>
           <t>specs/technician-utilization.md S2-R12; S8-R8; S8-R10</t>
         </is>
       </c>
-      <c r="I19" s="2" t="inlineStr"/>
-      <c r="J19" s="2" t="inlineStr"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="2" t="inlineStr">
+      <c r="I18" s="2" t="inlineStr"/>
+      <c r="J18" s="2" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
         <is>
           <t>All six columns sort on screen: ascending first, toggling with no third state, and Technician's first click goes descending</t>
         </is>
       </c>
-      <c r="B20" s="2" t="inlineStr">
+      <c r="B19" s="2" t="inlineStr">
         <is>
           <t>TU — Sorting</t>
         </is>
       </c>
-      <c r="C20" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="E19" s="2" t="inlineStr">
         <is>
           <t>1. You are on the Technician Utilization report with several rows loaded, including two technicians with the same value in one column.</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
+      <c r="F19" s="2" t="inlineStr">
         <is>
           <t>1. Click the Technician header (the active sort on load).
 2. Click the Total Hours header, then click it again, then keep clicking.
@@ -1381,7 +1341,7 @@
 5. Find two technicians tied in the sorted column and note their order.</t>
         </is>
       </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="G19" s="2" t="inlineStr">
         <is>
           <t>1. Because Technician-ascending is the active sort on load, the FIRST click on the Technician header sorts it DESCENDING (Z to A).
 2. Clicking a column that is not the active sort sorts it ascending; clicking the active column again toggles to descending; further clicks only ever toggle ascending↔descending - there is NO third 'cleared' state.
@@ -1390,191 +1350,191 @@
 5. Technicians tied in the sorted column are ordered by Technician name A to Z; two technicians sharing the same display name keep a stable order between renders.</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr">
+      <c r="H19" s="2" t="inlineStr">
         <is>
           <t>specs/technician-utilization.md S2-R13; S2-R14</t>
         </is>
       </c>
-      <c r="I20" s="2" t="inlineStr"/>
-      <c r="J20" s="2" t="inlineStr"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="2" t="inlineStr">
+      <c r="I19" s="2" t="inlineStr"/>
+      <c r="J19" s="2" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
         <is>
           <t>A data reload resets the sort to Technician A to Z, and sort is never persisted across visits</t>
         </is>
       </c>
-      <c r="B21" s="2" t="inlineStr">
+      <c r="B20" s="2" t="inlineStr">
         <is>
           <t>TU — Sorting</t>
         </is>
       </c>
-      <c r="C21" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="E20" s="2" t="inlineStr">
         <is>
           <t>1. You are on the Technician Utilization report with rows loaded.</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="F20" s="2" t="inlineStr">
         <is>
           <t>1. Sort by Est. Lost Labor descending.
 2. Change the date range (a reload) and read the row order.
 3. Sort by Total Hours, leave the report, and come back.</t>
         </is>
       </c>
-      <c r="G21" s="2" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr">
         <is>
           <t>1. After the reload, the rows are back to Technician name A to Z (the sort reset).
 2. On the return visit, the sort is again Technician A to Z - sort is NOT persisted (unlike the date range, technician selection, and location selection, which are).</t>
         </is>
       </c>
-      <c r="H21" s="2" t="inlineStr">
+      <c r="H20" s="2" t="inlineStr">
         <is>
           <t>specs/technician-utilization.md S2-R15; §3</t>
         </is>
       </c>
-      <c r="I21" s="2" t="inlineStr"/>
-      <c r="J21" s="2" t="inlineStr"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="2" t="inlineStr">
+      <c r="I20" s="2" t="inlineStr"/>
+      <c r="J20" s="2" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
         <is>
           <t>Sorting reorders only the technician rows - the Summary stays at the bottom and day rows stay under their technician in date order</t>
         </is>
       </c>
-      <c r="B22" s="2" t="inlineStr">
+      <c r="B21" s="2" t="inlineStr">
         <is>
           <t>TU — Sorting</t>
         </is>
       </c>
-      <c r="C22" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
+      <c r="E21" s="2" t="inlineStr">
         <is>
           <t>1. You are on the Technician Utilization report with several rows loaded and at least one technician row expanded to its day rows.</t>
         </is>
       </c>
-      <c r="F22" s="2" t="inlineStr">
+      <c r="F21" s="2" t="inlineStr">
         <is>
           <t>1. Sort by WO Hours descending.
 2. Look at the Summary row's position.
 3. Look at the expanded technician's day rows.</t>
         </is>
       </c>
-      <c r="G22" s="2" t="inlineStr">
+      <c r="G21" s="2" t="inlineStr">
         <is>
           <t>1. Only the technician rows reorder.
 2. The Summary row stays pinned at the bottom.
 3. Each technician's expanded day rows stay under that technician, still in date order (earliest to latest) - they do not re-sort by the clicked column.</t>
         </is>
       </c>
-      <c r="H22" s="2" t="inlineStr">
+      <c r="H21" s="2" t="inlineStr">
         <is>
           <t>specs/technician-utilization.md S2-R16</t>
         </is>
       </c>
-      <c r="I22" s="2" t="inlineStr"/>
-      <c r="J22" s="2" t="inlineStr"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="2" t="inlineStr">
+      <c r="I21" s="2" t="inlineStr"/>
+      <c r="J21" s="2" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
         <is>
           <t>Sorting by Est. Lost Labor keeps the em-dash rows at the bottom in both directions, while $0.00 sorts as zero</t>
         </is>
       </c>
-      <c r="B23" s="2" t="inlineStr">
+      <c r="B22" s="2" t="inlineStr">
         <is>
           <t>TU — Sorting</t>
         </is>
       </c>
-      <c r="C23" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
+      <c r="E22" s="2" t="inlineStr">
         <is>
           <t>1. Rows exist with: a normal Est. Lost Labor value, a "$0.00" value, and at least two "—" values (no rate configured).</t>
         </is>
       </c>
-      <c r="F23" s="2" t="inlineStr">
+      <c r="F22" s="2" t="inlineStr">
         <is>
           <t>1. Sort by Est. Lost Labor ascending and read the bottom rows.
 2. Sort by Est. Lost Labor descending and read the bottom rows.
 3. Note where the "$0.00" row lands in each direction, and the order of the "—" rows among themselves.</t>
         </is>
       </c>
-      <c r="G23" s="2" t="inlineStr">
+      <c r="G22" s="2" t="inlineStr">
         <is>
           <t>1. Rows whose Est. Lost Labor is "—" sort to the BOTTOM in BOTH ascending and descending order - they are never floated to the top by reversing direction.
 2. Among themselves, the "—" rows are ordered by Technician name A to Z.
 3. A "$0.00" value is a number, not "—" - it sorts as zero (lowest ascending, above only the — group).</t>
         </is>
       </c>
-      <c r="H23" s="2" t="inlineStr">
+      <c r="H22" s="2" t="inlineStr">
         <is>
           <t>specs/technician-utilization.md S2-R17</t>
         </is>
       </c>
-      <c r="I23" s="2" t="inlineStr"/>
-      <c r="J23" s="2" t="inlineStr"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="2" t="inlineStr">
+      <c r="I22" s="2" t="inlineStr"/>
+      <c r="J22" s="2" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
         <is>
           <t>A pinned Summary row labeled Summary sits at the bottom, stays visible on scroll, and uses the row formats with no prefix</t>
         </is>
       </c>
-      <c r="B24" s="2" t="inlineStr">
+      <c r="B23" s="2" t="inlineStr">
         <is>
           <t>TU — Summary</t>
         </is>
       </c>
-      <c r="C24" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
+      <c r="E23" s="2" t="inlineStr">
         <is>
           <t>1. You are on the Technician Utilization report with enough rows to scroll.</t>
         </is>
       </c>
-      <c r="F24" s="2" t="inlineStr">
+      <c r="F23" s="2" t="inlineStr">
         <is>
           <t>1. Look at the bottom of the report.
 2. Scroll the technician rows and watch the Summary row.
 3. Read the Summary row's label and its values' formats.</t>
         </is>
       </c>
-      <c r="G24" s="2" t="inlineStr">
+      <c r="G23" s="2" t="inlineStr">
         <is>
           <t>1. A Summary row is pinned to the bottom of the report, labeled "Summary".
 2. It stays visible at the bottom while the rows scroll.
@@ -1582,232 +1542,232 @@
 4. Its values carry NO label prefix such as "TOTAL:" or "AVG:".</t>
         </is>
       </c>
-      <c r="H24" s="2" t="inlineStr">
+      <c r="H23" s="2" t="inlineStr">
         <is>
           <t>specs/technician-utilization.md S3-R1; S3-R2; S3-R6; S3-R7; S8-R5</t>
         </is>
       </c>
-      <c r="I24" s="2" t="inlineStr"/>
-      <c r="J24" s="2" t="inlineStr"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>Summary hours total the visible technicians from unrounded values - eye-summing the rows may differ by a cent, and all-selected equals shop totals</t>
-        </is>
-      </c>
-      <c r="B25" s="2" t="inlineStr">
+      <c r="I23" s="2" t="inlineStr"/>
+      <c r="J23" s="2" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>Summary totals visible technicians from unrounded hours; 0.01 drift expected</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
         <is>
           <t>TU — Summary</t>
         </is>
       </c>
-      <c r="C25" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D25" s="2" t="inlineStr">
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E25" s="2" t="inlineStr">
+      <c r="E24" s="2" t="inlineStr">
         <is>
           <t>1. Several technicians with known clocked hours are visible (all selected in the technician filter).</t>
         </is>
       </c>
-      <c r="F25" s="2" t="inlineStr">
+      <c r="F24" s="2" t="inlineStr">
         <is>
           <t>1. Read the Summary Total Hours, WO Hours, and Internal Hours.
 2. Hand-sum the DISPLAYED per-row values and compare with the Summary.
 3. Compare the Summary against the known shop totals for the full range at the selected location(s).</t>
         </is>
       </c>
-      <c r="G25" s="2" t="inlineStr">
+      <c r="G24" s="2" t="inlineStr">
         <is>
           <t>1. Each Summary hours value is the total of that column across the VISIBLE technicians, computed from unrounded hours and rounded once for display (round-half-up).
-2. Eye-summing the displayed rows MAY differ from the displayed Summary by a cent - this is expected in a compute-from-unrounded report, not a defect.
+2. Eye-summing the displayed rows MAY differ from the displayed Summary by 0.01 — one unit in the last decimal (these values are HOURS, not money) — expected in a compute-from-unrounded report, not a defect.
 3. With every technician selected, the Summary row equals the shop totals for the full date range at the selected location(s).</t>
         </is>
       </c>
-      <c r="H25" s="2" t="inlineStr">
+      <c r="H24" s="2" t="inlineStr">
         <is>
           <t>specs/technician-utilization.md S3-R3; §3 context note; S5-E1</t>
         </is>
       </c>
-      <c r="I25" s="2" t="inlineStr"/>
-      <c r="J25" s="2" t="inlineStr"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="2" t="inlineStr">
+      <c r="I24" s="2" t="inlineStr"/>
+      <c r="J24" s="2" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
         <is>
           <t>Summary Utilization % is the weighted rate, not the average of the per-technician percentages</t>
         </is>
       </c>
-      <c r="B26" s="2" t="inlineStr">
+      <c r="B25" s="2" t="inlineStr">
         <is>
           <t>TU — Summary</t>
         </is>
       </c>
-      <c r="C26" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
+      <c r="E25" s="2" t="inlineStr">
         <is>
           <t>1. Two visible technicians with deliberately skewed hours - e.g. tech A: 1.00 total / 1.00 WO (100%); tech B: 9.00 total / 0.00 WO (0.0%) - so the weighted and averaged results differ clearly.</t>
         </is>
       </c>
-      <c r="F26" s="2" t="inlineStr">
+      <c r="F25" s="2" t="inlineStr">
         <is>
           <t>1. Compute the weighted rate: summed WO hours ÷ summed clocked hours × 100 (10% in the example).
 2. Compute the naive average of the two row percentages (50% in the example).
 3. Read the Summary Utilization %.</t>
         </is>
       </c>
-      <c r="G26" s="2" t="inlineStr">
+      <c r="G25" s="2" t="inlineStr">
         <is>
           <t>1. The Summary Utilization % shows the WEIGHTED rate - the visible technicians' total work-order hours as a percentage of their total clocked hours, from unrounded hours (10.0% in the example).
 2. It is NOT the average of the per-technician percentages (not 50.0%).</t>
         </is>
       </c>
-      <c r="H26" s="2" t="inlineStr">
+      <c r="H25" s="2" t="inlineStr">
         <is>
           <t>specs/technician-utilization.md S3-R4</t>
         </is>
       </c>
-      <c r="I26" s="2" t="inlineStr"/>
-      <c r="J26" s="2" t="inlineStr"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="2" t="inlineStr">
+      <c r="I25" s="2" t="inlineStr"/>
+      <c r="J25" s="2" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
         <is>
           <t>Summary Est. Lost Labor sums the rated contributions only, and shows an em-dash only when every visible technician is an em-dash</t>
         </is>
       </c>
-      <c r="B27" s="2" t="inlineStr">
+      <c r="B26" s="2" t="inlineStr">
         <is>
           <t>TU — Summary</t>
         </is>
       </c>
-      <c r="C27" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D27" s="2" t="inlineStr">
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E27" s="2" t="inlineStr">
+      <c r="E26" s="2" t="inlineStr">
         <is>
           <t>1. Visible technicians include: one with a normal Est. Lost Labor, one showing "—" (no rate anywhere), and (if possible) one partially valued (S2-E4).</t>
         </is>
       </c>
-      <c r="F27" s="2" t="inlineStr">
+      <c r="F26" s="2" t="inlineStr">
         <is>
           <t>1. Read the Summary Est. Lost Labor and compare against the sum of the visible rows' valued (rated-location) contributions.
 2. Use the technician filter to leave ONLY "—" technicians visible and read the Summary Est. Lost Labor.</t>
         </is>
       </c>
-      <c r="G27" s="2" t="inlineStr">
+      <c r="G26" s="2" t="inlineStr">
         <is>
           <t>1. The Summary Est. Lost Labor is computed like a row but over all visible technicians' internal hours: rate × internal hours per contributing rated location, summed at full precision and rounded once.
 2. A visible technician whose value is "—" contributes NOTHING to the sum - so the Summary understates true lost labor whenever any visible technician is "—" or partially valued (documented, expected).
 3. The Summary shows "—" only when EVERY visible technician's Est. Lost Labor is "—".</t>
         </is>
       </c>
-      <c r="H27" s="2" t="inlineStr">
+      <c r="H26" s="2" t="inlineStr">
         <is>
           <t>specs/technician-utilization.md S3-R5</t>
         </is>
       </c>
-      <c r="I27" s="2" t="inlineStr"/>
-      <c r="J27" s="2" t="inlineStr"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="2" t="inlineStr">
+      <c r="I26" s="2" t="inlineStr"/>
+      <c r="J26" s="2" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
         <is>
           <t>Each technician row has an accessible expand/collapse control named for its next action</t>
         </is>
       </c>
-      <c r="B28" s="2" t="inlineStr">
+      <c r="B27" s="2" t="inlineStr">
         <is>
           <t>TU — Per-Day Breakdown</t>
         </is>
       </c>
-      <c r="C28" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
+      <c r="E27" s="2" t="inlineStr">
         <is>
           <t>1. You are on the Technician Utilization report with rows loaded.</t>
         </is>
       </c>
-      <c r="F28" s="2" t="inlineStr">
+      <c r="F27" s="2" t="inlineStr">
         <is>
           <t>1. Find the expand control on a technician row and read its accessible name (accessibility tree or screen reader).
 2. Activate it with the keyboard (Enter, then again with Space) and re-read the name and exposed state.
 3. Collapse the row again.</t>
         </is>
       </c>
-      <c r="G28" s="2" t="inlineStr">
+      <c r="G27" s="2" t="inlineStr">
         <is>
           <t>1. Each technician row has a control to expand and collapse it.
 2. Its accessible name reflects the NEXT action, scoped to that technician: "Expand &lt;technician&gt;'s daily breakdown" when collapsed, "Collapse &lt;technician&gt;'s daily breakdown" when expanded.
 3. The control is keyboard-focusable, toggles on Enter and Space, and exposes its expanded/collapsed state to assistive technology.</t>
         </is>
       </c>
-      <c r="H28" s="2" t="inlineStr">
+      <c r="H27" s="2" t="inlineStr">
         <is>
           <t>specs/technician-utilization.md S4-R1; S8-R12</t>
         </is>
       </c>
-      <c r="I28" s="2" t="inlineStr"/>
-      <c r="J28" s="2" t="inlineStr"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="2" t="inlineStr">
+      <c r="I27" s="2" t="inlineStr"/>
+      <c r="J27" s="2" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
         <is>
           <t>Expanding shows one row per clocked day in date order, loaded on demand, with days pooled across selected locations</t>
         </is>
       </c>
-      <c r="B29" s="2" t="inlineStr">
+      <c r="B28" s="2" t="inlineStr">
         <is>
           <t>TU — Per-Day Breakdown</t>
         </is>
       </c>
-      <c r="C29" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D29" s="2" t="inlineStr">
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E29" s="2" t="inlineStr">
+      <c r="E28" s="2" t="inlineStr">
         <is>
           <t>1. A technician clocked time on several (but not all) days of the range - including, for the pooling check, time at two selected locations on the same day.
 2. Browser devtools (network tab) are open for the on-demand check.</t>
         </is>
       </c>
-      <c r="F29" s="2" t="inlineStr">
+      <c r="F28" s="2" t="inlineStr">
         <is>
           <t>1. Expand the technician's row and watch the network traffic.
 2. Read the day rows top to bottom.
@@ -1815,7 +1775,7 @@
 4. On the double-location day, count the rows for that date.</t>
         </is>
       </c>
-      <c r="G29" s="2" t="inlineStr">
+      <c r="G28" s="2" t="inlineStr">
         <is>
           <t>1. One row appears for each day the technician clocked time in the range, in date order from earliest to latest.
 2. The day rows are fetched ON EXPAND (on demand) - they are not shipped with the initial report payload.
@@ -1823,89 +1783,89 @@
 4. With several locations selected, a day's row POOLS that day's hours across the selected locations - one day row per date, not one per location.</t>
         </is>
       </c>
-      <c r="H29" s="2" t="inlineStr">
+      <c r="H28" s="2" t="inlineStr">
         <is>
           <t>specs/technician-utilization.md S4-R2; S4-N1; S9-R4</t>
         </is>
       </c>
-      <c r="I29" s="2" t="inlineStr"/>
-      <c r="J29" s="2" t="inlineStr"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="2" t="inlineStr">
+      <c r="I28" s="2" t="inlineStr"/>
+      <c r="J28" s="2" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
         <is>
           <t>Day rows use the same columns and formats as technician rows, including a per-day per-location Est. Lost Labor</t>
         </is>
       </c>
-      <c r="B30" s="2" t="inlineStr">
+      <c r="B29" s="2" t="inlineStr">
         <is>
           <t>TU — Per-Day Breakdown</t>
         </is>
       </c>
-      <c r="C30" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D30" s="2" t="inlineStr">
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E30" s="2" t="inlineStr">
+      <c r="E29" s="2" t="inlineStr">
         <is>
           <t>1. A technician with known per-day clock records (work-order + internal) is expanded.</t>
         </is>
       </c>
-      <c r="F30" s="2" t="inlineStr">
+      <c r="F29" s="2" t="inlineStr">
         <is>
           <t>1. Read one day row's Total Hours, WO Hours, Internal Hours, Utilization %, and Est. Lost Labor.
 2. Compare each against that single day's clock records.
 3. Check the number formats against the technician-row formats.</t>
         </is>
       </c>
-      <c r="G30" s="2" t="inlineStr">
+      <c r="G29" s="2" t="inlineStr">
         <is>
           <t>1. Each day row shows the same columns, in the same formats, as the technician row - with that day's values.
 2. The day's Est. Lost Labor is valued per location exactly like a technician row (that location's default labor rate × that day's internal hours there).
 3. Hours 2dp / Utilization one decimal + % / dollars with commas - all identical to the row formats, computed from unrounded values and rounded once.</t>
         </is>
       </c>
-      <c r="H30" s="2" t="inlineStr">
+      <c r="H29" s="2" t="inlineStr">
         <is>
           <t>specs/technician-utilization.md S4-R3; S2-R8; §3</t>
         </is>
       </c>
-      <c r="I30" s="2" t="inlineStr"/>
-      <c r="J30" s="2" t="inlineStr"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="2" t="inlineStr">
+      <c r="I29" s="2" t="inlineStr"/>
+      <c r="J29" s="2" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
         <is>
           <t>A single control in the table header expands or collapses all technician rows with the correct accessible names</t>
         </is>
       </c>
-      <c r="B31" s="2" t="inlineStr">
+      <c r="B30" s="2" t="inlineStr">
         <is>
           <t>TU — Per-Day Breakdown</t>
         </is>
       </c>
-      <c r="C31" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D31" s="2" t="inlineStr">
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E31" s="2" t="inlineStr">
+      <c r="E30" s="2" t="inlineStr">
         <is>
           <t>1. You are on the Technician Utilization report with several technician rows loaded.</t>
         </is>
       </c>
-      <c r="F31" s="2" t="inlineStr">
+      <c r="F30" s="2" t="inlineStr">
         <is>
           <t>1. Find the expand/collapse-all control in the table's header row (in the Technician column) and read its accessible name.
 2. With all rows collapsed, activate it.
@@ -1913,7 +1873,7 @@
 4. With every row expanded, activate it once more.</t>
         </is>
       </c>
-      <c r="G31" s="2" t="inlineStr">
+      <c r="G30" s="2" t="inlineStr">
         <is>
           <t>1. The control lives in the table's header row (Technician column) - NOT in the toolbar action cluster.
 2. If ANY row is collapsed, activating it expands ALL rows; only when EVERY row is already expanded does it collapse all rows (so step 3's activation re-expands the one collapsed row).
@@ -1921,145 +1881,145 @@
 4. It is keyboard-focusable, toggles on Enter/Space, and exposes its state to assistive technology.</t>
         </is>
       </c>
-      <c r="H31" s="2" t="inlineStr">
+      <c r="H30" s="2" t="inlineStr">
         <is>
           <t>specs/technician-utilization.md S4-R4; S8-R12; S8-R3</t>
         </is>
       </c>
-      <c r="I31" s="2" t="inlineStr"/>
-      <c r="J31" s="2" t="inlineStr"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="2" t="inlineStr">
+      <c r="I30" s="2" t="inlineStr"/>
+      <c r="J30" s="2" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
         <is>
           <t>Expansion state is view-only: it resets on any reload and fresh visit, and the technician filter does not disturb it</t>
         </is>
       </c>
-      <c r="B32" s="2" t="inlineStr">
+      <c r="B31" s="2" t="inlineStr">
         <is>
           <t>TU — Per-Day Breakdown</t>
         </is>
       </c>
-      <c r="C32" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D32" s="2" t="inlineStr">
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="E32" s="2" t="inlineStr">
+      <c r="E31" s="2" t="inlineStr">
         <is>
           <t>1. You are on the Technician Utilization report with several rows loaded.</t>
         </is>
       </c>
-      <c r="F32" s="2" t="inlineStr">
+      <c r="F31" s="2" t="inlineStr">
         <is>
           <t>1. Expand two technician rows, then change the date range.
 2. Expand two rows again, leave the report, and come back.
 3. Expand one technician's row, then deselect and re-select a DIFFERENT technician in the technician filter.</t>
         </is>
       </c>
-      <c r="G32" s="2" t="inlineStr">
+      <c r="G31" s="2" t="inlineStr">
         <is>
           <t>1. After the reload (date-range or location change), all rows are collapsed - expansion state resets.
 2. On a fresh visit, all rows start collapsed - expansion is never persisted.
 3. Deselecting and re-selecting a technician (an on-screen operation) does NOT change the expansion state of the other rows - the expanded row stays expanded.</t>
         </is>
       </c>
-      <c r="H32" s="2" t="inlineStr">
+      <c r="H31" s="2" t="inlineStr">
         <is>
           <t>specs/technician-utilization.md S4-R5</t>
         </is>
       </c>
-      <c r="I32" s="2" t="inlineStr"/>
-      <c r="J32" s="2" t="inlineStr"/>
-    </row>
-    <row r="33">
-      <c r="A33" s="2" t="inlineStr">
+      <c r="I31" s="2" t="inlineStr"/>
+      <c r="J31" s="2" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
         <is>
           <t>The Filter by Technician multi-select starts with every technician selected on a first visit</t>
         </is>
       </c>
-      <c r="B33" s="2" t="inlineStr">
+      <c r="B32" s="2" t="inlineStr">
         <is>
           <t>TU — Technician Filter</t>
         </is>
       </c>
-      <c r="C33" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D33" s="2" t="inlineStr">
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E33" s="2" t="inlineStr">
+      <c r="E32" s="2" t="inlineStr">
         <is>
           <t>1. You are on the Technician Utilization report on a first visit (no saved settings), with several technicians in the range.</t>
         </is>
       </c>
-      <c r="F33" s="2" t="inlineStr">
+      <c r="F32" s="2" t="inlineStr">
         <is>
           <t>1. Find the toolbar filter labeled "Filter by Technician" and open it.
 2. Check the selection state of every listed technician.
 3. Try selecting more than one change at once (multi-select).</t>
         </is>
       </c>
-      <c r="G33" s="2" t="inlineStr">
+      <c r="G32" s="2" t="inlineStr">
         <is>
           <t>1. The toolbar has a filter labeled "Filter by Technician" that allows selecting more than one technician.
 2. On the first visit, EVERY technician is selected.
 3. All technicians' rows are shown.</t>
         </is>
       </c>
-      <c r="H33" s="2" t="inlineStr">
+      <c r="H32" s="2" t="inlineStr">
         <is>
           <t>specs/technician-utilization.md S5-R1; S5-R2</t>
         </is>
       </c>
-      <c r="I33" s="2" t="inlineStr"/>
-      <c r="J33" s="2" t="inlineStr"/>
-    </row>
-    <row r="34">
-      <c r="A34" s="2" t="inlineStr">
+      <c r="I32" s="2" t="inlineStr"/>
+      <c r="J32" s="2" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
         <is>
           <t>Deselecting a technician hides the row and recalculates the Summary on screen without reloading; re-selecting restores it</t>
         </is>
       </c>
-      <c r="B34" s="2" t="inlineStr">
+      <c r="B33" s="2" t="inlineStr">
         <is>
           <t>TU — Technician Filter</t>
         </is>
       </c>
-      <c r="C34" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D34" s="2" t="inlineStr">
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E34" s="2" t="inlineStr">
+      <c r="E33" s="2" t="inlineStr">
         <is>
           <t>1. Several technician rows are visible and the Summary row shows their totals.
 2. Browser devtools (network tab) are open.</t>
         </is>
       </c>
-      <c r="F34" s="2" t="inlineStr">
+      <c r="F33" s="2" t="inlineStr">
         <is>
           <t>1. Note the Summary values, then deselect one technician in the Filter by Technician filter.
 2. Watch the network traffic and the Summary row.
 3. Re-select the technician.</t>
         </is>
       </c>
-      <c r="G34" s="2" t="inlineStr">
+      <c r="G33" s="2" t="inlineStr">
         <is>
           <t>1. The deselected technician's row is hidden.
 2. The Summary row recalculates over the technicians that remain visible.
@@ -2067,41 +2027,41 @@
 4. Re-selecting the technician shows the row again (and the Summary recalculates back).</t>
         </is>
       </c>
-      <c r="H34" s="2" t="inlineStr">
+      <c r="H33" s="2" t="inlineStr">
         <is>
           <t>specs/technician-utilization.md S5-R3; S5-R4; S5-R5; §3; S5 context note</t>
         </is>
       </c>
-      <c r="I34" s="2" t="inlineStr"/>
-      <c r="J34" s="2" t="inlineStr"/>
-    </row>
-    <row r="35">
-      <c r="A35" s="2" t="inlineStr">
+      <c r="I33" s="2" t="inlineStr"/>
+      <c r="J33" s="2" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
         <is>
           <t>Select all and Clear all controls work, and the deselected-set model keeps newly-appearing technicians selected</t>
         </is>
       </c>
-      <c r="B35" s="2" t="inlineStr">
+      <c r="B34" s="2" t="inlineStr">
         <is>
           <t>TU — Technician Filter</t>
         </is>
       </c>
-      <c r="C35" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D35" s="2" t="inlineStr">
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E35" s="2" t="inlineStr">
+      <c r="E34" s="2" t="inlineStr">
         <is>
           <t>1. Several technicians are in the current range; a different range exists in which an ADDITIONAL technician (not listed in the current range) has clocked time.</t>
         </is>
       </c>
-      <c r="F35" s="2" t="inlineStr">
+      <c r="F34" s="2" t="inlineStr">
         <is>
           <t>1. In the Filter by Technician filter, use the control labeled "Clear all".
 2. Use the control labeled "Select all".
@@ -2109,7 +2069,7 @@
 4. Use "Clear all" again, then switch to the range where the additional technician newly appears.</t>
         </is>
       </c>
-      <c r="G35" s="2" t="inlineStr">
+      <c r="G34" s="2" t="inlineStr">
         <is>
           <t>1. "Clear all" sets every currently-listed technician to deselected; "Select all" selects all technicians at once.
 2. Selection is tracked as the set of DESELECTED technicians: a technician you have not deselected is selected by default.
@@ -2117,565 +2077,519 @@
 4. After step 4, the newly-appearing technician is selected even though you had cleared all - "Clear all" only deselected the technicians listed at the time.</t>
         </is>
       </c>
-      <c r="H35" s="2" t="inlineStr">
+      <c r="H34" s="2" t="inlineStr">
         <is>
           <t>specs/technician-utilization.md S5-R6; S5-R7; S5-R8; S5-R9</t>
         </is>
       </c>
-      <c r="I35" s="2" t="inlineStr"/>
-      <c r="J35" s="2" t="inlineStr"/>
-    </row>
-    <row r="36">
-      <c r="A36" s="2" t="inlineStr">
+      <c r="I34" s="2" t="inlineStr"/>
+      <c r="J34" s="2" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
         <is>
           <t>Previously deselected technicians stay deselected when the user returns to the report</t>
         </is>
       </c>
-      <c r="B36" s="2" t="inlineStr">
+      <c r="B35" s="2" t="inlineStr">
         <is>
           <t>TU — Technician Filter</t>
         </is>
       </c>
-      <c r="C36" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D36" s="2" t="inlineStr">
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E36" s="2" t="inlineStr">
+      <c r="E35" s="2" t="inlineStr">
         <is>
           <t>1. You are on the Technician Utilization report with several technicians listed.</t>
         </is>
       </c>
-      <c r="F36" s="2" t="inlineStr">
+      <c r="F35" s="2" t="inlineStr">
         <is>
           <t>1. Deselect two technicians.
 2. Leave the report (navigate elsewhere), then return; also try a full page reload.
 3. Check the two technicians' selection state and the other technicians'.</t>
         </is>
       </c>
-      <c r="G36" s="2" t="inlineStr">
+      <c r="G35" s="2" t="inlineStr">
         <is>
           <t>1. The two deselected technicians are STILL deselected on return - the deselected set is what persists (saved in this browser, not on the account).
 2. All other technicians - including any who appear for the first time - are selected.
 3. The saved date range and location selection are restored alongside (per S1-R8).</t>
         </is>
       </c>
-      <c r="H36" s="2" t="inlineStr">
+      <c r="H35" s="2" t="inlineStr">
         <is>
           <t>specs/technician-utilization.md S5-R10; S1-R8; §3</t>
         </is>
       </c>
-      <c r="I36" s="2" t="inlineStr"/>
-      <c r="J36" s="2" t="inlineStr"/>
-    </row>
-    <row r="37">
-      <c r="A37" s="2" t="inlineStr">
-        <is>
-          <t>Clearing all technicians shows the no-data message and hides the Summary row</t>
-        </is>
-      </c>
-      <c r="B37" s="2" t="inlineStr">
-        <is>
-          <t>TU — Technician Filter</t>
-        </is>
-      </c>
-      <c r="C37" s="2" t="inlineStr">
-        <is>
-          <t>Negative</t>
-        </is>
-      </c>
-      <c r="D37" s="2" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="E37" s="2" t="inlineStr">
-        <is>
-          <t>1. You are on the Technician Utilization report with rows loaded.</t>
-        </is>
-      </c>
-      <c r="F37" s="2" t="inlineStr">
-        <is>
-          <t>1. In the Filter by Technician filter, use "Clear all" so every currently-listed technician is deselected.
-2. Read the data area and look for the Summary row.</t>
-        </is>
-      </c>
-      <c r="G37" s="2" t="inlineStr">
-        <is>
-          <t>1. The report shows the no-data message: "Empty bays, endless possibilities. Get Going!" (the same standard label as the genuinely-no-data case - no distinct copy in this version).
-2. The Summary row is hidden (no technician rows are visible).</t>
-        </is>
-      </c>
-      <c r="H37" s="2" t="inlineStr">
-        <is>
-          <t>specs/technician-utilization.md S5-N1; S3-N1; §7</t>
-        </is>
-      </c>
-      <c r="I37" s="2" t="inlineStr"/>
-      <c r="J37" s="2" t="inlineStr"/>
-    </row>
-    <row r="38">
-      <c r="A38" s="2" t="inlineStr">
+      <c r="I35" s="2" t="inlineStr"/>
+      <c r="J35" s="2" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
         <is>
           <t>Total Hours is a real link with a non-color affordance and keyboard access, while the Summary's Total Hours is not a link</t>
         </is>
       </c>
-      <c r="B38" s="2" t="inlineStr">
+      <c r="B36" s="2" t="inlineStr">
         <is>
           <t>TU — Deep Links</t>
         </is>
       </c>
-      <c r="C38" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D38" s="2" t="inlineStr">
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E38" s="2" t="inlineStr">
+      <c r="E36" s="2" t="inlineStr">
         <is>
           <t>1. You are on the Technician Utilization report with technician rows and the Summary row visible.</t>
         </is>
       </c>
-      <c r="F38" s="2" t="inlineStr">
+      <c r="F36" s="2" t="inlineStr">
         <is>
           <t>1. Look at a technician row's Total Hours value.
 2. Tab to it with the keyboard and check the focus indicator; press Enter.
 3. Go back and look at the Summary row's Total Hours value.</t>
         </is>
       </c>
-      <c r="G38" s="2" t="inlineStr">
+      <c r="G36" s="2" t="inlineStr">
         <is>
           <t>1. Every technician row's Total Hours is rendered as a link (every rendered row has clocked time &gt; 0, so the link always applies).
 2. The link is distinguished by more than color - it carries an underline (or equivalent non-color affordance), is keyboard-focusable with a visible focus indicator, and activates on Enter.
 3. The Summary row's Total Hours value is NOT a link.</t>
         </is>
       </c>
-      <c r="H38" s="2" t="inlineStr">
+      <c r="H36" s="2" t="inlineStr">
         <is>
           <t>specs/technician-utilization.md S6-R1; S6-N1; S8-R14</t>
         </is>
       </c>
-      <c r="I38" s="2" t="inlineStr"/>
-      <c r="J38" s="2" t="inlineStr"/>
-    </row>
-    <row r="39">
-      <c r="A39" s="2" t="inlineStr">
+      <c r="I36" s="2" t="inlineStr"/>
+      <c r="J36" s="2" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
         <is>
           <t>The Total Hours link opens Timesheet Activities in the same tab, pre-filtered to that technician and date range</t>
         </is>
       </c>
-      <c r="B39" s="2" t="inlineStr">
+      <c r="B37" s="2" t="inlineStr">
         <is>
           <t>TU — Deep Links</t>
         </is>
       </c>
-      <c r="C39" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D39" s="2" t="inlineStr">
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="E39" s="2" t="inlineStr">
+      <c r="E37" s="2" t="inlineStr">
         <is>
           <t>1. You are on the Technician Utilization report with a non-default date range selected (so the carried range is provable).</t>
         </is>
       </c>
-      <c r="F39" s="2" t="inlineStr">
+      <c r="F37" s="2" t="inlineStr">
         <is>
           <t>1. Click a technician's Total Hours link.
 2. Check which browser tab the Timesheet Activities report opened in.
 3. Read the technician filter and the date range on the opened report.</t>
         </is>
       </c>
-      <c r="G39" s="2" t="inlineStr">
+      <c r="G37" s="2" t="inlineStr">
         <is>
           <t>1. The Timesheet Activities report opens in the SAME browser tab.
 2. It is already filtered to that technician.
 3. It uses the same date range that was active on the Technician Utilization report.</t>
         </is>
       </c>
-      <c r="H39" s="2" t="inlineStr">
+      <c r="H37" s="2" t="inlineStr">
         <is>
           <t>specs/technician-utilization.md S6-R2; S6-R3; S6-R4</t>
         </is>
       </c>
-      <c r="I39" s="2" t="inlineStr"/>
-      <c r="J39" s="2" t="inlineStr"/>
-    </row>
-    <row r="40">
-      <c r="A40" s="2" t="inlineStr">
-        <is>
-          <t>For the same range and single active location with closed records, Total Hours reconciles to the Timesheet Activities total to the cent</t>
-        </is>
-      </c>
-      <c r="B40" s="2" t="inlineStr">
+      <c r="I37" s="2" t="inlineStr"/>
+      <c r="J37" s="2" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>Same range, single location, closed records: Total Hours matches Timesheet</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
         <is>
           <t>TU — Deep Links</t>
         </is>
       </c>
-      <c r="C40" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D40" s="2" t="inlineStr">
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="E40" s="2" t="inlineStr">
+      <c r="E38" s="2" t="inlineStr">
         <is>
           <t>1. A technician has only CLOSED (clocked-out) records in the range - no open clock.
 2. The report's location filter holds exactly ONE location, and it is the user's currently active shop.</t>
         </is>
       </c>
-      <c r="F40" s="2" t="inlineStr">
+      <c r="F38" s="2" t="inlineStr">
         <is>
           <t>1. Read the technician's Total Hours on the Technician Utilization report (two decimals).
 2. Click the Total Hours link and read the same technician's total on the opened Timesheet Activities report.
-3. Compare the two to the cent.</t>
-        </is>
-      </c>
-      <c r="G40" s="2" t="inlineStr">
-        <is>
-          <t>1. The two totals MATCH to the cent (two decimals) - both reports read the same clock records and round the same way (round-half-up, from unrounded values).
+3. Compare the two, to two decimals.</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>1. The two totals MATCH exactly, to two decimals (these values are hours, not money) - both reports read the same clock records and round the same way (round-half-up, from unrounded values).
 2. Under this exact scope (same range, same single location, closed records) a mismatch IS a defect.
 3. The two documented scope differences (open clocks, multi-location drill-through) are covered by separate cases and are NOT defects.</t>
         </is>
       </c>
-      <c r="H40" s="2" t="inlineStr">
+      <c r="H38" s="2" t="inlineStr">
         <is>
           <t>specs/technician-utilization.md S1-R9; §2; §5 Assumptions</t>
         </is>
       </c>
-      <c r="I40" s="2" t="inlineStr"/>
-      <c r="J40" s="2" t="inlineStr"/>
-    </row>
-    <row r="41">
-      <c r="A41" s="2" t="inlineStr">
+      <c r="I38" s="2" t="inlineStr"/>
+      <c r="J38" s="2" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
         <is>
           <t>Reconciliation exception (a): an open clock is snapshotted at each report's own load instant - a difference of the elapsed time is expected</t>
         </is>
       </c>
-      <c r="B41" s="2" t="inlineStr">
+      <c r="B39" s="2" t="inlineStr">
         <is>
           <t>TU — Deep Links</t>
         </is>
       </c>
-      <c r="C41" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D41" s="2" t="inlineStr">
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E41" s="2" t="inlineStr">
+      <c r="E39" s="2" t="inlineStr">
         <is>
           <t>1. A technician is still clocked in (an open, not-yet-clocked-out record) inside the range.</t>
         </is>
       </c>
-      <c r="F41" s="2" t="inlineStr">
+      <c r="F39" s="2" t="inlineStr">
         <is>
           <t>1. Load the Technician Utilization report and read the technician's Total Hours; watch whether the value ticks on screen.
 2. Wait a minute or two, then open Timesheet Activities via the Total Hours link and read its total.
 3. Compare the two values.</t>
         </is>
       </c>
-      <c r="G41" s="2" t="inlineStr">
+      <c r="G39" s="2" t="inlineStr">
         <is>
           <t>1. The open time is counted UP TO THE MOMENT THE REPORT LOADS - a fixed snapshot taken at load, not a value that keeps ticking on screen (matching how Timesheet Activities treats an open record).
 2. The two reports, loaded at different moments, MAY differ by the elapsed open time - this is a deliberate scope difference of the reconciliation guarantee, EXPECTED and NOT a defect.
 3. Reloading the Technician Utilization report takes a fresh snapshot (the value grows by the elapsed time).</t>
         </is>
       </c>
-      <c r="H41" s="2" t="inlineStr">
+      <c r="H39" s="2" t="inlineStr">
         <is>
           <t>specs/technician-utilization.md S1-R9(a); S1-E1</t>
         </is>
       </c>
-      <c r="I41" s="2" t="inlineStr"/>
-      <c r="J41" s="2" t="inlineStr"/>
-    </row>
-    <row r="42">
-      <c r="A42" s="2" t="inlineStr">
+      <c r="I39" s="2" t="inlineStr"/>
+      <c r="J39" s="2" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
         <is>
           <t>Reconciliation exception (b): the link passes no location, so with multiple locations selected the opened view shows only the active shop</t>
         </is>
       </c>
-      <c r="B42" s="2" t="inlineStr">
+      <c r="B40" s="2" t="inlineStr">
         <is>
           <t>TU — Deep Links</t>
         </is>
       </c>
-      <c r="C42" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D42" s="2" t="inlineStr">
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E42" s="2" t="inlineStr">
+      <c r="E40" s="2" t="inlineStr">
         <is>
           <t>1. A technician has clocked time at TWO locations in the range.
 2. Both locations are selected in the report's location filter; only one of them is the user's currently active shop.</t>
         </is>
       </c>
-      <c r="F42" s="2" t="inlineStr">
+      <c r="F40" s="2" t="inlineStr">
         <is>
           <t>1. Read the technician's pooled Total Hours (both locations).
 2. Click the Total Hours link and read the total on the opened Timesheet Activities report.
 3. Compare the two values.</t>
         </is>
       </c>
-      <c r="G42" s="2" t="inlineStr">
+      <c r="G40" s="2" t="inlineStr">
         <is>
           <t>1. The link passes the technician and the date range ONLY - it does NOT pass the location selection.
 2. Timesheet Activities opens for the user's currently active shop, so it shows one location's portion - it will differ from (or be disjoint with) the multi-location row value.
 3. This is a KNOWN drill-through limitation, EXPECTED and NOT a data defect (the same applies when the single selected location is not the active shop).</t>
         </is>
       </c>
-      <c r="H42" s="2" t="inlineStr">
+      <c r="H40" s="2" t="inlineStr">
         <is>
           <t>specs/technician-utilization.md S6-R6; S1-R9(b)</t>
         </is>
       </c>
-      <c r="I42" s="2" t="inlineStr"/>
-      <c r="J42" s="2" t="inlineStr"/>
-    </row>
-    <row r="43">
-      <c r="A43" s="2" t="inlineStr">
+      <c r="I40" s="2" t="inlineStr"/>
+      <c r="J40" s="2" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
         <is>
           <t>A day row's Total Hours links to Timesheet Activities for that technician on that single day</t>
         </is>
       </c>
-      <c r="B43" s="2" t="inlineStr">
+      <c r="B41" s="2" t="inlineStr">
         <is>
           <t>TU — Deep Links</t>
         </is>
       </c>
-      <c r="C43" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D43" s="2" t="inlineStr">
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E43" s="2" t="inlineStr">
+      <c r="E41" s="2" t="inlineStr">
         <is>
           <t>1. A technician row is expanded and shows day rows.</t>
         </is>
       </c>
-      <c r="F43" s="2" t="inlineStr">
+      <c r="F41" s="2" t="inlineStr">
         <is>
           <t>1. Click the Total Hours value on one day row.
 2. Read the technician filter and the date range on the opened Timesheet Activities report.</t>
         </is>
       </c>
-      <c r="G43" s="2" t="inlineStr">
+      <c r="G41" s="2" t="inlineStr">
         <is>
           <t>1. Timesheet Activities opens filtered to that technician.
 2. The date range covers ONLY that single day.</t>
         </is>
       </c>
-      <c r="H43" s="2" t="inlineStr">
+      <c r="H41" s="2" t="inlineStr">
         <is>
           <t>specs/technician-utilization.md S6-R5</t>
         </is>
       </c>
-      <c r="I43" s="2" t="inlineStr"/>
-      <c r="J43" s="2" t="inlineStr"/>
-    </row>
-    <row r="44">
-      <c r="A44" s="2" t="inlineStr">
+      <c r="I41" s="2" t="inlineStr"/>
+      <c r="J41" s="2" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
         <is>
           <t>The three-dot menu sits leftmost in the toolbar's action cluster and holds the three verbatim download options</t>
         </is>
       </c>
-      <c r="B44" s="2" t="inlineStr">
+      <c r="B42" s="2" t="inlineStr">
         <is>
           <t>TU — Exports</t>
         </is>
       </c>
-      <c r="C44" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D44" s="2" t="inlineStr">
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E44" s="2" t="inlineStr">
+      <c r="E42" s="2" t="inlineStr">
         <is>
           <t>1. You are on the Technician Utilization report with rows loaded.</t>
         </is>
       </c>
-      <c r="F44" s="2" t="inlineStr">
+      <c r="F42" s="2" t="inlineStr">
         <is>
           <t>1. Find the three-dot button in the toolbar and note its position in the action cluster.
 2. Open it and read the options.</t>
         </is>
       </c>
-      <c r="G44" s="2" t="inlineStr">
+      <c r="G42" s="2" t="inlineStr">
         <is>
           <t>1. The three-dot download menu sits LEFTMOST in the toolbar's action cluster.
 2. The menu holds: "Download Summary (PDF)", "Download Expanded View (PDF)", and "Download (CSV)".
 3. The labels match exactly - only the expanded option carries the word "View" (the shipped strings, documented as-is).</t>
         </is>
       </c>
-      <c r="H44" s="2" t="inlineStr">
+      <c r="H42" s="2" t="inlineStr">
         <is>
           <t>specs/technician-utilization.md S7-R1; S7-R2; S7-R3; S7-R4; S8-R2; S7-R12 note</t>
         </is>
       </c>
-      <c r="I44" s="2" t="inlineStr"/>
-      <c r="J44" s="2" t="inlineStr"/>
-    </row>
-    <row r="45">
-      <c r="A45" s="2" t="inlineStr">
+      <c r="I42" s="2" t="inlineStr"/>
+      <c r="J42" s="2" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
         <is>
           <t>The Summary PDF holds the technician rows plus the Summary, and the Expanded PDF adds every per-day breakdown</t>
         </is>
       </c>
-      <c r="B45" s="2" t="inlineStr">
+      <c r="B43" s="2" t="inlineStr">
         <is>
           <t>TU — Exports</t>
         </is>
       </c>
-      <c r="C45" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D45" s="2" t="inlineStr">
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E45" s="2" t="inlineStr">
+      <c r="E43" s="2" t="inlineStr">
         <is>
           <t>1. You are on the Technician Utilization report with several technicians who have multi-day clock records.</t>
         </is>
       </c>
-      <c r="F45" s="2" t="inlineStr">
+      <c r="F43" s="2" t="inlineStr">
         <is>
           <t>1. Choose "Download Summary (PDF)" and open the file; check its filename.
 2. Choose "Download Expanded View (PDF)" and open the file; check its filename.</t>
         </is>
       </c>
-      <c r="G45" s="2" t="inlineStr">
+      <c r="G43" s="2" t="inlineStr">
         <is>
           <t>1. The Summary PDF shows the technician rows and the Summary row (no day rows); it downloads as "Technician-Utilization-Summary.pdf".
 2. The Expanded PDF shows the technician rows, EACH technician's per-day breakdown, and the Summary row; it downloads as "Technician-Utilization-Expanded.pdf".
 3. The PDF filenames are Title-Case as shipped.</t>
         </is>
       </c>
-      <c r="H45" s="2" t="inlineStr">
+      <c r="H43" s="2" t="inlineStr">
         <is>
           <t>specs/technician-utilization.md S7-R5; S7-R6; S7-R12</t>
         </is>
       </c>
-      <c r="I45" s="2" t="inlineStr"/>
-      <c r="J45" s="2" t="inlineStr"/>
-    </row>
-    <row r="46">
-      <c r="A46" s="2" t="inlineStr">
+      <c r="I43" s="2" t="inlineStr"/>
+      <c r="J43" s="2" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
         <is>
           <t>The CSV is always summary-level, quotes comma-containing values, and downloads with the lower-case filename</t>
         </is>
       </c>
-      <c r="B46" s="2" t="inlineStr">
+      <c r="B44" s="2" t="inlineStr">
         <is>
           <t>TU — Exports</t>
         </is>
       </c>
-      <c r="C46" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D46" s="2" t="inlineStr">
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E46" s="2" t="inlineStr">
+      <c r="E44" s="2" t="inlineStr">
         <is>
           <t>1. At least one technician's Est. Lost Labor exceeds $1,000 (so a value contains a comma).</t>
         </is>
       </c>
-      <c r="F46" s="2" t="inlineStr">
+      <c r="F44" s="2" t="inlineStr">
         <is>
           <t>1. Choose "Download (CSV)" and check the filename.
 2. Open the file in a plain-text editor and find the over-$1,000 value.
 3. Check for any day rows in the file.</t>
         </is>
       </c>
-      <c r="G46" s="2" t="inlineStr">
+      <c r="G44" s="2" t="inlineStr">
         <is>
           <t>1. The file downloads as "technician-utilization.csv" (lower-case as shipped, unlike the Title-Case PDFs).
 2. The CSV shows the technician rows and the Summary row - always this summary-level content; it does NOT vary by the summary/expanded choice (no day rows).
 3. Any value containing a comma (e.g. "$1,234.50") is wrapped in double quotes per standard CSV escaping, so the columns parse correctly.</t>
         </is>
       </c>
-      <c r="H46" s="2" t="inlineStr">
+      <c r="H44" s="2" t="inlineStr">
         <is>
           <t>specs/technician-utilization.md S7-R7; S7-R10; S7-R12</t>
         </is>
       </c>
-      <c r="I46" s="2" t="inlineStr"/>
-      <c r="J46" s="2" t="inlineStr"/>
-    </row>
-    <row r="47">
-      <c r="A47" s="2" t="inlineStr">
+      <c r="I44" s="2" t="inlineStr"/>
+      <c r="J44" s="2" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
         <is>
           <t>Every download covers only the selected technicians, the selected locations, and the active date range</t>
         </is>
       </c>
-      <c r="B47" s="2" t="inlineStr">
+      <c r="B45" s="2" t="inlineStr">
         <is>
           <t>TU — Exports</t>
         </is>
       </c>
-      <c r="C47" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D47" s="2" t="inlineStr">
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E47" s="2" t="inlineStr">
+      <c r="E45" s="2" t="inlineStr">
         <is>
           <t>1. Several technicians are listed and the user has access to more than one location.</t>
         </is>
       </c>
-      <c r="F47" s="2" t="inlineStr">
+      <c r="F45" s="2" t="inlineStr">
         <is>
           <t>1. Deselect one technician, select a specific location set, and set a distinctive date range.
 2. Download the Summary PDF, the Expanded PDF, and the CSV.
@@ -2683,239 +2597,239 @@
 4. Re-select all technicians and download once more.</t>
         </is>
       </c>
-      <c r="G47" s="2" t="inlineStr">
+      <c r="G45" s="2" t="inlineStr">
         <is>
           <t>1. Every download includes ONLY the technicians currently selected in the technician filter - the deselected technician is absent from all three files.
 2. Every download covers the location(s) currently selected in the location filter and the date range currently active on the report.
 3. With every technician selected, the download covers all technicians for the range at the selected location(s).</t>
         </is>
       </c>
-      <c r="H47" s="2" t="inlineStr">
+      <c r="H45" s="2" t="inlineStr">
         <is>
           <t>specs/technician-utilization.md S7-R8; S7-R9; S7-E1; S9-R8</t>
         </is>
       </c>
-      <c r="I47" s="2" t="inlineStr"/>
-      <c r="J47" s="2" t="inlineStr"/>
-    </row>
-    <row r="48">
-      <c r="A48" s="2" t="inlineStr">
+      <c r="I45" s="2" t="inlineStr"/>
+      <c r="J45" s="2" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
         <is>
           <t>Downloads keep the on-screen column order and number formats but always order rows Technician A to Z, ignoring the on-screen sort</t>
         </is>
       </c>
-      <c r="B48" s="2" t="inlineStr">
+      <c r="B46" s="2" t="inlineStr">
         <is>
           <t>TU — Exports</t>
         </is>
       </c>
-      <c r="C48" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D48" s="2" t="inlineStr">
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E48" s="2" t="inlineStr">
+      <c r="E46" s="2" t="inlineStr">
         <is>
           <t>1. Rows exist including a "—" Est. Lost Labor value.
 2. The on-screen rows are sorted by something OTHER than Technician A to Z (e.g. Est. Lost Labor descending).</t>
         </is>
       </c>
-      <c r="F48" s="2" t="inlineStr">
+      <c r="F46" s="2" t="inlineStr">
         <is>
           <t>1. With the non-default sort applied, download the CSV and a PDF.
 2. Read each file's column order, number formats, and the "—" cell.
 3. Read each file's row order.</t>
         </is>
       </c>
-      <c r="G48" s="2" t="inlineStr">
+      <c r="G46" s="2" t="inlineStr">
         <is>
           <t>1. The downloaded files use the same column order and number formats as the on-screen report, including the "—" rendering for an unknown Est. Lost Labor.
 2. Rows in EVERY download are ordered by Technician name A to Z (the default order) - the on-screen column sort is client-side only and is NOT carried into the export.</t>
         </is>
       </c>
-      <c r="H48" s="2" t="inlineStr">
+      <c r="H46" s="2" t="inlineStr">
         <is>
           <t>specs/technician-utilization.md S7-R10; S7-R10a</t>
         </is>
       </c>
-      <c r="I48" s="2" t="inlineStr"/>
-      <c r="J48" s="2" t="inlineStr"/>
-    </row>
-    <row r="49">
-      <c r="A49" s="2" t="inlineStr">
+      <c r="I46" s="2" t="inlineStr"/>
+      <c r="J46" s="2" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
         <is>
           <t>The shop logo shows at the top of both PDF views when set, no logo shows when unset, and the CSV never includes it</t>
         </is>
       </c>
-      <c r="B49" s="2" t="inlineStr">
+      <c r="B47" s="2" t="inlineStr">
         <is>
           <t>TU — Exports</t>
         </is>
       </c>
-      <c r="C49" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D49" s="2" t="inlineStr">
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="E49" s="2" t="inlineStr">
+      <c r="E47" s="2" t="inlineStr">
         <is>
           <t>1. You can toggle the shop's logo in the shop settings (restore the original state afterwards - shared env).</t>
         </is>
       </c>
-      <c r="F49" s="2" t="inlineStr">
+      <c r="F47" s="2" t="inlineStr">
         <is>
           <t>1. With a shop logo set, download the Summary PDF and the Expanded PDF and look at the top of each.
 2. Download the CSV and inspect it.
 3. Remove the shop logo and download both PDFs again.</t>
         </is>
       </c>
-      <c r="G49" s="2" t="inlineStr">
+      <c r="G47" s="2" t="inlineStr">
         <is>
           <t>1. With a logo set, BOTH PDF views show that logo at the top of the report.
 2. The CSV never includes the logo.
 3. With no logo set, the PDF views show no logo (no placeholder, no error).</t>
         </is>
       </c>
-      <c r="H49" s="2" t="inlineStr">
+      <c r="H47" s="2" t="inlineStr">
         <is>
           <t>specs/technician-utilization.md S7-R11; S7-N2; S7-N3</t>
         </is>
       </c>
-      <c r="I49" s="2" t="inlineStr"/>
-      <c r="J49" s="2" t="inlineStr"/>
-    </row>
-    <row r="50">
-      <c r="A50" s="2" t="inlineStr">
+      <c r="I47" s="2" t="inlineStr"/>
+      <c r="J47" s="2" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
         <is>
           <t>Choosing a download with no technician selected is a silent no-op - no file and no message</t>
         </is>
       </c>
-      <c r="B50" s="2" t="inlineStr">
+      <c r="B48" s="2" t="inlineStr">
         <is>
           <t>TU — Exports</t>
         </is>
       </c>
-      <c r="C50" s="2" t="inlineStr">
+      <c r="C48" s="2" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="D50" s="2" t="inlineStr">
+      <c r="D48" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E50" s="2" t="inlineStr">
+      <c r="E48" s="2" t="inlineStr">
         <is>
           <t>1. You are on the Technician Utilization report with rows loaded.</t>
         </is>
       </c>
-      <c r="F50" s="2" t="inlineStr">
+      <c r="F48" s="2" t="inlineStr">
         <is>
           <t>1. Use "Clear all" in the Filter by Technician filter so no technician is selected.
 2. Choose each download option in turn (Summary PDF, Expanded PDF, CSV).
 3. Watch for any file download and any notification.</t>
         </is>
       </c>
-      <c r="G50" s="2" t="inlineStr">
+      <c r="G48" s="2" t="inlineStr">
         <is>
           <t>1. Nothing happens: NO file downloads and NO message appears (not even an error).
 2. This silent no-op is the specified behavior for every download option when no technician is selected.</t>
         </is>
       </c>
-      <c r="H50" s="2" t="inlineStr">
+      <c r="H48" s="2" t="inlineStr">
         <is>
           <t>specs/technician-utilization.md S7-N1; §7 context note</t>
         </is>
       </c>
-      <c r="I50" s="2" t="inlineStr"/>
-      <c r="J50" s="2" t="inlineStr"/>
-    </row>
-    <row r="51">
-      <c r="A51" s="2" t="inlineStr">
+      <c r="I48" s="2" t="inlineStr"/>
+      <c r="J48" s="2" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
         <is>
           <t>A starting download shows the Download started notification and a failed download shows Failed to download report</t>
         </is>
       </c>
-      <c r="B51" s="2" t="inlineStr">
+      <c r="B49" s="2" t="inlineStr">
         <is>
           <t>TU — Exports</t>
         </is>
       </c>
-      <c r="C51" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D51" s="2" t="inlineStr">
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E51" s="2" t="inlineStr">
+      <c r="E49" s="2" t="inlineStr">
         <is>
           <t>1. You are on the Technician Utilization report with rows loaded.
 2. You can force a download failure (e.g. drop the network connection just before triggering the download).</t>
         </is>
       </c>
-      <c r="F51" s="2" t="inlineStr">
+      <c r="F49" s="2" t="inlineStr">
         <is>
           <t>1. Trigger a normal download and read the notification.
 2. Trigger a download under the failure condition and read the notification.</t>
         </is>
       </c>
-      <c r="G51" s="2" t="inlineStr">
+      <c r="G49" s="2" t="inlineStr">
         <is>
           <t>1. When a download starts, a success notification reads exactly: "Download started".
 2. When a download fails, an error notification reads exactly: "Failed to download report".</t>
         </is>
       </c>
-      <c r="H51" s="2" t="inlineStr">
+      <c r="H49" s="2" t="inlineStr">
         <is>
           <t>specs/technician-utilization.md Story 7 Error Handling; §7</t>
         </is>
       </c>
-      <c r="I51" s="2" t="inlineStr"/>
-      <c r="J51" s="2" t="inlineStr"/>
-    </row>
-    <row r="52">
-      <c r="A52" s="2" t="inlineStr">
+      <c r="I49" s="2" t="inlineStr"/>
+      <c r="J49" s="2" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
         <is>
           <t>The Location filter is the rightmost multi-select; All Locations = select-all</t>
         </is>
       </c>
-      <c r="B52" s="2" t="inlineStr">
+      <c r="B50" s="2" t="inlineStr">
         <is>
           <t>TU — Location Filter</t>
         </is>
       </c>
-      <c r="C52" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D52" s="2" t="inlineStr">
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E52" s="2" t="inlineStr">
+      <c r="E50" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in as a user with access to at least two locations.
 2. You are on the Technician Utilization report.</t>
         </is>
       </c>
-      <c r="F52" s="2" t="inlineStr">
+      <c r="F50" s="2" t="inlineStr">
         <is>
           <t>1. Look at the rightmost control in the toolbar and read its label.
 2. Open it and read the listed options.
@@ -2923,7 +2837,7 @@
 4. With every accessible location selected, look at how the report tells you which location the shown data belongs to.</t>
         </is>
       </c>
-      <c r="G52" s="2" t="inlineStr">
+      <c r="G50" s="2" t="inlineStr">
         <is>
           <t>1. The toolbar has a location filter labeled "Location" - a multi-select and the RIGHTMOST control.
 2. It lists the locations the signed-in user has access to, plus an "All Locations" option.
@@ -2931,42 +2845,42 @@
 4. With all locations selected you can tell which location the shown data belongs to — a location label or marking is shown. (Exactly where and how it appears is confirmed in the build; this report pools each technician's hours into one row, so the marking may take a different form here.)</t>
         </is>
       </c>
-      <c r="H52" s="2" t="inlineStr">
+      <c r="H50" s="2" t="inlineStr">
         <is>
           <t>SV-8656 (specs/technician-utilization.md S9-R1 — per-row location identifier in All-Locations view ADDED per kickoff video P10 40:58-41:20, user ruling 2026-07-28: video overrides spec (video newer, last-update-wins))</t>
         </is>
       </c>
-      <c r="I52" s="2" t="inlineStr"/>
-      <c r="J52" s="2" t="inlineStr"/>
-    </row>
-    <row r="53">
-      <c r="A53" s="2" t="inlineStr">
+      <c r="I50" s="2" t="inlineStr"/>
+      <c r="J50" s="2" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
         <is>
           <t>Changing the location selection reloads the report with hours pooled into one row per technician, never beyond accessible locations</t>
         </is>
       </c>
-      <c r="B53" s="2" t="inlineStr">
+      <c r="B51" s="2" t="inlineStr">
         <is>
           <t>TU — Location Filter</t>
         </is>
       </c>
-      <c r="C53" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D53" s="2" t="inlineStr">
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="E53" s="2" t="inlineStr">
+      <c r="E51" s="2" t="inlineStr">
         <is>
           <t>1. A technician has clocked time at TWO accessible locations in the range.
 2. You are on the Technician Utilization report.</t>
         </is>
       </c>
-      <c r="F53" s="2" t="inlineStr">
+      <c r="F51" s="2" t="inlineStr">
         <is>
           <t>1. Select only location A and read the technician's hours.
 2. Add location B to the selection and watch the report.
@@ -2974,7 +2888,7 @@
 4. Expand the technician and check the day rows on a day with time at both locations.</t>
         </is>
       </c>
-      <c r="G53" s="2" t="inlineStr">
+      <c r="G51" s="2" t="inlineStr">
         <is>
           <t>1. Selecting one, several, or all locations RELOADS the report scoped to that set (unlike the technician filter, which is on-screen only).
 2. All metrics (technician rows, per-day rows, and the Summary) reflect only clock records at the selected location(s).
@@ -2982,56 +2896,149 @@
 4. Scoping never goes beyond the user's accessible locations - a location the user cannot access is never included.</t>
         </is>
       </c>
-      <c r="H53" s="2" t="inlineStr">
+      <c r="H51" s="2" t="inlineStr">
         <is>
           <t>specs/technician-utilization.md S9-R3; S9-R4; S9-R5</t>
         </is>
       </c>
-      <c r="I53" s="2" t="inlineStr"/>
-      <c r="J53" s="2" t="inlineStr"/>
-    </row>
-    <row r="54">
-      <c r="A54" s="2" t="inlineStr">
+      <c r="I51" s="2" t="inlineStr"/>
+      <c r="J51" s="2" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
         <is>
           <t>The saved location selection restores defensively - inaccessible locations are dropped and an empty remainder falls back to the active location</t>
         </is>
       </c>
-      <c r="B54" s="2" t="inlineStr">
+      <c r="B52" s="2" t="inlineStr">
         <is>
           <t>TU — Location Filter</t>
         </is>
       </c>
-      <c r="C54" s="2" t="inlineStr">
+      <c r="C52" s="2" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="D54" s="2" t="inlineStr">
+      <c r="D52" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E54" s="2" t="inlineStr">
+      <c r="E52" s="2" t="inlineStr">
         <is>
           <t>1. The user saved a location selection that includes a location their access to was later removed.</t>
         </is>
       </c>
-      <c r="F54" s="2" t="inlineStr">
+      <c r="F52" s="2" t="inlineStr">
         <is>
           <t>1. Return to the Technician Utilization report and read the restored location selection.
 2. Repeat with a saved selection consisting ONLY of now-inaccessible locations.</t>
         </is>
       </c>
-      <c r="G54" s="2" t="inlineStr">
+      <c r="G52" s="2" t="inlineStr">
         <is>
           <t>1. Any saved location the user can no longer access is DROPPED from the restored selection; the remaining accessible locations restore normally.
 2. If the remaining set is empty, the report falls back to the user's currently active location (the first-visit default).
 3. The report loads without an error in both cases.</t>
         </is>
       </c>
+      <c r="H52" s="2" t="inlineStr">
+        <is>
+          <t>specs/technician-utilization.md S9-R6; S1-R8; S9-R2</t>
+        </is>
+      </c>
+      <c r="I52" s="2" t="inlineStr"/>
+      <c r="J52" s="2" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t>Deselecting every location falls back to the active location instead of showing nothing</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>TU — Location Filter</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>1. You are on the Technician Utilization report with at least one location selected.</t>
+        </is>
+      </c>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
+          <t>1. In the Location filter, deselect every location (empty the filter).
+2. Watch what the report loads.</t>
+        </is>
+      </c>
+      <c r="G53" s="2" t="inlineStr">
+        <is>
+          <t>1. The report falls back to the user's currently active location rather than showing nothing.
+2. Rows for the active location load normally.</t>
+        </is>
+      </c>
+      <c r="H53" s="2" t="inlineStr">
+        <is>
+          <t>specs/technician-utilization.md S9-R7</t>
+        </is>
+      </c>
+      <c r="I53" s="2" t="inlineStr"/>
+      <c r="J53" s="2" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>The Location filter is hidden for a user with access to only one location</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>TU — Location Filter</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>1. You are signed in as a user with access to exactly one location.
+2. You are on the Technician Utilization report.</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t>1. Look for the Location filter in the toolbar.
+2. Then sign in as a user with access to two or more locations and look again.</t>
+        </is>
+      </c>
+      <c r="G54" s="2" t="inlineStr">
+        <is>
+          <t>1. For the single-location user the Location filter is NOT shown at all — the report simply shows that one location's data.
+2. For the user with access to two or more locations the Location filter IS shown.</t>
+        </is>
+      </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>specs/technician-utilization.md S9-R6; S1-R8; S9-R2</t>
+          <t>SV-8656 (specs/technician-utilization.md S9-N1 — expectation FLIPPED by kickoff video P33 46:10-46:28, user ruling 2026-07-28: video overrides spec (video newer, last-update-wins))</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr"/>
@@ -3040,17 +3047,17 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>Deselecting every location falls back to the active location instead of showing nothing</t>
+          <t>All-white table with no alternating row shading, and the toolbar controls run in the specified left-to-right order</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>TU — Location Filter</t>
+          <t>TU — Visual &amp; Accessibility</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>Negative</t>
+          <t>Functional</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
@@ -3060,152 +3067,59 @@
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>1. You are on the Technician Utilization report with at least one location selected.</t>
+          <t>1. You are on the Technician Utilization report with rows loaded, in light mode.</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
-        <is>
-          <t>1. In the Location filter, deselect every location (empty the filter).
-2. Watch what the report loads.</t>
-        </is>
-      </c>
-      <c r="G55" s="2" t="inlineStr">
-        <is>
-          <t>1. The report falls back to the user's currently active location rather than showing nothing.
-2. Rows for the active location load normally.</t>
-        </is>
-      </c>
-      <c r="H55" s="2" t="inlineStr">
-        <is>
-          <t>specs/technician-utilization.md S9-R7</t>
-        </is>
-      </c>
-      <c r="I55" s="2" t="inlineStr"/>
-      <c r="J55" s="2" t="inlineStr"/>
-    </row>
-    <row r="56">
-      <c r="A56" s="2" t="inlineStr">
-        <is>
-          <t>The Location filter is hidden for a user with access to only one location</t>
-        </is>
-      </c>
-      <c r="B56" s="2" t="inlineStr">
-        <is>
-          <t>TU — Location Filter</t>
-        </is>
-      </c>
-      <c r="C56" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D56" s="2" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="E56" s="2" t="inlineStr">
-        <is>
-          <t>1. You are signed in as a user with access to exactly one location.
-2. You are on the Technician Utilization report.</t>
-        </is>
-      </c>
-      <c r="F56" s="2" t="inlineStr">
-        <is>
-          <t>1. Look for the Location filter in the toolbar.
-2. Then sign in as a user with access to two or more locations and look again.</t>
-        </is>
-      </c>
-      <c r="G56" s="2" t="inlineStr">
-        <is>
-          <t>1. For the single-location user the Location filter is NOT shown at all — the report simply shows that one location's data.
-2. For the user with access to two or more locations the Location filter IS shown.</t>
-        </is>
-      </c>
-      <c r="H56" s="2" t="inlineStr">
-        <is>
-          <t>SV-8656 (specs/technician-utilization.md S9-N1 — expectation FLIPPED by kickoff video P33 46:10-46:28, user ruling 2026-07-28: video overrides spec (video newer, last-update-wins))</t>
-        </is>
-      </c>
-      <c r="I56" s="2" t="inlineStr"/>
-      <c r="J56" s="2" t="inlineStr"/>
-    </row>
-    <row r="57">
-      <c r="A57" s="2" t="inlineStr">
-        <is>
-          <t>All-white table with no alternating row shading, and the toolbar controls run in the specified left-to-right order</t>
-        </is>
-      </c>
-      <c r="B57" s="2" t="inlineStr">
-        <is>
-          <t>TU — Visual &amp; Accessibility</t>
-        </is>
-      </c>
-      <c r="C57" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D57" s="2" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="E57" s="2" t="inlineStr">
-        <is>
-          <t>1. You are on the Technician Utilization report with rows loaded, in light mode.</t>
-        </is>
-      </c>
-      <c r="F57" s="2" t="inlineStr">
         <is>
           <t>1. Look at the column headers and the data rows' backgrounds.
 2. Read the toolbar controls left to right.
 3. Look for the expand/collapse-all control's position.</t>
         </is>
       </c>
-      <c r="G57" s="2" t="inlineStr">
+      <c r="G55" s="2" t="inlineStr">
         <is>
           <t>1. The report uses an all-white table: white column headers and white data cells, with NO alternating row shading.
 2. The toolbar controls run, left to right: the three-dot download menu, the technician filter, the date-range picker, and the location filter (rightmost).
 3. The expand/collapse-all control is NOT a toolbar control - it lives in the table header (Technician column, per S4-R4).</t>
         </is>
       </c>
-      <c r="H57" s="2" t="inlineStr">
+      <c r="H55" s="2" t="inlineStr">
         <is>
           <t>specs/technician-utilization.md S8-R1; S8-R2; S8-R3</t>
         </is>
       </c>
-      <c r="I57" s="2" t="inlineStr"/>
-      <c r="J57" s="2" t="inlineStr"/>
-    </row>
-    <row r="58">
-      <c r="A58" s="2" t="inlineStr">
+      <c r="I55" s="2" t="inlineStr"/>
+      <c r="J55" s="2" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
         <is>
           <t>Dark mode keeps every report element legible, with the info icon at 3:1 contrast and the link affordance intact in both modes</t>
         </is>
       </c>
-      <c r="B58" s="2" t="inlineStr">
+      <c r="B56" s="2" t="inlineStr">
         <is>
           <t>TU — Visual &amp; Accessibility</t>
         </is>
       </c>
-      <c r="C58" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D58" s="2" t="inlineStr">
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="E58" s="2" t="inlineStr">
+      <c r="E56" s="2" t="inlineStr">
         <is>
           <t>1. You are on the Technician Utilization report with rows loaded, including a "—" Est. Lost Labor cell.
 2. Dark mode is available in the application.</t>
         </is>
       </c>
-      <c r="F58" s="2" t="inlineStr">
+      <c r="F56" s="2" t="inlineStr">
         <is>
           <t>1. Switch the application to dark mode.
 2. Check each element: page background, toolbar, cells, the Total Hours link, the information icon, the sort indicator, and a "—" glyph.
@@ -3213,96 +3127,96 @@
 4. Check the Total Hours link's underline/affordance and focus indicator in both modes.</t>
         </is>
       </c>
-      <c r="G58" s="2" t="inlineStr">
+      <c r="G56" s="2" t="inlineStr">
         <is>
           <t>1. The report supports dark mode: page background, toolbar, cells, the Total Hours link, the information icon, the sort indicator, and the "—" glyph all use dark-mode-legible colors meeting contrast.
 2. The information icon meets at least a 3:1 contrast ratio against its background in BOTH light and dark mode.
 3. The Total Hours link's non-color affordance and focus indicator apply in both modes.</t>
         </is>
       </c>
-      <c r="H58" s="2" t="inlineStr">
+      <c r="H56" s="2" t="inlineStr">
         <is>
           <t>specs/technician-utilization.md S8-R9; S8-R13; S8-R14</t>
         </is>
       </c>
-      <c r="I58" s="2" t="inlineStr"/>
-      <c r="J58" s="2" t="inlineStr"/>
-    </row>
-    <row r="59">
-      <c r="A59" s="2" t="inlineStr">
+      <c r="I56" s="2" t="inlineStr"/>
+      <c r="J56" s="2" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
         <is>
           <t>The per-day breakdown is fetched from the backend on demand when a row is expanded, not shipped with the initial payload</t>
         </is>
       </c>
-      <c r="B59" s="2" t="inlineStr">
+      <c r="B57" s="2" t="inlineStr">
         <is>
           <t>TU — API</t>
         </is>
       </c>
-      <c r="C59" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D59" s="2" t="inlineStr">
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E59" s="2" t="inlineStr">
+      <c r="E57" s="2" t="inlineStr">
         <is>
           <t>1. You are on the Technician Utilization report with rows loaded and browser devtools (network tab) open.</t>
         </is>
       </c>
-      <c r="F59" s="2" t="inlineStr">
+      <c r="F57" s="2" t="inlineStr">
         <is>
           <t>1. Load the report and inspect the initial data response for per-day content.
 2. Expand a technician row and watch the network traffic.
 3. Collapse and re-expand after a data reload.</t>
         </is>
       </c>
-      <c r="G59" s="2" t="inlineStr">
+      <c r="G57" s="2" t="inlineStr">
         <is>
           <t>1. The initial report payload does NOT ship the day rows.
 2. Expanding a technician row issues an on-demand backend request that returns that technician's per-day breakdown.
 3. Because expansion state resets (all collapsed) on any data reload, nothing is lost by the lazy loading - re-expanding fetches fresh day data.</t>
         </is>
       </c>
-      <c r="H59" s="2" t="inlineStr">
+      <c r="H57" s="2" t="inlineStr">
         <is>
           <t>specs/technician-utilization.md S4-R2; S4-R5</t>
         </is>
       </c>
-      <c r="I59" s="2" t="inlineStr"/>
-      <c r="J59" s="2" t="inlineStr"/>
-    </row>
-    <row r="60">
-      <c r="A60" s="2" t="inlineStr">
+      <c r="I57" s="2" t="inlineStr"/>
+      <c r="J57" s="2" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
         <is>
           <t>Date-range and location changes trigger a fresh server load, while the technician filter and column sorting stay on-screen only</t>
         </is>
       </c>
-      <c r="B60" s="2" t="inlineStr">
+      <c r="B58" s="2" t="inlineStr">
         <is>
           <t>TU — API</t>
         </is>
       </c>
-      <c r="C60" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D60" s="2" t="inlineStr">
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E60" s="2" t="inlineStr">
+      <c r="E58" s="2" t="inlineStr">
         <is>
           <t>1. You are on the Technician Utilization report with rows loaded and browser devtools (network tab) open.</t>
         </is>
       </c>
-      <c r="F60" s="2" t="inlineStr">
+      <c r="F58" s="2" t="inlineStr">
         <is>
           <t>1. Change the date range and watch the network traffic.
 2. Change the location selection and watch the traffic.
@@ -3310,7 +3224,7 @@
 4. Click several column headers to sort and watch the traffic.</t>
         </is>
       </c>
-      <c r="G60" s="2" t="inlineStr">
+      <c r="G58" s="2" t="inlineStr">
         <is>
           <t>1. A date-range change triggers a fresh server load of the rows.
 2. A location change triggers a fresh server load scoped to the selected set.
@@ -3318,13 +3232,13 @@
 4. Column sorting causes NO server request - it is applied on screen to the loaded rows.</t>
         </is>
       </c>
-      <c r="H60" s="2" t="inlineStr">
+      <c r="H58" s="2" t="inlineStr">
         <is>
           <t>specs/technician-utilization.md S1-R5; S9-R3; S5 context note; S2-R13; §3</t>
         </is>
       </c>
-      <c r="I60" s="2" t="inlineStr"/>
-      <c r="J60" s="2" t="inlineStr"/>
+      <c r="I58" s="2" t="inlineStr"/>
+      <c r="J58" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/testrail-import/Report-Suite_Technician-Utilization-Report_testrail-import.xlsx
+++ b/testrail-import/Report-Suite_Technician-Utilization-Report_testrail-import.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J58"/>
+  <dimension ref="A1:J59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
@@ -1695,7 +1695,7 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>Each technician row has an accessible expand/collapse control named for its next action</t>
+          <t>Each technician row has an accessible expand/collapse control</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
@@ -1728,13 +1728,13 @@
       <c r="G27" s="2" t="inlineStr">
         <is>
           <t>1. Each technician row has a control to expand and collapse it.
-2. Its accessible name reflects the NEXT action, scoped to that technician: "Expand &lt;technician&gt;'s daily breakdown" when collapsed, "Collapse &lt;technician&gt;'s daily breakdown" when expanded.
+2. Its accessible name reflects the NEXT action, scoped to that technician: when collapsed it reads Expand, then that technician's name, then daily breakdown (for example: Expand John Smith's daily breakdown); when expanded it reads Collapse, then the same name and words.
 3. The control is keyboard-focusable, toggles on Enter and Space, and exposes its expanded/collapsed state to assistive technology.</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>specs/technician-utilization.md S4-R1; S8-R12</t>
+          <t>SV-8651 (specs/technician-utilization.md S4-R1; S8-R12)</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr"/>
@@ -2566,7 +2566,7 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>Every download covers only the selected technicians, the selected locations, and the active date range</t>
+          <t>Downloads cover only selected technicians, locations, and date range</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
@@ -2601,12 +2601,13 @@
         <is>
           <t>1. Every download includes ONLY the technicians currently selected in the technician filter - the deselected technician is absent from all three files.
 2. Every download covers the location(s) currently selected in the location filter and the date range currently active on the report.
-3. With every technician selected, the download covers all technicians for the range at the selected location(s).</t>
+3. With every technician selected, the download covers all technicians for the range at the selected location(s).
+4. Every download (each PDF and the CSV) carries a "Locations:" line naming the location(s) the report was scoped to (exact position in the file is confirmed in the build).</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>specs/technician-utilization.md S7-R8; S7-R9; S7-E1; S9-R8</t>
+          <t>SV-8654 (specs/technician-utilization.md S7-R8; S7-R9; S7-E1; S9-R8 + Locations: line in every CSV/PDF export per Chris Ward group message 2026-07-29 (chris-update-2026-07-29/chris-message-2026-07-29.md; NEWEST source, last-update-wins))</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr"/>
@@ -2856,7 +2857,7 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>Changing the location selection reloads the report with hours pooled into one row per technician, never beyond accessible locations</t>
+          <t>Location changes reload with hours pooled into one row per technician</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
@@ -2893,12 +2894,13 @@
           <t>1. Selecting one, several, or all locations RELOADS the report scoped to that set (unlike the technician filter, which is on-screen only).
 2. All metrics (technician rows, per-day rows, and the Summary) reflect only clock records at the selected location(s).
 3. The technician's hours are POOLED across the selected locations into ONE row (one row per technician, not one per location); per-day rows pool the same way.
-4. Scoping never goes beyond the user's accessible locations - a location the user cannot access is never included.</t>
+4. Scoping never goes beyond the user's accessible locations - a location the user cannot access is never included.
+5. The page itself shows which location(s) the report is currently scoped to (the new on-screen scope indicator - exactly where and how it appears is confirmed in the build).</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>specs/technician-utilization.md S9-R3; S9-R4; S9-R5</t>
+          <t>SV-8656 (specs/technician-utilization.md S9-R3; S9-R4; S9-R5 + on-screen location-scope indicator per Chris Ward group message 2026-07-29 (chris-update-2026-07-29/chris-message-2026-07-29.md; NEWEST source, last-update-wins))</t>
         </is>
       </c>
       <c r="I51" s="2" t="inlineStr"/>
@@ -3047,79 +3049,127 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
+          <t>A column selector lets the user choose which columns show</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>TU — Visual &amp; Accessibility</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t>1. You are on the Technician Utilization report with rows loaded.</t>
+        </is>
+      </c>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
+          <t>1. Find the column selector control in the toolbar (on the other reports it is a separate button next to the download menu).
+2. Open it and read the list of column toggles.
+3. Turn one column off, then back on, watching the table.</t>
+        </is>
+      </c>
+      <c r="G55" s="2" t="inlineStr">
+        <is>
+          <t>1. The report has a column selector control, styled and placed like the other reports in the suite (this control was just added - the exact placement, tooltip, and list of toggleable columns are confirmed from the updated spec and the build).
+2. Turning a toggle off hides that column (header and cells); turning it back on restores the column to its usual place in the order.
+3. The change applies immediately with no reload - that is the suite convention on the other reports; confirm it holds here.</t>
+        </is>
+      </c>
+      <c r="H55" s="2" t="inlineStr">
+        <is>
+          <t>SV-8655 (specs/technician-utilization.md Story 8 Visual Conformance and Accessibility - column selector ADDED per Chris Ward group message 2026-07-29 (chris-update-2026-07-29/chris-message-2026-07-29.md; NEWEST source, last-update-wins) ['Column selector added for visual/natural conformance']; no spec anchor yet - confirm from the updated spec changelog)</t>
+        </is>
+      </c>
+      <c r="I55" s="2" t="inlineStr"/>
+      <c r="J55" s="2" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
           <t>All-white table with no alternating row shading, and the toolbar controls run in the specified left-to-right order</t>
         </is>
       </c>
-      <c r="B55" s="2" t="inlineStr">
+      <c r="B56" s="2" t="inlineStr">
         <is>
           <t>TU — Visual &amp; Accessibility</t>
         </is>
       </c>
-      <c r="C55" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D55" s="2" t="inlineStr">
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E55" s="2" t="inlineStr">
+      <c r="E56" s="2" t="inlineStr">
         <is>
           <t>1. You are on the Technician Utilization report with rows loaded, in light mode.</t>
         </is>
       </c>
-      <c r="F55" s="2" t="inlineStr">
+      <c r="F56" s="2" t="inlineStr">
         <is>
           <t>1. Look at the column headers and the data rows' backgrounds.
 2. Read the toolbar controls left to right.
 3. Look for the expand/collapse-all control's position.</t>
         </is>
       </c>
-      <c r="G55" s="2" t="inlineStr">
+      <c r="G56" s="2" t="inlineStr">
         <is>
           <t>1. The report uses an all-white table: white column headers and white data cells, with NO alternating row shading.
 2. The toolbar controls run, left to right: the three-dot download menu, the technician filter, the date-range picker, and the location filter (rightmost).
 3. The expand/collapse-all control is NOT a toolbar control - it lives in the table header (Technician column, per S4-R4).</t>
         </is>
       </c>
-      <c r="H55" s="2" t="inlineStr">
+      <c r="H56" s="2" t="inlineStr">
         <is>
           <t>specs/technician-utilization.md S8-R1; S8-R2; S8-R3</t>
         </is>
       </c>
-      <c r="I55" s="2" t="inlineStr"/>
-      <c r="J55" s="2" t="inlineStr"/>
-    </row>
-    <row r="56">
-      <c r="A56" s="2" t="inlineStr">
+      <c r="I56" s="2" t="inlineStr"/>
+      <c r="J56" s="2" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
         <is>
           <t>Dark mode keeps every report element legible, with the info icon at 3:1 contrast and the link affordance intact in both modes</t>
         </is>
       </c>
-      <c r="B56" s="2" t="inlineStr">
+      <c r="B57" s="2" t="inlineStr">
         <is>
           <t>TU — Visual &amp; Accessibility</t>
         </is>
       </c>
-      <c r="C56" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D56" s="2" t="inlineStr">
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="E56" s="2" t="inlineStr">
+      <c r="E57" s="2" t="inlineStr">
         <is>
           <t>1. You are on the Technician Utilization report with rows loaded, including a "—" Est. Lost Labor cell.
 2. Dark mode is available in the application.</t>
         </is>
       </c>
-      <c r="F56" s="2" t="inlineStr">
+      <c r="F57" s="2" t="inlineStr">
         <is>
           <t>1. Switch the application to dark mode.
 2. Check each element: page background, toolbar, cells, the Total Hours link, the information icon, the sort indicator, and a "—" glyph.
@@ -3127,96 +3177,96 @@
 4. Check the Total Hours link's underline/affordance and focus indicator in both modes.</t>
         </is>
       </c>
-      <c r="G56" s="2" t="inlineStr">
+      <c r="G57" s="2" t="inlineStr">
         <is>
           <t>1. The report supports dark mode: page background, toolbar, cells, the Total Hours link, the information icon, the sort indicator, and the "—" glyph all use dark-mode-legible colors meeting contrast.
 2. The information icon meets at least a 3:1 contrast ratio against its background in BOTH light and dark mode.
 3. The Total Hours link's non-color affordance and focus indicator apply in both modes.</t>
         </is>
       </c>
-      <c r="H56" s="2" t="inlineStr">
+      <c r="H57" s="2" t="inlineStr">
         <is>
           <t>specs/technician-utilization.md S8-R9; S8-R13; S8-R14</t>
         </is>
       </c>
-      <c r="I56" s="2" t="inlineStr"/>
-      <c r="J56" s="2" t="inlineStr"/>
-    </row>
-    <row r="57">
-      <c r="A57" s="2" t="inlineStr">
+      <c r="I57" s="2" t="inlineStr"/>
+      <c r="J57" s="2" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
         <is>
           <t>The per-day breakdown is fetched from the backend on demand when a row is expanded, not shipped with the initial payload</t>
         </is>
       </c>
-      <c r="B57" s="2" t="inlineStr">
+      <c r="B58" s="2" t="inlineStr">
         <is>
           <t>TU — API</t>
         </is>
       </c>
-      <c r="C57" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D57" s="2" t="inlineStr">
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E57" s="2" t="inlineStr">
+      <c r="E58" s="2" t="inlineStr">
         <is>
           <t>1. You are on the Technician Utilization report with rows loaded and browser devtools (network tab) open.</t>
         </is>
       </c>
-      <c r="F57" s="2" t="inlineStr">
+      <c r="F58" s="2" t="inlineStr">
         <is>
           <t>1. Load the report and inspect the initial data response for per-day content.
 2. Expand a technician row and watch the network traffic.
 3. Collapse and re-expand after a data reload.</t>
         </is>
       </c>
-      <c r="G57" s="2" t="inlineStr">
+      <c r="G58" s="2" t="inlineStr">
         <is>
           <t>1. The initial report payload does NOT ship the day rows.
 2. Expanding a technician row issues an on-demand backend request that returns that technician's per-day breakdown.
 3. Because expansion state resets (all collapsed) on any data reload, nothing is lost by the lazy loading - re-expanding fetches fresh day data.</t>
         </is>
       </c>
-      <c r="H57" s="2" t="inlineStr">
+      <c r="H58" s="2" t="inlineStr">
         <is>
           <t>specs/technician-utilization.md S4-R2; S4-R5</t>
         </is>
       </c>
-      <c r="I57" s="2" t="inlineStr"/>
-      <c r="J57" s="2" t="inlineStr"/>
-    </row>
-    <row r="58">
-      <c r="A58" s="2" t="inlineStr">
+      <c r="I58" s="2" t="inlineStr"/>
+      <c r="J58" s="2" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
         <is>
           <t>Date-range and location changes trigger a fresh server load, while the technician filter and column sorting stay on-screen only</t>
         </is>
       </c>
-      <c r="B58" s="2" t="inlineStr">
+      <c r="B59" s="2" t="inlineStr">
         <is>
           <t>TU — API</t>
         </is>
       </c>
-      <c r="C58" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D58" s="2" t="inlineStr">
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E58" s="2" t="inlineStr">
+      <c r="E59" s="2" t="inlineStr">
         <is>
           <t>1. You are on the Technician Utilization report with rows loaded and browser devtools (network tab) open.</t>
         </is>
       </c>
-      <c r="F58" s="2" t="inlineStr">
+      <c r="F59" s="2" t="inlineStr">
         <is>
           <t>1. Change the date range and watch the network traffic.
 2. Change the location selection and watch the traffic.
@@ -3224,7 +3274,7 @@
 4. Click several column headers to sort and watch the traffic.</t>
         </is>
       </c>
-      <c r="G58" s="2" t="inlineStr">
+      <c r="G59" s="2" t="inlineStr">
         <is>
           <t>1. A date-range change triggers a fresh server load of the rows.
 2. A location change triggers a fresh server load scoped to the selected set.
@@ -3232,13 +3282,13 @@
 4. Column sorting causes NO server request - it is applied on screen to the loaded rows.</t>
         </is>
       </c>
-      <c r="H58" s="2" t="inlineStr">
+      <c r="H59" s="2" t="inlineStr">
         <is>
           <t>specs/technician-utilization.md S1-R5; S9-R3; S5 context note; S2-R13; §3</t>
         </is>
       </c>
-      <c r="I58" s="2" t="inlineStr"/>
-      <c r="J58" s="2" t="inlineStr"/>
+      <c r="I59" s="2" t="inlineStr"/>
+      <c r="J59" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/testrail-import/Report-Suite_Technician-Utilization-Report_testrail-import.xlsx
+++ b/testrail-import/Report-Suite_Technician-Utilization-Report_testrail-import.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Technician Utilization" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Technician Utilization" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J59"/>
+  <dimension ref="A1:J60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
@@ -2806,31 +2806,81 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
+          <t>An over-cap Technician Utilization export is refused with the too-large message</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>TU — Exports</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>1. You are signed in to the ShopView App on a desktop browser.
+2. A range/location combination exists whose filtered set EXCEEDS the export row cap (widest date range + all locations; seed ZZAUTOTEST clock records in bulk if needed, or use the largest available data set).</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>1. Set the date range and locations so the filtered set exceeds the export row cap.
+2. Request the CSV download and read what happens.
+3. Request the PDF download and read what happens.
+4. Narrow the date range or filters below the cap and request a download again.</t>
+        </is>
+      </c>
+      <c r="G50" s="2" t="inlineStr">
+        <is>
+          <t>1. Neither the CSV nor the PDF is produced — no download starts.
+2. A clear too-large message appears telling the user to narrow the date range or filters, then try again — the standard wording is "This report is too large to export. Narrow the date range or filters, then try again."
+3. After narrowing below the cap, the downloads work again.</t>
+        </is>
+      </c>
+      <c r="H50" s="2" t="inlineStr">
+        <is>
+          <t>SV-8654 (specs/technician-utilization.md Story 7 exports — spec silent on a cap; tech-plan-2026-07-29 A3/FR-F4: suite-wide 10,000-row export cap, locked by Chris 2026-07-21)</t>
+        </is>
+      </c>
+      <c r="I50" s="2" t="inlineStr"/>
+      <c r="J50" s="2" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
           <t>The Location filter is the rightmost multi-select; All Locations = select-all</t>
         </is>
       </c>
-      <c r="B50" s="2" t="inlineStr">
+      <c r="B51" s="2" t="inlineStr">
         <is>
           <t>TU — Location Filter</t>
         </is>
       </c>
-      <c r="C50" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D50" s="2" t="inlineStr">
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E50" s="2" t="inlineStr">
+      <c r="E51" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in as a user with access to at least two locations.
 2. You are on the Technician Utilization report.</t>
         </is>
       </c>
-      <c r="F50" s="2" t="inlineStr">
+      <c r="F51" s="2" t="inlineStr">
         <is>
           <t>1. Look at the rightmost control in the toolbar and read its label.
 2. Open it and read the listed options.
@@ -2838,7 +2888,7 @@
 4. With every accessible location selected, look at how the report tells you which location the shown data belongs to.</t>
         </is>
       </c>
-      <c r="G50" s="2" t="inlineStr">
+      <c r="G51" s="2" t="inlineStr">
         <is>
           <t>1. The toolbar has a location filter labeled "Location" - a multi-select and the RIGHTMOST control.
 2. It lists the locations the signed-in user has access to, plus an "All Locations" option.
@@ -2846,42 +2896,42 @@
 4. With all locations selected you can tell which location the shown data belongs to — a location label or marking is shown. (Exactly where and how it appears is confirmed in the build; this report pools each technician's hours into one row, so the marking may take a different form here.)</t>
         </is>
       </c>
-      <c r="H50" s="2" t="inlineStr">
+      <c r="H51" s="2" t="inlineStr">
         <is>
           <t>SV-8656 (specs/technician-utilization.md S9-R1 — per-row location identifier in All-Locations view ADDED per kickoff video P10 40:58-41:20, user ruling 2026-07-28: video overrides spec (video newer, last-update-wins))</t>
         </is>
       </c>
-      <c r="I50" s="2" t="inlineStr"/>
-      <c r="J50" s="2" t="inlineStr"/>
-    </row>
-    <row r="51">
-      <c r="A51" s="2" t="inlineStr">
+      <c r="I51" s="2" t="inlineStr"/>
+      <c r="J51" s="2" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
         <is>
           <t>Location changes reload with hours pooled into one row per technician</t>
         </is>
       </c>
-      <c r="B51" s="2" t="inlineStr">
+      <c r="B52" s="2" t="inlineStr">
         <is>
           <t>TU — Location Filter</t>
         </is>
       </c>
-      <c r="C51" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D51" s="2" t="inlineStr">
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="E51" s="2" t="inlineStr">
+      <c r="E52" s="2" t="inlineStr">
         <is>
           <t>1. A technician has clocked time at TWO accessible locations in the range.
 2. You are on the Technician Utilization report.</t>
         </is>
       </c>
-      <c r="F51" s="2" t="inlineStr">
+      <c r="F52" s="2" t="inlineStr">
         <is>
           <t>1. Select only location A and read the technician's hours.
 2. Add location B to the selection and watch the report.
@@ -2889,7 +2939,7 @@
 4. Expand the technician and check the day rows on a day with time at both locations.</t>
         </is>
       </c>
-      <c r="G51" s="2" t="inlineStr">
+      <c r="G52" s="2" t="inlineStr">
         <is>
           <t>1. Selecting one, several, or all locations RELOADS the report scoped to that set (unlike the technician filter, which is on-screen only).
 2. All metrics (technician rows, per-day rows, and the Summary) reflect only clock records at the selected location(s).
@@ -2898,278 +2948,278 @@
 5. The page itself shows which location(s) the report is currently scoped to (the new on-screen scope indicator - exactly where and how it appears is confirmed in the build).</t>
         </is>
       </c>
-      <c r="H51" s="2" t="inlineStr">
+      <c r="H52" s="2" t="inlineStr">
         <is>
           <t>SV-8656 (specs/technician-utilization.md S9-R3; S9-R4; S9-R5 + on-screen location-scope indicator per Chris Ward group message 2026-07-29 (chris-update-2026-07-29/chris-message-2026-07-29.md; NEWEST source, last-update-wins))</t>
         </is>
       </c>
-      <c r="I51" s="2" t="inlineStr"/>
-      <c r="J51" s="2" t="inlineStr"/>
-    </row>
-    <row r="52">
-      <c r="A52" s="2" t="inlineStr">
+      <c r="I52" s="2" t="inlineStr"/>
+      <c r="J52" s="2" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
         <is>
           <t>The saved location selection restores defensively - inaccessible locations are dropped and an empty remainder falls back to the active location</t>
         </is>
       </c>
-      <c r="B52" s="2" t="inlineStr">
+      <c r="B53" s="2" t="inlineStr">
         <is>
           <t>TU — Location Filter</t>
         </is>
       </c>
-      <c r="C52" s="2" t="inlineStr">
+      <c r="C53" s="2" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="D52" s="2" t="inlineStr">
+      <c r="D53" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E52" s="2" t="inlineStr">
+      <c r="E53" s="2" t="inlineStr">
         <is>
           <t>1. The user saved a location selection that includes a location their access to was later removed.</t>
         </is>
       </c>
-      <c r="F52" s="2" t="inlineStr">
+      <c r="F53" s="2" t="inlineStr">
         <is>
           <t>1. Return to the Technician Utilization report and read the restored location selection.
 2. Repeat with a saved selection consisting ONLY of now-inaccessible locations.</t>
         </is>
       </c>
-      <c r="G52" s="2" t="inlineStr">
+      <c r="G53" s="2" t="inlineStr">
         <is>
           <t>1. Any saved location the user can no longer access is DROPPED from the restored selection; the remaining accessible locations restore normally.
 2. If the remaining set is empty, the report falls back to the user's currently active location (the first-visit default).
 3. The report loads without an error in both cases.</t>
         </is>
       </c>
-      <c r="H52" s="2" t="inlineStr">
+      <c r="H53" s="2" t="inlineStr">
         <is>
           <t>specs/technician-utilization.md S9-R6; S1-R8; S9-R2</t>
         </is>
       </c>
-      <c r="I52" s="2" t="inlineStr"/>
-      <c r="J52" s="2" t="inlineStr"/>
-    </row>
-    <row r="53">
-      <c r="A53" s="2" t="inlineStr">
+      <c r="I53" s="2" t="inlineStr"/>
+      <c r="J53" s="2" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
         <is>
           <t>Deselecting every location falls back to the active location instead of showing nothing</t>
         </is>
       </c>
-      <c r="B53" s="2" t="inlineStr">
+      <c r="B54" s="2" t="inlineStr">
         <is>
           <t>TU — Location Filter</t>
         </is>
       </c>
-      <c r="C53" s="2" t="inlineStr">
+      <c r="C54" s="2" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="D53" s="2" t="inlineStr">
+      <c r="D54" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E53" s="2" t="inlineStr">
+      <c r="E54" s="2" t="inlineStr">
         <is>
           <t>1. You are on the Technician Utilization report with at least one location selected.</t>
         </is>
       </c>
-      <c r="F53" s="2" t="inlineStr">
+      <c r="F54" s="2" t="inlineStr">
         <is>
           <t>1. In the Location filter, deselect every location (empty the filter).
 2. Watch what the report loads.</t>
         </is>
       </c>
-      <c r="G53" s="2" t="inlineStr">
+      <c r="G54" s="2" t="inlineStr">
         <is>
           <t>1. The report falls back to the user's currently active location rather than showing nothing.
 2. Rows for the active location load normally.</t>
         </is>
       </c>
-      <c r="H53" s="2" t="inlineStr">
+      <c r="H54" s="2" t="inlineStr">
         <is>
           <t>specs/technician-utilization.md S9-R7</t>
         </is>
       </c>
-      <c r="I53" s="2" t="inlineStr"/>
-      <c r="J53" s="2" t="inlineStr"/>
-    </row>
-    <row r="54">
-      <c r="A54" s="2" t="inlineStr">
+      <c r="I54" s="2" t="inlineStr"/>
+      <c r="J54" s="2" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
         <is>
           <t>The Location filter is hidden for a user with access to only one location</t>
         </is>
       </c>
-      <c r="B54" s="2" t="inlineStr">
+      <c r="B55" s="2" t="inlineStr">
         <is>
           <t>TU — Location Filter</t>
         </is>
       </c>
-      <c r="C54" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D54" s="2" t="inlineStr">
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="E54" s="2" t="inlineStr">
+      <c r="E55" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in as a user with access to exactly one location.
 2. You are on the Technician Utilization report.</t>
         </is>
       </c>
-      <c r="F54" s="2" t="inlineStr">
+      <c r="F55" s="2" t="inlineStr">
         <is>
           <t>1. Look for the Location filter in the toolbar.
 2. Then sign in as a user with access to two or more locations and look again.</t>
         </is>
       </c>
-      <c r="G54" s="2" t="inlineStr">
+      <c r="G55" s="2" t="inlineStr">
         <is>
           <t>1. For the single-location user the Location filter is NOT shown at all — the report simply shows that one location's data.
 2. For the user with access to two or more locations the Location filter IS shown.</t>
         </is>
       </c>
-      <c r="H54" s="2" t="inlineStr">
+      <c r="H55" s="2" t="inlineStr">
         <is>
           <t>SV-8656 (specs/technician-utilization.md S9-N1 — expectation FLIPPED by kickoff video P33 46:10-46:28, user ruling 2026-07-28: video overrides spec (video newer, last-update-wins))</t>
         </is>
       </c>
-      <c r="I54" s="2" t="inlineStr"/>
-      <c r="J54" s="2" t="inlineStr"/>
-    </row>
-    <row r="55">
-      <c r="A55" s="2" t="inlineStr">
+      <c r="I55" s="2" t="inlineStr"/>
+      <c r="J55" s="2" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
         <is>
           <t>A column selector lets the user choose which columns show</t>
         </is>
       </c>
-      <c r="B55" s="2" t="inlineStr">
+      <c r="B56" s="2" t="inlineStr">
         <is>
           <t>TU — Visual &amp; Accessibility</t>
         </is>
       </c>
-      <c r="C55" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D55" s="2" t="inlineStr">
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E55" s="2" t="inlineStr">
+      <c r="E56" s="2" t="inlineStr">
         <is>
           <t>1. You are on the Technician Utilization report with rows loaded.</t>
         </is>
       </c>
-      <c r="F55" s="2" t="inlineStr">
+      <c r="F56" s="2" t="inlineStr">
         <is>
           <t>1. Find the column selector control in the toolbar (on the other reports it is a separate button next to the download menu).
 2. Open it and read the list of column toggles.
 3. Turn one column off, then back on, watching the table.</t>
         </is>
       </c>
-      <c r="G55" s="2" t="inlineStr">
+      <c r="G56" s="2" t="inlineStr">
         <is>
           <t>1. The report has a column selector control, styled and placed like the other reports in the suite (this control was just added - the exact placement, tooltip, and list of toggleable columns are confirmed from the updated spec and the build).
 2. Turning a toggle off hides that column (header and cells); turning it back on restores the column to its usual place in the order.
 3. The change applies immediately with no reload - that is the suite convention on the other reports; confirm it holds here.</t>
         </is>
       </c>
-      <c r="H55" s="2" t="inlineStr">
+      <c r="H56" s="2" t="inlineStr">
         <is>
           <t>SV-8655 (specs/technician-utilization.md Story 8 Visual Conformance and Accessibility - column selector ADDED per Chris Ward group message 2026-07-29 (chris-update-2026-07-29/chris-message-2026-07-29.md; NEWEST source, last-update-wins) ['Column selector added for visual/natural conformance']; no spec anchor yet - confirm from the updated spec changelog)</t>
         </is>
       </c>
-      <c r="I55" s="2" t="inlineStr"/>
-      <c r="J55" s="2" t="inlineStr"/>
-    </row>
-    <row r="56">
-      <c r="A56" s="2" t="inlineStr">
+      <c r="I56" s="2" t="inlineStr"/>
+      <c r="J56" s="2" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
         <is>
           <t>All-white table with no alternating row shading, and the toolbar controls run in the specified left-to-right order</t>
         </is>
       </c>
-      <c r="B56" s="2" t="inlineStr">
+      <c r="B57" s="2" t="inlineStr">
         <is>
           <t>TU — Visual &amp; Accessibility</t>
         </is>
       </c>
-      <c r="C56" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D56" s="2" t="inlineStr">
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E56" s="2" t="inlineStr">
+      <c r="E57" s="2" t="inlineStr">
         <is>
           <t>1. You are on the Technician Utilization report with rows loaded, in light mode.</t>
         </is>
       </c>
-      <c r="F56" s="2" t="inlineStr">
+      <c r="F57" s="2" t="inlineStr">
         <is>
           <t>1. Look at the column headers and the data rows' backgrounds.
 2. Read the toolbar controls left to right.
 3. Look for the expand/collapse-all control's position.</t>
         </is>
       </c>
-      <c r="G56" s="2" t="inlineStr">
+      <c r="G57" s="2" t="inlineStr">
         <is>
           <t>1. The report uses an all-white table: white column headers and white data cells, with NO alternating row shading.
 2. The toolbar controls run, left to right: the three-dot download menu, the technician filter, the date-range picker, and the location filter (rightmost).
 3. The expand/collapse-all control is NOT a toolbar control - it lives in the table header (Technician column, per S4-R4).</t>
         </is>
       </c>
-      <c r="H56" s="2" t="inlineStr">
+      <c r="H57" s="2" t="inlineStr">
         <is>
           <t>specs/technician-utilization.md S8-R1; S8-R2; S8-R3</t>
         </is>
       </c>
-      <c r="I56" s="2" t="inlineStr"/>
-      <c r="J56" s="2" t="inlineStr"/>
-    </row>
-    <row r="57">
-      <c r="A57" s="2" t="inlineStr">
+      <c r="I57" s="2" t="inlineStr"/>
+      <c r="J57" s="2" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
         <is>
           <t>Dark mode keeps every report element legible, with the info icon at 3:1 contrast and the link affordance intact in both modes</t>
         </is>
       </c>
-      <c r="B57" s="2" t="inlineStr">
+      <c r="B58" s="2" t="inlineStr">
         <is>
           <t>TU — Visual &amp; Accessibility</t>
         </is>
       </c>
-      <c r="C57" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D57" s="2" t="inlineStr">
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="E57" s="2" t="inlineStr">
+      <c r="E58" s="2" t="inlineStr">
         <is>
           <t>1. You are on the Technician Utilization report with rows loaded, including a "—" Est. Lost Labor cell.
 2. Dark mode is available in the application.</t>
         </is>
       </c>
-      <c r="F57" s="2" t="inlineStr">
+      <c r="F58" s="2" t="inlineStr">
         <is>
           <t>1. Switch the application to dark mode.
 2. Check each element: page background, toolbar, cells, the Total Hours link, the information icon, the sort indicator, and a "—" glyph.
@@ -3177,96 +3227,96 @@
 4. Check the Total Hours link's underline/affordance and focus indicator in both modes.</t>
         </is>
       </c>
-      <c r="G57" s="2" t="inlineStr">
+      <c r="G58" s="2" t="inlineStr">
         <is>
           <t>1. The report supports dark mode: page background, toolbar, cells, the Total Hours link, the information icon, the sort indicator, and the "—" glyph all use dark-mode-legible colors meeting contrast.
 2. The information icon meets at least a 3:1 contrast ratio against its background in BOTH light and dark mode.
 3. The Total Hours link's non-color affordance and focus indicator apply in both modes.</t>
         </is>
       </c>
-      <c r="H57" s="2" t="inlineStr">
+      <c r="H58" s="2" t="inlineStr">
         <is>
           <t>specs/technician-utilization.md S8-R9; S8-R13; S8-R14</t>
         </is>
       </c>
-      <c r="I57" s="2" t="inlineStr"/>
-      <c r="J57" s="2" t="inlineStr"/>
-    </row>
-    <row r="58">
-      <c r="A58" s="2" t="inlineStr">
+      <c r="I58" s="2" t="inlineStr"/>
+      <c r="J58" s="2" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
         <is>
           <t>The per-day breakdown is fetched from the backend on demand when a row is expanded, not shipped with the initial payload</t>
         </is>
       </c>
-      <c r="B58" s="2" t="inlineStr">
+      <c r="B59" s="2" t="inlineStr">
         <is>
           <t>TU — API</t>
         </is>
       </c>
-      <c r="C58" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D58" s="2" t="inlineStr">
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E58" s="2" t="inlineStr">
+      <c r="E59" s="2" t="inlineStr">
         <is>
           <t>1. You are on the Technician Utilization report with rows loaded and browser devtools (network tab) open.</t>
         </is>
       </c>
-      <c r="F58" s="2" t="inlineStr">
+      <c r="F59" s="2" t="inlineStr">
         <is>
           <t>1. Load the report and inspect the initial data response for per-day content.
 2. Expand a technician row and watch the network traffic.
 3. Collapse and re-expand after a data reload.</t>
         </is>
       </c>
-      <c r="G58" s="2" t="inlineStr">
+      <c r="G59" s="2" t="inlineStr">
         <is>
           <t>1. The initial report payload does NOT ship the day rows.
 2. Expanding a technician row issues an on-demand backend request that returns that technician's per-day breakdown.
 3. Because expansion state resets (all collapsed) on any data reload, nothing is lost by the lazy loading - re-expanding fetches fresh day data.</t>
         </is>
       </c>
-      <c r="H58" s="2" t="inlineStr">
+      <c r="H59" s="2" t="inlineStr">
         <is>
           <t>specs/technician-utilization.md S4-R2; S4-R5</t>
         </is>
       </c>
-      <c r="I58" s="2" t="inlineStr"/>
-      <c r="J58" s="2" t="inlineStr"/>
-    </row>
-    <row r="59">
-      <c r="A59" s="2" t="inlineStr">
+      <c r="I59" s="2" t="inlineStr"/>
+      <c r="J59" s="2" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
         <is>
           <t>Date-range and location changes trigger a fresh server load, while the technician filter and column sorting stay on-screen only</t>
         </is>
       </c>
-      <c r="B59" s="2" t="inlineStr">
+      <c r="B60" s="2" t="inlineStr">
         <is>
           <t>TU — API</t>
         </is>
       </c>
-      <c r="C59" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D59" s="2" t="inlineStr">
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E59" s="2" t="inlineStr">
+      <c r="E60" s="2" t="inlineStr">
         <is>
           <t>1. You are on the Technician Utilization report with rows loaded and browser devtools (network tab) open.</t>
         </is>
       </c>
-      <c r="F59" s="2" t="inlineStr">
+      <c r="F60" s="2" t="inlineStr">
         <is>
           <t>1. Change the date range and watch the network traffic.
 2. Change the location selection and watch the traffic.
@@ -3274,7 +3324,7 @@
 4. Click several column headers to sort and watch the traffic.</t>
         </is>
       </c>
-      <c r="G59" s="2" t="inlineStr">
+      <c r="G60" s="2" t="inlineStr">
         <is>
           <t>1. A date-range change triggers a fresh server load of the rows.
 2. A location change triggers a fresh server load scoped to the selected set.
@@ -3282,13 +3332,13 @@
 4. Column sorting causes NO server request - it is applied on screen to the loaded rows.</t>
         </is>
       </c>
-      <c r="H59" s="2" t="inlineStr">
+      <c r="H60" s="2" t="inlineStr">
         <is>
           <t>specs/technician-utilization.md S1-R5; S9-R3; S5 context note; S2-R13; §3</t>
         </is>
       </c>
-      <c r="I59" s="2" t="inlineStr"/>
-      <c r="J59" s="2" t="inlineStr"/>
+      <c r="I60" s="2" t="inlineStr"/>
+      <c r="J60" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/testrail-import/Report-Suite_Technician-Utilization-Report_testrail-import.xlsx
+++ b/testrail-import/Report-Suite_Technician-Utilization-Report_testrail-import.xlsx
@@ -525,12 +525,12 @@
         <is>
           <t>1. The report is listed under the Performance group, labeled "Technician Utilization".
 2. Clicking it opens the report.
-3. The entry sits BELOW the previously existing report links (toward the bottom) — the new reports are added without moving or disturbing the existing entries.</t>
+3. The entry sits BELOW the pre-existing report links — Sales, Technician Efficiency, Advisor Analysis, Shop Efficiency — the new reports are added below those items without moving or disturbing them.</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>SV-8648 (specs/technician-utilization.md S1-R1 — nav placement tightened per kickoff video P3 05:11-05:19 [below existing items, additive not interruptive], user ruling 2026-07-28: video overrides spec (video newer, last-update-wins))</t>
+          <t>SV-8648 (specs/technician-utilization.md S1-R1 — below the named anchor items [Sales, Technician Efficiency, Advisor Analysis, Shop Efficiency] per the PRD companion video 2026-07-30 01:18-02:05, refining kickoff video P3; video authoritative, newest-wins)</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr"/>

--- a/testrail-import/Report-Suite_Technician-Utilization-Report_testrail-import.xlsx
+++ b/testrail-import/Report-Suite_Technician-Utilization-Report_testrail-import.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J60"/>
+  <dimension ref="A1:J61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
@@ -1070,7 +1070,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>Est. Lost Labor is pinned far right and bold, and only its header carries the info icon with the exact tooltip text</t>
+          <t>Est. Lost Labor, when shown, is pinned right and bold with the info icon</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
@@ -1090,26 +1090,29 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1. You are on the Technician Utilization report with rows loaded.</t>
+          <t>1. You are on the Technician Utilization report with rows loaded.
+2. Est. Lost Labor is turned ON in the Column Selection control (it is on by default).</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
           <t>1. Look at the position and weight of the Est. Lost Labor column (header and cells).
 2. Hover the information icon on the Est. Lost Labor header and read the text; also reach it by keyboard focus and by tap on a touch device.
-3. Check every other column header for an information icon.</t>
+3. Check every other column header for an information icon.
+4. Turn Est. Lost Labor off in the Column Selection control and look at the table again.</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>1. The Est. Lost Labor column is pinned to the far right; its cells are bold and its header is bold, matching.
-2. The information icon shows exactly: "Internal hours valued at each location's default labor rate" - on hover, on keyboard focus, and on tap; it is dismissible.
-3. NO column header other than Est. Lost Labor shows the information icon.</t>
+          <t>1. While Est. Lost Labor is shown, the column is pinned to the far right; its cells are bold and its header is bold, matching.
+2. The information icon shows exactly: "Internal hours valued at each location's default labor rate" — on hover, on keyboard focus, and on tap; it is dismissible.
+3. NO column header other than Est. Lost Labor shows the information icon.
+4. Est. Lost Labor can be turned OFF in the Column Selection control; when it is off the column, its bold styling and its information icon are all absent, and the report still works normally.</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>specs/technician-utilization.md S2-R10; S2-R11; S8-R4; S8-R6; S8-R7; S8-N1</t>
+          <t>SV-8652 (TU spec v5 2026-07-29 S2-R10; S2-R11; S8-R4; S8-R6; S8-R7; S8-N1 — each re-worded "When shown" now that Est. Lost Labor is a hideable column, new Story 10 S10-R3)</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr"/>
@@ -2424,7 +2427,7 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>The three-dot menu sits leftmost in the toolbar's action cluster and holds the three verbatim download options</t>
+          <t>Three-dot menu is leftmost, then Column Selection; three download options</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
@@ -2455,14 +2458,14 @@
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>1. The three-dot download menu sits LEFTMOST in the toolbar's action cluster.
+          <t>1. The three-dot download menu sits LEFTMOST in the toolbar's action cluster, with the Column Selection control immediately after it.
 2. The menu holds: "Download Summary (PDF)", "Download Expanded View (PDF)", and "Download (CSV)".
 3. The labels match exactly - only the expanded option carries the word "View" (the shipped strings, documented as-is).</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>specs/technician-utilization.md S7-R1; S7-R2; S7-R3; S7-R4; S8-R2; S7-R12 note</t>
+          <t>SV-8654 (TU spec v5 2026-07-29 S7-R1; S7-R2; S7-R3; S7-R4; S8-R2 — S8-R2 now adds "followed by the Column Selection control")</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr"/>
@@ -2594,7 +2597,8 @@
           <t>1. Deselect one technician, select a specific location set, and set a distinctive date range.
 2. Download the Summary PDF, the Expanded PDF, and the CSV.
 3. Check each file's technicians, the data scope, and the covered range.
-4. Re-select all technicians and download once more.</t>
+4. Re-select all technicians and download once more.
+5. Hide one column in the Column Selection control, download again and compare the file's columns.</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
@@ -2602,12 +2606,13 @@
           <t>1. Every download includes ONLY the technicians currently selected in the technician filter - the deselected technician is absent from all three files.
 2. Every download covers the location(s) currently selected in the location filter and the date range currently active on the report.
 3. With every technician selected, the download covers all technicians for the range at the selected location(s).
-4. Every download (each PDF and the CSV) carries a "Locations:" line naming the location(s) the report was scoped to (exact position in the file is confirmed in the build).</t>
+4. Every download (each PDF and the CSV) carries a "Locations:" line naming the location(s) the report was scoped to (exact position in the file is confirmed in the build).
+5. Every download also mirrors the columns currently shown on screen — a column hidden in the Column Selection control is absent from the files, and a re-shown column comes back.</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>SV-8654 (specs/technician-utilization.md S7-R8; S7-R9; S7-E1; S9-R8 + Locations: line in every CSV/PDF export per Chris Ward group message 2026-07-29 (chris-update-2026-07-29/chris-message-2026-07-29.md; NEWEST source, last-update-wins))</t>
+          <t>SV-8654 (TU spec v5 2026-07-29 S7-R8; S7-R9; S7-R10; S7-E1; S9-R8 — S7-R10 now says the downloads include the columns currently shown, mirroring the column selector)</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr"/>
@@ -2664,7 +2669,7 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>The shop logo shows at the top of both PDF views when set, no logo shows when unset, and the CSV never includes it</t>
+          <t>PDF logo: the uploaded logo, else the bundled ShopView logo; CSV never</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
@@ -2696,14 +2701,14 @@
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>1. With a logo set, BOTH PDF views show that logo at the top of the report.
+          <t>1. With an uploaded logo, BOTH PDF views show that logo at the top of the report.
 2. The CSV never includes the logo.
-3. With no logo set, the PDF views show no logo (no placeholder, no error).</t>
+3. With NO uploaded logo, the PDF views show the bundled ShopView logo instead — not a blank space and not an error.</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>specs/technician-utilization.md S7-R11; S7-N2; S7-N3</t>
+          <t>SV-8654 (TU spec v5 2026-07-29 S7-R11; S7-N2; S7-N3 — logo now resolved by the shared resolver: the organization's uploaded logo, else the bundled ShopView default)</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr"/>
@@ -3090,7 +3095,7 @@
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>SV-8656 (specs/technician-utilization.md S9-N1 — expectation FLIPPED by kickoff video P33 46:10-46:28, user ruling 2026-07-28: video overrides spec (video newer, last-update-wins))</t>
+          <t>SV-8656 (TU spec S9-N1 — RULED HIDDEN by Chris Ward answer 2026-07-31 Q1=A "classic spec drift"; the S9-N1 "still sees the filter" note is stale, spec edit pending)</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr"/>
@@ -3099,12 +3104,12 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>A column selector lets the user choose which columns show</t>
+          <t>The Location column shows only with more than one location; Summary row blank</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>TU — Visual &amp; Accessibility</t>
+          <t>TU — Location Filter</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
@@ -3114,31 +3119,43 @@
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>1. You are on the Technician Utilization report with rows loaded.</t>
+          <t>1. You are on the Technician Utilization report as a user with access to two or more locations.
+2. One technician clocked time at a single location in the range and another clocked time at two different locations.
+3. One of those days has hours at two locations (for the per-day check).</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>1. Find the column selector control in the toolbar (on the other reports it is a separate button next to the download menu).
-2. Open it and read the list of column toggles.
-3. Turn one column off, then back on, watching the table.</t>
+          <t>1. Select two or more locations and read the column headers from the left.
+2. Read the Location cell on the single-location technician's row.
+3. Read the Location cell on the technician whose hours span two locations.
+4. Expand that technician and read the Location cell on a single-location day and on the mixed day.
+5. Read the Location cell on the Summary row at the bottom.
+6. Open the Column Selection control and look for Location in the list.
+7. Narrow to a single location and read the headers again.
+8. Change the selection between one location, several, and "All Locations", watching the filter control's width.</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>1. The report has a column selector control, styled and placed like the other reports in the suite (this control was just added - the exact placement, tooltip, and list of toggleable columns are confirmed from the updated spec and the build).
-2. Turning a toggle off hides that column (header and cells); turning it back on restores the column to its usual place in the order.
-3. The change applies immediately with no reload - that is the suite convention on the other reports; confirm it holds here.</t>
+          <t>1. With more than one location in scope a Location column is shown as the LEFTMOST column, before Technician.
+2. A technician whose hours were all clocked at one location shows that location's name.
+3. A technician whose hours span more than one selected location shows "Multiple".
+4. An expanded day row shows the exact location when that day's hours were all at one location, and "Multiple" when the day spans more than one.
+5. The Summary row leaves the Location cell blank.
+6. Location is never listed in the Column Selection control — it follows the location scope on its own.
+7. With a single location in scope the Location column is hidden.
+8. The Location filter control keeps the same width whichever label it shows — one location, several, or "All locations" — so the toolbar does not shift as you change the selection.</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>SV-8655 (specs/technician-utilization.md Story 8 Visual Conformance and Accessibility - column selector ADDED per Chris Ward group message 2026-07-29 (chris-update-2026-07-29/chris-message-2026-07-29.md; NEWEST source, last-update-wins) ['Column selector added for visual/natural conformance']; no spec anchor yet - confirm from the updated spec changelog)</t>
+          <t>SV-8656 (TU spec v5 2026-07-29 S9-R9; S9-R10; S8-R15; S10-R4 — per-row Location column, leftmost before Technician, "Multiple" on a spanning row, Summary row blank, never in the selector)</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr"/>
@@ -3147,7 +3164,7 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>All-white table with no alternating row shading, and the toolbar controls run in the specified left-to-right order</t>
+          <t>Column Selection: Technician always on, the other five toggleable, remembered</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
@@ -3167,59 +3184,115 @@
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
+          <t>1. You are on the Technician Utilization report with rows loaded.
+2. This browser has never saved settings for this report (fresh visit), so every column is at its default.</t>
+        </is>
+      </c>
+      <c r="F57" s="2" t="inlineStr">
+        <is>
+          <t>1. Find the column-selection button in the toolbar and hover it to read its tooltip.
+2. Note its position relative to the three-dot download menu.
+3. Open it and read every toggle in the list, and which ones are on.
+4. Turn Est. Lost Labor off, then turn Internal Hours off, watching the table each time.
+5. Turn both back on and check where each column lands.
+6. Reload the page, then close the browser, reopen it and return to the report.</t>
+        </is>
+      </c>
+      <c r="G57" s="2" t="inlineStr">
+        <is>
+          <t>1. The control is an icon button whose tooltip reads "Column Selection", sitting immediately after the three-dot download menu in the toolbar.
+2. The list offers five toggles — Total Hours, WO Hours, Internal Hours, Utilization % and Est. Lost Labor — and all five are on by default.
+3. Technician is always shown and cannot be turned off (it is not offered as a toggle).
+4. The Location column is never listed here — it appears on its own whenever more than one location is in scope.
+5. Turning a toggle off hides that column (header and cells) immediately, with no reload; turning it back on returns it to its usual place in the fixed left-to-right order — the remaining columns never reorder.
+6. Est. Lost Labor can now be hidden like any other column (it used to be always on).
+7. Your column choice is remembered in this browser and is still applied when you come back.</t>
+        </is>
+      </c>
+      <c r="H57" s="2" t="inlineStr">
+        <is>
+          <t>SV-8655 (TU spec v5 2026-07-29 NEW Story 10 S10-R1; S10-R2; S10-R3; S10-R4; S10-R5; S10-R6 — column selector RATIFIED, replacing the placeholder written from the 2026-07-29 group message)</t>
+        </is>
+      </c>
+      <c r="I57" s="2" t="inlineStr"/>
+      <c r="J57" s="2" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>All-white table with no row shading; toolbar controls in the fixed order</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>TU — Visual &amp; Accessibility</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
           <t>1. You are on the Technician Utilization report with rows loaded, in light mode.</t>
         </is>
       </c>
-      <c r="F57" s="2" t="inlineStr">
+      <c r="F58" s="2" t="inlineStr">
         <is>
           <t>1. Look at the column headers and the data rows' backgrounds.
 2. Read the toolbar controls left to right.
 3. Look for the expand/collapse-all control's position.</t>
         </is>
       </c>
-      <c r="G57" s="2" t="inlineStr">
+      <c r="G58" s="2" t="inlineStr">
         <is>
           <t>1. The report uses an all-white table: white column headers and white data cells, with NO alternating row shading.
-2. The toolbar controls run, left to right: the three-dot download menu, the technician filter, the date-range picker, and the location filter (rightmost).
-3. The expand/collapse-all control is NOT a toolbar control - it lives in the table header (Technician column, per S4-R4).</t>
-        </is>
-      </c>
-      <c r="H57" s="2" t="inlineStr">
-        <is>
-          <t>specs/technician-utilization.md S8-R1; S8-R2; S8-R3</t>
-        </is>
-      </c>
-      <c r="I57" s="2" t="inlineStr"/>
-      <c r="J57" s="2" t="inlineStr"/>
-    </row>
-    <row r="58">
-      <c r="A58" s="2" t="inlineStr">
+2. The toolbar controls run, left to right: the three-dot download menu, the Column Selection control, the date-range picker, the technician filter, and the Location filter (rightmost).
+3. The expand/collapse-all control is NOT a toolbar control - it lives in the table header (in the Technician column).</t>
+        </is>
+      </c>
+      <c r="H58" s="2" t="inlineStr">
+        <is>
+          <t>SV-8655 (TU spec v5 2026-07-29 S8-R1; S8-R2; S8-R3 — toolbar order rewritten: Column Selection inserted after the three-dot menu, and the date-range picker now precedes the technician filter)</t>
+        </is>
+      </c>
+      <c r="I58" s="2" t="inlineStr"/>
+      <c r="J58" s="2" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
         <is>
           <t>Dark mode keeps every report element legible, with the info icon at 3:1 contrast and the link affordance intact in both modes</t>
         </is>
       </c>
-      <c r="B58" s="2" t="inlineStr">
+      <c r="B59" s="2" t="inlineStr">
         <is>
           <t>TU — Visual &amp; Accessibility</t>
         </is>
       </c>
-      <c r="C58" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D58" s="2" t="inlineStr">
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="E58" s="2" t="inlineStr">
+      <c r="E59" s="2" t="inlineStr">
         <is>
           <t>1. You are on the Technician Utilization report with rows loaded, including a "—" Est. Lost Labor cell.
 2. Dark mode is available in the application.</t>
         </is>
       </c>
-      <c r="F58" s="2" t="inlineStr">
+      <c r="F59" s="2" t="inlineStr">
         <is>
           <t>1. Switch the application to dark mode.
 2. Check each element: page background, toolbar, cells, the Total Hours link, the information icon, the sort indicator, and a "—" glyph.
@@ -3227,96 +3300,96 @@
 4. Check the Total Hours link's underline/affordance and focus indicator in both modes.</t>
         </is>
       </c>
-      <c r="G58" s="2" t="inlineStr">
+      <c r="G59" s="2" t="inlineStr">
         <is>
           <t>1. The report supports dark mode: page background, toolbar, cells, the Total Hours link, the information icon, the sort indicator, and the "—" glyph all use dark-mode-legible colors meeting contrast.
 2. The information icon meets at least a 3:1 contrast ratio against its background in BOTH light and dark mode.
 3. The Total Hours link's non-color affordance and focus indicator apply in both modes.</t>
         </is>
       </c>
-      <c r="H58" s="2" t="inlineStr">
+      <c r="H59" s="2" t="inlineStr">
         <is>
           <t>specs/technician-utilization.md S8-R9; S8-R13; S8-R14</t>
         </is>
       </c>
-      <c r="I58" s="2" t="inlineStr"/>
-      <c r="J58" s="2" t="inlineStr"/>
-    </row>
-    <row r="59">
-      <c r="A59" s="2" t="inlineStr">
+      <c r="I59" s="2" t="inlineStr"/>
+      <c r="J59" s="2" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
         <is>
           <t>The per-day breakdown is fetched from the backend on demand when a row is expanded, not shipped with the initial payload</t>
         </is>
       </c>
-      <c r="B59" s="2" t="inlineStr">
+      <c r="B60" s="2" t="inlineStr">
         <is>
           <t>TU — API</t>
         </is>
       </c>
-      <c r="C59" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D59" s="2" t="inlineStr">
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E59" s="2" t="inlineStr">
+      <c r="E60" s="2" t="inlineStr">
         <is>
           <t>1. You are on the Technician Utilization report with rows loaded and browser devtools (network tab) open.</t>
         </is>
       </c>
-      <c r="F59" s="2" t="inlineStr">
+      <c r="F60" s="2" t="inlineStr">
         <is>
           <t>1. Load the report and inspect the initial data response for per-day content.
 2. Expand a technician row and watch the network traffic.
 3. Collapse and re-expand after a data reload.</t>
         </is>
       </c>
-      <c r="G59" s="2" t="inlineStr">
+      <c r="G60" s="2" t="inlineStr">
         <is>
           <t>1. The initial report payload does NOT ship the day rows.
 2. Expanding a technician row issues an on-demand backend request that returns that technician's per-day breakdown.
 3. Because expansion state resets (all collapsed) on any data reload, nothing is lost by the lazy loading - re-expanding fetches fresh day data.</t>
         </is>
       </c>
-      <c r="H59" s="2" t="inlineStr">
+      <c r="H60" s="2" t="inlineStr">
         <is>
           <t>specs/technician-utilization.md S4-R2; S4-R5</t>
         </is>
       </c>
-      <c r="I59" s="2" t="inlineStr"/>
-      <c r="J59" s="2" t="inlineStr"/>
-    </row>
-    <row r="60">
-      <c r="A60" s="2" t="inlineStr">
+      <c r="I60" s="2" t="inlineStr"/>
+      <c r="J60" s="2" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
         <is>
           <t>Date-range and location changes trigger a fresh server load, while the technician filter and column sorting stay on-screen only</t>
         </is>
       </c>
-      <c r="B60" s="2" t="inlineStr">
+      <c r="B61" s="2" t="inlineStr">
         <is>
           <t>TU — API</t>
         </is>
       </c>
-      <c r="C60" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D60" s="2" t="inlineStr">
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E60" s="2" t="inlineStr">
+      <c r="E61" s="2" t="inlineStr">
         <is>
           <t>1. You are on the Technician Utilization report with rows loaded and browser devtools (network tab) open.</t>
         </is>
       </c>
-      <c r="F60" s="2" t="inlineStr">
+      <c r="F61" s="2" t="inlineStr">
         <is>
           <t>1. Change the date range and watch the network traffic.
 2. Change the location selection and watch the traffic.
@@ -3324,7 +3397,7 @@
 4. Click several column headers to sort and watch the traffic.</t>
         </is>
       </c>
-      <c r="G60" s="2" t="inlineStr">
+      <c r="G61" s="2" t="inlineStr">
         <is>
           <t>1. A date-range change triggers a fresh server load of the rows.
 2. A location change triggers a fresh server load scoped to the selected set.
@@ -3332,13 +3405,13 @@
 4. Column sorting causes NO server request - it is applied on screen to the loaded rows.</t>
         </is>
       </c>
-      <c r="H60" s="2" t="inlineStr">
+      <c r="H61" s="2" t="inlineStr">
         <is>
           <t>specs/technician-utilization.md S1-R5; S9-R3; S5 context note; S2-R13; §3</t>
         </is>
       </c>
-      <c r="I60" s="2" t="inlineStr"/>
-      <c r="J60" s="2" t="inlineStr"/>
+      <c r="I61" s="2" t="inlineStr"/>
+      <c r="J61" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/testrail-import/Report-Suite_Technician-Utilization-Report_testrail-import.xlsx
+++ b/testrail-import/Report-Suite_Technician-Utilization-Report_testrail-import.xlsx
@@ -530,7 +530,7 @@
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>SV-8648 (specs/technician-utilization.md S1-R1 — below the named anchor items [Sales, Technician Efficiency, Advisor Analysis, Shop Efficiency] per the PRD companion video 2026-07-30 01:18-02:05, refining kickoff video P3; video authoritative, newest-wins)</t>
+          <t>SV-8648 (TU spec S1-R1 — below the named anchor items [Sales; Technician Efficiency; Advisor Analysis; Shop Efficiency] per PRD video 2026-07-30 01:18-02:05; refines video P3 [newest-wins])</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr"/>
@@ -539,7 +539,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>The report shows one row for each technician who clocked time in the range at the selected locations</t>
+          <t>One row per technician who clocked time in the range at those locations</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
@@ -577,7 +577,7 @@
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>specs/technician-utilization.md S1-R2</t>
+          <t>SV-8648 (specs/technician-utilization.md S1-R2)</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr"/>
@@ -624,7 +624,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>specs/technician-utilization.md S1-R3; S9-R2</t>
+          <t>SV-8648 (specs/technician-utilization.md S1-R3; S9-R2)</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr"/>
@@ -633,7 +633,7 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>Changing the date range reloads the rows, and a Custom range is capped at 366 days</t>
+          <t>Changing the date range reloads the rows; a Custom range is capped at 366 days</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
@@ -672,7 +672,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>specs/technician-utilization.md S1-R4; S1-R5</t>
+          <t>SV-8648 (specs/technician-utilization.md S1-R4; S1-R5)</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr"/>
@@ -681,7 +681,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>The standard loading indicator shows on load and reload, rows swap only when data returns, and the toolbar stays interactive</t>
+          <t>The loading indicator shows on load and reload; rows swap only on data</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
@@ -720,7 +720,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>specs/technician-utilization.md S1-R10</t>
+          <t>SV-8648 (specs/technician-utilization.md S1-R10)</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr"/>
@@ -729,7 +729,7 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>All clock records are day-grouped and windowed in one report-level time zone, with partial and cross-midnight records split correctly</t>
+          <t>All clock records are day-grouped and windowed in one report-level time zone</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
@@ -771,7 +771,7 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>specs/technician-utilization.md S1-R7; S1 context notes</t>
+          <t>SV-8648 (specs/technician-utilization.md S1-R7; S1 context notes)</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr"/>
@@ -780,7 +780,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>A user without the timesheet-reports permission does not see the report in the navigation</t>
+          <t>Without the timesheet-reports permission Technician Utilization is hidden</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
@@ -816,7 +816,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>specs/technician-utilization.md S1-N1</t>
+          <t>SV-8648 (specs/technician-utilization.md S1-N1)</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr"/>
@@ -865,7 +865,7 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>specs/technician-utilization.md S1-N2; S9-N2; S5-N1; S3-N1; §7</t>
+          <t>SV-8648 (specs/technician-utilization.md S1-N2; S9-N2; S5-N1; S3-N1; §7)</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr"/>
@@ -917,7 +917,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>specs/technician-utilization.md S2-R1; S2-R2; S2-R3; S2-R4; S2-R5; §3</t>
+          <t>SV-8649 (specs/technician-utilization.md S2-R1; S2-R2; S2-R3; S2-R4; S2-R5; §3)</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr"/>
@@ -926,7 +926,7 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>Utilization % is WO hours over total hours computed from unrounded values, shown to one decimal with round-half-up</t>
+          <t>Utilization % is WO hours over total hours from unrounded values</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
@@ -963,7 +963,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>specs/technician-utilization.md S2-R6; S2-R7; §3</t>
+          <t>SV-8649 (specs/technician-utilization.md S2-R6; S2-R7; §3)</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr"/>
@@ -972,7 +972,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>A technician with only internal hours shows 0.0% utilization, and utilization never exceeds 100%</t>
+          <t>A technician with only internal hours shows 0.0% utilization</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>specs/technician-utilization.md S2-E1; S2-R7; S2 context note</t>
+          <t>SV-8649 (specs/technician-utilization.md S2-E1; S2-R7; S2 context note)</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr"/>
@@ -1020,7 +1020,7 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>Est. Lost Labor values internal hours at each location's default labor rate, summed at full precision and rounded once</t>
+          <t>Est. Lost Labor values internal hours at each location's default rate</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
@@ -1061,7 +1061,7 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>specs/technician-utilization.md S2-R8; S2-R9; §3</t>
+          <t>SV-8649 (specs/technician-utilization.md S2-R8; S2-R9; §3)</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr"/>
@@ -1112,7 +1112,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>SV-8652 (TU spec v5 2026-07-29 S2-R10; S2-R11; S8-R4; S8-R6; S8-R7; S8-N1 — each re-worded "When shown" now that Est. Lost Labor is a hideable column, new Story 10 S10-R3)</t>
+          <t>SV-8649 (TU spec v5 2026-07-29 S2-R10; S2-R11; S8-R4; S8-R6; S8-R7; S8-N1 — each re-worded "When shown" now that Est. Lost Labor is a hideable column; new Story 10 S10-R3)</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr"/>
@@ -1160,7 +1160,7 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>specs/technician-utilization.md S2-E2; §5 Assumptions; S2 context note</t>
+          <t>SV-8649 (specs/technician-utilization.md S2-E2; §5 Assumptions; S2 context note)</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr"/>
@@ -1169,7 +1169,7 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>Internal hours with no default labor rate at any contributing location show an em-dash with the correct assistive-technology label</t>
+          <t>Internal hours with no default labor rate anywhere show an em-dash</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
@@ -1207,7 +1207,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>specs/technician-utilization.md S2-E3; S8-R11; S2-R4</t>
+          <t>SV-8649 (specs/technician-utilization.md S2-E3; S8-R11; S2-R4)</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr"/>
@@ -1216,7 +1216,7 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>Internal hours split across rated and unrated locations show a partial dollar value with no indicator - expected, not a defect</t>
+          <t>Internal hours split across rated and unrated locations show a part value</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
@@ -1255,7 +1255,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>specs/technician-utilization.md S2-E4</t>
+          <t>SV-8649 (specs/technician-utilization.md S2-E4)</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr"/>
@@ -1264,7 +1264,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>On load the rows are sorted by Technician A to Z with the ascending indicator and correct aria-sort exposure</t>
+          <t>On load rows sort by Technician A to Z with the ascending indicator</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
@@ -1303,7 +1303,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>specs/technician-utilization.md S2-R12; S8-R8; S8-R10</t>
+          <t>SV-8649 (specs/technician-utilization.md S2-R12; S8-R8; S8-R10)</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr"/>
@@ -1312,7 +1312,7 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>All six columns sort on screen: ascending first, toggling with no third state, and Technician's first click goes descending</t>
+          <t>All six columns sort on screen: ascending first, toggling with no third state</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
@@ -1355,7 +1355,7 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>specs/technician-utilization.md S2-R13; S2-R14</t>
+          <t>SV-8649 (specs/technician-utilization.md S2-R13; S2-R14)</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr"/>
@@ -1364,7 +1364,7 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>A data reload resets the sort to Technician A to Z, and sort is never persisted across visits</t>
+          <t>A data reload resets the sort to Technician A to Z</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
@@ -1402,7 +1402,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>specs/technician-utilization.md S2-R15; §3</t>
+          <t>SV-8649 (specs/technician-utilization.md S2-R15; §3)</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr"/>
@@ -1411,7 +1411,7 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>Sorting reorders only the technician rows - the Summary stays at the bottom and day rows stay under their technician in date order</t>
+          <t>Sorting reorders only the technician rows</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
@@ -1450,7 +1450,7 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>specs/technician-utilization.md S2-R16</t>
+          <t>SV-8649 (specs/technician-utilization.md S2-R16)</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr"/>
@@ -1459,7 +1459,7 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>Sorting by Est. Lost Labor keeps the em-dash rows at the bottom in both directions, while $0.00 sorts as zero</t>
+          <t>Sorting Est. Lost Labor keeps em-dash rows last both ways; $0.00 sorts as 0</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
@@ -1498,7 +1498,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>specs/technician-utilization.md S2-R17</t>
+          <t>SV-8649 (specs/technician-utilization.md S2-R17)</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr"/>
@@ -1507,7 +1507,7 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>A pinned Summary row labeled Summary sits at the bottom, stays visible on scroll, and uses the row formats with no prefix</t>
+          <t>A pinned Summary row labeled Summary sits at the bottom, stays visible on scroll</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
@@ -1547,7 +1547,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>specs/technician-utilization.md S3-R1; S3-R2; S3-R6; S3-R7; S8-R5</t>
+          <t>SV-8650 (specs/technician-utilization.md S3-R1; S3-R2; S3-R6; S3-R7; S8-R5)</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr"/>
@@ -1595,7 +1595,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>specs/technician-utilization.md S3-R3; §3 context note; S5-E1</t>
+          <t>SV-8650 (specs/technician-utilization.md S3-R3; §3 context note; S5-E1)</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr"/>
@@ -1604,7 +1604,7 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>Summary Utilization % is the weighted rate, not the average of the per-technician percentages</t>
+          <t>Summary Utilization % is the weighted rate; not an average of the rows</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
@@ -1642,7 +1642,7 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>specs/technician-utilization.md S3-R4</t>
+          <t>SV-8650 (specs/technician-utilization.md S3-R4)</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr"/>
@@ -1651,7 +1651,7 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>Summary Est. Lost Labor sums the rated contributions only, and shows an em-dash only when every visible technician is an em-dash</t>
+          <t>Summary Est. Lost Labor sums rated contributions; em-dash only if all are</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
@@ -1671,7 +1671,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1. Visible technicians include: one with a normal Est. Lost Labor, one showing "—" (no rate anywhere), and (if possible) one partially valued (S2-E4).</t>
+          <t>1. Visible technicians include: one with a normal Est. Lost Labor, one showing "—" (no rate anywhere), and (if possible) one partially valued.</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -1689,7 +1689,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>specs/technician-utilization.md S3-R5</t>
+          <t>SV-8650 (specs/technician-utilization.md S3-R5)</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr"/>
@@ -1746,7 +1746,7 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>Expanding shows one row per clocked day in date order, loaded on demand, with days pooled across selected locations</t>
+          <t>Expanding shows one row per clocked day in date order, loaded on demand</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
@@ -1788,7 +1788,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>specs/technician-utilization.md S4-R2; S4-N1; S9-R4</t>
+          <t>SV-8651 (specs/technician-utilization.md S4-R2; S4-N1; S9-R4)</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr"/>
@@ -1797,7 +1797,7 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>Day rows use the same columns and formats as technician rows, including a per-day per-location Est. Lost Labor</t>
+          <t>Day rows use the same columns and formats as the technician rows</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
@@ -1836,7 +1836,7 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>specs/technician-utilization.md S4-R3; S2-R8; §3</t>
+          <t>SV-8651 (specs/technician-utilization.md S4-R3; S2-R8; §3)</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr"/>
@@ -1845,7 +1845,7 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>A single control in the table header expands or collapses all technician rows with the correct accessible names</t>
+          <t>One control in the table header expands or collapses all technician rows</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>specs/technician-utilization.md S4-R4; S8-R12; S8-R3</t>
+          <t>SV-8651 (specs/technician-utilization.md S4-R4; S8-R12; S8-R3)</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr"/>
@@ -1895,7 +1895,7 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>Expansion state is view-only: it resets on any reload and fresh visit, and the technician filter does not disturb it</t>
+          <t>Expansion state is view-only: it resets on any reload and fresh visit</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
@@ -1934,7 +1934,7 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>specs/technician-utilization.md S4-R5</t>
+          <t>SV-8651 (specs/technician-utilization.md S4-R5)</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr"/>
@@ -1943,7 +1943,7 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>The Filter by Technician multi-select starts with every technician selected on a first visit</t>
+          <t>Filter by Technician starts with every technician selected on a first visit</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
@@ -1982,7 +1982,7 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>specs/technician-utilization.md S5-R1; S5-R2</t>
+          <t>SV-8652 (specs/technician-utilization.md S5-R1; S5-R2)</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr"/>
@@ -1991,7 +1991,7 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>Deselecting a technician hides the row and recalculates the Summary on screen without reloading; re-selecting restores it</t>
+          <t>Deselecting a technician hides the row and recalculates the Summary</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
@@ -2032,7 +2032,7 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>specs/technician-utilization.md S5-R3; S5-R4; S5-R5; §3; S5 context note</t>
+          <t>SV-8652 (specs/technician-utilization.md S5-R3; S5-R4; S5-R5; §3; S5 context note)</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr"/>
@@ -2041,7 +2041,7 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>Select all and Clear all controls work, and the deselected-set model keeps newly-appearing technicians selected</t>
+          <t>Select all and Clear all controls set every technician on or off</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
@@ -2082,7 +2082,7 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>specs/technician-utilization.md S5-R6; S5-R7; S5-R8; S5-R9</t>
+          <t>SV-8652 (specs/technician-utilization.md S5-R6; S5-R7; S5-R8; S5-R9)</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr"/>
@@ -2091,7 +2091,7 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>Previously deselected technicians stay deselected when the user returns to the report</t>
+          <t>Previously deselected technicians stay deselected on the next visit</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
@@ -2125,12 +2125,12 @@
         <is>
           <t>1. The two deselected technicians are STILL deselected on return - the deselected set is what persists (saved in this browser, not on the account).
 2. All other technicians - including any who appear for the first time - are selected.
-3. The saved date range and location selection are restored alongside (per S1-R8).</t>
+3. The saved date range and location selection are restored alongside.</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>specs/technician-utilization.md S5-R10; S1-R8; §3</t>
+          <t>SV-8652 (specs/technician-utilization.md S5-R10; S1-R8; §3)</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr"/>
@@ -2139,7 +2139,7 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>Total Hours is a real link with a non-color affordance and keyboard access, while the Summary's Total Hours is not a link</t>
+          <t>Total Hours is a real link with a non-color affordance and keyboard access</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
@@ -2178,7 +2178,7 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>specs/technician-utilization.md S6-R1; S6-N1; S8-R14</t>
+          <t>SV-8653 (specs/technician-utilization.md S6-R1; S6-N1; S8-R14)</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr"/>
@@ -2187,7 +2187,7 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>The Total Hours link opens Timesheet Activities in the same tab, pre-filtered to that technician and date range</t>
+          <t>The Total Hours link opens Timesheet Activities in the same tab</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
@@ -2226,7 +2226,7 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>specs/technician-utilization.md S6-R2; S6-R3; S6-R4</t>
+          <t>SV-8653 (specs/technician-utilization.md S6-R2; S6-R3; S6-R4)</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr"/>
@@ -2275,7 +2275,7 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>specs/technician-utilization.md S1-R9; §2; §5 Assumptions</t>
+          <t>SV-8648 (specs/technician-utilization.md S1-R9; §2; §5 Assumptions)</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr"/>
@@ -2284,7 +2284,7 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>Reconciliation exception (a): an open clock is snapshotted at each report's own load instant - a difference of the elapsed time is expected</t>
+          <t>Reconcile exception (a): an open clock is snapshotted at each load instant</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
@@ -2323,7 +2323,7 @@
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>specs/technician-utilization.md S1-R9(a); S1-E1</t>
+          <t>SV-8648 (specs/technician-utilization.md S1-R9(a); S1-E1)</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr"/>
@@ -2332,7 +2332,7 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>Reconciliation exception (b): the link passes no location, so with multiple locations selected the opened view shows only the active shop</t>
+          <t>Reconciliation exception (b): the link passes no location</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
@@ -2372,7 +2372,7 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>specs/technician-utilization.md S6-R6; S1-R9(b)</t>
+          <t>SV-8653 (specs/technician-utilization.md S6-R6; S1-R9(b))</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr"/>
@@ -2381,7 +2381,7 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>A day row's Total Hours links to Timesheet Activities for that technician on that single day</t>
+          <t>A day row's Total Hours links to that technician's single-day timesheet</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
@@ -2418,7 +2418,7 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>specs/technician-utilization.md S6-R5</t>
+          <t>SV-8653 (specs/technician-utilization.md S6-R5)</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr"/>
@@ -2474,7 +2474,7 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>The Summary PDF holds the technician rows plus the Summary, and the Expanded PDF adds every per-day breakdown</t>
+          <t>The Summary PDF holds the technician rows plus the Summary</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
@@ -2512,7 +2512,7 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>specs/technician-utilization.md S7-R5; S7-R6; S7-R12</t>
+          <t>SV-8654 (specs/technician-utilization.md S7-R5; S7-R6; S7-R12)</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr"/>
@@ -2521,7 +2521,7 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>The CSV is always summary-level, quotes comma-containing values, and downloads with the lower-case filename</t>
+          <t>The CSV is always summary-level, quotes comma-containing values</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
@@ -2560,7 +2560,7 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>specs/technician-utilization.md S7-R7; S7-R10; S7-R12</t>
+          <t>SV-8654 (specs/technician-utilization.md S7-R7; S7-R10; S7-R12)</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr"/>
@@ -2612,7 +2612,7 @@
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>SV-8654 (TU spec v5 2026-07-29 S7-R8; S7-R9; S7-R10; S7-E1; S9-R8 — S7-R10 now says the downloads include the columns currently shown, mirroring the column selector)</t>
+          <t>SV-8654 (TU spec v5 2026-07-29 S7-R8; S7-R9; S7-R10; S7-E1; S9-R8 — S7-R10 now says the downloads include the columns currently shown; mirroring the column selector)</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr"/>
@@ -2621,7 +2621,7 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>Downloads keep the on-screen column order and number formats but always order rows Technician A to Z, ignoring the on-screen sort</t>
+          <t>Downloads always order rows Technician A to Z; the on-screen sort is ignored</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
@@ -2660,7 +2660,7 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>specs/technician-utilization.md S7-R10; S7-R10a</t>
+          <t>SV-8654 (specs/technician-utilization.md S7-R10; S7-R10a)</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr"/>
@@ -2708,7 +2708,7 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>SV-8654 (TU spec v5 2026-07-29 S7-R11; S7-N2; S7-N3 — logo now resolved by the shared resolver: the organization's uploaded logo, else the bundled ShopView default)</t>
+          <t>SV-8654 (TU spec v5 2026-07-29 S7-R11; S7-N2; S7-N3 — logo now resolved by the shared resolver: the organization's uploaded logo; else the bundled ShopView default)</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr"/>
@@ -2717,7 +2717,7 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>Choosing a download with no technician selected is a silent no-op - no file and no message</t>
+          <t>Choosing a download with no technician selected is a silent no-op</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
@@ -2755,7 +2755,7 @@
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>specs/technician-utilization.md S7-N1; §7 context note</t>
+          <t>SV-8654 (specs/technician-utilization.md S7-N1; §7 context note)</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr"/>
@@ -2764,7 +2764,7 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>A starting download shows the Download started notification and a failed download shows Failed to download report</t>
+          <t>A starting download notifies; a failed one shows the failure message</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
@@ -2802,7 +2802,7 @@
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>specs/technician-utilization.md Story 7 Error Handling; §7</t>
+          <t>SV-8654 (specs/technician-utilization.md Story 7 Error Handling; §7)</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr"/>
@@ -2852,7 +2852,7 @@
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>SV-8654 (specs/technician-utilization.md Story 7 exports — spec silent on a cap; tech-plan-2026-07-29 A3/FR-F4: suite-wide 10,000-row export cap, locked by Chris 2026-07-21)</t>
+          <t>SV-8654 (specs/technician-utilization.md Story 7 exports — spec silent on a cap; tech-plan-2026-07-29 A3/FR-F4: suite-wide 10; 000-row export cap; locked by Chris 2026-07-21)</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr"/>
@@ -2903,7 +2903,7 @@
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>SV-8656 (specs/technician-utilization.md S9-R1 — per-row location identifier in All-Locations view ADDED per kickoff video P10 40:58-41:20, user ruling 2026-07-28: video overrides spec (video newer, last-update-wins))</t>
+          <t>SV-8656 (specs/technician-utilization.md S9-R1 — per-row location identifier in All-Locations view ADDED per kickoff video P10 40:58-41:20; user ruling 2026-07-28: video overrides spec (video newer; last-update-wins))</t>
         </is>
       </c>
       <c r="I51" s="2" t="inlineStr"/>
@@ -2955,7 +2955,7 @@
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>SV-8656 (specs/technician-utilization.md S9-R3; S9-R4; S9-R5 + on-screen location-scope indicator per Chris Ward group message 2026-07-29 (chris-update-2026-07-29/chris-message-2026-07-29.md; NEWEST source, last-update-wins))</t>
+          <t>SV-8656 (specs/technician-utilization.md S9-R3; S9-R4; S9-R5 + on-screen location-scope indicator per Chris Ward group message 2026-07-29 (chris-update-2026-07-29/chris-message-2026-07-29.md; NEWEST source; last-update-wins))</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr"/>
@@ -2964,7 +2964,7 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>The saved location selection restores defensively - inaccessible locations are dropped and an empty remainder falls back to the active location</t>
+          <t>The saved location selection restores defensively; bad ones are dropped</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
@@ -3002,7 +3002,7 @@
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>specs/technician-utilization.md S9-R6; S1-R8; S9-R2</t>
+          <t>SV-8656 (specs/technician-utilization.md S9-R6; S1-R8; S9-R2)</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr"/>
@@ -3011,7 +3011,7 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>Deselecting every location falls back to the active location instead of showing nothing</t>
+          <t>Deselecting every location falls back to the active location</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>specs/technician-utilization.md S9-R7</t>
+          <t>SV-8656 (specs/technician-utilization.md S9-R7)</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr"/>
@@ -3057,7 +3057,7 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>The Location filter is hidden for a user with access to only one location</t>
+          <t>Technician Utilization: Location filter hidden for a one-location user</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
@@ -3095,7 +3095,7 @@
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>SV-8656 (TU spec S9-N1 — RULED HIDDEN by Chris Ward answer 2026-07-31 Q1=A "classic spec drift"; the S9-N1 "still sees the filter" note is stale, spec edit pending)</t>
+          <t>SV-8656 (TU spec S9-N1 — RULED HIDDEN by Chris Ward answer 2026-07-31 Q1=A "classic spec drift"; the S9-N1 "still sees the filter" note is stale; spec edit pending)</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr"/>
@@ -3155,7 +3155,7 @@
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>SV-8656 (TU spec v5 2026-07-29 S9-R9; S9-R10; S8-R15; S10-R4 — per-row Location column, leftmost before Technician, "Multiple" on a spanning row, Summary row blank, never in the selector)</t>
+          <t>SV-8656 (TU spec v5 2026-07-29 S9-R9; S9-R10; S8-R15; S10-R4 — per-row Location column; leftmost before Technician; "Multiple" on a spanning row; Summary row blank; never in the selector)</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr"/>
@@ -3211,7 +3211,7 @@
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>SV-8655 (TU spec v5 2026-07-29 NEW Story 10 S10-R1; S10-R2; S10-R3; S10-R4; S10-R5; S10-R6 — column selector RATIFIED, replacing the placeholder written from the 2026-07-29 group message)</t>
+          <t>SV-8582 (TU spec v5 2026-07-29 Story 10 S10-R1; S10-R2; S10-R3; S10-R4; S10-R5; S10-R6 column selector — NO OWNING JIRA STORY: epic SV-8582 carries no TU Story-10 ticket and the spec's own Jira field reads TBD; epic key used and FLAGGED)</t>
         </is>
       </c>
       <c r="I57" s="2" t="inlineStr"/>
@@ -3259,7 +3259,7 @@
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>SV-8655 (TU spec v5 2026-07-29 S8-R1; S8-R2; S8-R3 — toolbar order rewritten: Column Selection inserted after the three-dot menu, and the date-range picker now precedes the technician filter)</t>
+          <t>SV-8655 (TU spec v5 2026-07-29 S8-R1; S8-R2; S8-R3 — toolbar order rewritten: Column Selection inserted after the three-dot menu; and the date-range picker now precedes the technician filter)</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr"/>
@@ -3268,7 +3268,7 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>Dark mode keeps every report element legible, with the info icon at 3:1 contrast and the link affordance intact in both modes</t>
+          <t>Dark mode keeps every report element legible</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
@@ -3309,7 +3309,7 @@
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t>specs/technician-utilization.md S8-R9; S8-R13; S8-R14</t>
+          <t>SV-8655 (specs/technician-utilization.md S8-R9; S8-R13; S8-R14)</t>
         </is>
       </c>
       <c r="I59" s="2" t="inlineStr"/>
@@ -3318,7 +3318,7 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>The per-day breakdown is fetched from the backend on demand when a row is expanded, not shipped with the initial payload</t>
+          <t>The per-day breakdown is fetched only when a technician row is expanded</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
@@ -3357,7 +3357,7 @@
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>specs/technician-utilization.md S4-R2; S4-R5</t>
+          <t>SV-8651 (specs/technician-utilization.md S4-R2; S4-R5)</t>
         </is>
       </c>
       <c r="I60" s="2" t="inlineStr"/>
@@ -3366,7 +3366,7 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>Date-range and location changes trigger a fresh server load, while the technician filter and column sorting stay on-screen only</t>
+          <t>Date-range and location changes trigger a fresh server load</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
@@ -3407,7 +3407,7 @@
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>specs/technician-utilization.md S1-R5; S9-R3; S5 context note; S2-R13; §3</t>
+          <t>SV-8648 (specs/technician-utilization.md S1-R5; S9-R3; S5 context note; S2-R13; §3)</t>
         </is>
       </c>
       <c r="I61" s="2" t="inlineStr"/>

--- a/testrail-import/Report-Suite_Technician-Utilization-Report_testrail-import.xlsx
+++ b/testrail-import/Report-Suite_Technician-Utilization-Report_testrail-import.xlsx
@@ -624,7 +624,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>SV-8648 (specs/technician-utilization.md S1-R3; S9-R2)</t>
+          <t>SV-8648 (TU spec v5 2026-07-29 S1-R3; S1-R6; S9-R2)</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr"/>
@@ -908,16 +908,17 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>1. The headers appear in exactly this order: Technician, Total Hours, WO Hours, Internal Hours, Utilization %, Est. Lost Labor.
+          <t>1. With a single location in scope the headers appear in exactly this order: Technician, Total Hours, WO Hours, Internal Hours, Utilization %, Est. Lost Labor.
 2. Total Hours = all time the technician was clocked in for the range.
 3. WO Hours = time clocked directly to work orders; Internal Hours = time clocked to internal, non-billable activities.
 4. Internal Hours includes ALL internal time - including hours at a location with no configured labor rate.
-5. Hours show two decimal places with NO thousands separator (e.g. "107.70"), rounded from the unrounded hours using round-half-up (a tie rounds away from zero - 0.005 → 0.01).</t>
+5. Hours show two decimal places with NO thousands separator (e.g. "107.70"), rounded from the unrounded hours using round-half-up (a tie rounds away from zero - 0.005 → 0.01).
+6. When more than one location is in scope the automatic Location column also appears, leftmost before Technician — it is not in the Column Selection control and its presence is expected.</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>SV-8649 (specs/technician-utilization.md S2-R1; S2-R2; S2-R3; S2-R4; S2-R5; §3)</t>
+          <t>SV-8649; SV-8656 (TU spec v5 2026-07-29 S2-R1; S2-R2; S2-R3; S2-R4; S2-R5; §3 + Story 9 S9-R9 — header order and the hours columns; plus the automatic Location column leftmost when shown)</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr"/>
@@ -3138,7 +3139,8 @@
 5. Read the Location cell on the Summary row at the bottom.
 6. Open the Column Selection control and look for Location in the list.
 7. Narrow to a single location and read the headers again.
-8. Change the selection between one location, several, and "All Locations", watching the filter control's width.</t>
+8. Change the selection between one location, several, and "All Locations", watching the filter control's width.
+9. With more than one location still selected, download both PDF views and the CSV and read their columns from the left.</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
@@ -3150,12 +3152,13 @@
 5. The Summary row leaves the Location cell blank.
 6. Location is never listed in the Column Selection control — it follows the location scope on its own.
 7. With a single location in scope the Location column is hidden.
-8. The Location filter control keeps the same width whichever label it shows — one location, several, or "All locations" — so the toolbar does not shift as you change the selection.</t>
+8. The Location filter control keeps the same width whichever label it shows — one location, several, or "All locations" — so the toolbar does not shift as you change the selection.
+9. Every download — both PDF views and the CSV — includes the Location column in its on-screen leftmost position, carrying the same values you just read on screen.</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>SV-8656 (TU spec v5 2026-07-29 S9-R9; S9-R10; S8-R15; S10-R4 — per-row Location column; leftmost before Technician; "Multiple" on a spanning row; Summary row blank; never in the selector)</t>
+          <t>SV-8656; SV-8654 (TU spec v5 2026-07-29 S9-R9; S9-R10; S8-R15; S10-R4; S7-R13 — per-row Location column; leftmost before Technician; "Multiple" on a spanning row; Summary row blank; not in the selector; S7-R13 = same column in every download)</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr"/>
@@ -3191,27 +3194,29 @@
       <c r="F57" s="2" t="inlineStr">
         <is>
           <t>1. Find the column-selection button in the toolbar and hover it to read its tooltip.
-2. Note its position relative to the three-dot download menu.
-3. Open it and read every toggle in the list, and which ones are on.
-4. Turn Est. Lost Labor off, then turn Internal Hours off, watching the table each time.
-5. Turn both back on and check where each column lands.
-6. Reload the page, then close the browser, reopen it and return to the report.</t>
+2. With the button focused, read the name assistive technology gives it — use the browser's accessibility inspector or a screen reader.
+3. Note its position relative to the three-dot download menu.
+4. Open it and read every toggle in the list, and which ones are on.
+5. Turn Est. Lost Labor off, then turn Internal Hours off, watching the table each time.
+6. Turn both back on and check where each column lands.
+7. Reload the page, then close the browser, reopen it and return to the report.</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
           <t>1. The control is an icon button whose tooltip reads "Column Selection", sitting immediately after the three-dot download menu in the toolbar.
-2. The list offers five toggles — Total Hours, WO Hours, Internal Hours, Utilization % and Est. Lost Labor — and all five are on by default.
-3. Technician is always shown and cannot be turned off (it is not offered as a toggle).
-4. The Location column is never listed here — it appears on its own whenever more than one location is in scope.
-5. Turning a toggle off hides that column (header and cells) immediately, with no reload; turning it back on returns it to its usual place in the fixed left-to-right order — the remaining columns never reorder.
-6. Est. Lost Labor can now be hidden like any other column (it used to be always on).
-7. Your column choice is remembered in this browser and is still applied when you come back.</t>
+2. Because the button shows an icon and no text, it still carries a name that assistive technology reads out — it is not left unnamed. (The exact wording is confirmed in the build.)
+3. The list offers five toggles — Total Hours, WO Hours, Internal Hours, Utilization % and Est. Lost Labor — and all five are on by default.
+4. Technician is always shown and cannot be turned off (it is not offered as a toggle).
+5. The Location column is never listed here — it appears on its own whenever more than one location is in scope.
+6. Turning a toggle off hides that column (header and cells) immediately, with no reload; turning it back on returns it to its usual place in the fixed left-to-right order — the remaining columns never reorder.
+7. Est. Lost Labor can now be hidden like any other column (it used to be always on).
+8. Your column choice is remembered in this browser and is still applied when you come back.</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>SV-8582 (TU spec v5 2026-07-29 Story 10 S10-R1; S10-R2; S10-R3; S10-R4; S10-R5; S10-R6 column selector — NO OWNING JIRA STORY: epic SV-8582 carries no TU Story-10 ticket and the spec's own Jira field reads TBD; epic key used and FLAGGED)</t>
+          <t>SV-8655; SV-8582 (TU spec v5 2026-07-29 Story 10 S10-R1; S10-R2; S10-R3; S10-R4; S10-R5; S10-R6 column selector + Story 8 S8-R16 accessible name — Story 10 has NO owning Jira story so epic SV-8582 is used and FLAGGED; S8-R16 is owned by SV-8655)</t>
         </is>
       </c>
       <c r="I57" s="2" t="inlineStr"/>

--- a/testrail-import/Report-Suite_Technician-Utilization-Report_testrail-import.xlsx
+++ b/testrail-import/Report-Suite_Technician-Utilization-Report_testrail-import.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Technician Utilization" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Technician Utilization" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>

--- a/testrail-import/Report-Suite_Technician-Utilization-Report_testrail-import.xlsx
+++ b/testrail-import/Report-Suite_Technician-Utilization-Report_testrail-import.xlsx
@@ -510,7 +510,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>1. You are signed in as a user whose role has the timesheet-reports permission.</t>
+          <t>1. You are signed in as a user whose role has the ordinary reports access.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -530,7 +530,7 @@
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>SV-8648 (TU spec S1-R1 — below the named anchor items [Sales; Technician Efficiency; Advisor Analysis; Shop Efficiency] per PRD video 2026-07-30 01:18-02:05; refines video P3 [newest-wins])</t>
+          <t>SV-8648 (TU spec S1-R1 — below the named anchor items [Sales; Technician Efficiency; Advisor Analysis; Shop Efficiency] per the PRD video 2026-07-30; access = the one ordinary reports permission per QA lead 2026-08-03)</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr"/>
@@ -780,7 +780,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>Without the timesheet-reports permission Technician Utilization is hidden</t>
+          <t>Without reports access Technician Utilization is hidden</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
@@ -800,7 +800,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1. You are signed in as a user whose role lacks the permission that controls the Timesheet Activities report.</t>
+          <t>1. You are signed in as a user whose role does NOT have reports access.</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -816,7 +816,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>SV-8648 (specs/technician-utilization.md S1-N1)</t>
+          <t>SV-8648 (TU spec S1-N1 — the gate is the one ordinary reports access per Chris Ward Q2=A + QA lead 2026-08-03 "ONE permission FOR NOW"; the TU prerequisite still names the timesheet-reports permission — his spec edit owed)</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr"/>

--- a/testrail-import/Report-Suite_Technician-Utilization-Report_testrail-import.xlsx
+++ b/testrail-import/Report-Suite_Technician-Utilization-Report_testrail-import.xlsx
@@ -865,7 +865,7 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>SV-8648 (specs/technician-utilization.md S1-N2; S9-N2; S5-N1; S3-N1; §7)</t>
+          <t>SV-8648 (TU spec v5 2026-07-29 S1-N2; S3-N1; S5-N1; S9-N2; §7 — §7 CLOSES the no-data string verbatim ("Empty bays" ... "Get Going!") as the standard reports no-data label; so the exact string IS the requirement)</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr"/>
@@ -1767,29 +1767,30 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>1. A technician clocked time on several (but not all) days of the range - including, for the pooling check, time at two selected locations on the same day.
-2. Browser devtools (network tab) are open for the on-demand check.</t>
+          <t>1. A technician clocked time on several (but not all) days of the range - including, for the pooling check, time at two selected locations on the same day.</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>1. Expand the technician's row and watch the network traffic.
-2. Read the day rows top to bottom.
-3. Look for rows on days the technician did not clock time.
-4. On the double-location day, count the rows for that date.</t>
+          <t>1. Before expanding anything, look at the technician's row - there are no day rows under it yet.
+2. Expand the technician's row and watch the data area as the day rows appear.
+3. Read the day rows top to bottom.
+4. Look for rows on days the technician did not clock time.
+5. On the double-location day, count the rows for that date.</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
           <t>1. One row appears for each day the technician clocked time in the range, in date order from earliest to latest.
-2. The day rows are fetched ON EXPAND (on demand) - they are not shipped with the initial report payload.
+2. The day rows are not there until you expand the row - they arrive at the moment you expand it (you may briefly see the standard loading indicator in that area), and the rest of the report does not reload.
 3. A day with no clocked time has NO row.
-4. With several locations selected, a day's row POOLS that day's hours across the selected locations - one day row per date, not one per location.</t>
+4. With several locations selected, a day's row POOLS that day's hours across the selected locations - one day row per date, not one per location.
+5. Note for the tester: you do not need developer tools for this test - just watch the screen.</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>SV-8651 (specs/technician-utilization.md S4-R2; S4-N1; S9-R4)</t>
+          <t>SV-8651 (TU spec v5 2026-07-29 S4-R2; S4-N1; S9-R4 — one row per clocked day in date order; load-on-expand; no row for an unclocked day; per-day pooling across selected locations; the back-end half is covered by C30449 in "TU - API")</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr"/>
@@ -2013,13 +2014,13 @@
       <c r="E33" s="2" t="inlineStr">
         <is>
           <t>1. Several technician rows are visible and the Summary row shows their totals.
-2. Browser devtools (network tab) are open.</t>
+2. Note the current date range so you can confirm it does not change.</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
           <t>1. Note the Summary values, then deselect one technician in the Filter by Technician filter.
-2. Watch the network traffic and the Summary row.
+2. Watch the data area and the Summary row.
 3. Re-select the technician.</t>
         </is>
       </c>
@@ -2027,13 +2028,14 @@
         <is>
           <t>1. The deselected technician's row is hidden.
 2. The Summary row recalculates over the technicians that remain visible.
-3. NO reload happens - the technician filter works on screen only and does not change the date range or re-query the server.
-4. Re-selecting the technician shows the row again (and the Summary recalculates back).</t>
+3. The report does NOT reload - the technician filter works on screen only: the rows and the Summary update straight away, no loading indicator appears in the data area, and the date range does not change.
+4. Re-selecting the technician shows the row again (and the Summary recalculates back).
+5. Note for the tester: you do not need developer tools for this test - just watch the screen.</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>SV-8652 (specs/technician-utilization.md S5-R3; S5-R4; S5-R5; §3; S5 context note)</t>
+          <t>SV-8652 (TU spec v5 2026-07-29 S5-R3; S5-R4; S5-R5 + §3 Key Decisions ("the technician filter works on screen only and does not reload the report"); S5 context note — the server half is covered by C30450 in "TU - API")</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr"/>
@@ -2608,12 +2610,13 @@
 2. Every download covers the location(s) currently selected in the location filter and the date range currently active on the report.
 3. With every technician selected, the download covers all technicians for the range at the selected location(s).
 4. Every download (each PDF and the CSV) carries a "Locations:" line naming the location(s) the report was scoped to (exact position in the file is confirmed in the build).
-5. Every download also mirrors the columns currently shown on screen — a column hidden in the Column Selection control is absent from the files, and a re-shown column comes back.</t>
+5. Every download also mirrors the columns currently shown on screen — a column hidden in the Column Selection control is absent from the files, and a re-shown column comes back.
+6. Note for the tester: when you have more than one location in scope, the files also carry a Location column even though it is not in the Column Selection control. That is correct - it appears by itself. With a single location in scope there is no Location column, and that is also correct.</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>SV-8654 (TU spec v5 2026-07-29 S7-R8; S7-R9; S7-R10; S7-E1; S9-R8 — S7-R10 now says the downloads include the columns currently shown; mirroring the column selector)</t>
+          <t>SV-8654 (TU spec v5 2026-07-29 S7-R8; S7-R9; S7-R10; S7-R13; S7-E1; S9-R8 — downloads mirror the shown columns and the technician/location/date scope; S7-R13 = the "Locations:" line and the automatic Location column)</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr"/>
@@ -2803,7 +2806,7 @@
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>SV-8654 (specs/technician-utilization.md Story 7 Error Handling; §7)</t>
+          <t>SV-8654 (TU spec v5 2026-07-29 Story 7 Error Handling + §7 notifications table — these CLOSE both strings verbatim ("Download started" / "Failed to download report"); Story 7 has no S-anchor for them so §7 is the closing reference)</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr"/>
@@ -3301,20 +3304,21 @@
         <is>
           <t>1. Switch the application to dark mode.
 2. Check each element: page background, toolbar, cells, the Total Hours link, the information icon, the sort indicator, and a "—" glyph.
-3. Measure the information icon's contrast against its background in dark mode, then in light mode.
+3. Look at the information icon in dark mode, then switch back to light mode and look at it again.
 4. Check the Total Hours link's underline/affordance and focus indicator in both modes.</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>1. The report supports dark mode: page background, toolbar, cells, the Total Hours link, the information icon, the sort indicator, and the "—" glyph all use dark-mode-legible colors meeting contrast.
-2. The information icon meets at least a 3:1 contrast ratio against its background in BOTH light and dark mode.
-3. The Total Hours link's non-color affordance and focus indicator apply in both modes.</t>
+          <t>1. The report supports dark mode: page background, toolbar, cells, the Total Hours link, the information icon, the sort indicator, and the "—" glyph are all clearly legible in dark mode.
+2. In BOTH light mode and dark mode the information icon is clearly visible against the background behind it - you can see it at a glance and it does not disappear into the background.
+3. The Total Hours link's non-color affordance and focus indicator apply in both modes.
+4. Note for the tester: you do not need to measure anything and you do not need any tool. Just say whether you can see the icon easily in both modes, and only report it if you cannot. (The design rule behind this is a minimum 3:1 contrast ratio, which the design and engineering team check with a contrast tool - not by hand.)</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t>SV-8655 (specs/technician-utilization.md S8-R9; S8-R13; S8-R14)</t>
+          <t>SV-8655 (TU spec v5 2026-07-29 S8-R9; S8-R13; S8-R14 — dark-mode legibility of every named element; the info icon at ≥ 3:1 in both modes; the Total Hours link affordance/focus in both modes; the ratio is design-token-owned)</t>
         </is>
       </c>
       <c r="I59" s="2" t="inlineStr"/>

--- a/testrail-import/Report-Suite_Technician-Utilization-Report_testrail-import.xlsx
+++ b/testrail-import/Report-Suite_Technician-Utilization-Report_testrail-import.xlsx
@@ -1970,14 +1970,14 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>1. Find the toolbar filter labeled "Filter by Technician" and open it.
+          <t>1. Find the toolbar filter labeled "Technician" and open it.
 2. Check the selection state of every listed technician.
 3. Try selecting more than one change at once (multi-select).</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>1. The toolbar has a filter labeled "Filter by Technician" that allows selecting more than one technician.
+          <t>1. The toolbar has a filter labeled "Technician" that allows selecting more than one technician (when several are chosen its label reads, for example, "2 technicians").
 2. On the first visit, EVERY technician is selected.
 3. All technicians' rows are shown.</t>
         </is>
@@ -2044,7 +2044,7 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>Select all and Clear all controls set every technician on or off</t>
+          <t>All technicians and Clear all controls set every technician on or off</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
@@ -2069,15 +2069,15 @@
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>1. In the Filter by Technician filter, use the control labeled "Clear all".
-2. Use the control labeled "Select all".
+          <t>1. In the Technician filter, use the control labeled "Clear all".
+2. Use the control labeled "All technicians".
 3. Deselect one technician, then change the date range to the one containing the additional technician.
 4. Use "Clear all" again, then switch to the range where the additional technician newly appears.</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>1. "Clear all" sets every currently-listed technician to deselected; "Select all" selects all technicians at once.
+          <t>1. "Clear all" sets every currently-listed technician to deselected; "All technicians" selects all technicians at once.
 2. Selection is tracked as the set of DESELECTED technicians: a technician you have not deselected is selected by default.
 3. After step 3, your deselected technician STAYS deselected across the range change, while the newly-appearing technician is SELECTED (never explicitly deselected).
 4. After step 4, the newly-appearing technician is selected even though you had cleared all - "Clear all" only deselected the technicians listed at the time.</t>
@@ -2893,16 +2893,16 @@
         <is>
           <t>1. Look at the rightmost control in the toolbar and read its label.
 2. Open it and read the listed options.
-3. Choose "All Locations", then uncheck one individual location.
+3. Choose "All locations", then uncheck one individual location.
 4. With every accessible location selected, look at how the report tells you which location the shown data belongs to.</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
           <t>1. The toolbar has a location filter labeled "Location" - a multi-select and the RIGHTMOST control.
-2. It lists the locations the signed-in user has access to, plus an "All Locations" option.
-3. "All Locations" acts as a select-all shortcut: choosing it selects every accessible location; unchecking one location leaves the remaining specific locations selected - the selection is always the concrete set of checked locations.
-4. With all locations selected you can tell which location the shown data belongs to — a location label or marking is shown. (Exactly where and how it appears is confirmed in the build; this report pools each technician's hours into one row, so the marking may take a different form here.)</t>
+2. It lists the locations the signed-in user has access to, plus an "All locations" option and a "Clear all" action. (If you only have access to one location, the "All locations" entry is not offered - you see "Clear all" and your one location.)
+3. "All locations" acts as a select-all shortcut: choosing it selects every accessible location; unchecking one location leaves the remaining specific locations selected - the selection is always the concrete set of checked locations.
+4. With more than one location selected, a Location column appears in the table and each row names its location - or reads "Multiple" for a technician whose hours span more than one of them. (Where that column sits on screen is checked by its own test.)</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">

--- a/testrail-import/Report-Suite_Technician-Utilization-Report_testrail-import.xlsx
+++ b/testrail-import/Report-Suite_Technician-Utilization-Report_testrail-import.xlsx
@@ -525,7 +525,9 @@
         <is>
           <t>1. The report is listed under the Performance group, labeled "Technician Utilization".
 2. Clicking it opens the report.
-3. The entry sits BELOW the pre-existing report links — Sales, Technician Efficiency, Advisor Analysis, Shop Efficiency — the new reports are added below those items without moving or disturbing them.</t>
+3. The entry sits BELOW the pre-existing report links — Sales, Technician Efficiency, Advisor Analysis, Shop Efficiency — the new reports are added below those items without moving or disturbing them.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Technician Utilization report specification version 5 (S1-R1).</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
@@ -572,12 +574,14 @@
       <c r="G3" s="2" t="inlineStr">
         <is>
           <t>1. Technician A has exactly ONE row.
-2. Technician B has NO row - only technicians with clocked time in the selected range at the selected location(s) appear.</t>
+2. Technician B has NO row - only technicians with clocked time in the selected range at the selected location(s) appear.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Technician Utilization report specification version 5 (S1-R2).</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>SV-8648 (specs/technician-utilization.md S1-R2)</t>
+          <t>SV-8648 (TU spec v5 2026-07-29 S1-R2)</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr"/>
@@ -619,7 +623,9 @@
         <is>
           <t>1. The date range defaults to the current calendar month (the date picker's "This Month" preset).
 2. Because a range never extends past now, the current-month default effectively shows the month to date.
-3. The location filter defaults to the user's currently active location (the one in the application's global location switcher).</t>
+3. The location filter defaults to the user's currently active location (the one in the application's global location switcher).
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Technician Utilization report specification version 5 (S1-R3, S1-R6, S9-R2).</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -667,12 +673,14 @@
         <is>
           <t>1. Each range change reloads the report's rows for the new range.
 2. A valid Custom range applies normally.
-3. A Custom span wider than 366 days (matching the largest preset) is rejected - it cannot be applied.</t>
+3. A Custom span wider than 366 days (matching the largest preset) is rejected - it cannot be applied.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Technician Utilization report specification version 5 (S1-R4, S1-R5).</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>SV-8648 (specs/technician-utilization.md S1-R4; S1-R5)</t>
+          <t>SV-8648 (TU spec v5 2026-07-29 S1-R4; S1-R5)</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr"/>
@@ -715,12 +723,14 @@
         <is>
           <t>1. On the initial load and on every reload (date-range or location change), the data area shows the standard reports loading indicator.
 2. The existing rows are replaced only when the new data returns.
-3. The toolbar remains interactive during the load.</t>
+3. The toolbar remains interactive during the load.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Technician Utilization report specification version 5 (S1-R10).</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>SV-8648 (specs/technician-utilization.md S1-R10)</t>
+          <t>SV-8648 (TU spec v5 2026-07-29 S1-R10)</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr"/>
@@ -766,12 +776,14 @@
           <t>1. A record that crosses midnight is split by day - each day counts only its own hours; the midnight split is evaluated in the active workplace's time zone.
 2. A record that starts before the range (or ends after it) counts only the part inside the range.
 3. EVERY record is day-grouped and windowed in a SINGLE report-level time zone - the active workplace's - regardless of the location where it was clocked (a record's day, the current-month boundary, and the midnight split all use that one zone).
-4. This matches the Timesheet Activities report's single-time-zone grouping.</t>
+4. This matches the Timesheet Activities report's single-time-zone grouping.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Technician Utilization report specification version 5 (S1-R7).</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>SV-8648 (specs/technician-utilization.md S1-R7; S1 context notes)</t>
+          <t>SV-8648 (TU spec v5 2026-07-29 S1-R7; S1 context notes)</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr"/>
@@ -811,7 +823,9 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>1. The Technician Utilization report does NOT appear in the navigation.</t>
+          <t>1. The Technician Utilization report does NOT appear in the navigation.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Technician Utilization report specification version 5 (S1-N1); where the wording of that specification differs, the behaviour above follows a later product decision, which is the authority.</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
@@ -860,7 +874,9 @@
         <is>
           <t>1. Instead of rows, the data area shows exactly: "Empty bays, endless possibilities. Get Going!" (the application's standard reports no-data label).
 2. The Summary row is hidden.
-3. Clearing every technician shows the SAME message and hides the Summary row — this version does not use distinct copy for genuinely-no-data vs a cleared filter.</t>
+3. Clearing every technician shows the SAME message and hides the Summary row — this version does not use distinct copy for genuinely-no-data vs a cleared filter.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Technician Utilization report specification version 5 (S1-N2, S3-N1, S5-N1, S9-N2).</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -913,7 +929,9 @@
 3. WO Hours = time clocked directly to work orders; Internal Hours = time clocked to internal, non-billable activities.
 4. Internal Hours includes ALL internal time - including hours at a location with no configured labor rate.
 5. Hours show two decimal places with NO thousands separator (e.g. "107.70"), rounded from the unrounded hours using round-half-up (a tie rounds away from zero - 0.005 → 0.01).
-6. When more than one location is in scope the automatic Location column also appears, leftmost before Technician — it is not in the Column Selection control and its presence is expected.</t>
+6. When more than one location is in scope the automatic Location column also appears, leftmost before Technician — it is not in the Column Selection control and its presence is expected.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Technician Utilization report specification version 5 (S2-R1, S2-R2, S2-R3, S2-R4, S2-R5, S9-R9).</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
@@ -959,12 +977,14 @@
       <c r="G11" s="2" t="inlineStr">
         <is>
           <t>1. Utilization % = work-order hours as a percentage of total clocked hours, computed from the unrounded hours (not from the already-rounded displays).
-2. It shows one decimal place followed by a percent sign, rounded round-half-up (66.65% → 66.7%).</t>
+2. It shows one decimal place followed by a percent sign, rounded round-half-up (66.65% → 66.7%).
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Technician Utilization report specification version 5 (S2-R6, S2-R7).</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>SV-8649 (specs/technician-utilization.md S2-R6; S2-R7; §3)</t>
+          <t>SV-8649 (TU spec v5 2026-07-29 S2-R6; S2-R7; §3)</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr"/>
@@ -1007,12 +1027,14 @@
         <is>
           <t>1. The internal-only technician shows "0.0%".
 2. No row shows more than 100% - work-order hours are always part of total clocked hours.
-3. The "—" (undefined, total = 0) state is unreachable on a rendered technician or day row, because only technicians with clocked time get rows.</t>
+3. The "—" (undefined, total = 0) state is unreachable on a rendered technician or day row, because only technicians with clocked time get rows.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Technician Utilization report specification version 5 (S2-E1, S2-R7).</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>SV-8649 (specs/technician-utilization.md S2-E1; S2-R7; S2 context note)</t>
+          <t>SV-8649 (TU spec v5 2026-07-29 S2-E1; S2-R7; S2 context note)</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr"/>
@@ -1057,12 +1079,14 @@
         <is>
           <t>1. Est. Lost Labor = the sum, per contributing location, of that location's default labor rate × the technician's internal hours clocked there - summed at full precision, with the technician's total rounded ONCE (round-half-up).
 2. In a single-location view it is simply that one location's rate × the technician's internal hours.
-3. The value shows as dollars with two decimals and commas between thousands (e.g. "$1,234.50").</t>
+3. The value shows as dollars with two decimals and commas between thousands (e.g. "$1,234.50").
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Technician Utilization report specification version 5 (S2-R8, S2-R9).</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>SV-8649 (specs/technician-utilization.md S2-R8; S2-R9; §3)</t>
+          <t>SV-8649 (TU spec v5 2026-07-29 S2-R8; S2-R9; §3)</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr"/>
@@ -1108,7 +1132,9 @@
           <t>1. While Est. Lost Labor is shown, the column is pinned to the far right; its cells are bold and its header is bold, matching.
 2. The information icon shows exactly: "Internal hours valued at each location's default labor rate" — on hover, on keyboard focus, and on tap; it is dismissible.
 3. NO column header other than Est. Lost Labor shows the information icon.
-4. Est. Lost Labor can be turned OFF in the Column Selection control; when it is off the column, its bold styling and its information icon are all absent, and the report still works normally.</t>
+4. Est. Lost Labor can be turned OFF in the Column Selection control; when it is off the column, its bold styling and its information icon are all absent, and the report still works normally.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Technician Utilization report specification version 5 (S2-R10, S2-R11, S8-R4, S8-R6, S8-R7, S8-N1, S10-R3).</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
@@ -1156,12 +1182,14 @@
         <is>
           <t>1. Technician A shows "$0.00" - there is nothing to value, regardless of whether the location has a rate configured.
 2. Technician B also shows "$0.00" - a configured rate of exactly $0.00 is a KNOWN rate that values the hours at $0.00, not "—".
-3. "$0.00" means 'the rate is known and there is nothing (or $0) to value' - a different state from "—" ('the rate is unknown').</t>
+3. "$0.00" means 'the rate is known and there is nothing (or $0) to value' - a different state from "—" ('the rate is unknown').
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Technician Utilization report specification version 5 (S2-E2).</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>SV-8649 (specs/technician-utilization.md S2-E2; §5 Assumptions; S2 context note)</t>
+          <t>SV-8649 (TU spec v5 2026-07-29 S2-E2; §5 Assumptions; S2 context note)</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr"/>
@@ -1190,7 +1218,8 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1. A technician's in-range internal hours were all clocked at location(s) with NO default labor rate configured (rate absent, not $0.00).</t>
+          <t>1. A technician's in-range internal hours were all clocked at location(s) with NO default labor rate configured (rate absent, not $0.00).
+2. Part of this test checks what a blind user would hear, so you need a screen reader. On Windows install NVDA — it is free, from nvaccess.org. On a Mac use VoiceOver, which is already built in (Cmd+F5 turns it on and off). Alternatively the browser's developer tools (F12) have an "Accessibility" panel that shows the same names without you having to listen to anything.</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1203,12 +1232,14 @@
         <is>
           <t>1. Est. Lost Labor shows "—" (an em-dash), NOT "$0.00" - the rate is unknown, so the value cannot be computed.
 2. The "—" cell carries the assistive-technology label "No default labor rate configured" (distinguishing it from "$0.00", which reads as its dollar value).
-3. The technician's Internal Hours column still shows all the internal hours (they are counted even though they cannot be valued).</t>
+3. The technician's Internal Hours column still shows all the internal hours (they are counted even though they cannot be valued).
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Technician Utilization report specification version 5 (S2-E3, S8-R11, S2-R4).</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>SV-8649 (specs/technician-utilization.md S2-E3; S8-R11; S2-R4)</t>
+          <t>SV-8649 (TU spec v5 2026-07-29 S2-E3; S8-R11; S2-R4)</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr"/>
@@ -1251,12 +1282,14 @@
         <is>
           <t>1. Est. Lost Labor is the sum of the valued (rated-location) portions only - the unrated-location hours are excluded from the dollar amount.
 2. The amount shows as a normal "$X.XX" with NO partial-value indicator in this version - so the row's Est. Lost Labor values fewer hours than its Internal Hours column shows.
-3. This is a documented known limitation (a partial-value indicator is a possible follow-up) - expected behavior, not a defect.</t>
+3. This is a documented known limitation (a partial-value indicator is a possible follow-up) - expected behavior, not a defect.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Technician Utilization report specification version 5 (S2-E4).</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>SV-8649 (specs/technician-utilization.md S2-E4)</t>
+          <t>SV-8649 (TU spec v5 2026-07-29 S2-E4)</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr"/>
@@ -1285,7 +1318,8 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1. You are on the Technician Utilization report with several technician rows loaded.</t>
+          <t>1. You are on the Technician Utilization report with several technician rows loaded.
+2. Part of this test checks what a blind user would hear, so you need a screen reader. On Windows install NVDA — it is free, from nvaccess.org. On a Mac use VoiceOver, which is already built in (Cmd+F5 turns it on and off). Alternatively the browser's developer tools (F12) have an "Accessibility" panel that shows the same names without you having to listen to anything.</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1299,12 +1333,14 @@
         <is>
           <t>1. The technician rows are sorted by Technician name, A to Z.
 2. The Technician header shows the ascending sort indicator.
-3. The active sort header exposes its state to assistive technology (aria-sort = ascending on the Technician header; none on the others).</t>
+3. The active sort header exposes its state to assistive technology (aria-sort = ascending on the Technician header; none on the others).
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Technician Utilization report specification version 5 (S2-R12, S8-R8, S8-R10).</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>SV-8649 (specs/technician-utilization.md S2-R12; S8-R8; S8-R10)</t>
+          <t>SV-8649 (TU spec v5 2026-07-29 S2-R12; S8-R8; S8-R10)</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr"/>
@@ -1351,12 +1387,14 @@
 2. Clicking a column that is not the active sort sorts it ascending; clicking the active column again toggles to descending; further clicks only ever toggle ascending↔descending - there is NO third 'cleared' state.
 3. All six columns are sortable.
 4. Sorting is applied on screen to the loaded rows - NO reload/server request happens.
-5. Technicians tied in the sorted column are ordered by Technician name A to Z; two technicians sharing the same display name keep a stable order between renders.</t>
+5. Technicians tied in the sorted column are ordered by Technician name A to Z; two technicians sharing the same display name keep a stable order between renders.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Technician Utilization report specification version 5 (S2-R13, S2-R14).</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>SV-8649 (specs/technician-utilization.md S2-R13; S2-R14)</t>
+          <t>SV-8649 (TU spec v5 2026-07-29 S2-R13; S2-R14)</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr"/>
@@ -1398,12 +1436,14 @@
       <c r="G20" s="2" t="inlineStr">
         <is>
           <t>1. After the reload, the rows are back to Technician name A to Z (the sort reset).
-2. On the return visit, the sort is again Technician A to Z - sort is NOT persisted (unlike the date range, technician selection, and location selection, which are).</t>
+2. On the return visit, the sort is again Technician A to Z - sort is NOT persisted (unlike the date range, technician selection, and location selection, which are).
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Technician Utilization report specification version 5 (S2-R15).</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>SV-8649 (specs/technician-utilization.md S2-R15; §3)</t>
+          <t>SV-8649 (TU spec v5 2026-07-29 S2-R15; §3)</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr"/>
@@ -1446,12 +1486,14 @@
         <is>
           <t>1. Only the technician rows reorder.
 2. The Summary row stays pinned at the bottom.
-3. Each technician's expanded day rows stay under that technician, still in date order (earliest to latest) - they do not re-sort by the clicked column.</t>
+3. Each technician's expanded day rows stay under that technician, still in date order (earliest to latest) - they do not re-sort by the clicked column.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Technician Utilization report specification version 5 (S2-R16).</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>SV-8649 (specs/technician-utilization.md S2-R16)</t>
+          <t>SV-8649 (TU spec v5 2026-07-29 S2-R16)</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr"/>
@@ -1494,12 +1536,14 @@
         <is>
           <t>1. Rows whose Est. Lost Labor is "—" sort to the BOTTOM in BOTH ascending and descending order - they are never floated to the top by reversing direction.
 2. Among themselves, the "—" rows are ordered by Technician name A to Z.
-3. A "$0.00" value is a number, not "—" - it sorts as zero (lowest ascending, above only the — group).</t>
+3. A "$0.00" value is a number, not "—" - it sorts as zero (lowest ascending, above only the — group).
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Technician Utilization report specification version 5 (S2-R17).</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>SV-8649 (specs/technician-utilization.md S2-R17)</t>
+          <t>SV-8649 (TU spec v5 2026-07-29 S2-R17)</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr"/>
@@ -1543,12 +1587,14 @@
           <t>1. A Summary row is pinned to the bottom of the report, labeled "Summary".
 2. It stays visible at the bottom while the rows scroll.
 3. It uses the same number formats as the technician rows.
-4. Its values carry NO label prefix such as "TOTAL:" or "AVG:".</t>
+4. Its values carry NO label prefix such as "TOTAL:" or "AVG:".
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Technician Utilization report specification version 5 (S3-R1, S3-R2, S3-R6, S3-R7, S8-R5).</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>SV-8650 (specs/technician-utilization.md S3-R1; S3-R2; S3-R6; S3-R7; S8-R5)</t>
+          <t>SV-8650 (TU spec v5 2026-07-29 S3-R1; S3-R2; S3-R6; S3-R7; S8-R5)</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr"/>
@@ -1591,12 +1637,14 @@
         <is>
           <t>1. Each Summary hours value is the total of that column across the VISIBLE technicians, computed from unrounded hours and rounded once for display (round-half-up).
 2. Eye-summing the displayed rows MAY differ from the displayed Summary by 0.01 — one unit in the last decimal (these values are HOURS, not money) — expected in a compute-from-unrounded report, not a defect.
-3. With every technician selected, the Summary row equals the shop totals for the full date range at the selected location(s).</t>
+3. With every technician selected, the Summary row equals the shop totals for the full date range at the selected location(s).
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Technician Utilization report specification version 5 (S3-R3, S5-E1).</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>SV-8650 (specs/technician-utilization.md S3-R3; §3 context note; S5-E1)</t>
+          <t>SV-8650 (TU spec v5 2026-07-29 S3-R3; §3 context note; S5-E1)</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr"/>
@@ -1638,12 +1686,14 @@
       <c r="G25" s="2" t="inlineStr">
         <is>
           <t>1. The Summary Utilization % shows the WEIGHTED rate - the visible technicians' total work-order hours as a percentage of their total clocked hours, from unrounded hours (10.0% in the example).
-2. It is NOT the average of the per-technician percentages (not 50.0%).</t>
+2. It is NOT the average of the per-technician percentages (not 50.0%).
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Technician Utilization report specification version 5 (S3-R4).</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>SV-8650 (specs/technician-utilization.md S3-R4)</t>
+          <t>SV-8650 (TU spec v5 2026-07-29 S3-R4)</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr"/>
@@ -1685,12 +1735,14 @@
         <is>
           <t>1. The Summary Est. Lost Labor is computed like a row but over all visible technicians' internal hours: rate × internal hours per contributing rated location, summed at full precision and rounded once.
 2. A visible technician whose value is "—" contributes NOTHING to the sum - so the Summary understates true lost labor whenever any visible technician is "—" or partially valued (documented, expected).
-3. The Summary shows "—" only when EVERY visible technician's Est. Lost Labor is "—".</t>
+3. The Summary shows "—" only when EVERY visible technician's Est. Lost Labor is "—".
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Technician Utilization report specification version 5 (S3-R5).</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>SV-8650 (specs/technician-utilization.md S3-R5)</t>
+          <t>SV-8650 (TU spec v5 2026-07-29 S3-R5)</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr"/>
@@ -1719,7 +1771,8 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>1. You are on the Technician Utilization report with rows loaded.</t>
+          <t>1. You are on the Technician Utilization report with rows loaded.
+2. Part of this test checks what a blind user would hear, so you need a screen reader. On Windows install NVDA — it is free, from nvaccess.org. On a Mac use VoiceOver, which is already built in (Cmd+F5 turns it on and off). Alternatively the browser's developer tools (F12) have an "Accessibility" panel that shows the same names without you having to listen to anything.</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
@@ -1733,12 +1786,14 @@
         <is>
           <t>1. Each technician row has a control to expand and collapse it.
 2. Its accessible name reflects the NEXT action, scoped to that technician: when collapsed it reads Expand, then that technician's name, then daily breakdown (for example: Expand John Smith's daily breakdown); when expanded it reads Collapse, then the same name and words.
-3. The control is keyboard-focusable, toggles on Enter and Space, and exposes its expanded/collapsed state to assistive technology.</t>
+3. The control is keyboard-focusable, toggles on Enter and Space, and exposes its expanded/collapsed state to assistive technology.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Technician Utilization report specification version 5 (S4-R1, S8-R12).</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>SV-8651 (specs/technician-utilization.md S4-R1; S8-R12)</t>
+          <t>SV-8651 (TU spec v5 2026-07-29 S4-R1; S8-R12)</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr"/>
@@ -1785,7 +1840,9 @@
 2. The day rows are not there until you expand the row - they arrive at the moment you expand it (you may briefly see the standard loading indicator in that area), and the rest of the report does not reload.
 3. A day with no clocked time has NO row.
 4. With several locations selected, a day's row POOLS that day's hours across the selected locations - one day row per date, not one per location.
-5. Note for the tester: you do not need developer tools for this test - just watch the screen.</t>
+5. Note for the tester: you do not need developer tools for this test - just watch the screen.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Technician Utilization report specification version 5 (S4-R2, S4-N1, S9-R4).</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
@@ -1833,12 +1890,14 @@
         <is>
           <t>1. Each day row shows the same columns, in the same formats, as the technician row - with that day's values.
 2. The day's Est. Lost Labor is valued per location exactly like a technician row (that location's default labor rate × that day's internal hours there).
-3. Hours 2dp / Utilization one decimal + % / dollars with commas - all identical to the row formats, computed from unrounded values and rounded once.</t>
+3. Hours 2dp / Utilization one decimal + % / dollars with commas - all identical to the row formats, computed from unrounded values and rounded once.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Technician Utilization report specification version 5 (S4-R3, S2-R8).</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>SV-8651 (specs/technician-utilization.md S4-R3; S2-R8; §3)</t>
+          <t>SV-8651 (TU spec v5 2026-07-29 S4-R3; S2-R8; §3)</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr"/>
@@ -1867,7 +1926,8 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>1. You are on the Technician Utilization report with several technician rows loaded.</t>
+          <t>1. You are on the Technician Utilization report with several technician rows loaded.
+2. Part of this test checks what a blind user would hear, so you need a screen reader. On Windows install NVDA — it is free, from nvaccess.org. On a Mac use VoiceOver, which is already built in (Cmd+F5 turns it on and off). Alternatively the browser's developer tools (F12) have an "Accessibility" panel that shows the same names without you having to listen to anything.</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -1883,12 +1943,14 @@
           <t>1. The control lives in the table's header row (Technician column) - NOT in the toolbar action cluster.
 2. If ANY row is collapsed, activating it expands ALL rows; only when EVERY row is already expanded does it collapse all rows (so step 3's activation re-expands the one collapsed row).
 3. Its accessible name reflects the next action: "Expand all technicians" when it will expand, "Collapse all technicians" when every row is already expanded.
-4. It is keyboard-focusable, toggles on Enter/Space, and exposes its state to assistive technology.</t>
+4. It is keyboard-focusable, toggles on Enter/Space, and exposes its state to assistive technology.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Technician Utilization report specification version 5 (S4-R4, S8-R12, S8-R3).</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>SV-8651 (specs/technician-utilization.md S4-R4; S8-R12; S8-R3)</t>
+          <t>SV-8651 (TU spec v5 2026-07-29 S4-R4; S8-R12; S8-R3)</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr"/>
@@ -1931,12 +1993,14 @@
         <is>
           <t>1. After the reload (date-range or location change), all rows are collapsed - expansion state resets.
 2. On a fresh visit, all rows start collapsed - expansion is never persisted.
-3. Deselecting and re-selecting a technician (an on-screen operation) does NOT change the expansion state of the other rows - the expanded row stays expanded.</t>
+3. Deselecting and re-selecting a technician (an on-screen operation) does NOT change the expansion state of the other rows - the expanded row stays expanded.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Technician Utilization report specification version 5 (S4-R5).</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>SV-8651 (specs/technician-utilization.md S4-R5)</t>
+          <t>SV-8651 (TU spec v5 2026-07-29 S4-R5)</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr"/>
@@ -1979,12 +2043,14 @@
         <is>
           <t>1. The toolbar has a filter labeled "Technician" that allows selecting more than one technician (when several are chosen its label reads, for example, "2 technicians").
 2. On the first visit, EVERY technician is selected.
-3. All technicians' rows are shown.</t>
+3. All technicians' rows are shown.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Technician Utilization report specification version 5 (S5-R1, S5-R2).</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>SV-8652 (specs/technician-utilization.md S5-R1; S5-R2)</t>
+          <t>SV-8652 (TU spec v5 2026-07-29 S5-R1; S5-R2)</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr"/>
@@ -2030,7 +2096,9 @@
 2. The Summary row recalculates over the technicians that remain visible.
 3. The report does NOT reload - the technician filter works on screen only: the rows and the Summary update straight away, no loading indicator appears in the data area, and the date range does not change.
 4. Re-selecting the technician shows the row again (and the Summary recalculates back).
-5. Note for the tester: you do not need developer tools for this test - just watch the screen.</t>
+5. Note for the tester: you do not need developer tools for this test - just watch the screen.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Technician Utilization report specification version 5 (S5-R3, S5-R4, S5-R5).</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
@@ -2080,12 +2148,14 @@
           <t>1. "Clear all" sets every currently-listed technician to deselected; "All technicians" selects all technicians at once.
 2. Selection is tracked as the set of DESELECTED technicians: a technician you have not deselected is selected by default.
 3. After step 3, your deselected technician STAYS deselected across the range change, while the newly-appearing technician is SELECTED (never explicitly deselected).
-4. After step 4, the newly-appearing technician is selected even though you had cleared all - "Clear all" only deselected the technicians listed at the time.</t>
+4. After step 4, the newly-appearing technician is selected even though you had cleared all - "Clear all" only deselected the technicians listed at the time.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Technician Utilization report specification version 5 (S5-R6, S5-R7, S5-R8, S5-R9).</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>SV-8652 (specs/technician-utilization.md S5-R6; S5-R7; S5-R8; S5-R9)</t>
+          <t>SV-8652 (TU spec v5 2026-07-29 S5-R6; S5-R7; S5-R8; S5-R9)</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr"/>
@@ -2128,12 +2198,14 @@
         <is>
           <t>1. The two deselected technicians are STILL deselected on return - the deselected set is what persists (saved in this browser, not on the account).
 2. All other technicians - including any who appear for the first time - are selected.
-3. The saved date range and location selection are restored alongside.</t>
+3. The saved date range and location selection are restored alongside.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Technician Utilization report specification version 5 (S5-R10, S1-R8).</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>SV-8652 (specs/technician-utilization.md S5-R10; S1-R8; §3)</t>
+          <t>SV-8652 (TU spec v5 2026-07-29 S5-R10; S1-R8; §3)</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr"/>
@@ -2176,12 +2248,14 @@
         <is>
           <t>1. Every technician row's Total Hours is rendered as a link (every rendered row has clocked time &gt; 0, so the link always applies).
 2. The link is distinguished by more than color - it carries an underline (or equivalent non-color affordance), is keyboard-focusable with a visible focus indicator, and activates on Enter.
-3. The Summary row's Total Hours value is NOT a link.</t>
+3. The Summary row's Total Hours value is NOT a link.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Technician Utilization report specification version 5 (S6-R1, S6-N1, S8-R14).</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>SV-8653 (specs/technician-utilization.md S6-R1; S6-N1; S8-R14)</t>
+          <t>SV-8653 (TU spec v5 2026-07-29 S6-R1; S6-N1; S8-R14)</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr"/>
@@ -2224,12 +2298,14 @@
         <is>
           <t>1. The Timesheet Activities report opens in the SAME browser tab.
 2. It is already filtered to that technician.
-3. It uses the same date range that was active on the Technician Utilization report.</t>
+3. It uses the same date range that was active on the Technician Utilization report.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Technician Utilization report specification version 5 (S6-R2, S6-R3, S6-R4).</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>SV-8653 (specs/technician-utilization.md S6-R2; S6-R3; S6-R4)</t>
+          <t>SV-8653 (TU spec v5 2026-07-29 S6-R2; S6-R3; S6-R4)</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr"/>
@@ -2273,12 +2349,14 @@
         <is>
           <t>1. The two totals MATCH exactly, to two decimals (these values are hours, not money) - both reports read the same clock records and round the same way (round-half-up, from unrounded values).
 2. Under this exact scope (same range, same single location, closed records) a mismatch IS a defect.
-3. The two documented scope differences (open clocks, multi-location drill-through) are covered by separate cases and are NOT defects.</t>
+3. The two documented scope differences (open clocks, multi-location drill-through) are covered by separate cases and are NOT defects.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Technician Utilization report specification version 5 (S1-R9).</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>SV-8648 (specs/technician-utilization.md S1-R9; §2; §5 Assumptions)</t>
+          <t>SV-8648 (TU spec v5 2026-07-29 S1-R9; §2; §5 Assumptions)</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr"/>
@@ -2321,12 +2399,14 @@
         <is>
           <t>1. The open time is counted UP TO THE MOMENT THE REPORT LOADS - a fixed snapshot taken at load, not a value that keeps ticking on screen (matching how Timesheet Activities treats an open record).
 2. The two reports, loaded at different moments, MAY differ by the elapsed open time - this is a deliberate scope difference of the reconciliation guarantee, EXPECTED and NOT a defect.
-3. Reloading the Technician Utilization report takes a fresh snapshot (the value grows by the elapsed time).</t>
+3. Reloading the Technician Utilization report takes a fresh snapshot (the value grows by the elapsed time).
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Technician Utilization report specification version 5 (S1-R9, S1-E1).</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>SV-8648 (specs/technician-utilization.md S1-R9(a); S1-E1)</t>
+          <t>SV-8648 (TU spec v5 2026-07-29 S1-R9(a); S1-E1)</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr"/>
@@ -2370,12 +2450,14 @@
         <is>
           <t>1. The link passes the technician and the date range ONLY - it does NOT pass the location selection.
 2. Timesheet Activities opens for the user's currently active shop, so it shows one location's portion - it will differ from (or be disjoint with) the multi-location row value.
-3. This is a KNOWN drill-through limitation, EXPECTED and NOT a data defect (the same applies when the single selected location is not the active shop).</t>
+3. This is a KNOWN drill-through limitation, EXPECTED and NOT a data defect (the same applies when the single selected location is not the active shop).
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Technician Utilization report specification version 5 (S6-R6, S1-R9).</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>SV-8653 (specs/technician-utilization.md S6-R6; S1-R9(b))</t>
+          <t>SV-8653 (TU spec v5 2026-07-29 S6-R6; S1-R9(b))</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr"/>
@@ -2416,12 +2498,14 @@
       <c r="G41" s="2" t="inlineStr">
         <is>
           <t>1. Timesheet Activities opens filtered to that technician.
-2. The date range covers ONLY that single day.</t>
+2. The date range covers ONLY that single day.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Technician Utilization report specification version 5 (S6-R5).</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>SV-8653 (specs/technician-utilization.md S6-R5)</t>
+          <t>SV-8653 (TU spec v5 2026-07-29 S6-R5)</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr"/>
@@ -2463,7 +2547,9 @@
         <is>
           <t>1. The three-dot download menu sits LEFTMOST in the toolbar's action cluster, with the Column Selection control immediately after it.
 2. The menu holds: "Download Summary (PDF)", "Download Expanded View (PDF)", and "Download (CSV)".
-3. The labels match exactly - only the expanded option carries the word "View" (the shipped strings, documented as-is).</t>
+3. The labels match exactly - only the expanded option carries the word "View" (the shipped strings, documented as-is).
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Technician Utilization report specification version 5 (S7-R1, S7-R2, S7-R3, S7-R4, S8-R2).</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
@@ -2510,12 +2596,14 @@
         <is>
           <t>1. The Summary PDF shows the technician rows and the Summary row (no day rows); it downloads as "Technician-Utilization-Summary.pdf".
 2. The Expanded PDF shows the technician rows, EACH technician's per-day breakdown, and the Summary row; it downloads as "Technician-Utilization-Expanded.pdf".
-3. The PDF filenames are Title-Case as shipped.</t>
+3. The PDF filenames are Title-Case as shipped.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Technician Utilization report specification version 5 (S7-R5, S7-R6, S7-R12).</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>SV-8654 (specs/technician-utilization.md S7-R5; S7-R6; S7-R12)</t>
+          <t>SV-8654 (TU spec v5 2026-07-29 S7-R5; S7-R6; S7-R12)</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr"/>
@@ -2558,12 +2646,14 @@
         <is>
           <t>1. The file downloads as "technician-utilization.csv" (lower-case as shipped, unlike the Title-Case PDFs).
 2. The CSV shows the technician rows and the Summary row - always this summary-level content; it does NOT vary by the summary/expanded choice (no day rows).
-3. Any value containing a comma (e.g. "$1,234.50") is wrapped in double quotes per standard CSV escaping, so the columns parse correctly.</t>
+3. Any value containing a comma (e.g. "$1,234.50") is wrapped in double quotes per standard CSV escaping, so the columns parse correctly.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Technician Utilization report specification version 5 (S7-R7, S7-R10, S7-R12).</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>SV-8654 (specs/technician-utilization.md S7-R7; S7-R10; S7-R12)</t>
+          <t>SV-8654 (TU spec v5 2026-07-29 S7-R7; S7-R10; S7-R12)</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr"/>
@@ -2611,7 +2701,9 @@
 3. With every technician selected, the download covers all technicians for the range at the selected location(s).
 4. Every download (each PDF and the CSV) carries a "Locations:" line naming the location(s) the report was scoped to (exact position in the file is confirmed in the build).
 5. Every download also mirrors the columns currently shown on screen — a column hidden in the Column Selection control is absent from the files, and a re-shown column comes back.
-6. Note for the tester: when you have more than one location in scope, the files also carry a Location column even though it is not in the Column Selection control. That is correct - it appears by itself. With a single location in scope there is no Location column, and that is also correct.</t>
+6. Note for the tester: when you have more than one location in scope, the files also carry a Location column even though it is not in the Column Selection control. That is correct - it appears by itself. With a single location in scope there is no Location column, and that is also correct.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Technician Utilization report specification version 5 (S7-R8, S7-R9, S7-R10, S7-R13, S7-E1, S9-R8).</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
@@ -2659,12 +2751,14 @@
       <c r="G46" s="2" t="inlineStr">
         <is>
           <t>1. The downloaded files use the same column order and number formats as the on-screen report, including the "—" rendering for an unknown Est. Lost Labor.
-2. Rows in EVERY download are ordered by Technician name A to Z (the default order) - the on-screen column sort is client-side only and is NOT carried into the export.</t>
+2. Rows in EVERY download are ordered by Technician name A to Z (the default order) - the on-screen column sort is client-side only and is NOT carried into the export.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Technician Utilization report specification version 5 (S7-R10, S7-R10a).</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>SV-8654 (specs/technician-utilization.md S7-R10; S7-R10a)</t>
+          <t>SV-8654 (TU spec v5 2026-07-29 S7-R10; S7-R10a)</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr"/>
@@ -2707,7 +2801,9 @@
         <is>
           <t>1. With an uploaded logo, BOTH PDF views show that logo at the top of the report.
 2. The CSV never includes the logo.
-3. With NO uploaded logo, the PDF views show the bundled ShopView logo instead — not a blank space and not an error.</t>
+3. With NO uploaded logo, the PDF views show the bundled ShopView logo instead — not a blank space and not an error.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Technician Utilization report specification version 5 (S7-R11, S7-N2, S7-N3).</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
@@ -2754,12 +2850,14 @@
       <c r="G48" s="2" t="inlineStr">
         <is>
           <t>1. Nothing happens: NO file downloads and NO message appears (not even an error).
-2. This silent no-op is the specified behavior for every download option when no technician is selected.</t>
+2. This silent no-op is the specified behavior for every download option when no technician is selected.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Technician Utilization report specification version 5 (S7-N1).</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>SV-8654 (specs/technician-utilization.md S7-N1; §7 context note)</t>
+          <t>SV-8654 (TU spec v5 2026-07-29 S7-N1; §7 context note)</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr"/>
@@ -2801,7 +2899,9 @@
       <c r="G49" s="2" t="inlineStr">
         <is>
           <t>1. When a download starts, a success notification reads exactly: "Download started".
-2. When a download fails, an error notification reads exactly: "Failed to download report".</t>
+2. When a download fails, an error notification reads exactly: "Failed to download report".
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Technician Utilization report specification version 5 (§7 notifications table, Story 7 has no S, §7 is the closing reference).</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
@@ -2851,12 +2951,15 @@
         <is>
           <t>1. Neither the CSV nor the PDF is produced — no download starts.
 2. A clear too-large message appears telling the user to narrow the date range or filters, then try again — the standard wording is "This report is too large to export. Narrow the date range or filters, then try again."
-3. After narrowing below the cap, the downloads work again.</t>
+3. After narrowing below the cap, the downloads work again.
+Known issue: the product does not currently do this. It has been filed for a fix here: https://shopview.atlassian.net/browse/SV-8818
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Technician Utilization report specification version 5 (Story 7 exports).</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>SV-8654 (specs/technician-utilization.md Story 7 exports — spec silent on a cap; tech-plan-2026-07-29 A3/FR-F4: suite-wide 10; 000-row export cap; locked by Chris 2026-07-21)</t>
+          <t>SV-8654 (TU spec v5 2026-07-29 Story 7 exports — spec silent on a cap; tech-plan-2026-07-29 A3/FR-F4: suite-wide 10; 000-row export cap; locked by Chris 2026-07-21)</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr"/>
@@ -2902,12 +3005,14 @@
           <t>1. The toolbar has a location filter labeled "Location" - a multi-select and the RIGHTMOST control.
 2. It lists the locations the signed-in user has access to, plus an "All locations" option and a "Clear all" action. (If you only have access to one location, the "All locations" entry is not offered - you see "Clear all" and your one location.)
 3. "All locations" acts as a select-all shortcut: choosing it selects every accessible location; unchecking one location leaves the remaining specific locations selected - the selection is always the concrete set of checked locations.
-4. With more than one location selected, a Location column appears in the table and each row names its location - or reads "Multiple" for a technician whose hours span more than one of them. (Where that column sits on screen is checked by its own test.)</t>
+4. With more than one location selected, a Location column appears in the table and each row names its location - or reads "Multiple" for a technician whose hours span more than one of them. (Where that column sits on screen is checked by its own test.)
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Technician Utilization report specification version 5 (S9-R1); where the wording of that specification differs, the behaviour above follows a later product decision, which is the authority.</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>SV-8656 (specs/technician-utilization.md S9-R1 — per-row location identifier in All-Locations view ADDED per kickoff video P10 40:58-41:20; user ruling 2026-07-28: video overrides spec (video newer; last-update-wins))</t>
+          <t>SV-8656 (TU spec v5 2026-07-29 S9-R1 — per-row location identifier in All-Locations view ADDED per kickoff video P10 40:58-41:20; user ruling 2026-07-28: video overrides spec (video newer; last-update-wins))</t>
         </is>
       </c>
       <c r="I51" s="2" t="inlineStr"/>
@@ -2954,12 +3059,14 @@
 2. All metrics (technician rows, per-day rows, and the Summary) reflect only clock records at the selected location(s).
 3. The technician's hours are POOLED across the selected locations into ONE row (one row per technician, not one per location); per-day rows pool the same way.
 4. Scoping never goes beyond the user's accessible locations - a location the user cannot access is never included.
-5. The page itself shows which location(s) the report is currently scoped to (the new on-screen scope indicator - exactly where and how it appears is confirmed in the build).</t>
+5. The page itself shows which location(s) the report is currently scoped to (the new on-screen scope indicator - exactly where and how it appears is confirmed in the build).
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Technician Utilization report specification version 5 (S9-R3, S9-R4, S9-R5).</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>SV-8656 (specs/technician-utilization.md S9-R3; S9-R4; S9-R5 + on-screen location-scope indicator per Chris Ward group message 2026-07-29 (chris-update-2026-07-29/chris-message-2026-07-29.md; NEWEST source; last-update-wins))</t>
+          <t>SV-8656 (TU spec v5 2026-07-29 S9-R3; S9-R4; S9-R5 + on-screen location-scope indicator per Chris Ward group message 2026-07-29 (chris-update-2026-07-29/chris-message-2026-07-29.md; NEWEST source; last-update-wins))</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr"/>
@@ -3001,12 +3108,14 @@
         <is>
           <t>1. Any saved location the user can no longer access is DROPPED from the restored selection; the remaining accessible locations restore normally.
 2. If the remaining set is empty, the report falls back to the user's currently active location (the first-visit default).
-3. The report loads without an error in both cases.</t>
+3. The report loads without an error in both cases.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Technician Utilization report specification version 5 (S9-R6, S1-R8, S9-R2).</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>SV-8656 (specs/technician-utilization.md S9-R6; S1-R8; S9-R2)</t>
+          <t>SV-8656 (TU spec v5 2026-07-29 S9-R6; S1-R8; S9-R2)</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr"/>
@@ -3047,12 +3156,14 @@
       <c r="G54" s="2" t="inlineStr">
         <is>
           <t>1. The report falls back to the user's currently active location rather than showing nothing.
-2. Rows for the active location load normally.</t>
+2. Rows for the active location load normally.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Technician Utilization report specification version 5 (S9-R7).</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>SV-8656 (specs/technician-utilization.md S9-R7)</t>
+          <t>SV-8656 (TU spec v5 2026-07-29 S9-R7)</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr"/>
@@ -3094,7 +3205,9 @@
       <c r="G55" s="2" t="inlineStr">
         <is>
           <t>1. For the single-location user the Location filter is NOT shown at all — the report simply shows that one location's data.
-2. For the user with access to two or more locations the Location filter IS shown.</t>
+2. For the user with access to two or more locations the Location filter IS shown.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Technician Utilization report specification version 5 (S9-N1); where the wording of that specification differs, the behaviour above follows a later product decision, which is the authority.</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
@@ -3142,8 +3255,7 @@
 5. Read the Location cell on the Summary row at the bottom.
 6. Open the Column Selection control and look for Location in the list.
 7. Narrow to a single location and read the headers again.
-8. Change the selection between one location, several, and "All Locations", watching the filter control's width.
-9. With more than one location still selected, download both PDF views and the CSV and read their columns from the left.</t>
+8. With more than one location still selected, download both PDF views and the CSV and read their columns from the left.</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
@@ -3155,8 +3267,9 @@
 5. The Summary row leaves the Location cell blank.
 6. Location is never listed in the Column Selection control — it follows the location scope on its own.
 7. With a single location in scope the Location column is hidden.
-8. The Location filter control keeps the same width whichever label it shows — one location, several, or "All locations" — so the toolbar does not shift as you change the selection.
-9. Every download — both PDF views and the CSV — includes the Location column in its on-screen leftmost position, carrying the same values you just read on screen.</t>
+8. Every download — both PDF views and the CSV — includes the Location column in its on-screen leftmost position, carrying the same values you just read on screen.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Technician Utilization report specification version 5 (S9-R9, S9-R10, S8-R15, S10-R4, S7-R13).</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
@@ -3191,7 +3304,8 @@
       <c r="E57" s="2" t="inlineStr">
         <is>
           <t>1. You are on the Technician Utilization report with rows loaded.
-2. This browser has never saved settings for this report (fresh visit), so every column is at its default.</t>
+2. This browser has never saved settings for this report (fresh visit), so every column is at its default.
+3. Part of this test checks what a blind user would hear, so you need a screen reader. On Windows install NVDA — it is free, from nvaccess.org. On a Mac use VoiceOver, which is already built in (Cmd+F5 turns it on and off). Alternatively the browser's developer tools (F12) have an "Accessibility" panel that shows the same names without you having to listen to anything.</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
@@ -3214,7 +3328,9 @@
 5. The Location column is never listed here — it appears on its own whenever more than one location is in scope.
 6. Turning a toggle off hides that column (header and cells) immediately, with no reload; turning it back on returns it to its usual place in the fixed left-to-right order — the remaining columns never reorder.
 7. Est. Lost Labor can now be hidden like any other column (it used to be always on).
-8. Your column choice is remembered in this browser and is still applied when you come back.</t>
+8. Your column choice is remembered in this browser and is still applied when you come back.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Technician Utilization report specification version 5 (S10-R1, S10-R2, S10-R3, S10-R4, S10-R5, S10-R6, S8-R16).</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
@@ -3262,7 +3378,9 @@
         <is>
           <t>1. The report uses an all-white table: white column headers and white data cells, with NO alternating row shading.
 2. The toolbar controls run, left to right: the three-dot download menu, the Column Selection control, the date-range picker, the technician filter, and the Location filter (rightmost).
-3. The expand/collapse-all control is NOT a toolbar control - it lives in the table header (in the Technician column).</t>
+3. The expand/collapse-all control is NOT a toolbar control - it lives in the table header (in the Technician column).
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Technician Utilization report specification version 5 (S8-R1, S8-R2, S8-R3).</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
@@ -3313,7 +3431,9 @@
           <t>1. The report supports dark mode: page background, toolbar, cells, the Total Hours link, the information icon, the sort indicator, and the "—" glyph are all clearly legible in dark mode.
 2. In BOTH light mode and dark mode the information icon is clearly visible against the background behind it - you can see it at a glance and it does not disappear into the background.
 3. The Total Hours link's non-color affordance and focus indicator apply in both modes.
-4. Note for the tester: you do not need to measure anything and you do not need any tool. Just say whether you can see the icon easily in both modes, and only report it if you cannot. (The design rule behind this is a minimum 3:1 contrast ratio, which the design and engineering team check with a contrast tool - not by hand.)</t>
+4. Note for the tester: you do not need to measure anything and you do not need any tool. Just say whether you can see the icon easily in both modes, and only report it if you cannot. (The design rule behind this is a minimum 3:1 contrast ratio, which the design and engineering team check with a contrast tool - not by hand.)
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Technician Utilization report specification version 5 (S8-R9, S8-R13, S8-R14).</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
@@ -3347,7 +3467,8 @@
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>1. You are on the Technician Utilization report with rows loaded and browser devtools (network tab) open.</t>
+          <t>1. You are on the Technician Utilization report with rows loaded and browser devtools (network tab) open.
+2. To see the information this test asks for you need the browser's own developer tools: press F12 (or Ctrl+Shift+I; on a Mac Cmd+Option+I) and open the "Network" tab, then reload the page. There is nothing to install — it is built into Chrome, Edge and Firefox.</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
@@ -3361,12 +3482,14 @@
         <is>
           <t>1. The initial report payload does NOT ship the day rows.
 2. Expanding a technician row issues an on-demand backend request that returns that technician's per-day breakdown.
-3. Because expansion state resets (all collapsed) on any data reload, nothing is lost by the lazy loading - re-expanding fetches fresh day data.</t>
+3. Because expansion state resets (all collapsed) on any data reload, nothing is lost by the lazy loading - re-expanding fetches fresh day data.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Technician Utilization report specification version 5 (S4-R2, S4-R5).</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>SV-8651 (specs/technician-utilization.md S4-R2; S4-R5)</t>
+          <t>SV-8651 (TU spec v5 2026-07-29 S4-R2; S4-R5)</t>
         </is>
       </c>
       <c r="I60" s="2" t="inlineStr"/>
@@ -3395,7 +3518,8 @@
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>1. You are on the Technician Utilization report with rows loaded and browser devtools (network tab) open.</t>
+          <t>1. You are on the Technician Utilization report with rows loaded and browser devtools (network tab) open.
+2. To see the information this test asks for you need the browser's own developer tools: press F12 (or Ctrl+Shift+I; on a Mac Cmd+Option+I) and open the "Network" tab, then reload the page. There is nothing to install — it is built into Chrome, Edge and Firefox.</t>
         </is>
       </c>
       <c r="F61" s="2" t="inlineStr">
@@ -3411,12 +3535,14 @@
           <t>1. A date-range change triggers a fresh server load of the rows.
 2. A location change triggers a fresh server load scoped to the selected set.
 3. The technician filter causes NO server request - it works on screen only (hide/show + Summary recalculation).
-4. Column sorting causes NO server request - it is applied on screen to the loaded rows.</t>
+4. Column sorting causes NO server request - it is applied on screen to the loaded rows.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Technician Utilization report specification version 5 (S1-R5, S9-R3, S2-R13).</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>SV-8648 (specs/technician-utilization.md S1-R5; S9-R3; S5 context note; S2-R13; §3)</t>
+          <t>SV-8648 (TU spec v5 2026-07-29 S1-R5; S9-R3; S5 context note; S2-R13; §3)</t>
         </is>
       </c>
       <c r="I61" s="2" t="inlineStr"/>

--- a/testrail-import/Report-Suite_Technician-Utilization-Report_testrail-import.xlsx
+++ b/testrail-import/Report-Suite_Technician-Utilization-Report_testrail-import.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J61"/>
+  <dimension ref="A1:J60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
@@ -2549,6 +2549,8 @@
 2. The menu holds: "Download Summary (PDF)", "Download Expanded View (PDF)", and "Download (CSV)".
 3. The labels match exactly - only the expanded option carries the word "View" (the shipped strings, documented as-is).
 ---
+DO NOT AUTOMATE YET: this behaviour is waiting on an answer from the product owner. Automating it now could lock in the wrong behaviour.
+The open question is in: Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx — https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/chris-consolidated-2026-08-04/Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx
 This is the expected behaviour as per the build tested on 8/4/2026, and as per the Technician Utilization report specification version 5 (S7-R1, S7-R2, S7-R3, S7-R4, S8-R2).</t>
         </is>
       </c>
@@ -2598,6 +2600,8 @@
 2. The Expanded PDF shows the technician rows, EACH technician's per-day breakdown, and the Summary row; it downloads as "Technician-Utilization-Expanded.pdf".
 3. The PDF filenames are Title-Case as shipped.
 ---
+DO NOT AUTOMATE YET: this behaviour is waiting on an answer from the product owner. Automating it now could lock in the wrong behaviour.
+The open question is in: Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx — https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/chris-consolidated-2026-08-04/Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx
 This is the expected behaviour as per the build tested on 8/4/2026, and as per the Technician Utilization report specification version 5 (S7-R5, S7-R6, S7-R12).</t>
         </is>
       </c>
@@ -2803,6 +2807,8 @@
 2. The CSV never includes the logo.
 3. With NO uploaded logo, the PDF views show the bundled ShopView logo instead — not a blank space and not an error.
 ---
+DO NOT AUTOMATE YET: this behaviour is waiting on an answer from the product owner. Automating it now could lock in the wrong behaviour.
+The open question is in: Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx — https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/chris-consolidated-2026-08-04/Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx
 This is the expected behaviour as per the build tested on 8/4/2026, and as per the Technician Utilization report specification version 5 (S7-R11, S7-N2, S7-N3).</t>
         </is>
       </c>
@@ -2852,6 +2858,8 @@
           <t>1. Nothing happens: NO file downloads and NO message appears (not even an error).
 2. This silent no-op is the specified behavior for every download option when no technician is selected.
 ---
+DO NOT AUTOMATE YET: this behaviour is waiting on an answer from the product owner. Automating it now could lock in the wrong behaviour.
+The open question is in: Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx — https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/chris-consolidated-2026-08-04/Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx
 This is the expected behaviour as per the build tested on 8/4/2026, and as per the Technician Utilization report specification version 5 (S7-N1).</t>
         </is>
       </c>
@@ -3109,13 +3117,14 @@
           <t>1. Any saved location the user can no longer access is DROPPED from the restored selection; the remaining accessible locations restore normally.
 2. If the remaining set is empty, the report falls back to the user's currently active location (the first-visit default).
 3. The report loads without an error in both cases.
----
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Technician Utilization report specification version 5 (S9-R6, S1-R8, S9-R2).</t>
+4. The same fallback happens when you deselect every location by hand in the Location filter — the report loads the currently active location's rows rather than showing nothing.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Technician Utilization report specification version 5 (S9-R6, S1-R8, S9-R2, S9-R7).</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>SV-8656 (TU spec v5 2026-07-29 S9-R6; S1-R8; S9-R2)</t>
+          <t>SV-8656 (TU spec v5 2026-07-29 S9-R6; S1-R8; S9-R2; S9-R7)</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr"/>
@@ -3124,7 +3133,7 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>Deselecting every location falls back to the active location</t>
+          <t>Technician Utilization: Location filter hidden for a one-location user</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
@@ -3134,36 +3143,39 @@
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>Negative</t>
+          <t>Functional</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>1. You are on the Technician Utilization report with at least one location selected.</t>
+          <t>1. You are signed in as a user with access to exactly one location.
+2. You are on the Technician Utilization report.</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>1. In the Location filter, deselect every location (empty the filter).
-2. Watch what the report loads.</t>
+          <t>1. Look for the Location filter in the toolbar.
+2. Then sign in as a user with access to two or more locations and look again.</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>1. The report falls back to the user's currently active location rather than showing nothing.
-2. Rows for the active location load normally.
----
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Technician Utilization report specification version 5 (S9-R7).</t>
+          <t>1. For the single-location user the Location filter is NOT shown at all — the report simply shows that one location's data.
+2. For the user with access to two or more locations the Location filter IS shown.
+---
+DO NOT AUTOMATE YET: this behaviour is waiting on an answer from the product owner. Automating it now could lock in the wrong behaviour.
+The open question is in: Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx — https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/chris-consolidated-2026-08-04/Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Technician Utilization report specification version 5 (S9-N1); where the wording of that specification differs, the behaviour above follows a later product decision, which is the authority.</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>SV-8656 (TU spec v5 2026-07-29 S9-R7)</t>
+          <t>SV-8656 (TU spec S9-N1 — RULED HIDDEN by Chris Ward answer 2026-07-31 Q1=A "classic spec drift"; the S9-N1 "still sees the filter" note is stale; spec edit pending)</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr"/>
@@ -3172,7 +3184,7 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>Technician Utilization: Location filter hidden for a one-location user</t>
+          <t>The Location column shows only with more than one location; Summary row blank</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
@@ -3187,66 +3199,17 @@
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
-        <is>
-          <t>1. You are signed in as a user with access to exactly one location.
-2. You are on the Technician Utilization report.</t>
-        </is>
-      </c>
-      <c r="F55" s="2" t="inlineStr">
-        <is>
-          <t>1. Look for the Location filter in the toolbar.
-2. Then sign in as a user with access to two or more locations and look again.</t>
-        </is>
-      </c>
-      <c r="G55" s="2" t="inlineStr">
-        <is>
-          <t>1. For the single-location user the Location filter is NOT shown at all — the report simply shows that one location's data.
-2. For the user with access to two or more locations the Location filter IS shown.
----
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Technician Utilization report specification version 5 (S9-N1); where the wording of that specification differs, the behaviour above follows a later product decision, which is the authority.</t>
-        </is>
-      </c>
-      <c r="H55" s="2" t="inlineStr">
-        <is>
-          <t>SV-8656 (TU spec S9-N1 — RULED HIDDEN by Chris Ward answer 2026-07-31 Q1=A "classic spec drift"; the S9-N1 "still sees the filter" note is stale; spec edit pending)</t>
-        </is>
-      </c>
-      <c r="I55" s="2" t="inlineStr"/>
-      <c r="J55" s="2" t="inlineStr"/>
-    </row>
-    <row r="56">
-      <c r="A56" s="2" t="inlineStr">
-        <is>
-          <t>The Location column shows only with more than one location; Summary row blank</t>
-        </is>
-      </c>
-      <c r="B56" s="2" t="inlineStr">
-        <is>
-          <t>TU — Location Filter</t>
-        </is>
-      </c>
-      <c r="C56" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D56" s="2" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="E56" s="2" t="inlineStr">
         <is>
           <t>1. You are on the Technician Utilization report as a user with access to two or more locations.
 2. One technician clocked time at a single location in the range and another clocked time at two different locations.
 3. One of those days has hours at two locations (for the per-day check).</t>
         </is>
       </c>
-      <c r="F56" s="2" t="inlineStr">
+      <c r="F55" s="2" t="inlineStr">
         <is>
           <t>1. Select two or more locations and read the column headers from the left.
 2. Read the Location cell on the single-location technician's row.
@@ -3258,7 +3221,7 @@
 8. With more than one location still selected, download both PDF views and the CSV and read their columns from the left.</t>
         </is>
       </c>
-      <c r="G56" s="2" t="inlineStr">
+      <c r="G55" s="2" t="inlineStr">
         <is>
           <t>1. With more than one location in scope a Location column is shown as the LEFTMOST column, before Technician.
 2. A technician whose hours were all clocked at one location shows that location's name.
@@ -3272,43 +3235,43 @@
 This is the expected behaviour as per the build tested on 8/4/2026, and as per the Technician Utilization report specification version 5 (S9-R9, S9-R10, S8-R15, S10-R4, S7-R13).</t>
         </is>
       </c>
-      <c r="H56" s="2" t="inlineStr">
+      <c r="H55" s="2" t="inlineStr">
         <is>
           <t>SV-8656; SV-8654 (TU spec v5 2026-07-29 S9-R9; S9-R10; S8-R15; S10-R4; S7-R13 — per-row Location column; leftmost before Technician; "Multiple" on a spanning row; Summary row blank; not in the selector; S7-R13 = same column in every download)</t>
         </is>
       </c>
-      <c r="I56" s="2" t="inlineStr"/>
-      <c r="J56" s="2" t="inlineStr"/>
-    </row>
-    <row r="57">
-      <c r="A57" s="2" t="inlineStr">
+      <c r="I55" s="2" t="inlineStr"/>
+      <c r="J55" s="2" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
         <is>
           <t>Column Selection: Technician always on, the other five toggleable, remembered</t>
         </is>
       </c>
-      <c r="B57" s="2" t="inlineStr">
+      <c r="B56" s="2" t="inlineStr">
         <is>
           <t>TU — Visual &amp; Accessibility</t>
         </is>
       </c>
-      <c r="C57" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D57" s="2" t="inlineStr">
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E57" s="2" t="inlineStr">
+      <c r="E56" s="2" t="inlineStr">
         <is>
           <t>1. You are on the Technician Utilization report with rows loaded.
 2. This browser has never saved settings for this report (fresh visit), so every column is at its default.
 3. Part of this test checks what a blind user would hear, so you need a screen reader. On Windows install NVDA — it is free, from nvaccess.org. On a Mac use VoiceOver, which is already built in (Cmd+F5 turns it on and off). Alternatively the browser's developer tools (F12) have an "Accessibility" panel that shows the same names without you having to listen to anything.</t>
         </is>
       </c>
-      <c r="F57" s="2" t="inlineStr">
+      <c r="F56" s="2" t="inlineStr">
         <is>
           <t>1. Find the column-selection button in the toolbar and hover it to read its tooltip.
 2. With the button focused, read the name assistive technology gives it — use the browser's accessibility inspector or a screen reader.
@@ -3319,7 +3282,7 @@
 7. Reload the page, then close the browser, reopen it and return to the report.</t>
         </is>
       </c>
-      <c r="G57" s="2" t="inlineStr">
+      <c r="G56" s="2" t="inlineStr">
         <is>
           <t>1. The control is an icon button whose tooltip reads "Column Selection", sitting immediately after the three-dot download menu in the toolbar.
 2. Because the button shows an icon and no text, it still carries a name that assistive technology reads out — it is not left unnamed. (The exact wording is confirmed in the build.)
@@ -3333,48 +3296,48 @@
 This is the expected behaviour as per the build tested on 8/4/2026, and as per the Technician Utilization report specification version 5 (S10-R1, S10-R2, S10-R3, S10-R4, S10-R5, S10-R6, S8-R16).</t>
         </is>
       </c>
-      <c r="H57" s="2" t="inlineStr">
+      <c r="H56" s="2" t="inlineStr">
         <is>
           <t>SV-8655; SV-8582 (TU spec v5 2026-07-29 Story 10 S10-R1; S10-R2; S10-R3; S10-R4; S10-R5; S10-R6 column selector + Story 8 S8-R16 accessible name — Story 10 has NO owning Jira story so epic SV-8582 is used and FLAGGED; S8-R16 is owned by SV-8655)</t>
         </is>
       </c>
-      <c r="I57" s="2" t="inlineStr"/>
-      <c r="J57" s="2" t="inlineStr"/>
-    </row>
-    <row r="58">
-      <c r="A58" s="2" t="inlineStr">
+      <c r="I56" s="2" t="inlineStr"/>
+      <c r="J56" s="2" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
         <is>
           <t>All-white table with no row shading; toolbar controls in the fixed order</t>
         </is>
       </c>
-      <c r="B58" s="2" t="inlineStr">
+      <c r="B57" s="2" t="inlineStr">
         <is>
           <t>TU — Visual &amp; Accessibility</t>
         </is>
       </c>
-      <c r="C58" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D58" s="2" t="inlineStr">
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E58" s="2" t="inlineStr">
+      <c r="E57" s="2" t="inlineStr">
         <is>
           <t>1. You are on the Technician Utilization report with rows loaded, in light mode.</t>
         </is>
       </c>
-      <c r="F58" s="2" t="inlineStr">
+      <c r="F57" s="2" t="inlineStr">
         <is>
           <t>1. Look at the column headers and the data rows' backgrounds.
 2. Read the toolbar controls left to right.
 3. Look for the expand/collapse-all control's position.</t>
         </is>
       </c>
-      <c r="G58" s="2" t="inlineStr">
+      <c r="G57" s="2" t="inlineStr">
         <is>
           <t>1. The report uses an all-white table: white column headers and white data cells, with NO alternating row shading.
 2. The toolbar controls run, left to right: the three-dot download menu, the Column Selection control, the date-range picker, the technician filter, and the Location filter (rightmost).
@@ -3383,42 +3346,42 @@
 This is the expected behaviour as per the build tested on 8/4/2026, and as per the Technician Utilization report specification version 5 (S8-R1, S8-R2, S8-R3).</t>
         </is>
       </c>
-      <c r="H58" s="2" t="inlineStr">
+      <c r="H57" s="2" t="inlineStr">
         <is>
           <t>SV-8655 (TU spec v5 2026-07-29 S8-R1; S8-R2; S8-R3 — toolbar order rewritten: Column Selection inserted after the three-dot menu; and the date-range picker now precedes the technician filter)</t>
         </is>
       </c>
-      <c r="I58" s="2" t="inlineStr"/>
-      <c r="J58" s="2" t="inlineStr"/>
-    </row>
-    <row r="59">
-      <c r="A59" s="2" t="inlineStr">
+      <c r="I57" s="2" t="inlineStr"/>
+      <c r="J57" s="2" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
         <is>
           <t>Dark mode keeps every report element legible</t>
         </is>
       </c>
-      <c r="B59" s="2" t="inlineStr">
+      <c r="B58" s="2" t="inlineStr">
         <is>
           <t>TU — Visual &amp; Accessibility</t>
         </is>
       </c>
-      <c r="C59" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D59" s="2" t="inlineStr">
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="E59" s="2" t="inlineStr">
+      <c r="E58" s="2" t="inlineStr">
         <is>
           <t>1. You are on the Technician Utilization report with rows loaded, including a "—" Est. Lost Labor cell.
 2. Dark mode is available in the application.</t>
         </is>
       </c>
-      <c r="F59" s="2" t="inlineStr">
+      <c r="F58" s="2" t="inlineStr">
         <is>
           <t>1. Switch the application to dark mode.
 2. Check each element: page background, toolbar, cells, the Total Hours link, the information icon, the sort indicator, and a "—" glyph.
@@ -3426,7 +3389,7 @@
 4. Check the Total Hours link's underline/affordance and focus indicator in both modes.</t>
         </is>
       </c>
-      <c r="G59" s="2" t="inlineStr">
+      <c r="G58" s="2" t="inlineStr">
         <is>
           <t>1. The report supports dark mode: page background, toolbar, cells, the Total Hours link, the information icon, the sort indicator, and the "—" glyph are all clearly legible in dark mode.
 2. In BOTH light mode and dark mode the information icon is clearly visible against the background behind it - you can see it at a glance and it does not disappear into the background.
@@ -3436,49 +3399,49 @@
 This is the expected behaviour as per the build tested on 8/4/2026, and as per the Technician Utilization report specification version 5 (S8-R9, S8-R13, S8-R14).</t>
         </is>
       </c>
-      <c r="H59" s="2" t="inlineStr">
+      <c r="H58" s="2" t="inlineStr">
         <is>
           <t>SV-8655 (TU spec v5 2026-07-29 S8-R9; S8-R13; S8-R14 — dark-mode legibility of every named element; the info icon at ≥ 3:1 in both modes; the Total Hours link affordance/focus in both modes; the ratio is design-token-owned)</t>
         </is>
       </c>
-      <c r="I59" s="2" t="inlineStr"/>
-      <c r="J59" s="2" t="inlineStr"/>
-    </row>
-    <row r="60">
-      <c r="A60" s="2" t="inlineStr">
+      <c r="I58" s="2" t="inlineStr"/>
+      <c r="J58" s="2" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
         <is>
           <t>The per-day breakdown is fetched only when a technician row is expanded</t>
         </is>
       </c>
-      <c r="B60" s="2" t="inlineStr">
+      <c r="B59" s="2" t="inlineStr">
         <is>
           <t>TU — API</t>
         </is>
       </c>
-      <c r="C60" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D60" s="2" t="inlineStr">
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E60" s="2" t="inlineStr">
+      <c r="E59" s="2" t="inlineStr">
         <is>
           <t>1. You are on the Technician Utilization report with rows loaded and browser devtools (network tab) open.
 2. To see the information this test asks for you need the browser's own developer tools: press F12 (or Ctrl+Shift+I; on a Mac Cmd+Option+I) and open the "Network" tab, then reload the page. There is nothing to install — it is built into Chrome, Edge and Firefox.</t>
         </is>
       </c>
-      <c r="F60" s="2" t="inlineStr">
+      <c r="F59" s="2" t="inlineStr">
         <is>
           <t>1. Load the report and inspect the initial data response for per-day content.
 2. Expand a technician row and watch the network traffic.
 3. Collapse and re-expand after a data reload.</t>
         </is>
       </c>
-      <c r="G60" s="2" t="inlineStr">
+      <c r="G59" s="2" t="inlineStr">
         <is>
           <t>1. The initial report payload does NOT ship the day rows.
 2. Expanding a technician row issues an on-demand backend request that returns that technician's per-day breakdown.
@@ -3487,42 +3450,42 @@
 This is the expected behaviour as per the build tested on 8/4/2026, and as per the Technician Utilization report specification version 5 (S4-R2, S4-R5).</t>
         </is>
       </c>
-      <c r="H60" s="2" t="inlineStr">
+      <c r="H59" s="2" t="inlineStr">
         <is>
           <t>SV-8651 (TU spec v5 2026-07-29 S4-R2; S4-R5)</t>
         </is>
       </c>
-      <c r="I60" s="2" t="inlineStr"/>
-      <c r="J60" s="2" t="inlineStr"/>
-    </row>
-    <row r="61">
-      <c r="A61" s="2" t="inlineStr">
+      <c r="I59" s="2" t="inlineStr"/>
+      <c r="J59" s="2" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
         <is>
           <t>Date-range and location changes trigger a fresh server load</t>
         </is>
       </c>
-      <c r="B61" s="2" t="inlineStr">
+      <c r="B60" s="2" t="inlineStr">
         <is>
           <t>TU — API</t>
         </is>
       </c>
-      <c r="C61" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D61" s="2" t="inlineStr">
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E61" s="2" t="inlineStr">
+      <c r="E60" s="2" t="inlineStr">
         <is>
           <t>1. You are on the Technician Utilization report with rows loaded and browser devtools (network tab) open.
 2. To see the information this test asks for you need the browser's own developer tools: press F12 (or Ctrl+Shift+I; on a Mac Cmd+Option+I) and open the "Network" tab, then reload the page. There is nothing to install — it is built into Chrome, Edge and Firefox.</t>
         </is>
       </c>
-      <c r="F61" s="2" t="inlineStr">
+      <c r="F60" s="2" t="inlineStr">
         <is>
           <t>1. Change the date range and watch the network traffic.
 2. Change the location selection and watch the traffic.
@@ -3530,7 +3493,7 @@
 4. Click several column headers to sort and watch the traffic.</t>
         </is>
       </c>
-      <c r="G61" s="2" t="inlineStr">
+      <c r="G60" s="2" t="inlineStr">
         <is>
           <t>1. A date-range change triggers a fresh server load of the rows.
 2. A location change triggers a fresh server load scoped to the selected set.
@@ -3540,13 +3503,13 @@
 This is the expected behaviour as per the build tested on 8/4/2026, and as per the Technician Utilization report specification version 5 (S1-R5, S9-R3, S2-R13).</t>
         </is>
       </c>
-      <c r="H61" s="2" t="inlineStr">
+      <c r="H60" s="2" t="inlineStr">
         <is>
           <t>SV-8648 (TU spec v5 2026-07-29 S1-R5; S9-R3; S5 context note; S2-R13; §3)</t>
         </is>
       </c>
-      <c r="I61" s="2" t="inlineStr"/>
-      <c r="J61" s="2" t="inlineStr"/>
+      <c r="I60" s="2" t="inlineStr"/>
+      <c r="J60" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/testrail-import/Report-Suite_Technician-Utilization-Report_testrail-import.xlsx
+++ b/testrail-import/Report-Suite_Technician-Utilization-Report_testrail-import.xlsx
@@ -2549,8 +2549,6 @@
 2. The menu holds: "Download Summary (PDF)", "Download Expanded View (PDF)", and "Download (CSV)".
 3. The labels match exactly - only the expanded option carries the word "View" (the shipped strings, documented as-is).
 ---
-DO NOT AUTOMATE YET: this behaviour is waiting on an answer from the product owner. Automating it now could lock in the wrong behaviour.
-The open question is in: Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx — https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/chris-consolidated-2026-08-04/Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx
 This is the expected behaviour as per the build tested on 8/4/2026, and as per the Technician Utilization report specification version 5 (S7-R1, S7-R2, S7-R3, S7-R4, S8-R2).</t>
         </is>
       </c>
@@ -2600,8 +2598,6 @@
 2. The Expanded PDF shows the technician rows, EACH technician's per-day breakdown, and the Summary row; it downloads as "Technician-Utilization-Expanded.pdf".
 3. The PDF filenames are Title-Case as shipped.
 ---
-DO NOT AUTOMATE YET: this behaviour is waiting on an answer from the product owner. Automating it now could lock in the wrong behaviour.
-The open question is in: Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx — https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/chris-consolidated-2026-08-04/Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx
 This is the expected behaviour as per the build tested on 8/4/2026, and as per the Technician Utilization report specification version 5 (S7-R5, S7-R6, S7-R12).</t>
         </is>
       </c>
@@ -2807,8 +2803,6 @@
 2. The CSV never includes the logo.
 3. With NO uploaded logo, the PDF views show the bundled ShopView logo instead — not a blank space and not an error.
 ---
-DO NOT AUTOMATE YET: this behaviour is waiting on an answer from the product owner. Automating it now could lock in the wrong behaviour.
-The open question is in: Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx — https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/chris-consolidated-2026-08-04/Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx
 This is the expected behaviour as per the build tested on 8/4/2026, and as per the Technician Utilization report specification version 5 (S7-R11, S7-N2, S7-N3).</t>
         </is>
       </c>
@@ -2858,8 +2852,6 @@
           <t>1. Nothing happens: NO file downloads and NO message appears (not even an error).
 2. This silent no-op is the specified behavior for every download option when no technician is selected.
 ---
-DO NOT AUTOMATE YET: this behaviour is waiting on an answer from the product owner. Automating it now could lock in the wrong behaviour.
-The open question is in: Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx — https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/chris-consolidated-2026-08-04/Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx
 This is the expected behaviour as per the build tested on 8/4/2026, and as per the Technician Utilization report specification version 5 (S7-N1).</t>
         </is>
       </c>
@@ -3117,14 +3109,13 @@
           <t>1. Any saved location the user can no longer access is DROPPED from the restored selection; the remaining accessible locations restore normally.
 2. If the remaining set is empty, the report falls back to the user's currently active location (the first-visit default).
 3. The report loads without an error in both cases.
-4. The same fallback happens when you deselect every location by hand in the Location filter — the report loads the currently active location's rows rather than showing nothing.
----
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Technician Utilization report specification version 5 (S9-R6, S1-R8, S9-R2, S9-R7).</t>
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Technician Utilization report specification version 5 (S9-R6, S1-R8, S9-R2).</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>SV-8656 (TU spec v5 2026-07-29 S9-R6; S1-R8; S9-R2; S9-R7)</t>
+          <t>SV-8656 (TU spec v5 2026-07-29 S9-R6; S1-R8; S9-R2)</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr"/>
@@ -3168,8 +3159,6 @@
           <t>1. For the single-location user the Location filter is NOT shown at all — the report simply shows that one location's data.
 2. For the user with access to two or more locations the Location filter IS shown.
 ---
-DO NOT AUTOMATE YET: this behaviour is waiting on an answer from the product owner. Automating it now could lock in the wrong behaviour.
-The open question is in: Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx — https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/chris-consolidated-2026-08-04/Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx
 This is the expected behaviour as per the build tested on 8/4/2026, and as per the Technician Utilization report specification version 5 (S9-N1); where the wording of that specification differs, the behaviour above follows a later product decision, which is the authority.</t>
         </is>
       </c>

--- a/testrail-import/Report-Suite_Technician-Utilization-Report_testrail-import.xlsx
+++ b/testrail-import/Report-Suite_Technician-Utilization-Report_testrail-import.xlsx
@@ -2549,6 +2549,8 @@
 2. The menu holds: "Download Summary (PDF)", "Download Expanded View (PDF)", and "Download (CSV)".
 3. The labels match exactly - only the expanded option carries the word "View" (the shipped strings, documented as-is).
 ---
+DO NOT AUTOMATE YET: this behaviour is waiting on an answer from the product owner. Automating it now could lock in the wrong behaviour.
+The open question is in: Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx — https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/chris-consolidated-2026-08-04/Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx
 This is the expected behaviour as per the build tested on 8/4/2026, and as per the Technician Utilization report specification version 5 (S7-R1, S7-R2, S7-R3, S7-R4, S8-R2).</t>
         </is>
       </c>
@@ -2598,6 +2600,8 @@
 2. The Expanded PDF shows the technician rows, EACH technician's per-day breakdown, and the Summary row; it downloads as "Technician-Utilization-Expanded.pdf".
 3. The PDF filenames are Title-Case as shipped.
 ---
+DO NOT AUTOMATE YET: this behaviour is waiting on an answer from the product owner. Automating it now could lock in the wrong behaviour.
+The open question is in: Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx — https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/chris-consolidated-2026-08-04/Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx
 This is the expected behaviour as per the build tested on 8/4/2026, and as per the Technician Utilization report specification version 5 (S7-R5, S7-R6, S7-R12).</t>
         </is>
       </c>
@@ -2803,6 +2807,8 @@
 2. The CSV never includes the logo.
 3. With NO uploaded logo, the PDF views show the bundled ShopView logo instead — not a blank space and not an error.
 ---
+DO NOT AUTOMATE YET: this behaviour is waiting on an answer from the product owner. Automating it now could lock in the wrong behaviour.
+The open question is in: Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx — https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/chris-consolidated-2026-08-04/Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx
 This is the expected behaviour as per the build tested on 8/4/2026, and as per the Technician Utilization report specification version 5 (S7-R11, S7-N2, S7-N3).</t>
         </is>
       </c>
@@ -2852,6 +2858,8 @@
           <t>1. Nothing happens: NO file downloads and NO message appears (not even an error).
 2. This silent no-op is the specified behavior for every download option when no technician is selected.
 ---
+DO NOT AUTOMATE YET: this behaviour is waiting on an answer from the product owner. Automating it now could lock in the wrong behaviour.
+The open question is in: Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx — https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/chris-consolidated-2026-08-04/Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx
 This is the expected behaviour as per the build tested on 8/4/2026, and as per the Technician Utilization report specification version 5 (S7-N1).</t>
         </is>
       </c>
@@ -3109,13 +3117,14 @@
           <t>1. Any saved location the user can no longer access is DROPPED from the restored selection; the remaining accessible locations restore normally.
 2. If the remaining set is empty, the report falls back to the user's currently active location (the first-visit default).
 3. The report loads without an error in both cases.
----
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Technician Utilization report specification version 5 (S9-R6, S1-R8, S9-R2).</t>
+4. The same fallback happens when you deselect every location by hand in the Location filter — the report loads the currently active location's rows rather than showing nothing.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Technician Utilization report specification version 5 (S9-R6, S1-R8, S9-R2, S9-R7).</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>SV-8656 (TU spec v5 2026-07-29 S9-R6; S1-R8; S9-R2)</t>
+          <t>SV-8656 (TU spec v5 2026-07-29 S9-R6; S1-R8; S9-R2; S9-R7)</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr"/>
@@ -3159,6 +3168,8 @@
           <t>1. For the single-location user the Location filter is NOT shown at all — the report simply shows that one location's data.
 2. For the user with access to two or more locations the Location filter IS shown.
 ---
+DO NOT AUTOMATE YET: this behaviour is waiting on an answer from the product owner. Automating it now could lock in the wrong behaviour.
+The open question is in: Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx — https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/chris-consolidated-2026-08-04/Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx
 This is the expected behaviour as per the build tested on 8/4/2026, and as per the Technician Utilization report specification version 5 (S9-N1); where the wording of that specification differs, the behaviour above follows a later product decision, which is the authority.</t>
         </is>
       </c>

--- a/testrail-import/Report-Suite_Technician-Utilization-Report_testrail-import.xlsx
+++ b/testrail-import/Report-Suite_Technician-Utilization-Report_testrail-import.xlsx
@@ -527,7 +527,7 @@
 2. Clicking it opens the report.
 3. The entry sits BELOW the pre-existing report links — Sales, Technician Efficiency, Advisor Analysis, Shop Efficiency — the new reports are added below those items without moving or disturbing them.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Technician Utilization report specification version 5 (S1-R1).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Technician Utilization report specification version 5 (S1-R1).</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
@@ -576,7 +576,7 @@
           <t>1. Technician A has exactly ONE row.
 2. Technician B has NO row - only technicians with clocked time in the selected range at the selected location(s) appear.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Technician Utilization report specification version 5 (S1-R2).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Technician Utilization report specification version 5 (S1-R2).</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
@@ -625,7 +625,7 @@
 2. Because a range never extends past now, the current-month default effectively shows the month to date.
 3. The location filter defaults to the user's currently active location (the one in the application's global location switcher).
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Technician Utilization report specification version 5 (S1-R3, S1-R6, S9-R2).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Technician Utilization report specification version 5 (S1-R3, S1-R6, S9-R2).</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -675,7 +675,7 @@
 2. A valid Custom range applies normally.
 3. A Custom span wider than 366 days (matching the largest preset) is rejected - it cannot be applied.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Technician Utilization report specification version 5 (S1-R4, S1-R5).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Technician Utilization report specification version 5 (S1-R4, S1-R5).</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -725,7 +725,7 @@
 2. The existing rows are replaced only when the new data returns.
 3. The toolbar remains interactive during the load.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Technician Utilization report specification version 5 (S1-R10).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Technician Utilization report specification version 5 (S1-R10).</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -778,7 +778,7 @@
 3. EVERY record is day-grouped and windowed in a SINGLE report-level time zone - the active workplace's - regardless of the location where it was clocked (a record's day, the current-month boundary, and the midnight split all use that one zone).
 4. This matches the Timesheet Activities report's single-time-zone grouping.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Technician Utilization report specification version 5 (S1-R7).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Technician Utilization report specification version 5 (S1-R7).</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -825,7 +825,7 @@
         <is>
           <t>1. The Technician Utilization report does NOT appear in the navigation.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Technician Utilization report specification version 5 (S1-N1); where the wording of that specification differs, the behaviour above follows a later product decision, which is the authority.</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Technician Utilization report specification version 5 (S1-N1); where the wording of that specification differs, the behaviour above follows a later product decision, which is the authority.</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
@@ -876,7 +876,7 @@
 2. The Summary row is hidden.
 3. Clearing every technician shows the SAME message and hides the Summary row — this version does not use distinct copy for genuinely-no-data vs a cleared filter.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Technician Utilization report specification version 5 (S1-N2, S3-N1, S5-N1, S9-N2).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Technician Utilization report specification version 5 (S1-N2, S3-N1, S5-N1, S9-N2).</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -931,7 +931,7 @@
 5. Hours show two decimal places with NO thousands separator (e.g. "107.70"), rounded from the unrounded hours using round-half-up (a tie rounds away from zero - 0.005 → 0.01).
 6. When more than one location is in scope the automatic Location column also appears, leftmost before Technician — it is not in the Column Selection control and its presence is expected.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Technician Utilization report specification version 5 (S2-R1, S2-R2, S2-R3, S2-R4, S2-R5, S9-R9).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Technician Utilization report specification version 5 (S2-R1, S2-R2, S2-R3, S2-R4, S2-R5, S9-R9).</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
@@ -979,7 +979,7 @@
           <t>1. Utilization % = work-order hours as a percentage of total clocked hours, computed from the unrounded hours (not from the already-rounded displays).
 2. It shows one decimal place followed by a percent sign, rounded round-half-up (66.65% → 66.7%).
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Technician Utilization report specification version 5 (S2-R6, S2-R7).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Technician Utilization report specification version 5 (S2-R6, S2-R7).</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -1029,7 +1029,7 @@
 2. No row shows more than 100% - work-order hours are always part of total clocked hours.
 3. The "—" (undefined, total = 0) state is unreachable on a rendered technician or day row, because only technicians with clocked time get rows.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Technician Utilization report specification version 5 (S2-E1, S2-R7).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Technician Utilization report specification version 5 (S2-E1, S2-R7).</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
 2. In a single-location view it is simply that one location's rate × the technician's internal hours.
 3. The value shows as dollars with two decimals and commas between thousands (e.g. "$1,234.50").
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Technician Utilization report specification version 5 (S2-R8, S2-R9).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Technician Utilization report specification version 5 (S2-R8, S2-R9).</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1134,7 +1134,7 @@
 3. NO column header other than Est. Lost Labor shows the information icon.
 4. Est. Lost Labor can be turned OFF in the Column Selection control; when it is off the column, its bold styling and its information icon are all absent, and the report still works normally.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Technician Utilization report specification version 5 (S2-R10, S2-R11, S8-R4, S8-R6, S8-R7, S8-N1, S10-R3).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Technician Utilization report specification version 5 (S2-R10, S2-R11, S8-R4, S8-R6, S8-R7, S8-N1, S10-R3).</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
@@ -1184,7 +1184,7 @@
 2. Technician B also shows "$0.00" - a configured rate of exactly $0.00 is a KNOWN rate that values the hours at $0.00, not "—".
 3. "$0.00" means 'the rate is known and there is nothing (or $0) to value' - a different state from "—" ('the rate is unknown').
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Technician Utilization report specification version 5 (S2-E2).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Technician Utilization report specification version 5 (S2-E2).</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -1234,7 +1234,7 @@
 2. The "—" cell carries the assistive-technology label "No default labor rate configured" (distinguishing it from "$0.00", which reads as its dollar value).
 3. The technician's Internal Hours column still shows all the internal hours (they are counted even though they cannot be valued).
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Technician Utilization report specification version 5 (S2-E3, S8-R11, S2-R4).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Technician Utilization report specification version 5 (S2-E3, S8-R11, S2-R4).</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
@@ -1284,7 +1284,7 @@
 2. The amount shows as a normal "$X.XX" with NO partial-value indicator in this version - so the row's Est. Lost Labor values fewer hours than its Internal Hours column shows.
 3. This is a documented known limitation (a partial-value indicator is a possible follow-up) - expected behavior, not a defect.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Technician Utilization report specification version 5 (S2-E4).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Technician Utilization report specification version 5 (S2-E4).</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
@@ -1335,7 +1335,7 @@
 2. The Technician header shows the ascending sort indicator.
 3. The active sort header exposes its state to assistive technology (aria-sort = ascending on the Technician header; none on the others).
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Technician Utilization report specification version 5 (S2-R12, S8-R8, S8-R10).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Technician Utilization report specification version 5 (S2-R12, S8-R8, S8-R10).</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
@@ -1389,7 +1389,7 @@
 4. Sorting is applied on screen to the loaded rows - NO reload/server request happens.
 5. Technicians tied in the sorted column are ordered by Technician name A to Z; two technicians sharing the same display name keep a stable order between renders.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Technician Utilization report specification version 5 (S2-R13, S2-R14).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Technician Utilization report specification version 5 (S2-R13, S2-R14).</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
@@ -1438,7 +1438,7 @@
           <t>1. After the reload, the rows are back to Technician name A to Z (the sort reset).
 2. On the return visit, the sort is again Technician A to Z - sort is NOT persisted (unlike the date range, technician selection, and location selection, which are).
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Technician Utilization report specification version 5 (S2-R15).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Technician Utilization report specification version 5 (S2-R15).</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
@@ -1488,7 +1488,7 @@
 2. The Summary row stays pinned at the bottom.
 3. Each technician's expanded day rows stay under that technician, still in date order (earliest to latest) - they do not re-sort by the clicked column.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Technician Utilization report specification version 5 (S2-R16).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Technician Utilization report specification version 5 (S2-R16).</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
@@ -1538,7 +1538,7 @@
 2. Among themselves, the "—" rows are ordered by Technician name A to Z.
 3. A "$0.00" value is a number, not "—" - it sorts as zero (lowest ascending, above only the — group).
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Technician Utilization report specification version 5 (S2-R17).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Technician Utilization report specification version 5 (S2-R17).</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
@@ -1589,7 +1589,7 @@
 3. It uses the same number formats as the technician rows.
 4. Its values carry NO label prefix such as "TOTAL:" or "AVG:".
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Technician Utilization report specification version 5 (S3-R1, S3-R2, S3-R6, S3-R7, S8-R5).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Technician Utilization report specification version 5 (S3-R1, S3-R2, S3-R6, S3-R7, S8-R5).</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
@@ -1639,7 +1639,7 @@
 2. Eye-summing the displayed rows MAY differ from the displayed Summary by 0.01 — one unit in the last decimal (these values are HOURS, not money) — expected in a compute-from-unrounded report, not a defect.
 3. With every technician selected, the Summary row equals the shop totals for the full date range at the selected location(s).
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Technician Utilization report specification version 5 (S3-R3, S5-E1).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Technician Utilization report specification version 5 (S3-R3, S5-E1).</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
@@ -1688,7 +1688,7 @@
           <t>1. The Summary Utilization % shows the WEIGHTED rate - the visible technicians' total work-order hours as a percentage of their total clocked hours, from unrounded hours (10.0% in the example).
 2. It is NOT the average of the per-technician percentages (not 50.0%).
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Technician Utilization report specification version 5 (S3-R4).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Technician Utilization report specification version 5 (S3-R4).</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
@@ -1737,7 +1737,7 @@
 2. A visible technician whose value is "—" contributes NOTHING to the sum - so the Summary understates true lost labor whenever any visible technician is "—" or partially valued (documented, expected).
 3. The Summary shows "—" only when EVERY visible technician's Est. Lost Labor is "—".
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Technician Utilization report specification version 5 (S3-R5).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Technician Utilization report specification version 5 (S3-R5).</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
@@ -1788,7 +1788,7 @@
 2. Its accessible name reflects the NEXT action, scoped to that technician: when collapsed it reads Expand, then that technician's name, then daily breakdown (for example: Expand John Smith's daily breakdown); when expanded it reads Collapse, then the same name and words.
 3. The control is keyboard-focusable, toggles on Enter and Space, and exposes its expanded/collapsed state to assistive technology.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Technician Utilization report specification version 5 (S4-R1, S8-R12).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Technician Utilization report specification version 5 (S4-R1, S8-R12).</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
@@ -1842,7 +1842,7 @@
 4. With several locations selected, a day's row POOLS that day's hours across the selected locations - one day row per date, not one per location.
 5. Note for the tester: you do not need developer tools for this test - just watch the screen.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Technician Utilization report specification version 5 (S4-R2, S4-N1, S9-R4).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Technician Utilization report specification version 5 (S4-R2, S4-N1, S9-R4).</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
@@ -1892,7 +1892,7 @@
 2. The day's Est. Lost Labor is valued per location exactly like a technician row (that location's default labor rate × that day's internal hours there).
 3. Hours 2dp / Utilization one decimal + % / dollars with commas - all identical to the row formats, computed from unrounded values and rounded once.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Technician Utilization report specification version 5 (S4-R3, S2-R8).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Technician Utilization report specification version 5 (S4-R3, S2-R8).</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
@@ -1945,7 +1945,7 @@
 3. Its accessible name reflects the next action: "Expand all technicians" when it will expand, "Collapse all technicians" when every row is already expanded.
 4. It is keyboard-focusable, toggles on Enter/Space, and exposes its state to assistive technology.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Technician Utilization report specification version 5 (S4-R4, S8-R12, S8-R3).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Technician Utilization report specification version 5 (S4-R4, S8-R12, S8-R3).</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
@@ -1995,7 +1995,7 @@
 2. On a fresh visit, all rows start collapsed - expansion is never persisted.
 3. Deselecting and re-selecting a technician (an on-screen operation) does NOT change the expansion state of the other rows - the expanded row stays expanded.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Technician Utilization report specification version 5 (S4-R5).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Technician Utilization report specification version 5 (S4-R5).</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
@@ -2045,7 +2045,7 @@
 2. On the first visit, EVERY technician is selected.
 3. All technicians' rows are shown.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Technician Utilization report specification version 5 (S5-R1, S5-R2).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Technician Utilization report specification version 5 (S5-R1, S5-R2).</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
@@ -2098,7 +2098,7 @@
 4. Re-selecting the technician shows the row again (and the Summary recalculates back).
 5. Note for the tester: you do not need developer tools for this test - just watch the screen.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Technician Utilization report specification version 5 (S5-R3, S5-R4, S5-R5).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Technician Utilization report specification version 5 (S5-R3, S5-R4, S5-R5).</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
@@ -2150,7 +2150,7 @@
 3. After step 3, your deselected technician STAYS deselected across the range change, while the newly-appearing technician is SELECTED (never explicitly deselected).
 4. After step 4, the newly-appearing technician is selected even though you had cleared all - "Clear all" only deselected the technicians listed at the time.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Technician Utilization report specification version 5 (S5-R6, S5-R7, S5-R8, S5-R9).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Technician Utilization report specification version 5 (S5-R6, S5-R7, S5-R8, S5-R9).</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
@@ -2200,7 +2200,7 @@
 2. All other technicians - including any who appear for the first time - are selected.
 3. The saved date range and location selection are restored alongside.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Technician Utilization report specification version 5 (S5-R10, S1-R8).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Technician Utilization report specification version 5 (S5-R10, S1-R8).</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
@@ -2250,7 +2250,7 @@
 2. The link is distinguished by more than color - it carries an underline (or equivalent non-color affordance), is keyboard-focusable with a visible focus indicator, and activates on Enter.
 3. The Summary row's Total Hours value is NOT a link.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Technician Utilization report specification version 5 (S6-R1, S6-N1, S8-R14).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Technician Utilization report specification version 5 (S6-R1, S6-N1, S8-R14).</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
@@ -2300,7 +2300,7 @@
 2. It is already filtered to that technician.
 3. It uses the same date range that was active on the Technician Utilization report.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Technician Utilization report specification version 5 (S6-R2, S6-R3, S6-R4).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Technician Utilization report specification version 5 (S6-R2, S6-R3, S6-R4).</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
@@ -2351,7 +2351,7 @@
 2. Under this exact scope (same range, same single location, closed records) a mismatch IS a defect.
 3. The two documented scope differences (open clocks, multi-location drill-through) are covered by separate cases and are NOT defects.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Technician Utilization report specification version 5 (S1-R9).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Technician Utilization report specification version 5 (S1-R9).</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
@@ -2401,7 +2401,7 @@
 2. The two reports, loaded at different moments, MAY differ by the elapsed open time - this is a deliberate scope difference of the reconciliation guarantee, EXPECTED and NOT a defect.
 3. Reloading the Technician Utilization report takes a fresh snapshot (the value grows by the elapsed time).
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Technician Utilization report specification version 5 (S1-R9, S1-E1).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Technician Utilization report specification version 5 (S1-R9, S1-E1).</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
@@ -2452,7 +2452,7 @@
 2. Timesheet Activities opens for the user's currently active shop, so it shows one location's portion - it will differ from (or be disjoint with) the multi-location row value.
 3. This is a KNOWN drill-through limitation, EXPECTED and NOT a data defect (the same applies when the single selected location is not the active shop).
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Technician Utilization report specification version 5 (S6-R6, S1-R9).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Technician Utilization report specification version 5 (S6-R6, S1-R9).</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
@@ -2500,7 +2500,7 @@
           <t>1. Timesheet Activities opens filtered to that technician.
 2. The date range covers ONLY that single day.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Technician Utilization report specification version 5 (S6-R5).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Technician Utilization report specification version 5 (S6-R5).</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
@@ -2551,7 +2551,7 @@
 ---
 DO NOT AUTOMATE YET: this behaviour is waiting on an answer from the product owner. Automating it now could lock in the wrong behaviour.
 The open question is in: Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx — https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/chris-consolidated-2026-08-04/Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Technician Utilization report specification version 5 (S7-R1, S7-R2, S7-R3, S7-R4, S8-R2).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Technician Utilization report specification version 5 (S7-R1, S7-R2, S7-R3, S7-R4, S8-R2).</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
@@ -2602,7 +2602,7 @@
 ---
 DO NOT AUTOMATE YET: this behaviour is waiting on an answer from the product owner. Automating it now could lock in the wrong behaviour.
 The open question is in: Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx — https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/chris-consolidated-2026-08-04/Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Technician Utilization report specification version 5 (S7-R5, S7-R6, S7-R12).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Technician Utilization report specification version 5 (S7-R5, S7-R6, S7-R12).</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
@@ -2652,7 +2652,7 @@
 2. The CSV shows the technician rows and the Summary row - always this summary-level content; it does NOT vary by the summary/expanded choice (no day rows).
 3. Any value containing a comma (e.g. "$1,234.50") is wrapped in double quotes per standard CSV escaping, so the columns parse correctly.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Technician Utilization report specification version 5 (S7-R7, S7-R10, S7-R12).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Technician Utilization report specification version 5 (S7-R7, S7-R10, S7-R12).</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
@@ -2707,7 +2707,7 @@
 5. Every download also mirrors the columns currently shown on screen — a column hidden in the Column Selection control is absent from the files, and a re-shown column comes back.
 6. Note for the tester: when you have more than one location in scope, the files also carry a Location column even though it is not in the Column Selection control. That is correct - it appears by itself. With a single location in scope there is no Location column, and that is also correct.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Technician Utilization report specification version 5 (S7-R8, S7-R9, S7-R10, S7-R13, S7-E1, S9-R8).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Technician Utilization report specification version 5 (S7-R8, S7-R9, S7-R10, S7-R13, S7-E1, S9-R8).</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
@@ -2757,7 +2757,7 @@
           <t>1. The downloaded files use the same column order and number formats as the on-screen report, including the "—" rendering for an unknown Est. Lost Labor.
 2. Rows in EVERY download are ordered by Technician name A to Z (the default order) - the on-screen column sort is client-side only and is NOT carried into the export.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Technician Utilization report specification version 5 (S7-R10, S7-R10a).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Technician Utilization report specification version 5 (S7-R10, S7-R10a).</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
@@ -2809,7 +2809,7 @@
 ---
 DO NOT AUTOMATE YET: this behaviour is waiting on an answer from the product owner. Automating it now could lock in the wrong behaviour.
 The open question is in: Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx — https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/chris-consolidated-2026-08-04/Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Technician Utilization report specification version 5 (S7-R11, S7-N2, S7-N3).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Technician Utilization report specification version 5 (S7-R11, S7-N2, S7-N3).</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
@@ -2860,7 +2860,7 @@
 ---
 DO NOT AUTOMATE YET: this behaviour is waiting on an answer from the product owner. Automating it now could lock in the wrong behaviour.
 The open question is in: Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx — https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/chris-consolidated-2026-08-04/Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Technician Utilization report specification version 5 (S7-N1).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Technician Utilization report specification version 5 (S7-N1).</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
@@ -2909,7 +2909,7 @@
           <t>1. When a download starts, a success notification reads exactly: "Download started".
 2. When a download fails, an error notification reads exactly: "Failed to download report".
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Technician Utilization report specification version 5 (§7 notifications table, Story 7 has no S, §7 is the closing reference).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Technician Utilization report specification version 5 (§7 notifications table, Story 7 has no S, §7 is the closing reference).</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
@@ -2962,7 +2962,7 @@
 3. After narrowing below the cap, the downloads work again.
 Known issue: the product does not currently do this. It has been filed for a fix here: https://shopview.atlassian.net/browse/SV-8818
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Technician Utilization report specification version 5 (Story 7 exports).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Technician Utilization report specification version 5 (Story 7 exports).</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
@@ -3015,7 +3015,7 @@
 3. "All locations" acts as a select-all shortcut: choosing it selects every accessible location; unchecking one location leaves the remaining specific locations selected - the selection is always the concrete set of checked locations.
 4. With more than one location selected, a Location column appears in the table and each row names its location - or reads "Multiple" for a technician whose hours span more than one of them. (Where that column sits on screen is checked by its own test.)
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Technician Utilization report specification version 5 (S9-R1); where the wording of that specification differs, the behaviour above follows a later product decision, which is the authority.</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Technician Utilization report specification version 5 (S9-R1); where the wording of that specification differs, the behaviour above follows a later product decision, which is the authority.</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
@@ -3069,7 +3069,7 @@
 4. Scoping never goes beyond the user's accessible locations - a location the user cannot access is never included.
 5. The page itself shows which location(s) the report is currently scoped to (the new on-screen scope indicator - exactly where and how it appears is confirmed in the build).
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Technician Utilization report specification version 5 (S9-R3, S9-R4, S9-R5).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Technician Utilization report specification version 5 (S9-R3, S9-R4, S9-R5).</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
@@ -3119,7 +3119,7 @@
 3. The report loads without an error in both cases.
 4. The same fallback happens when you deselect every location by hand in the Location filter — the report loads the currently active location's rows rather than showing nothing.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Technician Utilization report specification version 5 (S9-R6, S1-R8, S9-R2, S9-R7).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Technician Utilization report specification version 5 (S9-R6, S1-R8, S9-R2, S9-R7).</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
@@ -3170,7 +3170,7 @@
 ---
 DO NOT AUTOMATE YET: this behaviour is waiting on an answer from the product owner. Automating it now could lock in the wrong behaviour.
 The open question is in: Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx — https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/chris-consolidated-2026-08-04/Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Technician Utilization report specification version 5 (S9-N1); where the wording of that specification differs, the behaviour above follows a later product decision, which is the authority.</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Technician Utilization report specification version 5 (S9-N1); where the wording of that specification differs, the behaviour above follows a later product decision, which is the authority.</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
@@ -3232,7 +3232,7 @@
 7. With a single location in scope the Location column is hidden.
 8. Every download — both PDF views and the CSV — includes the Location column in its on-screen leftmost position, carrying the same values you just read on screen.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Technician Utilization report specification version 5 (S9-R9, S9-R10, S8-R15, S10-R4, S7-R13).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Technician Utilization report specification version 5 (S9-R9, S9-R10, S8-R15, S10-R4, S7-R13).</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
@@ -3293,7 +3293,7 @@
 7. Est. Lost Labor can now be hidden like any other column (it used to be always on).
 8. Your column choice is remembered in this browser and is still applied when you come back.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Technician Utilization report specification version 5 (S10-R1, S10-R2, S10-R3, S10-R4, S10-R5, S10-R6, S8-R16).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Technician Utilization report specification version 5 (S10-R1, S10-R2, S10-R3, S10-R4, S10-R5, S10-R6, S8-R16).</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
@@ -3343,7 +3343,7 @@
 2. The toolbar controls run, left to right: the three-dot download menu, the Column Selection control, the date-range picker, the technician filter, and the Location filter (rightmost).
 3. The expand/collapse-all control is NOT a toolbar control - it lives in the table header (in the Technician column).
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Technician Utilization report specification version 5 (S8-R1, S8-R2, S8-R3).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Technician Utilization report specification version 5 (S8-R1, S8-R2, S8-R3).</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
@@ -3396,7 +3396,7 @@
 3. The Total Hours link's non-color affordance and focus indicator apply in both modes.
 4. Note for the tester: you do not need to measure anything and you do not need any tool. Just say whether you can see the icon easily in both modes, and only report it if you cannot. (The design rule behind this is a minimum 3:1 contrast ratio, which the design and engineering team check with a contrast tool - not by hand.)
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Technician Utilization report specification version 5 (S8-R9, S8-R13, S8-R14).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Technician Utilization report specification version 5 (S8-R9, S8-R13, S8-R14).</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
@@ -3447,7 +3447,7 @@
 2. Expanding a technician row issues an on-demand backend request that returns that technician's per-day breakdown.
 3. Because expansion state resets (all collapsed) on any data reload, nothing is lost by the lazy loading - re-expanding fetches fresh day data.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Technician Utilization report specification version 5 (S4-R2, S4-R5).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Technician Utilization report specification version 5 (S4-R2, S4-R5).</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
@@ -3500,7 +3500,7 @@
 3. The technician filter causes NO server request - it works on screen only (hide/show + Summary recalculation).
 4. Column sorting causes NO server request - it is applied on screen to the loaded rows.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Technician Utilization report specification version 5 (S1-R5, S9-R3, S2-R13).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Technician Utilization report specification version 5 (S1-R5, S9-R3, S2-R13).</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">

--- a/testrail-import/Report-Suite_Technician-Utilization-Report_testrail-import.xlsx
+++ b/testrail-import/Report-Suite_Technician-Utilization-Report_testrail-import.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J60"/>
+  <dimension ref="A1:J61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
@@ -929,9 +929,10 @@
 3. WO Hours = time clocked directly to work orders; Internal Hours = time clocked to internal, non-billable activities.
 4. Internal Hours includes ALL internal time - including hours at a location with no configured labor rate.
 5. Hours show two decimal places with NO thousands separator (e.g. "107.70"), rounded from the unrounded hours using round-half-up (a tie rounds away from zero - 0.005 → 0.01).
-6. When more than one location is in scope the automatic Location column also appears, leftmost before Technician — it is not in the Column Selection control and its presence is expected.
----
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Technician Utilization report specification version 5 (S2-R1, S2-R2, S2-R3, S2-R4, S2-R5, S9-R9).</t>
+6. When more than one location is in scope the Location column also appears, leftmost before Technician. Location is one of the columns in the column-selection control, and with more than one location SELECTED it is already switched on for you - you do not have to turn it on. You can still switch it off. If the signed-in person only has access to ONE location, Location is not offered in the column-selection list at all.
+---
+Note for the tester: on this build the column does not yet behave this way - record what you see and carry on. The change is with the developers.
+This is the expected behaviour as per Chris Ward's decision of 8/5/2026, recorded in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true. It does NOT match the build tested on 8/4/2026 (build v3.4.1-3d03023) - that change is with the developers - and where the Technician Utilization report specification version 5 (S2-R1, S2-R2, S2-R3, S2-R4, S2-R5, S9-R9) differs, his decision is the authority.</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
@@ -2546,12 +2547,10 @@
       <c r="G42" s="2" t="inlineStr">
         <is>
           <t>1. The three-dot download menu sits LEFTMOST in the toolbar's action cluster, with the Column Selection control immediately after it.
-2. The menu holds: "Download Summary (PDF)", "Download Expanded View (PDF)", and "Download (CSV)".
-3. The labels match exactly - only the expanded option carries the word "View" (the shipped strings, documented as-is).
----
-DO NOT AUTOMATE YET: this behaviour is waiting on an answer from the product owner. Automating it now could lock in the wrong behaviour.
-The open question is in: Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx — https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/chris-consolidated-2026-08-04/Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Technician Utilization report specification version 5 (S7-R1, S7-R2, S7-R3, S7-R4, S8-R2).</t>
+2. The menu holds four items, worded exactly as they are on Sales By Customer and Sales By Representative: "Download Summary (PDF)", "Download Expanded View (PDF)", "Download Summary (CSV)" and "Download Expanded View (CSV)".
+3. Note for the tester: on this build the four items are worded more briefly - "Summary (PDF)", "Summary (CSV)", "Expanded (PDF)" and "Expanded (CSV)" - without the word "Download". The product owner has decided they must match the other two reports, so record what you see; the change is with the developers.
+---
+This is the expected behaviour as per Chris Ward's decision of 8/5/2026, recorded in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true. It does NOT match the build tested on 8/4/2026 (build v3.4.1-3d03023) - that change is with the developers - and where the Technician Utilization report specification version 5 (S7-R1, S7-R2, S7-R3, S7-R4, S8-R2) differs, his decision is the authority.</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
@@ -2600,8 +2599,6 @@
 2. The Expanded PDF shows the technician rows, EACH technician's per-day breakdown, and the Summary row; it downloads as "Technician-Utilization-Expanded.pdf".
 3. The PDF filenames are Title-Case as shipped.
 ---
-DO NOT AUTOMATE YET: this behaviour is waiting on an answer from the product owner. Automating it now could lock in the wrong behaviour.
-The open question is in: Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx — https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/chris-consolidated-2026-08-04/Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx
 This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Technician Utilization report specification version 5 (S7-R5, S7-R6, S7-R12).</t>
         </is>
       </c>
@@ -2705,9 +2702,12 @@
 3. With every technician selected, the download covers all technicians for the range at the selected location(s).
 4. Every download (each PDF and the CSV) carries a "Locations:" line naming the location(s) the report was scoped to (exact position in the file is confirmed in the build).
 5. Every download also mirrors the columns currently shown on screen — a column hidden in the Column Selection control is absent from the files, and a re-shown column comes back.
-6. Note for the tester: when you have more than one location in scope, the files also carry a Location column even though it is not in the Column Selection control. That is correct - it appears by itself. With a single location in scope there is no Location column, and that is also correct.
----
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Technician Utilization report specification version 5 (S7-R8, S7-R9, S7-R10, S7-R13, S7-E1, S9-R8).</t>
+6. Note for the tester: when more than one location is in scope the files also carry a Location column. Location is one of the columns in the column-selection control, and with more than one location SELECTED it is already switched on for you - you do not have to turn it on. You can still switch it off. If the signed-in person only has access to ONE location, Location is not offered in the column-selection list at all. With a single location in scope there is no Location column in the files.
+---
+Note for the tester: on this build the column does not yet behave this way - record what you see and carry on. The change is with the developers.
+DO NOT AUTOMATE YET: part of this behaviour is still waiting on an answer from the product owner. Automating it now could lock in the wrong behaviour.
+The open question is in: Follow-up-Question-for-Chris-Ward_2026-08-05.xlsx — https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/rulings-2026-08-05/Follow-up-Question-for-Chris-Ward_2026-08-05.xlsx
+This is the expected behaviour as per Chris Ward's decision of 8/5/2026, recorded in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true. It does NOT match the build tested on 8/4/2026 (build v3.4.1-3d03023) - that change is with the developers - and where the Technician Utilization report specification version 5 (S7-R8, S7-R9, S7-R10, S7-R13, S7-E1, S9-R8) differs, his decision is the authority.</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
@@ -2771,7 +2771,7 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>PDF logo: the uploaded logo, else the bundled ShopView logo; CSV never</t>
+          <t>PDF logo follows the uploaded logo; the spreadsheet never carries one</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
@@ -2805,11 +2805,10 @@
         <is>
           <t>1. With an uploaded logo, BOTH PDF views show that logo at the top of the report.
 2. The CSV never includes the logo.
-3. With NO uploaded logo, the PDF views show the bundled ShopView logo instead — not a blank space and not an error.
----
-DO NOT AUTOMATE YET: this behaviour is waiting on an answer from the product owner. Automating it now could lock in the wrong behaviour.
-The open question is in: Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx — https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/chris-consolidated-2026-08-04/Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Technician Utilization report specification version 5 (S7-R11, S7-N2, S7-N3).</t>
+3. With a logo uploaded, that logo appears. If a logo is set but fails to load, the built-in ShopView logo is used instead. If no logo is uploaded at all, NO logo is printed and the text fills the space.
+Note for the tester: on this build a report with no uploaded logo still prints the built-in ShopView logo. The product owner has decided it should print no logo at all, so record what you see; the change is with the developers.
+---
+This is the expected behaviour as per Chris Ward's decision of 8/5/2026, recorded in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true. It does NOT match the build tested on 8/4/2026 (build v3.4.1-3d03023) - that change is with the developers - and where the Technician Utilization report specification version 5 (S7-R11, S7-N2, S7-N3) differs, his decision is the authority.</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
@@ -2857,9 +2856,8 @@
         <is>
           <t>1. Nothing happens: NO file downloads and NO message appears (not even an error).
 2. This silent no-op is the specified behavior for every download option when no technician is selected.
----
-DO NOT AUTOMATE YET: this behaviour is waiting on an answer from the product owner. Automating it now could lock in the wrong behaviour.
-The open question is in: Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx — https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/chris-consolidated-2026-08-04/Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx
+Known issue: the product does not currently do this — on the build tested, choosing a download with no technician selected still started the download and showed a success message. That is a fault for a developer to fix, not a decision for the product owner. No developer ticket has been raised for it yet, so this test will fail until it is fixed — record what you see and leave the test as it is.
+---
 This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Technician Utilization report specification version 5 (S7-N1).</t>
         </is>
       </c>
@@ -2976,31 +2974,83 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
+          <t>Both spreadsheet downloads hold the summary rows and no per-day rows</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>TU — Exports</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>1. You are on the Technician Utilization report with rows loaded, and several technicians who have clock records across more than one day.
+2. The three-dot download menu offers a spreadsheet option for the Summary view and a separate one for the Expanded view.</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t>1. Open the three-dot download menu (it sits leftmost in the toolbar's group of buttons) and read the options.
+2. Choose the Summary spreadsheet option, open the file that downloads, and write down its exact file name.
+3. Choose the Expanded spreadsheet option, open the file that downloads, and write down its exact file name.
+4. In both files, look for the technician rows, the Summary row, and any per-day rows.</t>
+        </is>
+      </c>
+      <c r="G51" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1. Both spreadsheet options download a file.
+2. Both files hold the technician rows and the Summary row.
+3. Neither file holds any per-day rows - the spreadsheet holds the same thing whichever of the two you pick.
+4. In both files any value with a comma in it (for example "$1,234.50") is wrapped in double quotes, so the columns still line up when you open it.
+5. Note for the tester: write down the exact file name each option gives you. Names for two separate spreadsheet files have never been written down anywhere, so we are collecting them, not checking them - do not fail this test over a file name.
+---
+This is the expected behaviour as per the Technician Utilization report specification version 5 (S7-R7), which says the spreadsheet always holds the technician rows and the Summary row and does not change with the Summary or Expanded choice. The test exists at all because of Chris Ward's decision of 8/5/2026, recorded in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true - he asked this report's download menu to match Sales By Customer and Sales By Representative, which each offer a spreadsheet for both views, whereas that specification describes only one spreadsheet download. That his answer leaves the menu with four options is our reading of his words and he has not confirmed it. It has not been checked on a build yet.
+AUTOMATION: HOLD - the build does not offer two spreadsheet options yet, and the product owner has not confirmed that it should.
+</t>
+        </is>
+      </c>
+      <c r="H51" s="2" t="inlineStr"/>
+      <c r="I51" s="2" t="inlineStr"/>
+      <c r="J51" s="2" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
           <t>The Location filter is the rightmost multi-select; All Locations = select-all</t>
         </is>
       </c>
-      <c r="B51" s="2" t="inlineStr">
+      <c r="B52" s="2" t="inlineStr">
         <is>
           <t>TU — Location Filter</t>
         </is>
       </c>
-      <c r="C51" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D51" s="2" t="inlineStr">
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E51" s="2" t="inlineStr">
+      <c r="E52" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in as a user with access to at least two locations.
 2. You are on the Technician Utilization report.</t>
         </is>
       </c>
-      <c r="F51" s="2" t="inlineStr">
+      <c r="F52" s="2" t="inlineStr">
         <is>
           <t>1. Look at the rightmost control in the toolbar and read its label.
 2. Open it and read the listed options.
@@ -3008,7 +3058,7 @@
 4. With every accessible location selected, look at how the report tells you which location the shown data belongs to.</t>
         </is>
       </c>
-      <c r="G51" s="2" t="inlineStr">
+      <c r="G52" s="2" t="inlineStr">
         <is>
           <t>1. The toolbar has a location filter labeled "Location" - a multi-select and the RIGHTMOST control.
 2. It lists the locations the signed-in user has access to, plus an "All locations" option and a "Clear all" action. (If you only have access to one location, the "All locations" entry is not offered - you see "Clear all" and your one location.)
@@ -3018,42 +3068,42 @@
 This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Technician Utilization report specification version 5 (S9-R1); where the wording of that specification differs, the behaviour above follows a later product decision, which is the authority.</t>
         </is>
       </c>
-      <c r="H51" s="2" t="inlineStr">
+      <c r="H52" s="2" t="inlineStr">
         <is>
           <t>SV-8656 (TU spec v5 2026-07-29 S9-R1 — per-row location identifier in All-Locations view ADDED per kickoff video P10 40:58-41:20; user ruling 2026-07-28: video overrides spec (video newer; last-update-wins))</t>
         </is>
       </c>
-      <c r="I51" s="2" t="inlineStr"/>
-      <c r="J51" s="2" t="inlineStr"/>
-    </row>
-    <row r="52">
-      <c r="A52" s="2" t="inlineStr">
+      <c r="I52" s="2" t="inlineStr"/>
+      <c r="J52" s="2" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
         <is>
           <t>Location changes reload with hours pooled into one row per technician</t>
         </is>
       </c>
-      <c r="B52" s="2" t="inlineStr">
+      <c r="B53" s="2" t="inlineStr">
         <is>
           <t>TU — Location Filter</t>
         </is>
       </c>
-      <c r="C52" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D52" s="2" t="inlineStr">
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="E52" s="2" t="inlineStr">
+      <c r="E53" s="2" t="inlineStr">
         <is>
           <t>1. A technician has clocked time at TWO accessible locations in the range.
 2. You are on the Technician Utilization report.</t>
         </is>
       </c>
-      <c r="F52" s="2" t="inlineStr">
+      <c r="F53" s="2" t="inlineStr">
         <is>
           <t>1. Select only location A and read the technician's hours.
 2. Add location B to the selection and watch the report.
@@ -3061,7 +3111,7 @@
 4. Expand the technician and check the day rows on a day with time at both locations.</t>
         </is>
       </c>
-      <c r="G52" s="2" t="inlineStr">
+      <c r="G53" s="2" t="inlineStr">
         <is>
           <t>1. Selecting one, several, or all locations RELOADS the report scoped to that set (unlike the technician filter, which is on-screen only).
 2. All metrics (technician rows, per-day rows, and the Summary) reflect only clock records at the selected location(s).
@@ -3072,47 +3122,47 @@
 This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Technician Utilization report specification version 5 (S9-R3, S9-R4, S9-R5).</t>
         </is>
       </c>
-      <c r="H52" s="2" t="inlineStr">
+      <c r="H53" s="2" t="inlineStr">
         <is>
           <t>SV-8656 (TU spec v5 2026-07-29 S9-R3; S9-R4; S9-R5 + on-screen location-scope indicator per Chris Ward group message 2026-07-29 (chris-update-2026-07-29/chris-message-2026-07-29.md; NEWEST source; last-update-wins))</t>
         </is>
       </c>
-      <c r="I52" s="2" t="inlineStr"/>
-      <c r="J52" s="2" t="inlineStr"/>
-    </row>
-    <row r="53">
-      <c r="A53" s="2" t="inlineStr">
+      <c r="I53" s="2" t="inlineStr"/>
+      <c r="J53" s="2" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
         <is>
           <t>The saved location selection restores defensively; bad ones are dropped</t>
         </is>
       </c>
-      <c r="B53" s="2" t="inlineStr">
+      <c r="B54" s="2" t="inlineStr">
         <is>
           <t>TU — Location Filter</t>
         </is>
       </c>
-      <c r="C53" s="2" t="inlineStr">
+      <c r="C54" s="2" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="D53" s="2" t="inlineStr">
+      <c r="D54" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E53" s="2" t="inlineStr">
+      <c r="E54" s="2" t="inlineStr">
         <is>
           <t>1. The user saved a location selection that includes a location their access to was later removed.</t>
         </is>
       </c>
-      <c r="F53" s="2" t="inlineStr">
+      <c r="F54" s="2" t="inlineStr">
         <is>
           <t>1. Return to the Technician Utilization report and read the restored location selection.
 2. Repeat with a saved selection consisting ONLY of now-inaccessible locations.</t>
         </is>
       </c>
-      <c r="G53" s="2" t="inlineStr">
+      <c r="G54" s="2" t="inlineStr">
         <is>
           <t>1. Any saved location the user can no longer access is DROPPED from the restored selection; the remaining accessible locations restore normally.
 2. If the remaining set is empty, the report falls back to the user's currently active location (the first-visit default).
@@ -3122,94 +3172,92 @@
 This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Technician Utilization report specification version 5 (S9-R6, S1-R8, S9-R2, S9-R7).</t>
         </is>
       </c>
-      <c r="H53" s="2" t="inlineStr">
+      <c r="H54" s="2" t="inlineStr">
         <is>
           <t>SV-8656 (TU spec v5 2026-07-29 S9-R6; S1-R8; S9-R2; S9-R7)</t>
         </is>
       </c>
-      <c r="I53" s="2" t="inlineStr"/>
-      <c r="J53" s="2" t="inlineStr"/>
-    </row>
-    <row r="54">
-      <c r="A54" s="2" t="inlineStr">
+      <c r="I54" s="2" t="inlineStr"/>
+      <c r="J54" s="2" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
         <is>
           <t>Technician Utilization: Location filter hidden for a one-location user</t>
         </is>
       </c>
-      <c r="B54" s="2" t="inlineStr">
+      <c r="B55" s="2" t="inlineStr">
         <is>
           <t>TU — Location Filter</t>
         </is>
       </c>
-      <c r="C54" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D54" s="2" t="inlineStr">
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="E54" s="2" t="inlineStr">
+      <c r="E55" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in as a user with access to exactly one location.
 2. You are on the Technician Utilization report.</t>
         </is>
       </c>
-      <c r="F54" s="2" t="inlineStr">
+      <c r="F55" s="2" t="inlineStr">
         <is>
           <t>1. Look for the Location filter in the toolbar.
 2. Then sign in as a user with access to two or more locations and look again.</t>
         </is>
       </c>
-      <c r="G54" s="2" t="inlineStr">
+      <c r="G55" s="2" t="inlineStr">
         <is>
           <t>1. For the single-location user the Location filter is NOT shown at all — the report simply shows that one location's data.
 2. For the user with access to two or more locations the Location filter IS shown.
 ---
-DO NOT AUTOMATE YET: this behaviour is waiting on an answer from the product owner. Automating it now could lock in the wrong behaviour.
-The open question is in: Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx — https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/chris-consolidated-2026-08-04/Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Technician Utilization report specification version 5 (S9-N1); where the wording of that specification differs, the behaviour above follows a later product decision, which is the authority.</t>
-        </is>
-      </c>
-      <c r="H54" s="2" t="inlineStr">
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Technician Utilization report specification version 5 (S9-N1). Chris Ward confirmed this on 8/5/2026 in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true</t>
+        </is>
+      </c>
+      <c r="H55" s="2" t="inlineStr">
         <is>
           <t>SV-8656 (TU spec S9-N1 — RULED HIDDEN by Chris Ward answer 2026-07-31 Q1=A "classic spec drift"; the S9-N1 "still sees the filter" note is stale; spec edit pending)</t>
         </is>
       </c>
-      <c r="I54" s="2" t="inlineStr"/>
-      <c r="J54" s="2" t="inlineStr"/>
-    </row>
-    <row r="55">
-      <c r="A55" s="2" t="inlineStr">
+      <c r="I55" s="2" t="inlineStr"/>
+      <c r="J55" s="2" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
         <is>
           <t>The Location column shows only with more than one location; Summary row blank</t>
         </is>
       </c>
-      <c r="B55" s="2" t="inlineStr">
+      <c r="B56" s="2" t="inlineStr">
         <is>
           <t>TU — Location Filter</t>
         </is>
       </c>
-      <c r="C55" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D55" s="2" t="inlineStr">
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E55" s="2" t="inlineStr">
+      <c r="E56" s="2" t="inlineStr">
         <is>
           <t>1. You are on the Technician Utilization report as a user with access to two or more locations.
 2. One technician clocked time at a single location in the range and another clocked time at two different locations.
 3. One of those days has hours at two locations (for the per-day check).</t>
         </is>
       </c>
-      <c r="F55" s="2" t="inlineStr">
+      <c r="F56" s="2" t="inlineStr">
         <is>
           <t>1. Select two or more locations and read the column headers from the left.
 2. Read the Location cell on the single-location technician's row.
@@ -3221,57 +3269,60 @@
 8. With more than one location still selected, download both PDF views and the CSV and read their columns from the left.</t>
         </is>
       </c>
-      <c r="G55" s="2" t="inlineStr">
+      <c r="G56" s="2" t="inlineStr">
         <is>
           <t>1. With more than one location in scope a Location column is shown as the LEFTMOST column, before Technician.
 2. A technician whose hours were all clocked at one location shows that location's name.
 3. A technician whose hours span more than one selected location shows "Multiple".
 4. An expanded day row shows the exact location when that day's hours were all at one location, and "Multiple" when the day spans more than one.
 5. The Summary row leaves the Location cell blank.
-6. Location is never listed in the Column Selection control — it follows the location scope on its own.
+6. Location is one of the columns in the column-selection control, and with more than one location SELECTED it is already switched on for you - you do not have to turn it on. You can still switch it off. If the signed-in person only has access to ONE location, Location is not offered in the column-selection list at all.
 7. With a single location in scope the Location column is hidden.
 8. Every download — both PDF views and the CSV — includes the Location column in its on-screen leftmost position, carrying the same values you just read on screen.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Technician Utilization report specification version 5 (S9-R9, S9-R10, S8-R15, S10-R4, S7-R13).</t>
-        </is>
-      </c>
-      <c r="H55" s="2" t="inlineStr">
+Note for the tester: on this build the column does not yet behave this way - record what you see and carry on. The change is with the developers.
+DO NOT AUTOMATE YET: part of this behaviour is still waiting on an answer from the product owner. Automating it now could lock in the wrong behaviour.
+The open question is in: Follow-up-Question-for-Chris-Ward_2026-08-05.xlsx — https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/rulings-2026-08-05/Follow-up-Question-for-Chris-Ward_2026-08-05.xlsx
+This is the expected behaviour as per Chris Ward's decision of 8/5/2026, recorded in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true. It does NOT match the build tested on 8/4/2026 (build v3.4.1-3d03023) - that change is with the developers - and where the Technician Utilization report specification version 5 (S9-R9, S9-R10, S8-R15, S10-R4, S7-R13) differs, his decision is the authority.</t>
+        </is>
+      </c>
+      <c r="H56" s="2" t="inlineStr">
         <is>
           <t>SV-8656; SV-8654 (TU spec v5 2026-07-29 S9-R9; S9-R10; S8-R15; S10-R4; S7-R13 — per-row Location column; leftmost before Technician; "Multiple" on a spanning row; Summary row blank; not in the selector; S7-R13 = same column in every download)</t>
         </is>
       </c>
-      <c r="I55" s="2" t="inlineStr"/>
-      <c r="J55" s="2" t="inlineStr"/>
-    </row>
-    <row r="56">
-      <c r="A56" s="2" t="inlineStr">
+      <c r="I56" s="2" t="inlineStr"/>
+      <c r="J56" s="2" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
         <is>
           <t>Column Selection: Technician always on, the other five toggleable, remembered</t>
         </is>
       </c>
-      <c r="B56" s="2" t="inlineStr">
+      <c r="B57" s="2" t="inlineStr">
         <is>
           <t>TU — Visual &amp; Accessibility</t>
         </is>
       </c>
-      <c r="C56" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D56" s="2" t="inlineStr">
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E56" s="2" t="inlineStr">
+      <c r="E57" s="2" t="inlineStr">
         <is>
           <t>1. You are on the Technician Utilization report with rows loaded.
 2. This browser has never saved settings for this report (fresh visit), so every column is at its default.
 3. Part of this test checks what a blind user would hear, so you need a screen reader. On Windows install NVDA — it is free, from nvaccess.org. On a Mac use VoiceOver, which is already built in (Cmd+F5 turns it on and off). Alternatively the browser's developer tools (F12) have an "Accessibility" panel that shows the same names without you having to listen to anything.</t>
         </is>
       </c>
-      <c r="F56" s="2" t="inlineStr">
+      <c r="F57" s="2" t="inlineStr">
         <is>
           <t>1. Find the column-selection button in the toolbar and hover it to read its tooltip.
 2. With the button focused, read the name assistive technology gives it — use the browser's accessibility inspector or a screen reader.
@@ -3282,7 +3333,7 @@
 7. Reload the page, then close the browser, reopen it and return to the report.</t>
         </is>
       </c>
-      <c r="G56" s="2" t="inlineStr">
+      <c r="G57" s="2" t="inlineStr">
         <is>
           <t>1. The control is an icon button whose tooltip reads "Column Selection", sitting immediately after the three-dot download menu in the toolbar.
 2. Because the button shows an icon and no text, it still carries a name that assistive technology reads out — it is not left unnamed. (The exact wording is confirmed in the build.)
@@ -3296,48 +3347,48 @@
 This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Technician Utilization report specification version 5 (S10-R1, S10-R2, S10-R3, S10-R4, S10-R5, S10-R6, S8-R16).</t>
         </is>
       </c>
-      <c r="H56" s="2" t="inlineStr">
+      <c r="H57" s="2" t="inlineStr">
         <is>
           <t>SV-8655; SV-8582 (TU spec v5 2026-07-29 Story 10 S10-R1; S10-R2; S10-R3; S10-R4; S10-R5; S10-R6 column selector + Story 8 S8-R16 accessible name — Story 10 has NO owning Jira story so epic SV-8582 is used and FLAGGED; S8-R16 is owned by SV-8655)</t>
         </is>
       </c>
-      <c r="I56" s="2" t="inlineStr"/>
-      <c r="J56" s="2" t="inlineStr"/>
-    </row>
-    <row r="57">
-      <c r="A57" s="2" t="inlineStr">
+      <c r="I57" s="2" t="inlineStr"/>
+      <c r="J57" s="2" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
         <is>
           <t>All-white table with no row shading; toolbar controls in the fixed order</t>
         </is>
       </c>
-      <c r="B57" s="2" t="inlineStr">
+      <c r="B58" s="2" t="inlineStr">
         <is>
           <t>TU — Visual &amp; Accessibility</t>
         </is>
       </c>
-      <c r="C57" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D57" s="2" t="inlineStr">
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E57" s="2" t="inlineStr">
+      <c r="E58" s="2" t="inlineStr">
         <is>
           <t>1. You are on the Technician Utilization report with rows loaded, in light mode.</t>
         </is>
       </c>
-      <c r="F57" s="2" t="inlineStr">
+      <c r="F58" s="2" t="inlineStr">
         <is>
           <t>1. Look at the column headers and the data rows' backgrounds.
 2. Read the toolbar controls left to right.
 3. Look for the expand/collapse-all control's position.</t>
         </is>
       </c>
-      <c r="G57" s="2" t="inlineStr">
+      <c r="G58" s="2" t="inlineStr">
         <is>
           <t>1. The report uses an all-white table: white column headers and white data cells, with NO alternating row shading.
 2. The toolbar controls run, left to right: the three-dot download menu, the Column Selection control, the date-range picker, the technician filter, and the Location filter (rightmost).
@@ -3346,42 +3397,42 @@
 This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Technician Utilization report specification version 5 (S8-R1, S8-R2, S8-R3).</t>
         </is>
       </c>
-      <c r="H57" s="2" t="inlineStr">
+      <c r="H58" s="2" t="inlineStr">
         <is>
           <t>SV-8655 (TU spec v5 2026-07-29 S8-R1; S8-R2; S8-R3 — toolbar order rewritten: Column Selection inserted after the three-dot menu; and the date-range picker now precedes the technician filter)</t>
         </is>
       </c>
-      <c r="I57" s="2" t="inlineStr"/>
-      <c r="J57" s="2" t="inlineStr"/>
-    </row>
-    <row r="58">
-      <c r="A58" s="2" t="inlineStr">
+      <c r="I58" s="2" t="inlineStr"/>
+      <c r="J58" s="2" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
         <is>
           <t>Dark mode keeps every report element legible</t>
         </is>
       </c>
-      <c r="B58" s="2" t="inlineStr">
+      <c r="B59" s="2" t="inlineStr">
         <is>
           <t>TU — Visual &amp; Accessibility</t>
         </is>
       </c>
-      <c r="C58" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D58" s="2" t="inlineStr">
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="E58" s="2" t="inlineStr">
+      <c r="E59" s="2" t="inlineStr">
         <is>
           <t>1. You are on the Technician Utilization report with rows loaded, including a "—" Est. Lost Labor cell.
 2. Dark mode is available in the application.</t>
         </is>
       </c>
-      <c r="F58" s="2" t="inlineStr">
+      <c r="F59" s="2" t="inlineStr">
         <is>
           <t>1. Switch the application to dark mode.
 2. Check each element: page background, toolbar, cells, the Total Hours link, the information icon, the sort indicator, and a "—" glyph.
@@ -3389,7 +3440,7 @@
 4. Check the Total Hours link's underline/affordance and focus indicator in both modes.</t>
         </is>
       </c>
-      <c r="G58" s="2" t="inlineStr">
+      <c r="G59" s="2" t="inlineStr">
         <is>
           <t>1. The report supports dark mode: page background, toolbar, cells, the Total Hours link, the information icon, the sort indicator, and the "—" glyph are all clearly legible in dark mode.
 2. In BOTH light mode and dark mode the information icon is clearly visible against the background behind it - you can see it at a glance and it does not disappear into the background.
@@ -3399,49 +3450,49 @@
 This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Technician Utilization report specification version 5 (S8-R9, S8-R13, S8-R14).</t>
         </is>
       </c>
-      <c r="H58" s="2" t="inlineStr">
+      <c r="H59" s="2" t="inlineStr">
         <is>
           <t>SV-8655 (TU spec v5 2026-07-29 S8-R9; S8-R13; S8-R14 — dark-mode legibility of every named element; the info icon at ≥ 3:1 in both modes; the Total Hours link affordance/focus in both modes; the ratio is design-token-owned)</t>
         </is>
       </c>
-      <c r="I58" s="2" t="inlineStr"/>
-      <c r="J58" s="2" t="inlineStr"/>
-    </row>
-    <row r="59">
-      <c r="A59" s="2" t="inlineStr">
+      <c r="I59" s="2" t="inlineStr"/>
+      <c r="J59" s="2" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
         <is>
           <t>The per-day breakdown is fetched only when a technician row is expanded</t>
         </is>
       </c>
-      <c r="B59" s="2" t="inlineStr">
+      <c r="B60" s="2" t="inlineStr">
         <is>
           <t>TU — API</t>
         </is>
       </c>
-      <c r="C59" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D59" s="2" t="inlineStr">
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E59" s="2" t="inlineStr">
+      <c r="E60" s="2" t="inlineStr">
         <is>
           <t>1. You are on the Technician Utilization report with rows loaded and browser devtools (network tab) open.
 2. To see the information this test asks for you need the browser's own developer tools: press F12 (or Ctrl+Shift+I; on a Mac Cmd+Option+I) and open the "Network" tab, then reload the page. There is nothing to install — it is built into Chrome, Edge and Firefox.</t>
         </is>
       </c>
-      <c r="F59" s="2" t="inlineStr">
+      <c r="F60" s="2" t="inlineStr">
         <is>
           <t>1. Load the report and inspect the initial data response for per-day content.
 2. Expand a technician row and watch the network traffic.
 3. Collapse and re-expand after a data reload.</t>
         </is>
       </c>
-      <c r="G59" s="2" t="inlineStr">
+      <c r="G60" s="2" t="inlineStr">
         <is>
           <t>1. The initial report payload does NOT ship the day rows.
 2. Expanding a technician row issues an on-demand backend request that returns that technician's per-day breakdown.
@@ -3450,42 +3501,42 @@
 This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Technician Utilization report specification version 5 (S4-R2, S4-R5).</t>
         </is>
       </c>
-      <c r="H59" s="2" t="inlineStr">
+      <c r="H60" s="2" t="inlineStr">
         <is>
           <t>SV-8651 (TU spec v5 2026-07-29 S4-R2; S4-R5)</t>
         </is>
       </c>
-      <c r="I59" s="2" t="inlineStr"/>
-      <c r="J59" s="2" t="inlineStr"/>
-    </row>
-    <row r="60">
-      <c r="A60" s="2" t="inlineStr">
+      <c r="I60" s="2" t="inlineStr"/>
+      <c r="J60" s="2" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
         <is>
           <t>Date-range and location changes trigger a fresh server load</t>
         </is>
       </c>
-      <c r="B60" s="2" t="inlineStr">
+      <c r="B61" s="2" t="inlineStr">
         <is>
           <t>TU — API</t>
         </is>
       </c>
-      <c r="C60" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D60" s="2" t="inlineStr">
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E60" s="2" t="inlineStr">
+      <c r="E61" s="2" t="inlineStr">
         <is>
           <t>1. You are on the Technician Utilization report with rows loaded and browser devtools (network tab) open.
 2. To see the information this test asks for you need the browser's own developer tools: press F12 (or Ctrl+Shift+I; on a Mac Cmd+Option+I) and open the "Network" tab, then reload the page. There is nothing to install — it is built into Chrome, Edge and Firefox.</t>
         </is>
       </c>
-      <c r="F60" s="2" t="inlineStr">
+      <c r="F61" s="2" t="inlineStr">
         <is>
           <t>1. Change the date range and watch the network traffic.
 2. Change the location selection and watch the traffic.
@@ -3493,7 +3544,7 @@
 4. Click several column headers to sort and watch the traffic.</t>
         </is>
       </c>
-      <c r="G60" s="2" t="inlineStr">
+      <c r="G61" s="2" t="inlineStr">
         <is>
           <t>1. A date-range change triggers a fresh server load of the rows.
 2. A location change triggers a fresh server load scoped to the selected set.
@@ -3503,13 +3554,13 @@
 This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Technician Utilization report specification version 5 (S1-R5, S9-R3, S2-R13).</t>
         </is>
       </c>
-      <c r="H60" s="2" t="inlineStr">
+      <c r="H61" s="2" t="inlineStr">
         <is>
           <t>SV-8648 (TU spec v5 2026-07-29 S1-R5; S9-R3; S5 context note; S2-R13; §3)</t>
         </is>
       </c>
-      <c r="I60" s="2" t="inlineStr"/>
-      <c r="J60" s="2" t="inlineStr"/>
+      <c r="I61" s="2" t="inlineStr"/>
+      <c r="J61" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/testrail-import/Report-Suite_Technician-Utilization-Report_testrail-import.xlsx
+++ b/testrail-import/Report-Suite_Technician-Utilization-Report_testrail-import.xlsx
@@ -523,11 +523,13 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>1. The report is listed under the Performance group, labeled "Technician Utilization".
+          <t xml:space="preserve">1. The report is listed under the Performance group, labeled "Technician Utilization".
 2. Clicking it opens the report.
 3. The entry sits BELOW the pre-existing report links — Sales, Technician Efficiency, Advisor Analysis, Shop Efficiency — the new reports are added below those items without moving or disturbing them.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Technician Utilization report specification version 5 (S1-R1).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Technician Utilization report specification version 5 (S1-R1).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
@@ -573,10 +575,12 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>1. Technician A has exactly ONE row.
+          <t xml:space="preserve">1. Technician A has exactly ONE row.
 2. Technician B has NO row - only technicians with clocked time in the selected range at the selected location(s) appear.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Technician Utilization report specification version 5 (S1-R2).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Technician Utilization report specification version 5 (S1-R2).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
@@ -621,11 +625,13 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>1. The date range defaults to the current calendar month (the date picker's "This Month" preset).
+          <t xml:space="preserve">1. The date range defaults to the current calendar month (the date picker's "This Month" preset).
 2. Because a range never extends past now, the current-month default effectively shows the month to date.
 3. The location filter defaults to the user's currently active location (the one in the application's global location switcher).
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Technician Utilization report specification version 5 (S1-R3, S1-R6, S9-R2).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Technician Utilization report specification version 5 (S1-R3, S1-R6, S9-R2).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -671,11 +677,13 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>1. Each range change reloads the report's rows for the new range.
+          <t xml:space="preserve">1. Each range change reloads the report's rows for the new range.
 2. A valid Custom range applies normally.
 3. A Custom span wider than 366 days (matching the largest preset) is rejected - it cannot be applied.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Technician Utilization report specification version 5 (S1-R4, S1-R5).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Technician Utilization report specification version 5 (S1-R4, S1-R5).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -721,11 +729,13 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>1. On the initial load and on every reload (date-range or location change), the data area shows the standard reports loading indicator.
+          <t xml:space="preserve">1. On the initial load and on every reload (date-range or location change), the data area shows the standard reports loading indicator.
 2. The existing rows are replaced only when the new data returns.
 3. The toolbar remains interactive during the load.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Technician Utilization report specification version 5 (S1-R10).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Technician Utilization report specification version 5 (S1-R10).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -773,12 +783,14 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>1. A record that crosses midnight is split by day - each day counts only its own hours; the midnight split is evaluated in the active workplace's time zone.
+          <t xml:space="preserve">1. A record that crosses midnight is split by day - each day counts only its own hours; the midnight split is evaluated in the active workplace's time zone.
 2. A record that starts before the range (or ends after it) counts only the part inside the range.
 3. EVERY record is day-grouped and windowed in a SINGLE report-level time zone - the active workplace's - regardless of the location where it was clocked (a record's day, the current-month boundary, and the midnight split all use that one zone).
 4. This matches the Timesheet Activities report's single-time-zone grouping.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Technician Utilization report specification version 5 (S1-R7).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Technician Utilization report specification version 5 (S1-R7).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -823,9 +835,11 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>1. The Technician Utilization report does NOT appear in the navigation.
----
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Technician Utilization report specification version 5 (S1-N1); where the wording of that specification differs, the behaviour above follows a later product decision, which is the authority.</t>
+          <t xml:space="preserve">1. The Technician Utilization report does NOT appear in the navigation.
+---
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Technician Utilization report specification version 5 (S1-N1); where the wording of that specification differs, the behaviour above follows a later product decision, which is the authority.
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
@@ -872,11 +886,13 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1. Instead of rows, the data area shows exactly: "Empty bays, endless possibilities. Get Going!" (the application's standard reports no-data label).
+          <t xml:space="preserve">1. Instead of rows, the data area shows exactly: "Empty bays, endless possibilities. Get Going!" (the application's standard reports no-data label).
 2. The Summary row is hidden.
 3. Clearing every technician shows the SAME message and hides the Summary row — this version does not use distinct copy for genuinely-no-data vs a cleared filter.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Technician Utilization report specification version 5 (S1-N2, S3-N1, S5-N1, S9-N2).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Technician Utilization report specification version 5 (S1-N2, S3-N1, S5-N1, S9-N2).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -924,15 +940,21 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>1. With a single location in scope the headers appear in exactly this order: Technician, Total Hours, WO Hours, Internal Hours, Utilization %, Est. Lost Labor.
+          <t xml:space="preserve">1. With a single location in scope the headers appear in exactly this order: Technician, Total Hours, WO Hours, Internal Hours, Utilization %, Est. Lost Labor.
 2. Total Hours = all time the technician was clocked in for the range.
 3. WO Hours = time clocked directly to work orders; Internal Hours = time clocked to internal, non-billable activities.
 4. Internal Hours includes ALL internal time - including hours at a location with no configured labor rate.
 5. Hours show two decimal places with NO thousands separator (e.g. "107.70"), rounded from the unrounded hours using round-half-up (a tie rounds away from zero - 0.005 → 0.01).
-6. When more than one location is in scope the Location column also appears, leftmost before Technician. Location is one of the columns in the column-selection control, and with more than one location SELECTED it is already switched on for you - you do not have to turn it on. You can still switch it off. If the signed-in person only has access to ONE location, Location is not offered in the column-selection list at all.
+6. When more than one location is in scope the Location column also appears, leftmost before Technician.
 ---
 Note for the tester: on this build the column does not yet behave this way - record what you see and carry on. The change is with the developers.
-This is the expected behaviour as per Chris Ward's decision of 8/5/2026, recorded in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true. It does NOT match the build tested on 8/4/2026 (build v3.4.1-3d03023) - that change is with the developers - and where the Technician Utilization report specification version 5 (S2-R1, S2-R2, S2-R3, S2-R4, S2-R5, S9-R9) differs, his decision is the authority.</t>
+The Location column is never listed in the column-selection control and you cannot switch it on or off: it appears by itself whenever more than one location is in scope, and is hidden whenever a single location is in scope.
+Note for the tester: the product owner has been asked to confirm this one point and has not answered yet, so do not raise a bug either way — record what you see. The question is in Follow-up-Question-for-Chris-Ward_2026-08-05.xlsx: https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/rulings-2026-08-05/Follow-up-Question-for-Chris-Ward_2026-08-05.xlsx
+---
+---
+This is the expected behaviour as per the Technician Utilization report specification version 5 (S2-R1, S2-R2, S2-R3, S2-R4, S2-R5, S9-R9), and as per the build tested on 8/4/2026 (build v3.4.1-3d03023). The product owner's answer of 8/5/2026 in this file reads both ways on the one point about the Location column, so it has NOT been treated as overriding the specification and he has been asked again: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true
+AUTOMATION: HOLD - waiting on one answer from the product owner about the Location column
+</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
@@ -977,10 +999,12 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>1. Utilization % = work-order hours as a percentage of total clocked hours, computed from the unrounded hours (not from the already-rounded displays).
+          <t xml:space="preserve">1. Utilization % = work-order hours as a percentage of total clocked hours, computed from the unrounded hours (not from the already-rounded displays).
 2. It shows one decimal place followed by a percent sign, rounded round-half-up (66.65% → 66.7%).
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Technician Utilization report specification version 5 (S2-R6, S2-R7).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Technician Utilization report specification version 5 (S2-R6, S2-R7).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -1026,11 +1050,13 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>1. The internal-only technician shows "0.0%".
+          <t xml:space="preserve">1. The internal-only technician shows "0.0%".
 2. No row shows more than 100% - work-order hours are always part of total clocked hours.
 3. The "—" (undefined, total = 0) state is unreachable on a rendered technician or day row, because only technicians with clocked time get rows.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Technician Utilization report specification version 5 (S2-E1, S2-R7).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Technician Utilization report specification version 5 (S2-E1, S2-R7).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
@@ -1078,11 +1104,13 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>1. Est. Lost Labor = the sum, per contributing location, of that location's default labor rate × the technician's internal hours clocked there - summed at full precision, with the technician's total rounded ONCE (round-half-up).
+          <t xml:space="preserve">1. Est. Lost Labor = the sum, per contributing location, of that location's default labor rate × the technician's internal hours clocked there - summed at full precision, with the technician's total rounded ONCE (round-half-up).
 2. In a single-location view it is simply that one location's rate × the technician's internal hours.
 3. The value shows as dollars with two decimals and commas between thousands (e.g. "$1,234.50").
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Technician Utilization report specification version 5 (S2-R8, S2-R9).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Technician Utilization report specification version 5 (S2-R8, S2-R9).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1130,12 +1158,14 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>1. While Est. Lost Labor is shown, the column is pinned to the far right; its cells are bold and its header is bold, matching.
+          <t xml:space="preserve">1. While Est. Lost Labor is shown, the column is pinned to the far right; its cells are bold and its header is bold, matching.
 2. The information icon shows exactly: "Internal hours valued at each location's default labor rate" — on hover, on keyboard focus, and on tap; it is dismissible.
 3. NO column header other than Est. Lost Labor shows the information icon.
 4. Est. Lost Labor can be turned OFF in the Column Selection control; when it is off the column, its bold styling and its information icon are all absent, and the report still works normally.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Technician Utilization report specification version 5 (S2-R10, S2-R11, S8-R4, S8-R6, S8-R7, S8-N1, S10-R3).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Technician Utilization report specification version 5 (S2-R10, S2-R11, S8-R4, S8-R6, S8-R7, S8-N1, S10-R3).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
@@ -1181,11 +1211,13 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>1. Technician A shows "$0.00" - there is nothing to value, regardless of whether the location has a rate configured.
+          <t xml:space="preserve">1. Technician A shows "$0.00" - there is nothing to value, regardless of whether the location has a rate configured.
 2. Technician B also shows "$0.00" - a configured rate of exactly $0.00 is a KNOWN rate that values the hours at $0.00, not "—".
 3. "$0.00" means 'the rate is known and there is nothing (or $0) to value' - a different state from "—" ('the rate is unknown').
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Technician Utilization report specification version 5 (S2-E2).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Technician Utilization report specification version 5 (S2-E2).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -1231,11 +1263,13 @@
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>1. Est. Lost Labor shows "—" (an em-dash), NOT "$0.00" - the rate is unknown, so the value cannot be computed.
+          <t xml:space="preserve">1. Est. Lost Labor shows "—" (an em-dash), NOT "$0.00" - the rate is unknown, so the value cannot be computed.
 2. The "—" cell carries the assistive-technology label "No default labor rate configured" (distinguishing it from "$0.00", which reads as its dollar value).
 3. The technician's Internal Hours column still shows all the internal hours (they are counted even though they cannot be valued).
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Technician Utilization report specification version 5 (S2-E3, S8-R11, S2-R4).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Technician Utilization report specification version 5 (S2-E3, S8-R11, S2-R4).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
@@ -1281,11 +1315,13 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>1. Est. Lost Labor is the sum of the valued (rated-location) portions only - the unrated-location hours are excluded from the dollar amount.
+          <t xml:space="preserve">1. Est. Lost Labor is the sum of the valued (rated-location) portions only - the unrated-location hours are excluded from the dollar amount.
 2. The amount shows as a normal "$X.XX" with NO partial-value indicator in this version - so the row's Est. Lost Labor values fewer hours than its Internal Hours column shows.
 3. This is a documented known limitation (a partial-value indicator is a possible follow-up) - expected behavior, not a defect.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Technician Utilization report specification version 5 (S2-E4).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Technician Utilization report specification version 5 (S2-E4).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
@@ -1332,11 +1368,13 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>1. The technician rows are sorted by Technician name, A to Z.
+          <t xml:space="preserve">1. The technician rows are sorted by Technician name, A to Z.
 2. The Technician header shows the ascending sort indicator.
 3. The active sort header exposes its state to assistive technology (aria-sort = ascending on the Technician header; none on the others).
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Technician Utilization report specification version 5 (S2-R12, S8-R8, S8-R10).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Technician Utilization report specification version 5 (S2-R12, S8-R8, S8-R10).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
@@ -1384,13 +1422,15 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>1. Because Technician-ascending is the active sort on load, the FIRST click on the Technician header sorts it DESCENDING (Z to A).
+          <t xml:space="preserve">1. Because Technician-ascending is the active sort on load, the FIRST click on the Technician header sorts it DESCENDING (Z to A).
 2. Clicking a column that is not the active sort sorts it ascending; clicking the active column again toggles to descending; further clicks only ever toggle ascending↔descending - there is NO third 'cleared' state.
 3. All six columns are sortable.
 4. Sorting is applied on screen to the loaded rows - NO reload/server request happens.
 5. Technicians tied in the sorted column are ordered by Technician name A to Z; two technicians sharing the same display name keep a stable order between renders.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Technician Utilization report specification version 5 (S2-R13, S2-R14).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Technician Utilization report specification version 5 (S2-R13, S2-R14).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
@@ -1436,10 +1476,12 @@
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>1. After the reload, the rows are back to Technician name A to Z (the sort reset).
+          <t xml:space="preserve">1. After the reload, the rows are back to Technician name A to Z (the sort reset).
 2. On the return visit, the sort is again Technician A to Z - sort is NOT persisted (unlike the date range, technician selection, and location selection, which are).
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Technician Utilization report specification version 5 (S2-R15).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Technician Utilization report specification version 5 (S2-R15).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
@@ -1485,11 +1527,13 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>1. Only the technician rows reorder.
+          <t xml:space="preserve">1. Only the technician rows reorder.
 2. The Summary row stays pinned at the bottom.
 3. Each technician's expanded day rows stay under that technician, still in date order (earliest to latest) - they do not re-sort by the clicked column.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Technician Utilization report specification version 5 (S2-R16).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Technician Utilization report specification version 5 (S2-R16).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
@@ -1535,11 +1579,13 @@
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>1. Rows whose Est. Lost Labor is "—" sort to the BOTTOM in BOTH ascending and descending order - they are never floated to the top by reversing direction.
+          <t xml:space="preserve">1. Rows whose Est. Lost Labor is "—" sort to the BOTTOM in BOTH ascending and descending order - they are never floated to the top by reversing direction.
 2. Among themselves, the "—" rows are ordered by Technician name A to Z.
 3. A "$0.00" value is a number, not "—" - it sorts as zero (lowest ascending, above only the — group).
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Technician Utilization report specification version 5 (S2-R17).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Technician Utilization report specification version 5 (S2-R17).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
@@ -1585,12 +1631,14 @@
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>1. A Summary row is pinned to the bottom of the report, labeled "Summary".
+          <t xml:space="preserve">1. A Summary row is pinned to the bottom of the report, labeled "Summary".
 2. It stays visible at the bottom while the rows scroll.
 3. It uses the same number formats as the technician rows.
 4. Its values carry NO label prefix such as "TOTAL:" or "AVG:".
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Technician Utilization report specification version 5 (S3-R1, S3-R2, S3-R6, S3-R7, S8-R5).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Technician Utilization report specification version 5 (S3-R1, S3-R2, S3-R6, S3-R7, S8-R5).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
@@ -1636,11 +1684,13 @@
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>1. Each Summary hours value is the total of that column across the VISIBLE technicians, computed from unrounded hours and rounded once for display (round-half-up).
+          <t xml:space="preserve">1. Each Summary hours value is the total of that column across the VISIBLE technicians, computed from unrounded hours and rounded once for display (round-half-up).
 2. Eye-summing the displayed rows MAY differ from the displayed Summary by 0.01 — one unit in the last decimal (these values are HOURS, not money) — expected in a compute-from-unrounded report, not a defect.
 3. With every technician selected, the Summary row equals the shop totals for the full date range at the selected location(s).
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Technician Utilization report specification version 5 (S3-R3, S5-E1).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Technician Utilization report specification version 5 (S3-R3, S5-E1).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
@@ -1686,10 +1736,12 @@
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>1. The Summary Utilization % shows the WEIGHTED rate - the visible technicians' total work-order hours as a percentage of their total clocked hours, from unrounded hours (10.0% in the example).
+          <t xml:space="preserve">1. The Summary Utilization % shows the WEIGHTED rate - the visible technicians' total work-order hours as a percentage of their total clocked hours, from unrounded hours (10.0% in the example).
 2. It is NOT the average of the per-technician percentages (not 50.0%).
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Technician Utilization report specification version 5 (S3-R4).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Technician Utilization report specification version 5 (S3-R4).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
@@ -1734,11 +1786,13 @@
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>1. The Summary Est. Lost Labor is computed like a row but over all visible technicians' internal hours: rate × internal hours per contributing rated location, summed at full precision and rounded once.
+          <t xml:space="preserve">1. The Summary Est. Lost Labor is computed like a row but over all visible technicians' internal hours: rate × internal hours per contributing rated location, summed at full precision and rounded once.
 2. A visible technician whose value is "—" contributes NOTHING to the sum - so the Summary understates true lost labor whenever any visible technician is "—" or partially valued (documented, expected).
 3. The Summary shows "—" only when EVERY visible technician's Est. Lost Labor is "—".
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Technician Utilization report specification version 5 (S3-R5).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Technician Utilization report specification version 5 (S3-R5).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
@@ -1785,11 +1839,13 @@
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>1. Each technician row has a control to expand and collapse it.
+          <t xml:space="preserve">1. Each technician row has a control to expand and collapse it.
 2. Its accessible name reflects the NEXT action, scoped to that technician: when collapsed it reads Expand, then that technician's name, then daily breakdown (for example: Expand John Smith's daily breakdown); when expanded it reads Collapse, then the same name and words.
 3. The control is keyboard-focusable, toggles on Enter and Space, and exposes its expanded/collapsed state to assistive technology.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Technician Utilization report specification version 5 (S4-R1, S8-R12).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Technician Utilization report specification version 5 (S4-R1, S8-R12).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
@@ -1837,13 +1893,15 @@
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>1. One row appears for each day the technician clocked time in the range, in date order from earliest to latest.
+          <t xml:space="preserve">1. One row appears for each day the technician clocked time in the range, in date order from earliest to latest.
 2. The day rows are not there until you expand the row - they arrive at the moment you expand it (you may briefly see the standard loading indicator in that area), and the rest of the report does not reload.
 3. A day with no clocked time has NO row.
 4. With several locations selected, a day's row POOLS that day's hours across the selected locations - one day row per date, not one per location.
 5. Note for the tester: you do not need developer tools for this test - just watch the screen.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Technician Utilization report specification version 5 (S4-R2, S4-N1, S9-R4).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Technician Utilization report specification version 5 (S4-R2, S4-N1, S9-R4).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
@@ -1889,11 +1947,13 @@
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>1. Each day row shows the same columns, in the same formats, as the technician row - with that day's values.
+          <t xml:space="preserve">1. Each day row shows the same columns, in the same formats, as the technician row - with that day's values.
 2. The day's Est. Lost Labor is valued per location exactly like a technician row (that location's default labor rate × that day's internal hours there).
 3. Hours 2dp / Utilization one decimal + % / dollars with commas - all identical to the row formats, computed from unrounded values and rounded once.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Technician Utilization report specification version 5 (S4-R3, S2-R8).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Technician Utilization report specification version 5 (S4-R3, S2-R8).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
@@ -1941,12 +2001,14 @@
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>1. The control lives in the table's header row (Technician column) - NOT in the toolbar action cluster.
+          <t xml:space="preserve">1. The control lives in the table's header row (Technician column) - NOT in the toolbar action cluster.
 2. If ANY row is collapsed, activating it expands ALL rows; only when EVERY row is already expanded does it collapse all rows (so step 3's activation re-expands the one collapsed row).
 3. Its accessible name reflects the next action: "Expand all technicians" when it will expand, "Collapse all technicians" when every row is already expanded.
 4. It is keyboard-focusable, toggles on Enter/Space, and exposes its state to assistive technology.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Technician Utilization report specification version 5 (S4-R4, S8-R12, S8-R3).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Technician Utilization report specification version 5 (S4-R4, S8-R12, S8-R3).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
@@ -1992,11 +2054,13 @@
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>1. After the reload (date-range or location change), all rows are collapsed - expansion state resets.
+          <t xml:space="preserve">1. After the reload (date-range or location change), all rows are collapsed - expansion state resets.
 2. On a fresh visit, all rows start collapsed - expansion is never persisted.
 3. Deselecting and re-selecting a technician (an on-screen operation) does NOT change the expansion state of the other rows - the expanded row stays expanded.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Technician Utilization report specification version 5 (S4-R5).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Technician Utilization report specification version 5 (S4-R5).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
@@ -2042,11 +2106,13 @@
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>1. The toolbar has a filter labeled "Technician" that allows selecting more than one technician (when several are chosen its label reads, for example, "2 technicians").
+          <t xml:space="preserve">1. The toolbar has a filter labeled "Technician" that allows selecting more than one technician (when several are chosen its label reads, for example, "2 technicians").
 2. On the first visit, EVERY technician is selected.
 3. All technicians' rows are shown.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Technician Utilization report specification version 5 (S5-R1, S5-R2).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Technician Utilization report specification version 5 (S5-R1, S5-R2).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
@@ -2093,13 +2159,15 @@
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>1. The deselected technician's row is hidden.
+          <t xml:space="preserve">1. The deselected technician's row is hidden.
 2. The Summary row recalculates over the technicians that remain visible.
 3. The report does NOT reload - the technician filter works on screen only: the rows and the Summary update straight away, no loading indicator appears in the data area, and the date range does not change.
 4. Re-selecting the technician shows the row again (and the Summary recalculates back).
 5. Note for the tester: you do not need developer tools for this test - just watch the screen.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Technician Utilization report specification version 5 (S5-R3, S5-R4, S5-R5).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Technician Utilization report specification version 5 (S5-R3, S5-R4, S5-R5).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
@@ -2146,12 +2214,14 @@
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>1. "Clear all" sets every currently-listed technician to deselected; "All technicians" selects all technicians at once.
+          <t xml:space="preserve">1. "Clear all" sets every currently-listed technician to deselected; "All technicians" selects all technicians at once.
 2. Selection is tracked as the set of DESELECTED technicians: a technician you have not deselected is selected by default.
 3. After step 3, your deselected technician STAYS deselected across the range change, while the newly-appearing technician is SELECTED (never explicitly deselected).
 4. After step 4, the newly-appearing technician is selected even though you had cleared all - "Clear all" only deselected the technicians listed at the time.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Technician Utilization report specification version 5 (S5-R6, S5-R7, S5-R8, S5-R9).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Technician Utilization report specification version 5 (S5-R6, S5-R7, S5-R8, S5-R9).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
@@ -2197,11 +2267,13 @@
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>1. The two deselected technicians are STILL deselected on return - the deselected set is what persists (saved in this browser, not on the account).
+          <t xml:space="preserve">1. The two deselected technicians are STILL deselected on return - the deselected set is what persists (saved in this browser, not on the account).
 2. All other technicians - including any who appear for the first time - are selected.
 3. The saved date range and location selection are restored alongside.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Technician Utilization report specification version 5 (S5-R10, S1-R8).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Technician Utilization report specification version 5 (S5-R10, S1-R8).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
@@ -2247,11 +2319,13 @@
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>1. Every technician row's Total Hours is rendered as a link (every rendered row has clocked time &gt; 0, so the link always applies).
+          <t xml:space="preserve">1. Every technician row's Total Hours is rendered as a link (every rendered row has clocked time &gt; 0, so the link always applies).
 2. The link is distinguished by more than color - it carries an underline (or equivalent non-color affordance), is keyboard-focusable with a visible focus indicator, and activates on Enter.
 3. The Summary row's Total Hours value is NOT a link.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Technician Utilization report specification version 5 (S6-R1, S6-N1, S8-R14).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Technician Utilization report specification version 5 (S6-R1, S6-N1, S8-R14).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
@@ -2297,11 +2371,13 @@
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>1. The Timesheet Activities report opens in the SAME browser tab.
+          <t xml:space="preserve">1. The Timesheet Activities report opens in the SAME browser tab.
 2. It is already filtered to that technician.
 3. It uses the same date range that was active on the Technician Utilization report.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Technician Utilization report specification version 5 (S6-R2, S6-R3, S6-R4).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Technician Utilization report specification version 5 (S6-R2, S6-R3, S6-R4).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
@@ -2348,11 +2424,13 @@
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>1. The two totals MATCH exactly, to two decimals (these values are hours, not money) - both reports read the same clock records and round the same way (round-half-up, from unrounded values).
+          <t xml:space="preserve">1. The two totals MATCH exactly, to two decimals (these values are hours, not money) - both reports read the same clock records and round the same way (round-half-up, from unrounded values).
 2. Under this exact scope (same range, same single location, closed records) a mismatch IS a defect.
 3. The two documented scope differences (open clocks, multi-location drill-through) are covered by separate cases and are NOT defects.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Technician Utilization report specification version 5 (S1-R9).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Technician Utilization report specification version 5 (S1-R9).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
@@ -2398,11 +2476,13 @@
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>1. The open time is counted UP TO THE MOMENT THE REPORT LOADS - a fixed snapshot taken at load, not a value that keeps ticking on screen (matching how Timesheet Activities treats an open record).
+          <t xml:space="preserve">1. The open time is counted UP TO THE MOMENT THE REPORT LOADS - a fixed snapshot taken at load, not a value that keeps ticking on screen (matching how Timesheet Activities treats an open record).
 2. The two reports, loaded at different moments, MAY differ by the elapsed open time - this is a deliberate scope difference of the reconciliation guarantee, EXPECTED and NOT a defect.
 3. Reloading the Technician Utilization report takes a fresh snapshot (the value grows by the elapsed time).
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Technician Utilization report specification version 5 (S1-R9, S1-E1).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Technician Utilization report specification version 5 (S1-R9, S1-E1).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
@@ -2449,11 +2529,13 @@
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>1. The link passes the technician and the date range ONLY - it does NOT pass the location selection.
+          <t xml:space="preserve">1. The link passes the technician and the date range ONLY - it does NOT pass the location selection.
 2. Timesheet Activities opens for the user's currently active shop, so it shows one location's portion - it will differ from (or be disjoint with) the multi-location row value.
 3. This is a KNOWN drill-through limitation, EXPECTED and NOT a data defect (the same applies when the single selected location is not the active shop).
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Technician Utilization report specification version 5 (S6-R6, S1-R9).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Technician Utilization report specification version 5 (S6-R6, S1-R9).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
@@ -2498,10 +2580,12 @@
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>1. Timesheet Activities opens filtered to that technician.
+          <t xml:space="preserve">1. Timesheet Activities opens filtered to that technician.
 2. The date range covers ONLY that single day.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Technician Utilization report specification version 5 (S6-R5).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Technician Utilization report specification version 5 (S6-R5).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
@@ -2546,11 +2630,13 @@
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>1. The three-dot download menu sits LEFTMOST in the toolbar's action cluster, with the Column Selection control immediately after it.
+          <t xml:space="preserve">1. The three-dot download menu sits LEFTMOST in the toolbar's action cluster, with the Column Selection control immediately after it.
 2. The menu holds four items, worded exactly as they are on Sales By Customer and Sales By Representative: "Download Summary (PDF)", "Download Expanded View (PDF)", "Download Summary (CSV)" and "Download Expanded View (CSV)".
 3. Note for the tester: on this build the four items are worded more briefly - "Summary (PDF)", "Summary (CSV)", "Expanded (PDF)" and "Expanded (CSV)" - without the word "Download". The product owner has decided they must match the other two reports, so record what you see; the change is with the developers.
 ---
-This is the expected behaviour as per Chris Ward's decision of 8/5/2026, recorded in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true. It does NOT match the build tested on 8/4/2026 (build v3.4.1-3d03023) - that change is with the developers - and where the Technician Utilization report specification version 5 (S7-R1, S7-R2, S7-R3, S7-R4, S8-R2) differs, his decision is the authority.</t>
+This is the expected behaviour as per Chris Ward's decision of 8/5/2026, recorded in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true. It does NOT match the build tested on 8/4/2026 (build v3.4.1-3d03023) - that change is with the developers - and where the Technician Utilization report specification version 5 (S7-R1, S7-R2, S7-R3, S7-R4, S8-R2) differs, his decision is the authority.
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
@@ -2595,11 +2681,13 @@
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>1. The Summary PDF shows the technician rows and the Summary row (no day rows); it downloads as "Technician-Utilization-Summary.pdf".
+          <t xml:space="preserve">1. The Summary PDF shows the technician rows and the Summary row (no day rows); it downloads as "Technician-Utilization-Summary.pdf".
 2. The Expanded PDF shows the technician rows, EACH technician's per-day breakdown, and the Summary row; it downloads as "Technician-Utilization-Expanded.pdf".
 3. The PDF filenames are Title-Case as shipped.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Technician Utilization report specification version 5 (S7-R5, S7-R6, S7-R12).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Technician Utilization report specification version 5 (S7-R5, S7-R6, S7-R12).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
@@ -2645,11 +2733,13 @@
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>1. The file downloads as "technician-utilization.csv" (lower-case as shipped, unlike the Title-Case PDFs).
+          <t xml:space="preserve">1. The file downloads as "technician-utilization.csv" (lower-case as shipped, unlike the Title-Case PDFs).
 2. The CSV shows the technician rows and the Summary row - always this summary-level content; it does NOT vary by the summary/expanded choice (no day rows).
 3. Any value containing a comma (e.g. "$1,234.50") is wrapped in double quotes per standard CSV escaping, so the columns parse correctly.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Technician Utilization report specification version 5 (S7-R7, S7-R10, S7-R12).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Technician Utilization report specification version 5 (S7-R7, S7-R10, S7-R12).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
@@ -2697,17 +2787,21 @@
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>1. Every download includes ONLY the technicians currently selected in the technician filter - the deselected technician is absent from all three files.
+          <t xml:space="preserve">1. Every download includes ONLY the technicians currently selected in the technician filter - the deselected technician is absent from all three files.
 2. Every download covers the location(s) currently selected in the location filter and the date range currently active on the report.
 3. With every technician selected, the download covers all technicians for the range at the selected location(s).
-4. Every download (each PDF and the CSV) carries a "Locations:" line naming the location(s) the report was scoped to (exact position in the file is confirmed in the build).
+4. Every download (each PDF and the CSV) carries a "Locations:" line naming the location(s) the report was scoped to.
 5. Every download also mirrors the columns currently shown on screen — a column hidden in the Column Selection control is absent from the files, and a re-shown column comes back.
-6. Note for the tester: when more than one location is in scope the files also carry a Location column. Location is one of the columns in the column-selection control, and with more than one location SELECTED it is already switched on for you - you do not have to turn it on. You can still switch it off. If the signed-in person only has access to ONE location, Location is not offered in the column-selection list at all. With a single location in scope there is no Location column in the files.
+6. Note for the tester: when more than one location is in scope the files also carry a Location column. With a single location in scope there is no Location column in the files.
 ---
 Note for the tester: on this build the column does not yet behave this way - record what you see and carry on. The change is with the developers.
-DO NOT AUTOMATE YET: part of this behaviour is still waiting on an answer from the product owner. Automating it now could lock in the wrong behaviour.
-The open question is in: Follow-up-Question-for-Chris-Ward_2026-08-05.xlsx — https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/rulings-2026-08-05/Follow-up-Question-for-Chris-Ward_2026-08-05.xlsx
-This is the expected behaviour as per Chris Ward's decision of 8/5/2026, recorded in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true. It does NOT match the build tested on 8/4/2026 (build v3.4.1-3d03023) - that change is with the developers - and where the Technician Utilization report specification version 5 (S7-R8, S7-R9, S7-R10, S7-R13, S7-E1, S9-R8) differs, his decision is the authority.</t>
+The Location column is never listed in the column-selection control and you cannot switch it on or off: it appears by itself whenever more than one location is in scope, and is hidden whenever a single location is in scope.
+Note for the tester: the product owner has been asked to confirm this one point and has not answered yet, so do not raise a bug either way — record what you see. The question is in Follow-up-Question-for-Chris-Ward_2026-08-05.xlsx: https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/rulings-2026-08-05/Follow-up-Question-for-Chris-Ward_2026-08-05.xlsx
+---
+---
+This is the expected behaviour as per the Technician Utilization report specification version 5 (S7-R8, S7-R9, S7-R10, S7-R13, S7-E1, S9-R8), and as per the build tested on 8/4/2026 (build v3.4.1-3d03023). The product owner's answer of 8/5/2026 in this file reads both ways on the one point about the Location column, so it has NOT been treated as overriding the specification and he has been asked again: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true
+AUTOMATION: HOLD - waiting on one answer from the product owner about the Location column
+</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
@@ -2754,10 +2848,12 @@
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>1. The downloaded files use the same column order and number formats as the on-screen report, including the "—" rendering for an unknown Est. Lost Labor.
+          <t xml:space="preserve">1. The downloaded files use the same column order and number formats as the on-screen report, including the "—" rendering for an unknown Est. Lost Labor.
 2. Rows in EVERY download are ordered by Technician name A to Z (the default order) - the on-screen column sort is client-side only and is NOT carried into the export.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Technician Utilization report specification version 5 (S7-R10, S7-R10a).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Technician Utilization report specification version 5 (S7-R10, S7-R10a).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
@@ -2803,12 +2899,14 @@
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>1. With an uploaded logo, BOTH PDF views show that logo at the top of the report.
+          <t xml:space="preserve">1. With an uploaded logo, BOTH PDF views show that logo at the top of the report.
 2. The CSV never includes the logo.
 3. With a logo uploaded, that logo appears. If a logo is set but fails to load, the built-in ShopView logo is used instead. If no logo is uploaded at all, NO logo is printed and the text fills the space.
 Note for the tester: on this build a report with no uploaded logo still prints the built-in ShopView logo. The product owner has decided it should print no logo at all, so record what you see; the change is with the developers.
 ---
-This is the expected behaviour as per Chris Ward's decision of 8/5/2026, recorded in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true. It does NOT match the build tested on 8/4/2026 (build v3.4.1-3d03023) - that change is with the developers - and where the Technician Utilization report specification version 5 (S7-R11, S7-N2, S7-N3) differs, his decision is the authority.</t>
+This is the expected behaviour as per Chris Ward's decision of 8/5/2026, recorded in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true. It does NOT match the build tested on 8/4/2026 (build v3.4.1-3d03023) - that change is with the developers - and where the Technician Utilization report specification version 5 (S7-R11, S7-N2, S7-N3) differs, his decision is the authority.
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
@@ -2854,11 +2952,13 @@
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>1. Nothing happens: NO file downloads and NO message appears (not even an error).
+          <t xml:space="preserve">1. Nothing happens: NO file downloads and NO message appears (not even an error).
 2. This silent no-op is the specified behavior for every download option when no technician is selected.
 Known issue: the product does not currently do this — on the build tested, choosing a download with no technician selected still started the download and showed a success message. That is a fault for a developer to fix, not a decision for the product owner. No developer ticket has been raised for it yet, so this test will fail until it is fixed — record what you see and leave the test as it is.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Technician Utilization report specification version 5 (S7-N1).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Technician Utilization report specification version 5 (S7-N1).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
@@ -2904,10 +3004,12 @@
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>1. When a download starts, a success notification reads exactly: "Download started".
+          <t xml:space="preserve">1. When a download starts, a success notification reads exactly: "Download started".
 2. When a download fails, an error notification reads exactly: "Failed to download report".
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Technician Utilization report specification version 5 (§7 notifications table, Story 7 has no S, §7 is the closing reference).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Technician Utilization report specification version 5 (§7 notifications table, Story 7 has no S, §7 is the closing reference).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
@@ -2955,12 +3057,14 @@
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>1. Neither the CSV nor the PDF is produced — no download starts.
+          <t xml:space="preserve">1. Neither the CSV nor the PDF is produced — no download starts.
 2. A clear too-large message appears telling the user to narrow the date range or filters, then try again — the standard wording is "This report is too large to export. Narrow the date range or filters, then try again."
 3. After narrowing below the cap, the downloads work again.
 Known issue: the product does not currently do this. It has been filed for a fix here: https://shopview.atlassian.net/browse/SV-8818
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Technician Utilization report specification version 5 (Story 7 exports).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Technician Utilization report specification version 5 (Story 7 exports).
+AUTOMATION: READY - EXPECT FAIL (SV-8818)
+</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
@@ -3015,7 +3119,7 @@
 5. Note for the tester: write down the exact file name each option gives you. Names for two separate spreadsheet files have never been written down anywhere, so we are collecting them, not checking them - do not fail this test over a file name.
 ---
 This is the expected behaviour as per the Technician Utilization report specification version 5 (S7-R7), which says the spreadsheet always holds the technician rows and the Summary row and does not change with the Summary or Expanded choice. The test exists at all because of Chris Ward's decision of 8/5/2026, recorded in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true - he asked this report's download menu to match Sales By Customer and Sales By Representative, which each offer a spreadsheet for both views, whereas that specification describes only one spreadsheet download. That his answer leaves the menu with four options is our reading of his words and he has not confirmed it. It has not been checked on a build yet.
-AUTOMATION: HOLD - the build does not offer two spreadsheet options yet, and the product owner has not confirmed that it should.
+AUTOMATION: HOLD - the two spreadsheet downloads do not exist yet and the product owner has not confirmed them
 </t>
         </is>
       </c>
@@ -3060,12 +3164,14 @@
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>1. The toolbar has a location filter labeled "Location" - a multi-select and the RIGHTMOST control.
+          <t xml:space="preserve">1. The toolbar has a location filter labeled "Location" - a multi-select and the RIGHTMOST control.
 2. It lists the locations the signed-in user has access to, plus an "All locations" option and a "Clear all" action. (If you only have access to one location, the "All locations" entry is not offered - you see "Clear all" and your one location.)
 3. "All locations" acts as a select-all shortcut: choosing it selects every accessible location; unchecking one location leaves the remaining specific locations selected - the selection is always the concrete set of checked locations.
 4. With more than one location selected, a Location column appears in the table and each row names its location - or reads "Multiple" for a technician whose hours span more than one of them. (Where that column sits on screen is checked by its own test.)
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Technician Utilization report specification version 5 (S9-R1); where the wording of that specification differs, the behaviour above follows a later product decision, which is the authority.</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Technician Utilization report specification version 5 (S9-R1); where the wording of that specification differs, the behaviour above follows a later product decision, which is the authority.
+AUTOMATION: HOLD - this part of the report is not built yet
+</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
@@ -3113,13 +3219,14 @@
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>1. Selecting one, several, or all locations RELOADS the report scoped to that set (unlike the technician filter, which is on-screen only).
+          <t xml:space="preserve">1. Selecting one, several, or all locations RELOADS the report scoped to that set (unlike the technician filter, which is on-screen only).
 2. All metrics (technician rows, per-day rows, and the Summary) reflect only clock records at the selected location(s).
 3. The technician's hours are POOLED across the selected locations into ONE row (one row per technician, not one per location); per-day rows pool the same way.
 4. Scoping never goes beyond the user's accessible locations - a location the user cannot access is never included.
-5. The page itself shows which location(s) the report is currently scoped to (the new on-screen scope indicator - exactly where and how it appears is confirmed in the build).
----
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Technician Utilization report specification version 5 (S9-R3, S9-R4, S9-R5).</t>
+---
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Technician Utilization report specification version 5 (S9-R3, S9-R4, S9-R5).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
@@ -3164,12 +3271,14 @@
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>1. Any saved location the user can no longer access is DROPPED from the restored selection; the remaining accessible locations restore normally.
+          <t xml:space="preserve">1. Any saved location the user can no longer access is DROPPED from the restored selection; the remaining accessible locations restore normally.
 2. If the remaining set is empty, the report falls back to the user's currently active location (the first-visit default).
 3. The report loads without an error in both cases.
 4. The same fallback happens when you deselect every location by hand in the Location filter — the report loads the currently active location's rows rather than showing nothing.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Technician Utilization report specification version 5 (S9-R6, S1-R8, S9-R2, S9-R7).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Technician Utilization report specification version 5 (S9-R6, S1-R8, S9-R2, S9-R7).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
@@ -3215,10 +3324,12 @@
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>1. For the single-location user the Location filter is NOT shown at all — the report simply shows that one location's data.
+          <t xml:space="preserve">1. For the single-location user the Location filter is NOT shown at all — the report simply shows that one location's data.
 2. For the user with access to two or more locations the Location filter IS shown.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Technician Utilization report specification version 5 (S9-N1). Chris Ward confirmed this on 8/5/2026 in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Technician Utilization report specification version 5 (S9-N1). Chris Ward confirmed this on 8/5/2026 in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
@@ -3271,19 +3382,22 @@
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>1. With more than one location in scope a Location column is shown as the LEFTMOST column, before Technician.
+          <t xml:space="preserve">1. With more than one location in scope a Location column is shown as the LEFTMOST column, before Technician.
 2. A technician whose hours were all clocked at one location shows that location's name.
 3. A technician whose hours span more than one selected location shows "Multiple".
 4. An expanded day row shows the exact location when that day's hours were all at one location, and "Multiple" when the day spans more than one.
 5. The Summary row leaves the Location cell blank.
-6. Location is one of the columns in the column-selection control, and with more than one location SELECTED it is already switched on for you - you do not have to turn it on. You can still switch it off. If the signed-in person only has access to ONE location, Location is not offered in the column-selection list at all.
-7. With a single location in scope the Location column is hidden.
-8. Every download — both PDF views and the CSV — includes the Location column in its on-screen leftmost position, carrying the same values you just read on screen.
+6. With a single location in scope the Location column is hidden.
+7. Every download — both PDF views and the CSV — includes the Location column in its on-screen leftmost position, carrying the same values you just read on screen.
 ---
 Note for the tester: on this build the column does not yet behave this way - record what you see and carry on. The change is with the developers.
-DO NOT AUTOMATE YET: part of this behaviour is still waiting on an answer from the product owner. Automating it now could lock in the wrong behaviour.
-The open question is in: Follow-up-Question-for-Chris-Ward_2026-08-05.xlsx — https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/rulings-2026-08-05/Follow-up-Question-for-Chris-Ward_2026-08-05.xlsx
-This is the expected behaviour as per Chris Ward's decision of 8/5/2026, recorded in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true. It does NOT match the build tested on 8/4/2026 (build v3.4.1-3d03023) - that change is with the developers - and where the Technician Utilization report specification version 5 (S9-R9, S9-R10, S8-R15, S10-R4, S7-R13) differs, his decision is the authority.</t>
+The Location column is never listed in the column-selection control and you cannot switch it on or off: it appears by itself whenever more than one location is in scope, and is hidden whenever a single location is in scope.
+Note for the tester: the product owner has been asked to confirm this one point and has not answered yet, so do not raise a bug either way — record what you see. The question is in Follow-up-Question-for-Chris-Ward_2026-08-05.xlsx: https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/rulings-2026-08-05/Follow-up-Question-for-Chris-Ward_2026-08-05.xlsx
+---
+---
+This is the expected behaviour as per the Technician Utilization report specification version 5 (S9-R9, S9-R10, S8-R15, S10-R4, S7-R13), and as per the build tested on 8/4/2026 (build v3.4.1-3d03023). The product owner's answer of 8/5/2026 in this file reads both ways on the one point about the Location column, so it has NOT been treated as overriding the specification and he has been asked again: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true
+AUTOMATION: HOLD - waiting on one answer from the product owner about the Location column
+</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
@@ -3335,8 +3449,8 @@
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>1. The control is an icon button whose tooltip reads "Column Selection", sitting immediately after the three-dot download menu in the toolbar.
-2. Because the button shows an icon and no text, it still carries a name that assistive technology reads out — it is not left unnamed. (The exact wording is confirmed in the build.)
+          <t xml:space="preserve">1. The control is an icon button whose tooltip reads "Column Selection", sitting immediately after the three-dot download menu in the toolbar.
+2. Because the button shows an icon and no text, it still carries a name that assistive technology reads out — it is not left unnamed.
 3. The list offers five toggles — Total Hours, WO Hours, Internal Hours, Utilization % and Est. Lost Labor — and all five are on by default.
 4. Technician is always shown and cannot be turned off (it is not offered as a toggle).
 5. The Location column is never listed here — it appears on its own whenever more than one location is in scope.
@@ -3344,7 +3458,9 @@
 7. Est. Lost Labor can now be hidden like any other column (it used to be always on).
 8. Your column choice is remembered in this browser and is still applied when you come back.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Technician Utilization report specification version 5 (S10-R1, S10-R2, S10-R3, S10-R4, S10-R5, S10-R6, S8-R16).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Technician Utilization report specification version 5 (S10-R1, S10-R2, S10-R3, S10-R4, S10-R5, S10-R6, S8-R16).
+AUTOMATION: HOLD - this part of the report is not built yet
+</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
@@ -3390,11 +3506,13 @@
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>1. The report uses an all-white table: white column headers and white data cells, with NO alternating row shading.
+          <t xml:space="preserve">1. The report uses an all-white table: white column headers and white data cells, with NO alternating row shading.
 2. The toolbar controls run, left to right: the three-dot download menu, the Column Selection control, the date-range picker, the technician filter, and the Location filter (rightmost).
 3. The expand/collapse-all control is NOT a toolbar control - it lives in the table header (in the Technician column).
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Technician Utilization report specification version 5 (S8-R1, S8-R2, S8-R3).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Technician Utilization report specification version 5 (S8-R1, S8-R2, S8-R3).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
@@ -3442,12 +3560,14 @@
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>1. The report supports dark mode: page background, toolbar, cells, the Total Hours link, the information icon, the sort indicator, and the "—" glyph are all clearly legible in dark mode.
+          <t xml:space="preserve">1. The report supports dark mode: page background, toolbar, cells, the Total Hours link, the information icon, the sort indicator, and the "—" glyph are all clearly legible in dark mode.
 2. In BOTH light mode and dark mode the information icon is clearly visible against the background behind it - you can see it at a glance and it does not disappear into the background.
 3. The Total Hours link's non-color affordance and focus indicator apply in both modes.
 4. Note for the tester: you do not need to measure anything and you do not need any tool. Just say whether you can see the icon easily in both modes, and only report it if you cannot. (The design rule behind this is a minimum 3:1 contrast ratio, which the design and engineering team check with a contrast tool - not by hand.)
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Technician Utilization report specification version 5 (S8-R9, S8-R13, S8-R14).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Technician Utilization report specification version 5 (S8-R9, S8-R13, S8-R14).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
@@ -3494,11 +3614,13 @@
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>1. The initial report payload does NOT ship the day rows.
+          <t xml:space="preserve">1. The initial report payload does NOT ship the day rows.
 2. Expanding a technician row issues an on-demand backend request that returns that technician's per-day breakdown.
 3. Because expansion state resets (all collapsed) on any data reload, nothing is lost by the lazy loading - re-expanding fetches fresh day data.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Technician Utilization report specification version 5 (S4-R2, S4-R5).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Technician Utilization report specification version 5 (S4-R2, S4-R5).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
@@ -3546,12 +3668,14 @@
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>1. A date-range change triggers a fresh server load of the rows.
+          <t xml:space="preserve">1. A date-range change triggers a fresh server load of the rows.
 2. A location change triggers a fresh server load scoped to the selected set.
 3. The technician filter causes NO server request - it works on screen only (hide/show + Summary recalculation).
 4. Column sorting causes NO server request - it is applied on screen to the loaded rows.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Technician Utilization report specification version 5 (S1-R5, S9-R3, S2-R13).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Technician Utilization report specification version 5 (S1-R5, S9-R3, S2-R13).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">

--- a/testrail-import/Report-Suite_Technician-Utilization-Report_testrail-import.xlsx
+++ b/testrail-import/Report-Suite_Technician-Utilization-Report_testrail-import.xlsx
@@ -527,7 +527,8 @@
 2. Clicking it opens the report.
 3. The entry sits BELOW the pre-existing report links — Sales, Technician Efficiency, Advisor Analysis, Shop Efficiency — the new reports are added below those items without moving or disturbing them.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Technician Utilization report specification version 5 (S1-R1).
+This is the expected behaviour as per epic SV-8582 and the Technician Utilization report specification version 6 (S1-R1).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -578,7 +579,8 @@
           <t xml:space="preserve">1. Technician A has exactly ONE row.
 2. Technician B has NO row - only technicians with clocked time in the selected range at the selected location(s) appear.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Technician Utilization report specification version 5 (S1-R2).
+This is the expected behaviour as per epic SV-8582 and the Technician Utilization report specification version 6 (S1-R2).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -629,7 +631,8 @@
 2. Because a range never extends past now, the current-month default effectively shows the month to date.
 3. The location filter defaults to the user's currently active location (the one in the application's global location switcher).
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Technician Utilization report specification version 5 (S1-R3, S1-R6, S9-R2).
+This is the expected behaviour as per epic SV-8582 and the Technician Utilization report specification version 6 (S1-R3, S1-R6, S9-R2).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -681,7 +684,8 @@
 2. A valid Custom range applies normally.
 3. A Custom span wider than 366 days (matching the largest preset) is rejected - it cannot be applied.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Technician Utilization report specification version 5 (S1-R4, S1-R5).
+This is the expected behaviour as per epic SV-8582 and the Technician Utilization report specification version 6 (S1-R4, S1-R5).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -733,7 +737,8 @@
 2. The existing rows are replaced only when the new data returns.
 3. The toolbar remains interactive during the load.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Technician Utilization report specification version 5 (S1-R10).
+This is the expected behaviour as per epic SV-8582 and the Technician Utilization report specification version 6 (S1-R10).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -788,7 +793,8 @@
 3. EVERY record is day-grouped and windowed in a SINGLE report-level time zone - the active workplace's - regardless of the location where it was clocked (a record's day, the current-month boundary, and the midnight split all use that one zone).
 4. This matches the Timesheet Activities report's single-time-zone grouping.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Technician Utilization report specification version 5 (S1-R7).
+This is the expected behaviour as per epic SV-8582 and the Technician Utilization report specification version 6 (S1-R7).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -837,7 +843,8 @@
         <is>
           <t xml:space="preserve">1. The Technician Utilization report does NOT appear in the navigation.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Technician Utilization report specification version 5 (S1-N1); where the wording of that specification differs, the behaviour above follows a later product decision, which is the authority.
+This is the expected behaviour as per epic SV-8582 and the Technician Utilization report specification version 6 (S1-N1).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -890,7 +897,8 @@
 2. The Summary row is hidden.
 3. Clearing every technician shows the SAME message and hides the Summary row — this version does not use distinct copy for genuinely-no-data vs a cleared filter.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Technician Utilization report specification version 5 (S1-N2, S3-N1, S5-N1, S9-N2).
+This is the expected behaviour as per epic SV-8582 and the Technician Utilization report specification version 6 (S1-N2, S3-N1, S5-N1, S9-N2).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -945,15 +953,14 @@
 3. WO Hours = time clocked directly to work orders; Internal Hours = time clocked to internal, non-billable activities.
 4. Internal Hours includes ALL internal time - including hours at a location with no configured labor rate.
 5. Hours show two decimal places with NO thousands separator (e.g. "107.70"), rounded from the unrounded hours using round-half-up (a tie rounds away from zero - 0.005 → 0.01).
-6. When more than one location is in scope the Location column also appears, leftmost before Technician.
----
-Note for the tester: on this build the column does not yet behave this way - record what you see and carry on. The change is with the developers.
-The Location column is never listed in the column-selection control and you cannot switch it on or off: it appears by itself whenever more than one location is in scope, and is hidden whenever a single location is in scope.
-Note for the tester: the product owner has been asked to confirm this one point and has not answered yet, so do not raise a bug either way — record what you see. The question is in Follow-up-Question-for-Chris-Ward_2026-08-05.xlsx: https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/rulings-2026-08-05/Follow-up-Question-for-Chris-Ward_2026-08-05.xlsx
----
----
-This is the expected behaviour as per the Technician Utilization report specification version 5 (S2-R1, S2-R2, S2-R3, S2-R4, S2-R5, S9-R9), and as per the build tested on 8/4/2026 (build v3.4.1-3d03023). The product owner's answer of 8/5/2026 in this file reads both ways on the one point about the Location column, so it has NOT been treated as overriding the specification and he has been asked again: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true
-AUTOMATION: HOLD - waiting on one answer from the product owner about the Location column
+6. If your own account can reach more than one location, a Location column also appears, leftmost before Technician, and it is already switched on when you arrive.
+---
+Note for the tester: if the Location column does not behave this way on the build, mark this test Failed and report it - do not change the test.
+Location is one of the columns you can switch on and off in the column-selection control, but only if your own account can reach more than one location: for you it is already switched on when you arrive, and you can switch it off. Someone whose account can reach only one location never sees the column and it is not offered to them in that list.
+---
+This is the expected behaviour as per epic SV-8582 and the Technician Utilization report specification version 6 (S2-R1, S2-R2, S2-R3, S2-R4, S2-R5, S9-R9). Version 6 of that specification, published on 5 August 2026, is what settles the one point about the Location column: it now states in both of its own requirements that the column belongs to anyone whose account can reach more than one location and can be switched on and off in the column-selection control. Chris Ward asked for that change in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
+AUTOMATION: READY
 </t>
         </is>
       </c>
@@ -1002,7 +1009,8 @@
           <t xml:space="preserve">1. Utilization % = work-order hours as a percentage of total clocked hours, computed from the unrounded hours (not from the already-rounded displays).
 2. It shows one decimal place followed by a percent sign, rounded round-half-up (66.65% → 66.7%).
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Technician Utilization report specification version 5 (S2-R6, S2-R7).
+This is the expected behaviour as per epic SV-8582 and the Technician Utilization report specification version 6 (S2-R6, S2-R7).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -1054,7 +1062,8 @@
 2. No row shows more than 100% - work-order hours are always part of total clocked hours.
 3. The "—" (undefined, total = 0) state is unreachable on a rendered technician or day row, because only technicians with clocked time get rows.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Technician Utilization report specification version 5 (S2-E1, S2-R7).
+This is the expected behaviour as per epic SV-8582 and the Technician Utilization report specification version 6 (S2-E1, S2-R7).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -1108,7 +1117,8 @@
 2. In a single-location view it is simply that one location's rate × the technician's internal hours.
 3. The value shows as dollars with two decimals and commas between thousands (e.g. "$1,234.50").
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Technician Utilization report specification version 5 (S2-R8, S2-R9).
+This is the expected behaviour as per epic SV-8582 and the Technician Utilization report specification version 6 (S2-R8, S2-R9).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -1163,7 +1173,8 @@
 3. NO column header other than Est. Lost Labor shows the information icon.
 4. Est. Lost Labor can be turned OFF in the Column Selection control; when it is off the column, its bold styling and its information icon are all absent, and the report still works normally.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Technician Utilization report specification version 5 (S2-R10, S2-R11, S8-R4, S8-R6, S8-R7, S8-N1, S10-R3).
+This is the expected behaviour as per epic SV-8582 and the Technician Utilization report specification version 6 (S2-R10, S2-R11, S8-R4, S8-R6, S8-R7, S8-N1, S10-R3).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -1215,7 +1226,8 @@
 2. Technician B also shows "$0.00" - a configured rate of exactly $0.00 is a KNOWN rate that values the hours at $0.00, not "—".
 3. "$0.00" means 'the rate is known and there is nothing (or $0) to value' - a different state from "—" ('the rate is unknown').
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Technician Utilization report specification version 5 (S2-E2).
+This is the expected behaviour as per epic SV-8582 and the Technician Utilization report specification version 6 (S2-E2).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -1267,7 +1279,8 @@
 2. The "—" cell carries the assistive-technology label "No default labor rate configured" (distinguishing it from "$0.00", which reads as its dollar value).
 3. The technician's Internal Hours column still shows all the internal hours (they are counted even though they cannot be valued).
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Technician Utilization report specification version 5 (S2-E3, S8-R11, S2-R4).
+This is the expected behaviour as per epic SV-8582 and the Technician Utilization report specification version 6 (S2-E3, S8-R11, S2-R4).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -1319,7 +1332,8 @@
 2. The amount shows as a normal "$X.XX" with NO partial-value indicator in this version - so the row's Est. Lost Labor values fewer hours than its Internal Hours column shows.
 3. This is a documented known limitation (a partial-value indicator is a possible follow-up) - expected behavior, not a defect.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Technician Utilization report specification version 5 (S2-E4).
+This is the expected behaviour as per epic SV-8582 and the Technician Utilization report specification version 6 (S2-E4).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -1372,7 +1386,8 @@
 2. The Technician header shows the ascending sort indicator.
 3. The active sort header exposes its state to assistive technology (aria-sort = ascending on the Technician header; none on the others).
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Technician Utilization report specification version 5 (S2-R12, S8-R8, S8-R10).
+This is the expected behaviour as per epic SV-8582 and the Technician Utilization report specification version 6 (S2-R12, S8-R8, S8-R10).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -1428,7 +1443,8 @@
 4. Sorting is applied on screen to the loaded rows - NO reload/server request happens.
 5. Technicians tied in the sorted column are ordered by Technician name A to Z; two technicians sharing the same display name keep a stable order between renders.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Technician Utilization report specification version 5 (S2-R13, S2-R14).
+This is the expected behaviour as per epic SV-8582 and the Technician Utilization report specification version 6 (S2-R13, S2-R14).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -1479,7 +1495,8 @@
           <t xml:space="preserve">1. After the reload, the rows are back to Technician name A to Z (the sort reset).
 2. On the return visit, the sort is again Technician A to Z - sort is NOT persisted (unlike the date range, technician selection, and location selection, which are).
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Technician Utilization report specification version 5 (S2-R15).
+This is the expected behaviour as per epic SV-8582 and the Technician Utilization report specification version 6 (S2-R15).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -1531,7 +1548,8 @@
 2. The Summary row stays pinned at the bottom.
 3. Each technician's expanded day rows stay under that technician, still in date order (earliest to latest) - they do not re-sort by the clicked column.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Technician Utilization report specification version 5 (S2-R16).
+This is the expected behaviour as per epic SV-8582 and the Technician Utilization report specification version 6 (S2-R16).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -1583,7 +1601,8 @@
 2. Among themselves, the "—" rows are ordered by Technician name A to Z.
 3. A "$0.00" value is a number, not "—" - it sorts as zero (lowest ascending, above only the — group).
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Technician Utilization report specification version 5 (S2-R17).
+This is the expected behaviour as per epic SV-8582 and the Technician Utilization report specification version 6 (S2-R17).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -1636,7 +1655,8 @@
 3. It uses the same number formats as the technician rows.
 4. Its values carry NO label prefix such as "TOTAL:" or "AVG:".
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Technician Utilization report specification version 5 (S3-R1, S3-R2, S3-R6, S3-R7, S8-R5).
+This is the expected behaviour as per epic SV-8582 and the Technician Utilization report specification version 6 (S3-R1, S3-R2, S3-R6, S3-R7, S8-R5).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -1688,7 +1708,8 @@
 2. Eye-summing the displayed rows MAY differ from the displayed Summary by 0.01 — one unit in the last decimal (these values are HOURS, not money) — expected in a compute-from-unrounded report, not a defect.
 3. With every technician selected, the Summary row equals the shop totals for the full date range at the selected location(s).
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Technician Utilization report specification version 5 (S3-R3, S5-E1).
+This is the expected behaviour as per epic SV-8582 and the Technician Utilization report specification version 6 (S3-R3, S5-E1).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -1739,7 +1760,8 @@
           <t xml:space="preserve">1. The Summary Utilization % shows the WEIGHTED rate - the visible technicians' total work-order hours as a percentage of their total clocked hours, from unrounded hours (10.0% in the example).
 2. It is NOT the average of the per-technician percentages (not 50.0%).
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Technician Utilization report specification version 5 (S3-R4).
+This is the expected behaviour as per epic SV-8582 and the Technician Utilization report specification version 6 (S3-R4).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -1790,7 +1812,8 @@
 2. A visible technician whose value is "—" contributes NOTHING to the sum - so the Summary understates true lost labor whenever any visible technician is "—" or partially valued (documented, expected).
 3. The Summary shows "—" only when EVERY visible technician's Est. Lost Labor is "—".
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Technician Utilization report specification version 5 (S3-R5).
+This is the expected behaviour as per epic SV-8582 and the Technician Utilization report specification version 6 (S3-R5).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -1843,7 +1866,8 @@
 2. Its accessible name reflects the NEXT action, scoped to that technician: when collapsed it reads Expand, then that technician's name, then daily breakdown (for example: Expand John Smith's daily breakdown); when expanded it reads Collapse, then the same name and words.
 3. The control is keyboard-focusable, toggles on Enter and Space, and exposes its expanded/collapsed state to assistive technology.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Technician Utilization report specification version 5 (S4-R1, S8-R12).
+This is the expected behaviour as per epic SV-8582 and the Technician Utilization report specification version 6 (S4-R1, S8-R12).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -1899,7 +1923,8 @@
 4. With several locations selected, a day's row POOLS that day's hours across the selected locations - one day row per date, not one per location.
 5. Note for the tester: you do not need developer tools for this test - just watch the screen.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Technician Utilization report specification version 5 (S4-R2, S4-N1, S9-R4).
+This is the expected behaviour as per epic SV-8582 and the Technician Utilization report specification version 6 (S4-R2, S4-N1, S9-R4).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -1951,7 +1976,8 @@
 2. The day's Est. Lost Labor is valued per location exactly like a technician row (that location's default labor rate × that day's internal hours there).
 3. Hours 2dp / Utilization one decimal + % / dollars with commas - all identical to the row formats, computed from unrounded values and rounded once.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Technician Utilization report specification version 5 (S4-R3, S2-R8).
+This is the expected behaviour as per epic SV-8582 and the Technician Utilization report specification version 6 (S4-R3, S2-R8).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -2006,7 +2032,8 @@
 3. Its accessible name reflects the next action: "Expand all technicians" when it will expand, "Collapse all technicians" when every row is already expanded.
 4. It is keyboard-focusable, toggles on Enter/Space, and exposes its state to assistive technology.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Technician Utilization report specification version 5 (S4-R4, S8-R12, S8-R3).
+This is the expected behaviour as per epic SV-8582 and the Technician Utilization report specification version 6 (S4-R4, S8-R12, S8-R3).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -2058,7 +2085,8 @@
 2. On a fresh visit, all rows start collapsed - expansion is never persisted.
 3. Deselecting and re-selecting a technician (an on-screen operation) does NOT change the expansion state of the other rows - the expanded row stays expanded.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Technician Utilization report specification version 5 (S4-R5).
+This is the expected behaviour as per epic SV-8582 and the Technician Utilization report specification version 6 (S4-R5).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -2110,7 +2138,8 @@
 2. On the first visit, EVERY technician is selected.
 3. All technicians' rows are shown.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Technician Utilization report specification version 5 (S5-R1, S5-R2).
+This is the expected behaviour as per epic SV-8582 and the Technician Utilization report specification version 6 (S5-R1, S5-R2).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -2165,7 +2194,8 @@
 4. Re-selecting the technician shows the row again (and the Summary recalculates back).
 5. Note for the tester: you do not need developer tools for this test - just watch the screen.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Technician Utilization report specification version 5 (S5-R3, S5-R4, S5-R5).
+This is the expected behaviour as per epic SV-8582 and the Technician Utilization report specification version 6 (S5-R3, S5-R4, S5-R5).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -2219,7 +2249,8 @@
 3. After step 3, your deselected technician STAYS deselected across the range change, while the newly-appearing technician is SELECTED (never explicitly deselected).
 4. After step 4, the newly-appearing technician is selected even though you had cleared all - "Clear all" only deselected the technicians listed at the time.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Technician Utilization report specification version 5 (S5-R6, S5-R7, S5-R8, S5-R9).
+This is the expected behaviour as per epic SV-8582 and the Technician Utilization report specification version 6 (S5-R6, S5-R7, S5-R8, S5-R9).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -2271,7 +2302,8 @@
 2. All other technicians - including any who appear for the first time - are selected.
 3. The saved date range and location selection are restored alongside.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Technician Utilization report specification version 5 (S5-R10, S1-R8).
+This is the expected behaviour as per epic SV-8582 and the Technician Utilization report specification version 6 (S5-R10, S1-R8).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -2323,7 +2355,8 @@
 2. The link is distinguished by more than color - it carries an underline (or equivalent non-color affordance), is keyboard-focusable with a visible focus indicator, and activates on Enter.
 3. The Summary row's Total Hours value is NOT a link.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Technician Utilization report specification version 5 (S6-R1, S6-N1, S8-R14).
+This is the expected behaviour as per epic SV-8582 and the Technician Utilization report specification version 6 (S6-R1, S6-N1, S8-R14).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -2375,7 +2408,8 @@
 2. It is already filtered to that technician.
 3. It uses the same date range that was active on the Technician Utilization report.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Technician Utilization report specification version 5 (S6-R2, S6-R3, S6-R4).
+This is the expected behaviour as per epic SV-8582 and the Technician Utilization report specification version 6 (S6-R2, S6-R3, S6-R4).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -2428,7 +2462,8 @@
 2. Under this exact scope (same range, same single location, closed records) a mismatch IS a defect.
 3. The two documented scope differences (open clocks, multi-location drill-through) are covered by separate cases and are NOT defects.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Technician Utilization report specification version 5 (S1-R9).
+This is the expected behaviour as per epic SV-8582 and the Technician Utilization report specification version 6 (S1-R9).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -2480,7 +2515,8 @@
 2. The two reports, loaded at different moments, MAY differ by the elapsed open time - this is a deliberate scope difference of the reconciliation guarantee, EXPECTED and NOT a defect.
 3. Reloading the Technician Utilization report takes a fresh snapshot (the value grows by the elapsed time).
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Technician Utilization report specification version 5 (S1-R9, S1-E1).
+This is the expected behaviour as per epic SV-8582 and the Technician Utilization report specification version 6 (S1-R9, S1-E1).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -2533,7 +2569,8 @@
 2. Timesheet Activities opens for the user's currently active shop, so it shows one location's portion - it will differ from (or be disjoint with) the multi-location row value.
 3. This is a KNOWN drill-through limitation, EXPECTED and NOT a data defect (the same applies when the single selected location is not the active shop).
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Technician Utilization report specification version 5 (S6-R6, S1-R9).
+This is the expected behaviour as per epic SV-8582 and the Technician Utilization report specification version 6 (S6-R6, S1-R9).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -2583,7 +2620,8 @@
           <t xml:space="preserve">1. Timesheet Activities opens filtered to that technician.
 2. The date range covers ONLY that single day.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Technician Utilization report specification version 5 (S6-R5).
+This is the expected behaviour as per epic SV-8582 and the Technician Utilization report specification version 6 (S6-R5).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -2634,7 +2672,8 @@
 2. The menu holds four items, worded exactly as they are on Sales By Customer and Sales By Representative: "Download Summary (PDF)", "Download Expanded View (PDF)", "Download Summary (CSV)" and "Download Expanded View (CSV)".
 3. Note for the tester: on this build the four items are worded more briefly - "Summary (PDF)", "Summary (CSV)", "Expanded (PDF)" and "Expanded (CSV)" - without the word "Download". The product owner has decided they must match the other two reports, so record what you see; the change is with the developers.
 ---
-This is the expected behaviour as per Chris Ward's decision of 8/5/2026, recorded in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true. It does NOT match the build tested on 8/4/2026 (build v3.4.1-3d03023) - that change is with the developers - and where the Technician Utilization report specification version 5 (S7-R1, S7-R2, S7-R3, S7-R4, S8-R2) differs, his decision is the authority.
+This is the expected behaviour as per epic SV-8582 and Chris Ward's decision of 8/5/2026, recorded in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true; where the Technician Utilization report specification version 6 (S7-R1, S7-R2, S7-R3, S7-R4, S8-R2) differs, his decision is the authority.
+Last checked against build v3.4.1-3d03023 on 8/4/2026, which does not yet match it - that change is with the developers.
 AUTOMATION: READY
 </t>
         </is>
@@ -2685,7 +2724,8 @@
 2. The Expanded PDF shows the technician rows, EACH technician's per-day breakdown, and the Summary row; it downloads as "Technician-Utilization-Expanded.pdf".
 3. The PDF filenames are Title-Case as shipped.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Technician Utilization report specification version 5 (S7-R5, S7-R6, S7-R12).
+This is the expected behaviour as per epic SV-8582 and the Technician Utilization report specification version 6 (S7-R5, S7-R6, S7-R12).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -2737,7 +2777,8 @@
 2. The CSV shows the technician rows and the Summary row - always this summary-level content; it does NOT vary by the summary/expanded choice (no day rows).
 3. Any value containing a comma (e.g. "$1,234.50") is wrapped in double quotes per standard CSV escaping, so the columns parse correctly.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Technician Utilization report specification version 5 (S7-R7, S7-R10, S7-R12).
+This is the expected behaviour as per epic SV-8582 and the Technician Utilization report specification version 6 (S7-R7, S7-R10, S7-R12).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -2792,15 +2833,14 @@
 3. With every technician selected, the download covers all technicians for the range at the selected location(s).
 4. Every download (each PDF and the CSV) carries a "Locations:" line naming the location(s) the report was scoped to.
 5. Every download also mirrors the columns currently shown on screen — a column hidden in the Column Selection control is absent from the files, and a re-shown column comes back.
-6. Note for the tester: when more than one location is in scope the files also carry a Location column. With a single location in scope there is no Location column in the files.
----
-Note for the tester: on this build the column does not yet behave this way - record what you see and carry on. The change is with the developers.
-The Location column is never listed in the column-selection control and you cannot switch it on or off: it appears by itself whenever more than one location is in scope, and is hidden whenever a single location is in scope.
-Note for the tester: the product owner has been asked to confirm this one point and has not answered yet, so do not raise a bug either way — record what you see. The question is in Follow-up-Question-for-Chris-Ward_2026-08-05.xlsx: https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/rulings-2026-08-05/Follow-up-Question-for-Chris-Ward_2026-08-05.xlsx
----
----
-This is the expected behaviour as per the Technician Utilization report specification version 5 (S7-R8, S7-R9, S7-R10, S7-R13, S7-E1, S9-R8), and as per the build tested on 8/4/2026 (build v3.4.1-3d03023). The product owner's answer of 8/5/2026 in this file reads both ways on the one point about the Location column, so it has NOT been treated as overriding the specification and he has been asked again: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true
-AUTOMATION: HOLD - waiting on one answer from the product owner about the Location column
+6. Note for the tester: the files carry a Location column whenever that column is showing on screen. If your own account can reach only one location there is no Location column on screen and none in the files.
+---
+Note for the tester: if the Location column does not behave this way on the build, mark this test Failed and report it - do not change the test.
+Location is one of the columns you can switch on and off in the column-selection control, but only if your own account can reach more than one location: for you it is already switched on when you arrive, and you can switch it off. Someone whose account can reach only one location never sees the column and it is not offered to them in that list.
+---
+This is the expected behaviour as per epic SV-8582 and the Technician Utilization report specification version 6 (S7-R8, S7-R9, S7-R10, S7-R13, S7-E1, S9-R8). Version 6 of that specification, published on 5 August 2026, is what settles the one point about the Location column: it now states in both of its own requirements that the column belongs to anyone whose account can reach more than one location and can be switched on and off in the column-selection control. Chris Ward asked for that change in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
+AUTOMATION: READY
 </t>
         </is>
       </c>
@@ -2851,7 +2891,8 @@
           <t xml:space="preserve">1. The downloaded files use the same column order and number formats as the on-screen report, including the "—" rendering for an unknown Est. Lost Labor.
 2. Rows in EVERY download are ordered by Technician name A to Z (the default order) - the on-screen column sort is client-side only and is NOT carried into the export.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Technician Utilization report specification version 5 (S7-R10, S7-R10a).
+This is the expected behaviour as per epic SV-8582 and the Technician Utilization report specification version 6 (S7-R10, S7-R10a).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -2904,7 +2945,8 @@
 3. With a logo uploaded, that logo appears. If a logo is set but fails to load, the built-in ShopView logo is used instead. If no logo is uploaded at all, NO logo is printed and the text fills the space.
 Note for the tester: on this build a report with no uploaded logo still prints the built-in ShopView logo. The product owner has decided it should print no logo at all, so record what you see; the change is with the developers.
 ---
-This is the expected behaviour as per Chris Ward's decision of 8/5/2026, recorded in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true. It does NOT match the build tested on 8/4/2026 (build v3.4.1-3d03023) - that change is with the developers - and where the Technician Utilization report specification version 5 (S7-R11, S7-N2, S7-N3) differs, his decision is the authority.
+This is the expected behaviour as per epic SV-8582 and Chris Ward's decision of 8/5/2026, recorded in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true; where the Technician Utilization report specification version 6 (S7-R11, S7-N2, S7-N3) differs, his decision is the authority.
+Last checked against build v3.4.1-3d03023 on 8/4/2026, which does not yet match it - that change is with the developers.
 AUTOMATION: READY
 </t>
         </is>
@@ -2956,7 +2998,8 @@
 2. This silent no-op is the specified behavior for every download option when no technician is selected.
 Known issue: the product does not currently do this — on the build tested, choosing a download with no technician selected still started the download and showed a success message. That is a fault for a developer to fix, not a decision for the product owner. No developer ticket has been raised for it yet, so this test will fail until it is fixed — record what you see and leave the test as it is.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Technician Utilization report specification version 5 (S7-N1).
+This is the expected behaviour as per epic SV-8582 and the Technician Utilization report specification version 6 (S7-N1).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -3007,7 +3050,8 @@
           <t xml:space="preserve">1. When a download starts, a success notification reads exactly: "Download started".
 2. When a download fails, an error notification reads exactly: "Failed to download report".
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Technician Utilization report specification version 5 (§7 notifications table, Story 7 has no S, §7 is the closing reference).
+This is the expected behaviour as per epic SV-8582 and the Technician Utilization report specification version 6 (§7 notifications table, Story 7 has no S, §7 is the closing reference).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -3062,7 +3106,8 @@
 3. After narrowing below the cap, the downloads work again.
 Known issue: the product does not currently do this. It has been filed for a fix here: https://shopview.atlassian.net/browse/SV-8818
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Technician Utilization report specification version 5 (Story 7 exports).
+This is the expected behaviour as per epic SV-8582 and the Technician Utilization report specification version 6 (Story 7 exports).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY - EXPECT FAIL (SV-8818)
 </t>
         </is>
@@ -3118,12 +3163,17 @@
 4. In both files any value with a comma in it (for example "$1,234.50") is wrapped in double quotes, so the columns still line up when you open it.
 5. Note for the tester: write down the exact file name each option gives you. Names for two separate spreadsheet files have never been written down anywhere, so we are collecting them, not checking them - do not fail this test over a file name.
 ---
-This is the expected behaviour as per the Technician Utilization report specification version 5 (S7-R7), which says the spreadsheet always holds the technician rows and the Summary row and does not change with the Summary or Expanded choice. The test exists at all because of Chris Ward's decision of 8/5/2026, recorded in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true - he asked this report's download menu to match Sales By Customer and Sales By Representative, which each offer a spreadsheet for both views, whereas that specification describes only one spreadsheet download. That his answer leaves the menu with four options is our reading of his words and he has not confirmed it. It has not been checked on a build yet.
+This is the expected behaviour as per epic SV-8582 and the Technician Utilization report specification version 6 (S7-R7), which says the spreadsheet always holds the technician rows and the Summary row and does not change with the Summary or Expanded choice. The test exists at all because of Chris Ward's decision of 8/5/2026, recorded in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true - he asked this report's download menu to match Sales By Customer and Sales By Representative, which each offer a spreadsheet for both views, whereas that written description covers only one spreadsheet download. That his answer leaves the menu with four options is our reading of his words and he has not confirmed it.
+This has not yet been checked against a build.
 AUTOMATION: HOLD - the two spreadsheet downloads do not exist yet and the product owner has not confirmed them
 </t>
         </is>
       </c>
-      <c r="H51" s="2" t="inlineStr"/>
+      <c r="H51" s="2" t="inlineStr">
+        <is>
+          <t>SV-8654 (TU spec v5 2026-07-29 S7-R7 - the spreadsheet is always summary-level; a SECOND spreadsheet option exists only because of Chris Ward's answer T2-6 option B of 2026-08-05)</t>
+        </is>
+      </c>
       <c r="I51" s="2" t="inlineStr"/>
       <c r="J51" s="2" t="inlineStr"/>
     </row>
@@ -3169,7 +3219,8 @@
 3. "All locations" acts as a select-all shortcut: choosing it selects every accessible location; unchecking one location leaves the remaining specific locations selected - the selection is always the concrete set of checked locations.
 4. With more than one location selected, a Location column appears in the table and each row names its location - or reads "Multiple" for a technician whose hours span more than one of them. (Where that column sits on screen is checked by its own test.)
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Technician Utilization report specification version 5 (S9-R1); where the wording of that specification differs, the behaviour above follows a later product decision, which is the authority.
+This is the expected behaviour as per epic SV-8582 and the Technician Utilization report specification version 6 (S9-R1); where the wording of that specification differs, the behaviour above follows Chris Ward's later decision, recorded in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true, which is the authority.
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: HOLD - this part of the report is not built yet
 </t>
         </is>
@@ -3224,7 +3275,8 @@
 3. The technician's hours are POOLED across the selected locations into ONE row (one row per technician, not one per location); per-day rows pool the same way.
 4. Scoping never goes beyond the user's accessible locations - a location the user cannot access is never included.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Technician Utilization report specification version 5 (S9-R3, S9-R4, S9-R5).
+This is the expected behaviour as per epic SV-8582 and the Technician Utilization report specification version 6 (S9-R3, S9-R4, S9-R5).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -3276,7 +3328,8 @@
 3. The report loads without an error in both cases.
 4. The same fallback happens when you deselect every location by hand in the Location filter — the report loads the currently active location's rows rather than showing nothing.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Technician Utilization report specification version 5 (S9-R6, S1-R8, S9-R2, S9-R7).
+This is the expected behaviour as per epic SV-8582 and the Technician Utilization report specification version 6 (S9-R6, S1-R8, S9-R2, S9-R7).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -3327,7 +3380,8 @@
           <t xml:space="preserve">1. For the single-location user the Location filter is NOT shown at all — the report simply shows that one location's data.
 2. For the user with access to two or more locations the Location filter IS shown.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Technician Utilization report specification version 5 (S9-N1). Chris Ward confirmed this on 8/5/2026 in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true
+This is the expected behaviour as per epic SV-8582 and the Technician Utilization report specification version 6 (S9-N1). Chris Ward confirmed this on 8/5/2026 in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -3382,21 +3436,20 @@
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. With more than one location in scope a Location column is shown as the LEFTMOST column, before Technician.
+          <t xml:space="preserve">1. Signed in as someone whose account can reach more than one location, a Location column is shown as the LEFTMOST column, before Technician, already switched on.
 2. A technician whose hours were all clocked at one location shows that location's name.
 3. A technician whose hours span more than one selected location shows "Multiple".
 4. An expanded day row shows the exact location when that day's hours were all at one location, and "Multiple" when the day spans more than one.
 5. The Summary row leaves the Location cell blank.
-6. With a single location in scope the Location column is hidden.
+6. Signed in as someone whose account can reach only one location, the Location column is not shown at all and is not offered in the column-selection control.
 7. Every download — both PDF views and the CSV — includes the Location column in its on-screen leftmost position, carrying the same values you just read on screen.
 ---
-Note for the tester: on this build the column does not yet behave this way - record what you see and carry on. The change is with the developers.
-The Location column is never listed in the column-selection control and you cannot switch it on or off: it appears by itself whenever more than one location is in scope, and is hidden whenever a single location is in scope.
-Note for the tester: the product owner has been asked to confirm this one point and has not answered yet, so do not raise a bug either way — record what you see. The question is in Follow-up-Question-for-Chris-Ward_2026-08-05.xlsx: https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/rulings-2026-08-05/Follow-up-Question-for-Chris-Ward_2026-08-05.xlsx
----
----
-This is the expected behaviour as per the Technician Utilization report specification version 5 (S9-R9, S9-R10, S8-R15, S10-R4, S7-R13), and as per the build tested on 8/4/2026 (build v3.4.1-3d03023). The product owner's answer of 8/5/2026 in this file reads both ways on the one point about the Location column, so it has NOT been treated as overriding the specification and he has been asked again: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true
-AUTOMATION: HOLD - waiting on one answer from the product owner about the Location column
+Note for the tester: if the Location column does not behave this way on the build, mark this test Failed and report it - do not change the test.
+Location is one of the columns you can switch on and off in the column-selection control, but only if your own account can reach more than one location: for you it is already switched on when you arrive, and you can switch it off. Someone whose account can reach only one location never sees the column and it is not offered to them in that list.
+---
+This is the expected behaviour as per epic SV-8582 and the Technician Utilization report specification version 6 (S9-R9, S9-R10, S8-R15, S10-R4, S7-R13). Version 6 of that specification, published on 5 August 2026, is what settles the one point about the Location column: it now states in both of its own requirements that the column belongs to anyone whose account can reach more than one location and can be switched on and off in the column-selection control. Chris Ward asked for that change in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
+AUTOMATION: READY
 </t>
         </is>
       </c>
@@ -3458,7 +3511,8 @@
 7. Est. Lost Labor can now be hidden like any other column (it used to be always on).
 8. Your column choice is remembered in this browser and is still applied when you come back.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Technician Utilization report specification version 5 (S10-R1, S10-R2, S10-R3, S10-R4, S10-R5, S10-R6, S8-R16).
+This is the expected behaviour as per epic SV-8582 and the Technician Utilization report specification version 6 (S10-R1, S10-R2, S10-R3, S10-R4, S10-R5, S10-R6, S8-R16).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: HOLD - this part of the report is not built yet
 </t>
         </is>
@@ -3510,7 +3564,8 @@
 2. The toolbar controls run, left to right: the three-dot download menu, the Column Selection control, the date-range picker, the technician filter, and the Location filter (rightmost).
 3. The expand/collapse-all control is NOT a toolbar control - it lives in the table header (in the Technician column).
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Technician Utilization report specification version 5 (S8-R1, S8-R2, S8-R3).
+This is the expected behaviour as per epic SV-8582 and the Technician Utilization report specification version 6 (S8-R1, S8-R2, S8-R3).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -3565,7 +3620,8 @@
 3. The Total Hours link's non-color affordance and focus indicator apply in both modes.
 4. Note for the tester: you do not need to measure anything and you do not need any tool. Just say whether you can see the icon easily in both modes, and only report it if you cannot. (The design rule behind this is a minimum 3:1 contrast ratio, which the design and engineering team check with a contrast tool - not by hand.)
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Technician Utilization report specification version 5 (S8-R9, S8-R13, S8-R14).
+This is the expected behaviour as per epic SV-8582 and the Technician Utilization report specification version 6 (S8-R9, S8-R13, S8-R14).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -3618,7 +3674,8 @@
 2. Expanding a technician row issues an on-demand backend request that returns that technician's per-day breakdown.
 3. Because expansion state resets (all collapsed) on any data reload, nothing is lost by the lazy loading - re-expanding fetches fresh day data.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Technician Utilization report specification version 5 (S4-R2, S4-R5).
+This is the expected behaviour as per epic SV-8582 and the Technician Utilization report specification version 6 (S4-R2, S4-R5).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -3673,7 +3730,8 @@
 3. The technician filter causes NO server request - it works on screen only (hide/show + Summary recalculation).
 4. Column sorting causes NO server request - it is applied on screen to the loaded rows.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Technician Utilization report specification version 5 (S1-R5, S9-R3, S2-R13).
+This is the expected behaviour as per epic SV-8582 and the Technician Utilization report specification version 6 (S1-R5, S9-R3, S2-R13).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>

--- a/testrail-import/Report-Suite_Technician-Utilization-Report_testrail-import.xlsx
+++ b/testrail-import/Report-Suite_Technician-Utilization-Report_testrail-import.xlsx
@@ -523,14 +523,13 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. The report is listed under the Performance group, labeled "Technician Utilization".
+          <t>1. The report is listed under the Performance group, labeled "Technician Utilization".
 2. Clicking it opens the report.
 3. The entry sits BELOW the pre-existing report links — Sales, Technician Efficiency, Advisor Analysis, Shop Efficiency — the new reports are added below those items without moving or disturbing them.
 ---
-This is the expected behaviour as per epic SV-8582 and the Technician Utilization report specification version 6 (S1-R1).
-Last checked against build v3.4.1-3d03023 on 8/4/2026.
-AUTOMATION: READY
-</t>
+This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Technician Utilization report specification version 7 (S1-R1), read on 11 August 2026.
+Last checked against build v3.5-16cf83f on 8/6/2026.
+AUTOMATION: READY</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
@@ -576,13 +575,12 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Technician A has exactly ONE row.
+          <t>1. Technician A has exactly ONE row.
 2. Technician B has NO row - only technicians with clocked time in the selected range at the selected location(s) appear.
 ---
-This is the expected behaviour as per epic SV-8582 and the Technician Utilization report specification version 6 (S1-R2).
-Last checked against build v3.4.1-3d03023 on 8/4/2026.
-AUTOMATION: READY
-</t>
+This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Technician Utilization report specification version 7 (S1-R2), read on 11 August 2026.
+Last checked against build v3.5-16cf83f on 8/6/2026.
+AUTOMATION: READY</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
@@ -627,14 +625,17 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. The date range defaults to the current calendar month (the date picker's "This Month" preset).
+          <t>1. The date range defaults to the current calendar month (the date picker's "This Month" preset).
 2. Because a range never extends past now, the current-month default effectively shows the month to date.
 3. The location filter defaults to the user's currently active location (the one in the application's global location switcher).
----
-This is the expected behaviour as per epic SV-8582 and the Technician Utilization report specification version 6 (S1-R3, S1-R6, S9-R2).
-Last checked against build v3.4.1-3d03023 on 8/4/2026.
-AUTOMATION: READY
-</t>
+What you should see today: the Location filter reads "All locations" and the table returns rows from both Staging Heavy Duty - 9919 and Staging Lethbridge - 4310, instead of opening on the one location shown beside your name. The date range half is correct - it reads This Month. This is a known problem and it is already reported - see https://shopview.atlassian.net/browse/SV-8943
+· If you see exactly that, mark this test FAILED and do not raise anything new.
+· If it fails in a DIFFERENT way from what is described above, that is a NEW problem - please report it.
+· If it PASSES, the fix has shipped: tell the QA lead so the ticket can be closed and this note removed.
+---
+This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Technician Utilization report specification version 7 (S1-R3, S1-R6, S9-R2), read on 11 August 2026.
+Last checked against build v3.5-16cf83f on 8/6/2026.
+AUTOMATION: READY - EXPECT FAIL (SV-8943)</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -680,14 +681,13 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Each range change reloads the report's rows for the new range.
+          <t>1. Each range change reloads the report's rows for the new range.
 2. A valid Custom range applies normally.
 3. A Custom span wider than 366 days (matching the largest preset) is rejected - it cannot be applied.
 ---
-This is the expected behaviour as per epic SV-8582 and the Technician Utilization report specification version 6 (S1-R4, S1-R5).
-Last checked against build v3.4.1-3d03023 on 8/4/2026.
-AUTOMATION: READY
-</t>
+This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Technician Utilization report specification version 7 (S1-R4, S1-R5), read on 11 August 2026.
+Last checked against build v3.5-16cf83f on 8/6/2026.
+AUTOMATION: READY</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -733,14 +733,13 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. On the initial load and on every reload (date-range or location change), the data area shows the standard reports loading indicator.
+          <t>1. On the initial load and on every reload (date-range or location change), the data area shows the standard reports loading indicator.
 2. The existing rows are replaced only when the new data returns.
 3. The toolbar remains interactive during the load.
 ---
-This is the expected behaviour as per epic SV-8582 and the Technician Utilization report specification version 6 (S1-R10).
-Last checked against build v3.4.1-3d03023 on 8/4/2026.
-AUTOMATION: READY
-</t>
+This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Technician Utilization report specification version 7 (S1-R10), read on 11 August 2026.
+Last checked against build v3.5-16cf83f on 8/6/2026.
+AUTOMATION: READY</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -788,15 +787,14 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. A record that crosses midnight is split by day - each day counts only its own hours; the midnight split is evaluated in the active workplace's time zone.
+          <t>1. A record that crosses midnight is split by day - each day counts only its own hours; the midnight split is evaluated in the active workplace's time zone.
 2. A record that starts before the range (or ends after it) counts only the part inside the range.
 3. EVERY record is day-grouped and windowed in a SINGLE report-level time zone - the active workplace's - regardless of the location where it was clocked (a record's day, the current-month boundary, and the midnight split all use that one zone).
 4. This matches the Timesheet Activities report's single-time-zone grouping.
 ---
-This is the expected behaviour as per epic SV-8582 and the Technician Utilization report specification version 6 (S1-R7).
-Last checked against build v3.4.1-3d03023 on 8/4/2026.
-AUTOMATION: READY
-</t>
+This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Technician Utilization report specification version 7 (S1-R7), read on 11 August 2026.
+Last checked against build v3.5-16cf83f on 8/6/2026.
+AUTOMATION: READY</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -841,12 +839,11 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. The Technician Utilization report does NOT appear in the navigation.
----
-This is the expected behaviour as per epic SV-8582 and the Technician Utilization report specification version 6 (S1-N1).
-Last checked against build v3.4.1-3d03023 on 8/4/2026.
-AUTOMATION: READY
-</t>
+          <t>1. The Technician Utilization report does NOT appear in the navigation.
+---
+This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Technician Utilization report specification version 7 (S1-N1), read on 11 August 2026.
+Last checked against build v3.5-16cf83f on 8/6/2026.
+AUTOMATION: HOLD - needs a second sign-in as a user without reports access, and there is one shared sign-in on this environment</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
@@ -893,14 +890,13 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Instead of rows, the data area shows exactly: "Empty bays, endless possibilities. Get Going!" (the application's standard reports no-data label).
+          <t>1. Instead of rows, the data area shows exactly: "Empty bays, endless possibilities. Get Going!" (the application's standard reports no-data label).
 2. The Summary row is hidden.
 3. Clearing every technician shows the SAME message and hides the Summary row — this version does not use distinct copy for genuinely-no-data vs a cleared filter.
 ---
-This is the expected behaviour as per epic SV-8582 and the Technician Utilization report specification version 6 (S1-N2, S3-N1, S5-N1, S9-N2).
-Last checked against build v3.4.1-3d03023 on 8/4/2026.
-AUTOMATION: READY
-</t>
+This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Technician Utilization report specification version 7 (S1-N2, S3-N1, S5-N1, S9-N2), read on 11 August 2026.
+Last checked against build v3.5-16cf83f on 8/6/2026.
+AUTOMATION: READY</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -948,7 +944,7 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. With a single location in scope the headers appear in exactly this order: Technician, Total Hours, WO Hours, Internal Hours, Utilization %, Est. Lost Labor.
+          <t>1. With a single location in scope the headers appear in exactly this order: Technician, Total Hours, WO Hours, Internal Hours, Utilization %, Est. Lost Labor.
 2. Total Hours = all time the technician was clocked in for the range.
 3. WO Hours = time clocked directly to work orders; Internal Hours = time clocked to internal, non-billable activities.
 4. Internal Hours includes ALL internal time - including hours at a location with no configured labor rate.
@@ -958,10 +954,9 @@
 Note for the tester: if the Location column does not behave this way on the build, mark this test Failed and report it - do not change the test.
 Location is one of the columns you can switch on and off in the column-selection control, but only if your own account can reach more than one location: for you it is already switched on when you arrive, and you can switch it off. Someone whose account can reach only one location never sees the column and it is not offered to them in that list.
 ---
-This is the expected behaviour as per epic SV-8582 and the Technician Utilization report specification version 6 (S2-R1, S2-R2, S2-R3, S2-R4, S2-R5, S9-R9). Version 6 of that specification, published on 5 August 2026, is what settles the one point about the Location column: it now states in both of its own requirements that the column belongs to anyone whose account can reach more than one location and can be switched on and off in the column-selection control. Chris Ward asked for that change in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true
-Last checked against build v3.4.1-3d03023 on 8/4/2026.
-AUTOMATION: READY
-</t>
+This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Technician Utilization report specification version 7 (S2-R1, S2-R2, S2-R3, S2-R4, S2-R5, S9-R9), read on 11 August 2026. Version 6 of that specification, published on 5 August 2026, is what settles the one point about the Location column: it now states in both of its own requirements that the column belongs to anyone whose account can reach more than one location and can be switched on and off in the column-selection control. Chris Ward asked for that change in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true, read on 11 August 2026
+Last checked against build v3.5-16cf83f on 8/6/2026.
+AUTOMATION: READY</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
@@ -1006,13 +1001,12 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Utilization % = work-order hours as a percentage of total clocked hours, computed from the unrounded hours (not from the already-rounded displays).
+          <t>1. Utilization % = work-order hours as a percentage of total clocked hours, computed from the unrounded hours (not from the already-rounded displays).
 2. It shows one decimal place followed by a percent sign, rounded round-half-up (66.65% → 66.7%).
 ---
-This is the expected behaviour as per epic SV-8582 and the Technician Utilization report specification version 6 (S2-R6, S2-R7).
-Last checked against build v3.4.1-3d03023 on 8/4/2026.
-AUTOMATION: READY
-</t>
+This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Technician Utilization report specification version 7 (S2-R6, S2-R7), read on 11 August 2026.
+Last checked against build v3.5-16cf83f on 8/6/2026.
+AUTOMATION: READY</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -1058,14 +1052,13 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. The internal-only technician shows "0.0%".
+          <t>1. The internal-only technician shows "0.0%".
 2. No row shows more than 100% - work-order hours are always part of total clocked hours.
 3. The "—" (undefined, total = 0) state is unreachable on a rendered technician or day row, because only technicians with clocked time get rows.
 ---
-This is the expected behaviour as per epic SV-8582 and the Technician Utilization report specification version 6 (S2-E1, S2-R7).
-Last checked against build v3.4.1-3d03023 on 8/4/2026.
-AUTOMATION: READY
-</t>
+This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Technician Utilization report specification version 7 (S2-E1, S2-R7), read on 11 August 2026.
+Last checked against build v3.5-16cf83f on 8/6/2026.
+AUTOMATION: READY</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
@@ -1113,14 +1106,13 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Est. Lost Labor = the sum, per contributing location, of that location's default labor rate × the technician's internal hours clocked there - summed at full precision, with the technician's total rounded ONCE (round-half-up).
+          <t>1. Est. Lost Labor = the sum, per contributing location, of that location's default labor rate × the technician's internal hours clocked there - summed at full precision, with the technician's total rounded ONCE (round-half-up).
 2. In a single-location view it is simply that one location's rate × the technician's internal hours.
 3. The value shows as dollars with two decimals and commas between thousands (e.g. "$1,234.50").
 ---
-This is the expected behaviour as per epic SV-8582 and the Technician Utilization report specification version 6 (S2-R8, S2-R9).
-Last checked against build v3.4.1-3d03023 on 8/4/2026.
-AUTOMATION: READY
-</t>
+This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Technician Utilization report specification version 7 (S2-R8, S2-R9), read on 11 August 2026.
+Last checked against build v3.5-16cf83f on 8/6/2026.
+AUTOMATION: READY</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1168,15 +1160,14 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. While Est. Lost Labor is shown, the column is pinned to the far right; its cells are bold and its header is bold, matching.
+          <t>1. While Est. Lost Labor is shown, the column is pinned to the far right; its cells are bold and its header is bold, matching.
 2. The information icon shows exactly: "Internal hours valued at each location's default labor rate" — on hover, on keyboard focus, and on tap; it is dismissible.
 3. NO column header other than Est. Lost Labor shows the information icon.
 4. Est. Lost Labor can be turned OFF in the Column Selection control; when it is off the column, its bold styling and its information icon are all absent, and the report still works normally.
 ---
-This is the expected behaviour as per epic SV-8582 and the Technician Utilization report specification version 6 (S2-R10, S2-R11, S8-R4, S8-R6, S8-R7, S8-N1, S10-R3).
-Last checked against build v3.4.1-3d03023 on 8/4/2026.
-AUTOMATION: READY
-</t>
+This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Technician Utilization report specification version 7 (S2-R10, S2-R11, S8-R4, S8-R6, S8-R7, S8-N1, S10-R3), read on 11 August 2026.
+Last checked against build v3.5-16cf83f on 8/6/2026.
+AUTOMATION: READY</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
@@ -1222,14 +1213,13 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Technician A shows "$0.00" - there is nothing to value, regardless of whether the location has a rate configured.
+          <t>1. Technician A shows "$0.00" - there is nothing to value, regardless of whether the location has a rate configured.
 2. Technician B also shows "$0.00" - a configured rate of exactly $0.00 is a KNOWN rate that values the hours at $0.00, not "—".
 3. "$0.00" means 'the rate is known and there is nothing (or $0) to value' - a different state from "—" ('the rate is unknown').
 ---
-This is the expected behaviour as per epic SV-8582 and the Technician Utilization report specification version 6 (S2-E2).
-Last checked against build v3.4.1-3d03023 on 8/4/2026.
-AUTOMATION: READY
-</t>
+This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Technician Utilization report specification version 7 (S2-E2), read on 11 August 2026.
+Last checked against build v3.5-16cf83f on 8/6/2026.
+AUTOMATION: READY</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -1275,14 +1265,13 @@
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Est. Lost Labor shows "—" (an em-dash), NOT "$0.00" - the rate is unknown, so the value cannot be computed.
+          <t>1. Est. Lost Labor shows "—" (an em-dash), NOT "$0.00" - the rate is unknown, so the value cannot be computed.
 2. The "—" cell carries the assistive-technology label "No default labor rate configured" (distinguishing it from "$0.00", which reads as its dollar value).
 3. The technician's Internal Hours column still shows all the internal hours (they are counted even though they cannot be valued).
 ---
-This is the expected behaviour as per epic SV-8582 and the Technician Utilization report specification version 6 (S2-E3, S8-R11, S2-R4).
-Last checked against build v3.4.1-3d03023 on 8/4/2026.
-AUTOMATION: READY
-</t>
+This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Technician Utilization report specification version 7 (S2-E3, S8-R11, S2-R4), read on 11 August 2026.
+Last checked against build v3.5-16cf83f on 8/6/2026.
+AUTOMATION: HOLD - no location on this environment is set up without a default labor rate, so the em-dash state cannot be produced</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
@@ -1328,14 +1317,13 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Est. Lost Labor is the sum of the valued (rated-location) portions only - the unrated-location hours are excluded from the dollar amount.
+          <t>1. Est. Lost Labor is the sum of the valued (rated-location) portions only - the unrated-location hours are excluded from the dollar amount.
 2. The amount shows as a normal "$X.XX" with NO partial-value indicator in this version - so the row's Est. Lost Labor values fewer hours than its Internal Hours column shows.
 3. This is a documented known limitation (a partial-value indicator is a possible follow-up) - expected behavior, not a defect.
 ---
-This is the expected behaviour as per epic SV-8582 and the Technician Utilization report specification version 6 (S2-E4).
-Last checked against build v3.4.1-3d03023 on 8/4/2026.
-AUTOMATION: READY
-</t>
+This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Technician Utilization report specification version 7 (S2-E4), read on 11 August 2026.
+Last checked against build v3.5-16cf83f on 8/6/2026.
+AUTOMATION: HOLD - no location on this environment is set up without a default labor rate, so a part-valued row cannot be produced</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
@@ -1382,14 +1370,13 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. The technician rows are sorted by Technician name, A to Z.
+          <t>1. The technician rows are sorted by Technician name, A to Z.
 2. The Technician header shows the ascending sort indicator.
 3. The active sort header exposes its state to assistive technology (aria-sort = ascending on the Technician header; none on the others).
 ---
-This is the expected behaviour as per epic SV-8582 and the Technician Utilization report specification version 6 (S2-R12, S8-R8, S8-R10).
-Last checked against build v3.4.1-3d03023 on 8/4/2026.
-AUTOMATION: READY
-</t>
+This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Technician Utilization report specification version 7 (S2-R12, S8-R8, S8-R10), read on 11 August 2026.
+Last checked against build v3.5-16cf83f on 8/6/2026.
+AUTOMATION: READY</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
@@ -1437,16 +1424,15 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Because Technician-ascending is the active sort on load, the FIRST click on the Technician header sorts it DESCENDING (Z to A).
+          <t>1. Because Technician-ascending is the active sort on load, the FIRST click on the Technician header sorts it DESCENDING (Z to A).
 2. Clicking a column that is not the active sort sorts it ascending; clicking the active column again toggles to descending; further clicks only ever toggle ascending↔descending - there is NO third 'cleared' state.
 3. All six columns are sortable.
 4. Sorting is applied on screen to the loaded rows - NO reload/server request happens.
 5. Technicians tied in the sorted column are ordered by Technician name A to Z; two technicians sharing the same display name keep a stable order between renders.
 ---
-This is the expected behaviour as per epic SV-8582 and the Technician Utilization report specification version 6 (S2-R13, S2-R14).
-Last checked against build v3.4.1-3d03023 on 8/4/2026.
-AUTOMATION: READY
-</t>
+This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Technician Utilization report specification version 7 (S2-R13, S2-R14), read on 11 August 2026.
+Last checked against build v3.5-4795eee on 8/10/2026.
+AUTOMATION: READY</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
@@ -1492,13 +1478,12 @@
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. After the reload, the rows are back to Technician name A to Z (the sort reset).
+          <t>1. After the reload, the rows are back to Technician name A to Z (the sort reset).
 2. On the return visit, the sort is again Technician A to Z - sort is NOT persisted (unlike the date range, technician selection, and location selection, which are).
 ---
-This is the expected behaviour as per epic SV-8582 and the Technician Utilization report specification version 6 (S2-R15).
-Last checked against build v3.4.1-3d03023 on 8/4/2026.
-AUTOMATION: READY
-</t>
+This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Technician Utilization report specification version 7 (S2-R15), read on 11 August 2026.
+Last checked against build v3.5-16cf83f on 8/6/2026.
+AUTOMATION: READY</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
@@ -1544,14 +1529,13 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Only the technician rows reorder.
+          <t>1. Only the technician rows reorder.
 2. The Summary row stays pinned at the bottom.
 3. Each technician's expanded day rows stay under that technician, still in date order (earliest to latest) - they do not re-sort by the clicked column.
 ---
-This is the expected behaviour as per epic SV-8582 and the Technician Utilization report specification version 6 (S2-R16).
-Last checked against build v3.4.1-3d03023 on 8/4/2026.
-AUTOMATION: READY
-</t>
+This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Technician Utilization report specification version 7 (S2-R16), read on 11 August 2026.
+Last checked against build v3.5-16cf83f on 8/6/2026.
+AUTOMATION: READY</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
@@ -1597,14 +1581,13 @@
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Rows whose Est. Lost Labor is "—" sort to the BOTTOM in BOTH ascending and descending order - they are never floated to the top by reversing direction.
+          <t>1. Rows whose Est. Lost Labor is "—" sort to the BOTTOM in BOTH ascending and descending order - they are never floated to the top by reversing direction.
 2. Among themselves, the "—" rows are ordered by Technician name A to Z.
 3. A "$0.00" value is a number, not "—" - it sorts as zero (lowest ascending, above only the — group).
 ---
-This is the expected behaviour as per epic SV-8582 and the Technician Utilization report specification version 6 (S2-R17).
-Last checked against build v3.4.1-3d03023 on 8/4/2026.
-AUTOMATION: READY
-</t>
+This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Technician Utilization report specification version 7 (S2-R17), read on 11 August 2026.
+Last checked against build v3.5-16cf83f on 8/6/2026.
+AUTOMATION: HOLD - no technician on this environment has an em-dash in Est. Lost Labor, because both locations have a default labor rate</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
@@ -1650,15 +1633,14 @@
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. A Summary row is pinned to the bottom of the report, labeled "Summary".
+          <t>1. A Summary row is pinned to the bottom of the report, labeled "Summary".
 2. It stays visible at the bottom while the rows scroll.
 3. It uses the same number formats as the technician rows.
 4. Its values carry NO label prefix such as "TOTAL:" or "AVG:".
 ---
-This is the expected behaviour as per epic SV-8582 and the Technician Utilization report specification version 6 (S3-R1, S3-R2, S3-R6, S3-R7, S8-R5).
-Last checked against build v3.4.1-3d03023 on 8/4/2026.
-AUTOMATION: READY
-</t>
+This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Technician Utilization report specification version 7 (S3-R1, S3-R2, S3-R6, S3-R7, S8-R5), read on 11 August 2026.
+Last checked against build v3.5-16cf83f on 8/6/2026.
+AUTOMATION: READY</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
@@ -1704,14 +1686,13 @@
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Each Summary hours value is the total of that column across the VISIBLE technicians, computed from unrounded hours and rounded once for display (round-half-up).
+          <t>1. Each Summary hours value is the total of that column across the VISIBLE technicians, computed from unrounded hours and rounded once for display (round-half-up).
 2. Eye-summing the displayed rows MAY differ from the displayed Summary by 0.01 — one unit in the last decimal (these values are HOURS, not money) — expected in a compute-from-unrounded report, not a defect.
 3. With every technician selected, the Summary row equals the shop totals for the full date range at the selected location(s).
 ---
-This is the expected behaviour as per epic SV-8582 and the Technician Utilization report specification version 6 (S3-R3, S5-E1).
-Last checked against build v3.4.1-3d03023 on 8/4/2026.
-AUTOMATION: READY
-</t>
+This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Technician Utilization report specification version 7 (S3-R3, S5-E1), read on 11 August 2026.
+Last checked against build v3.5-16cf83f on 8/6/2026.
+AUTOMATION: READY</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
@@ -1757,13 +1738,12 @@
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. The Summary Utilization % shows the WEIGHTED rate - the visible technicians' total work-order hours as a percentage of their total clocked hours, from unrounded hours (10.0% in the example).
+          <t>1. The Summary Utilization % shows the WEIGHTED rate - the visible technicians' total work-order hours as a percentage of their total clocked hours, from unrounded hours (10.0% in the example).
 2. It is NOT the average of the per-technician percentages (not 50.0%).
 ---
-This is the expected behaviour as per epic SV-8582 and the Technician Utilization report specification version 6 (S3-R4).
-Last checked against build v3.4.1-3d03023 on 8/4/2026.
-AUTOMATION: READY
-</t>
+This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Technician Utilization report specification version 7 (S3-R4), read on 11 August 2026.
+Last checked against build v3.5-16cf83f on 8/6/2026.
+AUTOMATION: READY</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
@@ -1808,14 +1788,13 @@
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. The Summary Est. Lost Labor is computed like a row but over all visible technicians' internal hours: rate × internal hours per contributing rated location, summed at full precision and rounded once.
+          <t>1. The Summary Est. Lost Labor is computed like a row but over all visible technicians' internal hours: rate × internal hours per contributing rated location, summed at full precision and rounded once.
 2. A visible technician whose value is "—" contributes NOTHING to the sum - so the Summary understates true lost labor whenever any visible technician is "—" or partially valued (documented, expected).
 3. The Summary shows "—" only when EVERY visible technician's Est. Lost Labor is "—".
 ---
-This is the expected behaviour as per epic SV-8582 and the Technician Utilization report specification version 6 (S3-R5).
-Last checked against build v3.4.1-3d03023 on 8/4/2026.
-AUTOMATION: READY
-</t>
+This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Technician Utilization report specification version 7 (S3-R5), read on 11 August 2026.
+Last checked against build v3.5-16cf83f on 8/6/2026.
+AUTOMATION: READY</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
@@ -1862,14 +1841,17 @@
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Each technician row has a control to expand and collapse it.
+          <t>1. Each technician row has a control to expand and collapse it.
 2. Its accessible name reflects the NEXT action, scoped to that technician: when collapsed it reads Expand, then that technician's name, then daily breakdown (for example: Expand John Smith's daily breakdown); when expanded it reads Collapse, then the same name and words.
 3. The control is keyboard-focusable, toggles on Enter and Space, and exposes its expanded/collapsed state to assistive technology.
----
-This is the expected behaviour as per epic SV-8582 and the Technician Utilization report specification version 6 (S4-R1, S8-R12).
-Last checked against build v3.4.1-3d03023 on 8/4/2026.
-AUTOMATION: READY
-</t>
+What you should see today: items 1 and 2 pass - the control is there and its name reads "Expand Christian Pitts's daily breakdown" and then "Collapse Christian Pitts's daily breakdown" - but item 3 does not: the control never reports its open or closed state to a screen reader. This is a known problem and it is already reported - see https://shopview.atlassian.net/browse/SV-8953
+· If you see exactly that, mark this test FAILED and do not raise anything new.
+· If it fails in a DIFFERENT way from what is described above, that is a NEW problem - please report it.
+· If it PASSES, the fix has shipped: tell the QA lead so the ticket can be closed and this note removed.
+---
+This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Technician Utilization report specification version 7 (S4-R1, S8-R12), read on 11 August 2026.
+Last checked against build v3.5-4795eee on 8/10/2026.
+AUTOMATION: READY - EXPECT FAIL (SV-8953)</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
@@ -1917,16 +1899,15 @@
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. One row appears for each day the technician clocked time in the range, in date order from earliest to latest.
+          <t>1. One row appears for each day the technician clocked time in the range, in date order from earliest to latest.
 2. The day rows are not there until you expand the row - they arrive at the moment you expand it (you may briefly see the standard loading indicator in that area), and the rest of the report does not reload.
 3. A day with no clocked time has NO row.
 4. With several locations selected, a day's row POOLS that day's hours across the selected locations - one day row per date, not one per location.
 5. Note for the tester: you do not need developer tools for this test - just watch the screen.
 ---
-This is the expected behaviour as per epic SV-8582 and the Technician Utilization report specification version 6 (S4-R2, S4-N1, S9-R4).
-Last checked against build v3.4.1-3d03023 on 8/4/2026.
-AUTOMATION: READY
-</t>
+This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Technician Utilization report specification version 7 (S4-R2, S4-N1, S9-R4), read on 11 August 2026.
+Last checked against build v3.5-16cf83f on 8/6/2026.
+AUTOMATION: READY</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
@@ -1972,14 +1953,13 @@
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Each day row shows the same columns, in the same formats, as the technician row - with that day's values.
+          <t>1. Each day row shows the same columns, in the same formats, as the technician row - with that day's values.
 2. The day's Est. Lost Labor is valued per location exactly like a technician row (that location's default labor rate × that day's internal hours there).
 3. Hours 2dp / Utilization one decimal + % / dollars with commas - all identical to the row formats, computed from unrounded values and rounded once.
 ---
-This is the expected behaviour as per epic SV-8582 and the Technician Utilization report specification version 6 (S4-R3, S2-R8).
-Last checked against build v3.4.1-3d03023 on 8/4/2026.
-AUTOMATION: READY
-</t>
+This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Technician Utilization report specification version 7 (S4-R3, S2-R8), read on 11 August 2026.
+Last checked against build v3.5-16cf83f on 8/6/2026.
+AUTOMATION: READY</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
@@ -2027,15 +2007,18 @@
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. The control lives in the table's header row (Technician column) - NOT in the toolbar action cluster.
+          <t>1. The control lives in the table's header row (Technician column) - NOT in the toolbar action cluster.
 2. If ANY row is collapsed, activating it expands ALL rows; only when EVERY row is already expanded does it collapse all rows (so step 3's activation re-expands the one collapsed row).
 3. Its accessible name reflects the next action: "Expand all technicians" when it will expand, "Collapse all technicians" when every row is already expanded.
 4. It is keyboard-focusable, toggles on Enter/Space, and exposes its state to assistive technology.
----
-This is the expected behaviour as per epic SV-8582 and the Technician Utilization report specification version 6 (S4-R4, S8-R12, S8-R3).
-Last checked against build v3.4.1-3d03023 on 8/4/2026.
-AUTOMATION: READY
-</t>
+What you should see today: items 1, 2 and 3 pass, but item 4 does not: the control never reports its open or closed state to a screen reader, only its name. This is a known problem and it is already reported - see https://shopview.atlassian.net/browse/SV-8953
+· If you see exactly that, mark this test FAILED and do not raise anything new.
+· If it fails in a DIFFERENT way from what is described above, that is a NEW problem - please report it.
+· If it PASSES, the fix has shipped: tell the QA lead so the ticket can be closed and this note removed.
+---
+This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Technician Utilization report specification version 7 (S4-R4, S8-R12, S8-R3), read on 11 August 2026.
+Last checked against build v3.5-16cf83f on 8/6/2026.
+AUTOMATION: READY - EXPECT FAIL (SV-8953)</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
@@ -2081,14 +2064,13 @@
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. After the reload (date-range or location change), all rows are collapsed - expansion state resets.
+          <t>1. After the reload (date-range or location change), all rows are collapsed - expansion state resets.
 2. On a fresh visit, all rows start collapsed - expansion is never persisted.
 3. Deselecting and re-selecting a technician (an on-screen operation) does NOT change the expansion state of the other rows - the expanded row stays expanded.
 ---
-This is the expected behaviour as per epic SV-8582 and the Technician Utilization report specification version 6 (S4-R5).
-Last checked against build v3.4.1-3d03023 on 8/4/2026.
-AUTOMATION: READY
-</t>
+This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Technician Utilization report specification version 7 (S4-R5), read on 11 August 2026.
+Last checked against build v3.5-16cf83f on 8/6/2026.
+AUTOMATION: READY</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
@@ -2134,14 +2116,13 @@
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. The toolbar has a filter labeled "Technician" that allows selecting more than one technician (when several are chosen its label reads, for example, "2 technicians").
+          <t>1. The toolbar has a filter labeled "Filter by Technician" that allows selecting more than one technician (when several are chosen its label reads, for example, "2 technicians").
 2. On the first visit, EVERY technician is selected.
 3. All technicians' rows are shown.
 ---
-This is the expected behaviour as per epic SV-8582 and the Technician Utilization report specification version 6 (S5-R1, S5-R2).
-Last checked against build v3.4.1-3d03023 on 8/4/2026.
-AUTOMATION: READY
-</t>
+This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Technician Utilization report specification version 7 (S5-R1, S5-R2), read on 11 August 2026.
+Last checked against build v3.5-4795eee on 8/10/2026.
+AUTOMATION: READY</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
@@ -2188,16 +2169,19 @@
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. The deselected technician's row is hidden.
+          <t>1. The deselected technician's row is hidden.
 2. The Summary row recalculates over the technicians that remain visible.
 3. The report does NOT reload - the technician filter works on screen only: the rows and the Summary update straight away, no loading indicator appears in the data area, and the date range does not change.
 4. Re-selecting the technician shows the row again (and the Summary recalculates back).
 5. Note for the tester: you do not need developer tools for this test - just watch the screen.
----
-This is the expected behaviour as per epic SV-8582 and the Technician Utilization report specification version 6 (S5-R3, S5-R4, S5-R5).
-Last checked against build v3.4.1-3d03023 on 8/4/2026.
-AUTOMATION: READY
-</t>
+What you should see today: items 1, 2 and 4 pass - the row hides, the Summary recalculates and re-selecting brings it back - but item 3 does not: the report reloads from the server when you tick or untick a technician. This is a known problem and it is already reported - see https://shopview.atlassian.net/browse/SV-8946
+· If you see exactly that, mark this test FAILED and do not raise anything new.
+· If it fails in a DIFFERENT way from what is described above, that is a NEW problem - please report it.
+· If it PASSES, the fix has shipped: tell the QA lead so the ticket can be closed and this note removed.
+---
+This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Technician Utilization report specification version 7 (S5-R3, S5-R4, S5-R5), read on 11 August 2026.
+Last checked against build v3.5-4795eee on 8/10/2026.
+AUTOMATION: READY - EXPECT FAIL (SV-8946)</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
@@ -2244,15 +2228,18 @@
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. "Clear all" sets every currently-listed technician to deselected; "All technicians" selects all technicians at once.
+          <t>1. "Clear all" sets every currently-listed technician to deselected; "Select all" selects all technicians at once.
 2. Selection is tracked as the set of DESELECTED technicians: a technician you have not deselected is selected by default.
 3. After step 3, your deselected technician STAYS deselected across the range change, while the newly-appearing technician is SELECTED (never explicitly deselected).
 4. After step 4, the newly-appearing technician is selected even though you had cleared all - "Clear all" only deselected the technicians listed at the time.
----
-This is the expected behaviour as per epic SV-8582 and the Technician Utilization report specification version 6 (S5-R6, S5-R7, S5-R8, S5-R9).
-Last checked against build v3.4.1-3d03023 on 8/4/2026.
-AUTOMATION: READY
-</t>
+What you should see today: the control that selects everybody is labelled "All technicians" and not "Select all". The behaviour itself passes - clearing everybody really does deselect the whole list, and a technician you deselected stays deselected when you change the date range. This is a known problem and it is already reported - see https://shopview.atlassian.net/browse/SV-8947
+· If you see exactly that, mark this test FAILED and do not raise anything new.
+· If it fails in a DIFFERENT way from what is described above, that is a NEW problem - please report it.
+· If it PASSES, the fix has shipped: tell the QA lead so the ticket can be closed and this note removed.
+---
+This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Technician Utilization report specification version 7 (S5-R6, S5-R7, S5-R8, S5-R9), read on 11 August 2026.
+Last checked against build v3.5-16cf83f on 8/6/2026.
+AUTOMATION: READY - EXPECT FAIL (SV-8947)</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
@@ -2298,14 +2285,13 @@
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. The two deselected technicians are STILL deselected on return - the deselected set is what persists (saved in this browser, not on the account).
+          <t>1. The two deselected technicians are STILL deselected on return - the deselected set is what persists (saved in this browser, not on the account).
 2. All other technicians - including any who appear for the first time - are selected.
 3. The saved date range and location selection are restored alongside.
 ---
-This is the expected behaviour as per epic SV-8582 and the Technician Utilization report specification version 6 (S5-R10, S1-R8).
-Last checked against build v3.4.1-3d03023 on 8/4/2026.
-AUTOMATION: READY
-</t>
+This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Technician Utilization report specification version 7 (S5-R10, S1-R8), read on 11 August 2026.
+Last checked against build v3.5-16cf83f on 8/6/2026.
+AUTOMATION: READY</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
@@ -2351,14 +2337,13 @@
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Every technician row's Total Hours is rendered as a link (every rendered row has clocked time &gt; 0, so the link always applies).
+          <t>1. Every technician row's Total Hours is rendered as a link (every rendered row has clocked time &gt; 0, so the link always applies).
 2. The link is distinguished by more than color - it carries an underline (or equivalent non-color affordance), is keyboard-focusable with a visible focus indicator, and activates on Enter.
 3. The Summary row's Total Hours value is NOT a link.
 ---
-This is the expected behaviour as per epic SV-8582 and the Technician Utilization report specification version 6 (S6-R1, S6-N1, S8-R14).
-Last checked against build v3.4.1-3d03023 on 8/4/2026.
-AUTOMATION: READY
-</t>
+This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Technician Utilization report specification version 7 (S6-R1, S6-N1, S8-R14), read on 11 August 2026.
+Last checked against build v3.5-16cf83f on 8/6/2026.
+AUTOMATION: READY</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
@@ -2404,14 +2389,13 @@
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. The Timesheet Activities report opens in the SAME browser tab.
+          <t>1. The Timesheet Activities report opens in the SAME browser tab.
 2. It is already filtered to that technician.
 3. It uses the same date range that was active on the Technician Utilization report.
 ---
-This is the expected behaviour as per epic SV-8582 and the Technician Utilization report specification version 6 (S6-R2, S6-R3, S6-R4).
-Last checked against build v3.4.1-3d03023 on 8/4/2026.
-AUTOMATION: READY
-</t>
+This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Technician Utilization report specification version 7 (S6-R2, S6-R3, S6-R4), read on 11 August 2026.
+Last checked against build v3.5-16cf83f on 8/6/2026.
+AUTOMATION: READY</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
@@ -2458,14 +2442,17 @@
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. The two totals MATCH exactly, to two decimals (these values are hours, not money) - both reports read the same clock records and round the same way (round-half-up, from unrounded values).
+          <t>1. The two totals MATCH exactly, to two decimals (these values are hours, not money) - both reports read the same clock records and round the same way (round-half-up, from unrounded values).
 2. Under this exact scope (same range, same single location, closed records) a mismatch IS a defect.
 3. The two documented scope differences (open clocks, multi-location drill-through) are covered by separate cases and are NOT defects.
----
-This is the expected behaviour as per epic SV-8582 and the Technician Utilization report specification version 6 (S1-R9).
-Last checked against build v3.4.1-3d03023 on 8/4/2026.
-AUTOMATION: READY
-</t>
+What you should see today: the two totals do not match. Andrew Wade reads 1080.44 on Technician Utilization and 1080.64 on Timesheet Activities for the same dates and the same single location, and six of the eight technicians checked disagree by up to 0.25 hours. This is a known problem and it is already reported - see https://shopview.atlassian.net/browse/SV-8944
+· If you see exactly that, mark this test FAILED and do not raise anything new.
+· If it fails in a DIFFERENT way from what is described above, that is a NEW problem - please report it.
+· If it PASSES, the fix has shipped: tell the QA lead so the ticket can be closed and this note removed.
+---
+This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Technician Utilization report specification version 7 (S1-R9), read on 11 August 2026.
+Last checked against build v3.5-16cf83f on 8/6/2026.
+AUTOMATION: READY - EXPECT FAIL (SV-8944)</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
@@ -2511,14 +2498,13 @@
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. The open time is counted UP TO THE MOMENT THE REPORT LOADS - a fixed snapshot taken at load, not a value that keeps ticking on screen (matching how Timesheet Activities treats an open record).
+          <t>1. The open time is counted UP TO THE MOMENT THE REPORT LOADS - a fixed snapshot taken at load, not a value that keeps ticking on screen (matching how Timesheet Activities treats an open record).
 2. The two reports, loaded at different moments, MAY differ by the elapsed open time - this is a deliberate scope difference of the reconciliation guarantee, EXPECTED and NOT a defect.
 3. Reloading the Technician Utilization report takes a fresh snapshot (the value grows by the elapsed time).
 ---
-This is the expected behaviour as per epic SV-8582 and the Technician Utilization report specification version 6 (S1-R9, S1-E1).
-Last checked against build v3.4.1-3d03023 on 8/4/2026.
-AUTOMATION: READY
-</t>
+This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Technician Utilization report specification version 7 (S1-R9, S1-E1), read on 11 August 2026.
+Last checked against build v3.5-16cf83f on 8/6/2026.
+AUTOMATION: HOLD - needs a technician clocked in at the moment of the test, and no technician on this environment is currently clocked in</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
@@ -2565,14 +2551,13 @@
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. The link passes the technician and the date range ONLY - it does NOT pass the location selection.
+          <t>1. The link passes the technician and the date range ONLY - it does NOT pass the location selection.
 2. Timesheet Activities opens for the user's currently active shop, so it shows one location's portion - it will differ from (or be disjoint with) the multi-location row value.
 3. This is a KNOWN drill-through limitation, EXPECTED and NOT a data defect (the same applies when the single selected location is not the active shop).
 ---
-This is the expected behaviour as per epic SV-8582 and the Technician Utilization report specification version 6 (S6-R6, S1-R9).
-Last checked against build v3.4.1-3d03023 on 8/4/2026.
-AUTOMATION: READY
-</t>
+This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Technician Utilization report specification version 7 (S6-R6, S1-R9), read on 11 August 2026.
+Last checked against build v3.5-16cf83f on 8/6/2026.
+AUTOMATION: READY</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
@@ -2617,13 +2602,12 @@
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Timesheet Activities opens filtered to that technician.
+          <t>1. Timesheet Activities opens filtered to that technician.
 2. The date range covers ONLY that single day.
 ---
-This is the expected behaviour as per epic SV-8582 and the Technician Utilization report specification version 6 (S6-R5).
-Last checked against build v3.4.1-3d03023 on 8/4/2026.
-AUTOMATION: READY
-</t>
+This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Technician Utilization report specification version 7 (S6-R5), read on 11 August 2026.
+Last checked against build v3.5-16cf83f on 8/6/2026.
+AUTOMATION: READY</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
@@ -2637,7 +2621,7 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>Three-dot menu is leftmost, then Column Selection; three download options</t>
+          <t>Three-dot menu is leftmost, then Column Selection; four download options</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
@@ -2668,14 +2652,13 @@
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. The three-dot download menu sits LEFTMOST in the toolbar's action cluster, with the Column Selection control immediately after it.
-2. The menu holds four items, worded exactly as they are on Sales By Customer and Sales By Representative: "Download Summary (PDF)", "Download Expanded View (PDF)", "Download Summary (CSV)" and "Download Expanded View (CSV)".
-3. Note for the tester: on this build the four items are worded more briefly - "Summary (PDF)", "Summary (CSV)", "Expanded (PDF)" and "Expanded (CSV)" - without the word "Download". The product owner has decided they must match the other two reports, so record what you see; the change is with the developers.
----
-This is the expected behaviour as per epic SV-8582 and Chris Ward's decision of 8/5/2026, recorded in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true; where the Technician Utilization report specification version 6 (S7-R1, S7-R2, S7-R3, S7-R4, S8-R2) differs, his decision is the authority.
-Last checked against build v3.4.1-3d03023 on 8/4/2026, which does not yet match it - that change is with the developers.
-AUTOMATION: READY
-</t>
+          <t>1. The three-dot download menu sits LEFTMOST in the toolbar's action cluster, with the Column Selection control immediately after it.
+2. The menu holds four download options, labeled exactly: "Download Summary (PDF)", "Download Expanded View (PDF)", "Download Summary (CSV)" and "Download Expanded View (CSV)".
+3. The order these four options appear in is NOT part of this check. The specification requires each option to be present with that exact label; it does not fix the order they are listed in. Do not fail this test on the order alone.
+---
+This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and its story SV-8654, read on 11 August 2026, and the Technician Utilization report specification version 7 (S7-R1, S7-R2, S7-R3, S7-R4, S7-R4a, S8-R2), read on 11 August 2026. Chris Ward asked for this menu wording in his answers of 5 August 2026 in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true, read on 11 August 2026; the specification now carries the same wording, so the two agree.
+Last checked against build v3.5-16cf83f on 8/6/2026.
+AUTOMATION: READY</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
@@ -2720,14 +2703,17 @@
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. The Summary PDF shows the technician rows and the Summary row (no day rows); it downloads as "Technician-Utilization-Summary.pdf".
+          <t>1. The Summary PDF shows the technician rows and the Summary row (no day rows); it downloads as "Technician-Utilization-Summary.pdf".
 2. The Expanded PDF shows the technician rows, EACH technician's per-day breakdown, and the Summary row; it downloads as "Technician-Utilization-Expanded.pdf".
 3. The PDF filenames are Title-Case as shipped.
----
-This is the expected behaviour as per epic SV-8582 and the Technician Utilization report specification version 6 (S7-R5, S7-R6, S7-R12).
-Last checked against build v3.4.1-3d03023 on 8/4/2026.
-AUTOMATION: READY
-</t>
+What you should see today: both PDFs stop at the last technician - neither contains the Summary row - and the file names come out lower-case as technician-utilization-summary.pdf and technician-utilization-expanded.pdf rather than Title-Case. The per-day breakdown itself is in the Expanded PDF, correctly. This is a known problem and it is already reported - see https://shopview.atlassian.net/browse/SV-8950
+· If you see exactly that, mark this test FAILED and do not raise anything new.
+· If it fails in a DIFFERENT way from what is described above, that is a NEW problem - please report it.
+· If it PASSES, the fix has shipped: tell the QA lead so the ticket can be closed and this note removed.
+---
+This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Technician Utilization report specification version 7 (S7-R5, S7-R6, S7-R12), read on 11 August 2026.
+Last checked against build v3.5-16cf83f on 8/6/2026.
+AUTOMATION: READY - EXPECT FAIL (SV-8950)</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
@@ -2766,21 +2752,24 @@
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>1. Choose "Download (CSV)" and check the filename.
+          <t>1. Choose "Download Summary (CSV)" and check the filename.
 2. Open the file in a plain-text editor and find the over-$1,000 value.
 3. Check for any day rows in the file.</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. The file downloads as "technician-utilization.csv" (lower-case as shipped, unlike the Title-Case PDFs).
+          <t>1. The file downloads as "technician-utilization.csv" (lower-case as shipped, unlike the Title-Case PDFs).
 2. The CSV shows the technician rows and the Summary row - always this summary-level content; it does NOT vary by the summary/expanded choice (no day rows).
 3. Any value containing a comma (e.g. "$1,234.50") is wrapped in double quotes per standard CSV escaping, so the columns parse correctly.
----
-This is the expected behaviour as per epic SV-8582 and the Technician Utilization report specification version 6 (S7-R7, S7-R10, S7-R12).
-Last checked against build v3.4.1-3d03023 on 8/4/2026.
-AUTOMATION: READY
-</t>
+What you should see today: there are two spreadsheet files, not one: technician-utilization-summary.csv and technician-utilization-expanded.csv, and the expanded one holds a row for each day as well. Neither contains the Summary row. The comma quoting in item 3 does pass - "$7,248.85" comes out wrapped in double quotes. This is a known problem and it is already reported - see https://shopview.atlassian.net/browse/SV-8951
+· If you see exactly that, mark this test FAILED and do not raise anything new.
+· If it fails in a DIFFERENT way from what is described above, that is a NEW problem - please report it.
+· If it PASSES, the fix has shipped: tell the QA lead so the ticket can be closed and this note removed.
+---
+This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Technician Utilization report specification version 7 (S7-R7, S7-R10, S7-R12), read on 11 August 2026.
+Last checked against build v3.5-16cf83f on 8/6/2026.
+AUTOMATION: READY - EXPECT FAIL (SV-8951)</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
@@ -2828,20 +2817,23 @@
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Every download includes ONLY the technicians currently selected in the technician filter - the deselected technician is absent from all three files.
+          <t>1. Every download includes ONLY the technicians currently selected in the technician filter - the deselected technician is absent from all three files.
 2. Every download covers the location(s) currently selected in the location filter and the date range currently active on the report.
 3. With every technician selected, the download covers all technicians for the range at the selected location(s).
 4. Every download (each PDF and the CSV) carries a "Locations:" line naming the location(s) the report was scoped to.
 5. Every download also mirrors the columns currently shown on screen — a column hidden in the Column Selection control is absent from the files, and a re-shown column comes back.
 6. Note for the tester: the files carry a Location column whenever that column is showing on screen. If your own account can reach only one location there is no Location column on screen and none in the files.
+What you should see today: item 1 does not pass: a technician you untick is still in every downloaded file. Items 2, 3, 4 and 5 do pass - the location, the date range, the "Locations:" line and the shown columns are all carried into the files correctly. This is a known problem and it is already reported - see https://shopview.atlassian.net/browse/SV-8948
+· If you see exactly that, mark this test FAILED and do not raise anything new.
+· If it fails in a DIFFERENT way from what is described above, that is a NEW problem - please report it.
+· If it PASSES, the fix has shipped: tell the QA lead so the ticket can be closed and this note removed.
 ---
 Note for the tester: if the Location column does not behave this way on the build, mark this test Failed and report it - do not change the test.
 Location is one of the columns you can switch on and off in the column-selection control, but only if your own account can reach more than one location: for you it is already switched on when you arrive, and you can switch it off. Someone whose account can reach only one location never sees the column and it is not offered to them in that list.
 ---
-This is the expected behaviour as per epic SV-8582 and the Technician Utilization report specification version 6 (S7-R8, S7-R9, S7-R10, S7-R13, S7-E1, S9-R8). Version 6 of that specification, published on 5 August 2026, is what settles the one point about the Location column: it now states in both of its own requirements that the column belongs to anyone whose account can reach more than one location and can be switched on and off in the column-selection control. Chris Ward asked for that change in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true
-Last checked against build v3.4.1-3d03023 on 8/4/2026.
-AUTOMATION: READY
-</t>
+This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Technician Utilization report specification version 7 (S7-R8, S7-R9, S7-R10, S7-R13, S7-E1, S9-R8), read on 11 August 2026. Version 6 of that specification, published on 5 August 2026, is what settles the one point about the Location column: it now states in both of its own requirements that the column belongs to anyone whose account can reach more than one location and can be switched on and off in the column-selection control. Chris Ward asked for that change in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true, read on 11 August 2026
+Last checked against build v3.5-16cf83f on 8/6/2026.
+AUTOMATION: READY - EXPECT FAIL (SV-8948)</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
@@ -2888,13 +2880,16 @@
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. The downloaded files use the same column order and number formats as the on-screen report, including the "—" rendering for an unknown Est. Lost Labor.
+          <t>1. The downloaded files use the same column order and number formats as the on-screen report, including the "—" rendering for an unknown Est. Lost Labor.
 2. Rows in EVERY download are ordered by Technician name A to Z (the default order) - the on-screen column sort is client-side only and is NOT carried into the export.
----
-This is the expected behaviour as per epic SV-8582 and the Technician Utilization report specification version 6 (S7-R10, S7-R10a).
-Last checked against build v3.4.1-3d03023 on 8/4/2026.
-AUTOMATION: READY
-</t>
+What you should see today: item 2 does not pass: the rows in both the spreadsheet and the PDF come out in no recognisable order - they begin Alexander Cohen, Brittany Anderson, Colleen Guerrero, Wesley Mcclure, Jacob Chung - even though the screen was in its normal A to Z order. Item 1 passes. This is a known problem and it is already reported - see https://shopview.atlassian.net/browse/SV-8949
+· If you see exactly that, mark this test FAILED and do not raise anything new.
+· If it fails in a DIFFERENT way from what is described above, that is a NEW problem - please report it.
+· If it PASSES, the fix has shipped: tell the QA lead so the ticket can be closed and this note removed.
+---
+This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Technician Utilization report specification version 7 (S7-R10, S7-R10a), read on 11 August 2026.
+Last checked against build v3.5-16cf83f on 8/6/2026.
+AUTOMATION: READY - EXPECT FAIL (SV-8949)</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
@@ -2940,15 +2935,14 @@
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. With an uploaded logo, BOTH PDF views show that logo at the top of the report.
+          <t>1. With an uploaded logo, BOTH PDF views show that logo at the top of the report.
 2. The CSV never includes the logo.
 3. With a logo uploaded, that logo appears. If a logo is set but fails to load, the built-in ShopView logo is used instead. If no logo is uploaded at all, NO logo is printed and the text fills the space.
 Note for the tester: on this build a report with no uploaded logo still prints the built-in ShopView logo. The product owner has decided it should print no logo at all, so record what you see; the change is with the developers.
 ---
-This is the expected behaviour as per epic SV-8582 and Chris Ward's decision of 8/5/2026, recorded in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true; where the Technician Utilization report specification version 6 (S7-R11, S7-N2, S7-N3) differs, his decision is the authority.
-Last checked against build v3.4.1-3d03023 on 8/4/2026, which does not yet match it - that change is with the developers.
-AUTOMATION: READY
-</t>
+This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and Chris Ward's decision of 8/5/2026, recorded in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true, read on 11 August 2026; where the Technician Utilization report specification version 7 (S7-R11, S7-N2, S7-N3), read on 11 August 2026, differs, his decision is the authority.
+Last checked against build v3.5-16cf83f on 8/6/2026.
+AUTOMATION: READY</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
@@ -2994,14 +2988,16 @@
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Nothing happens: NO file downloads and NO message appears (not even an error).
+          <t>1. Nothing happens: NO file downloads and NO message appears (not even an error).
 2. This silent no-op is the specified behavior for every download option when no technician is selected.
-Known issue: the product does not currently do this — on the build tested, choosing a download with no technician selected still started the download and showed a success message. That is a fault for a developer to fix, not a decision for the product owner. No developer ticket has been raised for it yet, so this test will fail until it is fixed — record what you see and leave the test as it is.
----
-This is the expected behaviour as per epic SV-8582 and the Technician Utilization report specification version 6 (S7-N1).
-Last checked against build v3.4.1-3d03023 on 8/4/2026.
-AUTOMATION: READY
-</t>
+What you should see today: the download is not silent: a file still arrives, holding every technician, and a message reads "Success / Data exported successfully.". This is a known problem and it is already reported - see https://shopview.atlassian.net/browse/SV-8948
+· If you see exactly that, mark this test FAILED and do not raise anything new.
+· If it fails in a DIFFERENT way from what is described above, that is a NEW problem - please report it.
+· If it PASSES, the fix has shipped: tell the QA lead so the ticket can be closed and this note removed.
+---
+This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Technician Utilization report specification version 7 (S7-N1), read on 11 August 2026.
+Last checked against build v3.5-16cf83f on 8/6/2026.
+AUTOMATION: READY - EXPECT FAIL (SV-8948)</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
@@ -3047,13 +3043,16 @@
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. When a download starts, a success notification reads exactly: "Download started".
+          <t>1. When a download starts, a success notification reads exactly: "Download started".
 2. When a download fails, an error notification reads exactly: "Failed to download report".
----
-This is the expected behaviour as per epic SV-8582 and the Technician Utilization report specification version 6 (§7 notifications table, Story 7 has no S, §7 is the closing reference).
-Last checked against build v3.4.1-3d03023 on 8/4/2026.
-AUTOMATION: READY
-</t>
+What you should see today: a download that starts shows "Success / Data exported successfully." instead of "Download started", and a download that fails shows no message at all. This is a known problem and it is already reported - see https://shopview.atlassian.net/browse/SV-8952
+· If you see exactly that, mark this test FAILED and do not raise anything new.
+· If it fails in a DIFFERENT way from what is described above, that is a NEW problem - please report it.
+· If it PASSES, the fix has shipped: tell the QA lead so the ticket can be closed and this note removed.
+---
+This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Technician Utilization report specification version 7 (§7 notifications table, Story 7 has no S, §7 is the closing reference), read on 11 August 2026.
+Last checked against build v3.5-16cf83f on 8/6/2026.
+AUTOMATION: READY - EXPECT FAIL (SV-8952)</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
@@ -3101,15 +3100,17 @@
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Neither the CSV nor the PDF is produced — no download starts.
+          <t>1. Neither the CSV nor the PDF is produced — no download starts.
 2. A clear too-large message appears telling the user to narrow the date range or filters, then try again — the standard wording is "This report is too large to export. Narrow the date range or filters, then try again."
 3. After narrowing below the cap, the downloads work again.
-Known issue: the product does not currently do this. It has been filed for a fix here: https://shopview.atlassian.net/browse/SV-8818
----
-This is the expected behaviour as per epic SV-8582 and the Technician Utilization report specification version 6 (Story 7 exports).
-Last checked against build v3.4.1-3d03023 on 8/4/2026.
-AUTOMATION: READY - EXPECT FAIL (SV-8818)
-</t>
+What you should see today: the spreadsheet download works and produces a file, but the PDF download of the same view fails with a server error and no file arrives. It depends on how much is in the view, not on which report - filtered down to one or two rows the PDF downloads normally, and on a full unfiltered view of several thousand rows it fails every time. This is a known problem and it is already reported - see https://shopview.atlassian.net/browse/SV-8818
+- If you see exactly that, mark this test FAILED and do not raise anything new.
+- If it fails in a DIFFERENT way from what is described above, that is a NEW problem - please report it.
+- If it PASSES, the fix has shipped: tell the QA lead so the ticket can be closed and this note removed.
+---
+This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Technician Utilization report specification version 7 (S7-R14), read on 11 August 2026, which was added to that specification on 2026-08-06 and states this row limit and its exact message. Before that the specification said nothing about a limit and this expectation came from the engineering plan of 2026-07-29; the written description now says the same thing, so the two agree.
+Last checked against build v3.5-16cf83f on 8/6/2026.
+AUTOMATION: READY - EXPECT FAIL (SV-8818)</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
@@ -3157,16 +3158,19 @@
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Both spreadsheet options download a file.
+          <t>1. Both spreadsheet options download a file.
 2. Both files hold the technician rows and the Summary row.
 3. Neither file holds any per-day rows - the spreadsheet holds the same thing whichever of the two you pick.
 4. In both files any value with a comma in it (for example "$1,234.50") is wrapped in double quotes, so the columns still line up when you open it.
 5. Note for the tester: write down the exact file name each option gives you. Names for two separate spreadsheet files have never been written down anywhere, so we are collecting them, not checking them - do not fail this test over a file name.
----
-This is the expected behaviour as per epic SV-8582 and the Technician Utilization report specification version 6 (S7-R7), which says the spreadsheet always holds the technician rows and the Summary row and does not change with the Summary or Expanded choice. The test exists at all because of Chris Ward's decision of 8/5/2026, recorded in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true - he asked this report's download menu to match Sales By Customer and Sales By Representative, which each offer a spreadsheet for both views, whereas that written description covers only one spreadsheet download. That his answer leaves the menu with four options is our reading of his words and he has not confirmed it.
-This has not yet been checked against a build.
-AUTOMATION: HOLD - the two spreadsheet downloads do not exist yet and the product owner has not confirmed them
-</t>
+What you should see today: the two spreadsheets are not the same: the Expanded one holds a row for each day beneath each technician. Neither file holds the Summary row. The comma quoting in item 4 does pass. The two names, for the record, are technician-utilization-summary.csv and technician-utilization-expanded.csv. This is a known problem and it is already reported - see https://shopview.atlassian.net/browse/SV-8951
+· If you see exactly that, mark this test FAILED and do not raise anything new.
+· If it fails in a DIFFERENT way from what is described above, that is a NEW problem - please report it.
+· If it PASSES, the fix has shipped: tell the QA lead so the ticket can be closed and this note removed.
+---
+This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Technician Utilization report specification version 7 (S7-R7), read on 11 August 2026, which says the spreadsheet always holds the technician rows and the Summary row and does not change with the Summary or Expanded choice. The test exists at all because of Chris Ward's decision of 8/5/2026, recorded in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true, read on 11 August 2026, - he asked this report's download menu to match Sales By Customer and Sales By Representative, which each offer a spreadsheet for both views, whereas that written description covers only one spreadsheet download. That his answer leaves the menu with four options is our reading of his words and he has not confirmed it.
+Last checked against build v3.5-16cf83f on 8/6/2026.
+AUTOMATION: READY - EXPECT FAIL (SV-8951)</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
@@ -3219,9 +3223,9 @@
 3. "All locations" acts as a select-all shortcut: choosing it selects every accessible location; unchecking one location leaves the remaining specific locations selected - the selection is always the concrete set of checked locations.
 4. With more than one location selected, a Location column appears in the table and each row names its location - or reads "Multiple" for a technician whose hours span more than one of them. (Where that column sits on screen is checked by its own test.)
 ---
-This is the expected behaviour as per epic SV-8582 and the Technician Utilization report specification version 6 (S9-R1); where the wording of that specification differs, the behaviour above follows Chris Ward's later decision, recorded in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true, which is the authority.
-Last checked against build v3.4.1-3d03023 on 8/4/2026.
-AUTOMATION: HOLD - this part of the report is not built yet
+This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Technician Utilization report specification version 7 (S9-R1), read on 11 August 2026.
+Last checked against build v3.5-16cf83f on 8/5/2026.
+AUTOMATION: READY
 </t>
         </is>
       </c>
@@ -3270,15 +3274,14 @@
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Selecting one, several, or all locations RELOADS the report scoped to that set (unlike the technician filter, which is on-screen only).
+          <t>1. Selecting one, several, or all locations RELOADS the report scoped to that set (unlike the technician filter, which is on-screen only).
 2. All metrics (technician rows, per-day rows, and the Summary) reflect only clock records at the selected location(s).
 3. The technician's hours are POOLED across the selected locations into ONE row (one row per technician, not one per location); per-day rows pool the same way.
 4. Scoping never goes beyond the user's accessible locations - a location the user cannot access is never included.
 ---
-This is the expected behaviour as per epic SV-8582 and the Technician Utilization report specification version 6 (S9-R3, S9-R4, S9-R5).
-Last checked against build v3.4.1-3d03023 on 8/4/2026.
-AUTOMATION: READY
-</t>
+This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Technician Utilization report specification version 7 (S9-R3, S9-R4, S9-R5), read on 11 August 2026.
+Last checked against build v3.5-16cf83f on 8/6/2026.
+AUTOMATION: READY</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
@@ -3323,15 +3326,14 @@
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Any saved location the user can no longer access is DROPPED from the restored selection; the remaining accessible locations restore normally.
+          <t>1. Any saved location the user can no longer access is DROPPED from the restored selection; the remaining accessible locations restore normally.
 2. If the remaining set is empty, the report falls back to the user's currently active location (the first-visit default).
 3. The report loads without an error in both cases.
 4. The same fallback happens when you deselect every location by hand in the Location filter — the report loads the currently active location's rows rather than showing nothing.
 ---
-This is the expected behaviour as per epic SV-8582 and the Technician Utilization report specification version 6 (S9-R6, S1-R8, S9-R2, S9-R7).
-Last checked against build v3.4.1-3d03023 on 8/4/2026.
-AUTOMATION: READY
-</t>
+This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Technician Utilization report specification version 7 (S9-R6, S1-R8, S9-R2, S9-R7), read on 11 August 2026.
+Last checked against build v3.5-16cf83f on 8/6/2026.
+AUTOMATION: READY</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
@@ -3377,13 +3379,12 @@
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. For the single-location user the Location filter is NOT shown at all — the report simply shows that one location's data.
+          <t>1. For the single-location user the Location filter is NOT shown at all — the report simply shows that one location's data.
 2. For the user with access to two or more locations the Location filter IS shown.
 ---
-This is the expected behaviour as per epic SV-8582 and the Technician Utilization report specification version 6 (S9-N1). Chris Ward confirmed this on 8/5/2026 in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true
-Last checked against build v3.4.1-3d03023 on 8/4/2026.
-AUTOMATION: READY
-</t>
+This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Technician Utilization report specification version 7 (S9-N1), read on 11 August 2026. Chris Ward confirmed this on 8/5/2026 in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true, read on 11 August 2026
+Last checked against build v3.5-16cf83f on 8/6/2026.
+AUTOMATION: HOLD - needs a second sign-in as a user who can reach only one location, and there is one shared sign-in on this environment</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
@@ -3397,7 +3398,7 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>The Location column shows only with more than one location; Summary row blank</t>
+          <t>Location column: leftmost for a multi-location user; Summary row blank</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
@@ -3436,21 +3437,24 @@
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Signed in as someone whose account can reach more than one location, a Location column is shown as the LEFTMOST column, before Technician, already switched on.
+          <t>1. Signed in as someone whose account can reach more than one location, a Location column is shown as the LEFTMOST column, before Technician, already switched on.
 2. A technician whose hours were all clocked at one location shows that location's name.
 3. A technician whose hours span more than one selected location shows "Multiple".
 4. An expanded day row shows the exact location when that day's hours were all at one location, and "Multiple" when the day spans more than one.
 5. The Summary row leaves the Location cell blank.
 6. Signed in as someone whose account can reach only one location, the Location column is not shown at all and is not offered in the column-selection control.
-7. Every download — both PDF views and the CSV — includes the Location column in its on-screen leftmost position, carrying the same values you just read on screen.
----
-Note for the tester: if the Location column does not behave this way on the build, mark this test Failed and report it - do not change the test.
-Location is one of the columns you can switch on and off in the column-selection control, but only if your own account can reach more than one location: for you it is already switched on when you arrive, and you can switch it off. Someone whose account can reach only one location never sees the column and it is not offered to them in that list.
----
-This is the expected behaviour as per epic SV-8582 and the Technician Utilization report specification version 6 (S9-R9, S9-R10, S8-R15, S10-R4, S7-R13). Version 6 of that specification, published on 5 August 2026, is what settles the one point about the Location column: it now states in both of its own requirements that the column belongs to anyone whose account can reach more than one location and can be switched on and off in the column-selection control. Chris Ward asked for that change in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true
-Last checked against build v3.4.1-3d03023 on 8/4/2026.
-AUTOMATION: READY
-</t>
+7. Every download - both PDF views and the CSV - includes the Location column in its on-screen leftmost position, carrying the same values you just read on screen.
+8. Narrowing the Location filter to a single location does NOT remove the column: what decides whether it is shown is how many locations the person can reach, not how many are selected.
+Note for the tester: Location is one of the columns you can switch on and off in the column-selection control, but only if your own account can reach more than one location: for you it is already switched on when you arrive, and you can switch it off. Someone whose account can reach only one location never sees the column and it is not offered to them in that list.
+What you should see today: the Location column is decided by how many locations are SELECTED, not by what the signed-in person can reach - narrow the Location filter to a single location and the column disappears even though the person can still reach five. Location is also never offered in the Column Selection control, so it cannot be switched on or off by hand. This is already reported - see https://shopview.atlassian.net/browse/SV-8954 - but note that ticket is currently closed as obsolete while the problem still happens, so the QA lead is deciding whether to reopen it.
+- If you see exactly that, mark this test FAILED and do not raise anything new.
+- If it fails in a DIFFERENT way from what is described above, that is a NEW problem - please report it.
+- If it PASSES, the fix has shipped: tell the QA lead so this note can be removed.
+Also today: the column is drawn SECOND, after Technician, not leftmost as item 1 requires - count that as part of the same failure. Item 3 CAN now be checked on this environment: a technician with hours at more than one location does show "Multiple" (seen on 8/10/2026). Item 6 still needs a second sign-in as a one-location user.
+---
+This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Technician Utilization report specification version 7 (S9-R9, S9-R10, S8-R15, S10-R4, S7-R13, S2-R1), read on 11 August 2026. Chris Ward confirmed this same access-gated, switchable rule in his answers of 8/10/2026, in this file: build/report-suite/chris-answers-2026-08-10/ - his answer and the specification agree.
+Last checked against build v3.5-4795eee on 8/10/2026.
+AUTOMATION: READY - EXPECT FAIL (SV-8954)</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
@@ -3511,9 +3515,9 @@
 7. Est. Lost Labor can now be hidden like any other column (it used to be always on).
 8. Your column choice is remembered in this browser and is still applied when you come back.
 ---
-This is the expected behaviour as per epic SV-8582 and the Technician Utilization report specification version 6 (S10-R1, S10-R2, S10-R3, S10-R4, S10-R5, S10-R6, S8-R16).
-Last checked against build v3.4.1-3d03023 on 8/4/2026.
-AUTOMATION: HOLD - this part of the report is not built yet
+This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Technician Utilization report specification version 7 (S10-R1, S10-R2, S10-R3, S10-R4, S10-R5, S10-R6, S8-R16), read on 11 August 2026.
+Last checked against build v3.5-16cf83f on 8/5/2026.
+AUTOMATION: READY
 </t>
         </is>
       </c>
@@ -3560,14 +3564,13 @@
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. The report uses an all-white table: white column headers and white data cells, with NO alternating row shading.
+          <t>1. The report uses an all-white table: white column headers and white data cells, with NO alternating row shading.
 2. The toolbar controls run, left to right: the three-dot download menu, the Column Selection control, the date-range picker, the technician filter, and the Location filter (rightmost).
 3. The expand/collapse-all control is NOT a toolbar control - it lives in the table header (in the Technician column).
 ---
-This is the expected behaviour as per epic SV-8582 and the Technician Utilization report specification version 6 (S8-R1, S8-R2, S8-R3).
-Last checked against build v3.4.1-3d03023 on 8/4/2026.
-AUTOMATION: READY
-</t>
+This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Technician Utilization report specification version 7 (S8-R1, S8-R2, S8-R3), read on 11 August 2026.
+Last checked against build v3.5-16cf83f on 8/6/2026.
+AUTOMATION: READY</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
@@ -3615,15 +3618,14 @@
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. The report supports dark mode: page background, toolbar, cells, the Total Hours link, the information icon, the sort indicator, and the "—" glyph are all clearly legible in dark mode.
+          <t>1. The report supports dark mode: page background, toolbar, cells, the Total Hours link, the information icon, the sort indicator, and the "—" glyph are all clearly legible in dark mode.
 2. In BOTH light mode and dark mode the information icon is clearly visible against the background behind it - you can see it at a glance and it does not disappear into the background.
 3. The Total Hours link's non-color affordance and focus indicator apply in both modes.
 4. Note for the tester: you do not need to measure anything and you do not need any tool. Just say whether you can see the icon easily in both modes, and only report it if you cannot. (The design rule behind this is a minimum 3:1 contrast ratio, which the design and engineering team check with a contrast tool - not by hand.)
 ---
-This is the expected behaviour as per epic SV-8582 and the Technician Utilization report specification version 6 (S8-R9, S8-R13, S8-R14).
-Last checked against build v3.4.1-3d03023 on 8/4/2026.
-AUTOMATION: READY
-</t>
+This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Technician Utilization report specification version 7 (S8-R9, S8-R13, S8-R14), read on 11 August 2026.
+Last checked against build v3.5-16cf83f on 8/6/2026.
+AUTOMATION: READY</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
@@ -3670,14 +3672,13 @@
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. The initial report payload does NOT ship the day rows.
+          <t>1. The initial report payload does NOT ship the day rows.
 2. Expanding a technician row issues an on-demand backend request that returns that technician's per-day breakdown.
 3. Because expansion state resets (all collapsed) on any data reload, nothing is lost by the lazy loading - re-expanding fetches fresh day data.
 ---
-This is the expected behaviour as per epic SV-8582 and the Technician Utilization report specification version 6 (S4-R2, S4-R5).
-Last checked against build v3.4.1-3d03023 on 8/4/2026.
-AUTOMATION: READY
-</t>
+This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Technician Utilization report specification version 7 (S4-R2, S4-R5), read on 11 August 2026.
+Last checked against build v3.5-16cf83f on 8/6/2026.
+AUTOMATION: READY</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
@@ -3725,15 +3726,18 @@
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. A date-range change triggers a fresh server load of the rows.
+          <t>1. A date-range change triggers a fresh server load of the rows.
 2. A location change triggers a fresh server load scoped to the selected set.
 3. The technician filter causes NO server request - it works on screen only (hide/show + Summary recalculation).
 4. Column sorting causes NO server request - it is applied on screen to the loaded rows.
----
-This is the expected behaviour as per epic SV-8582 and the Technician Utilization report specification version 6 (S1-R5, S9-R3, S2-R13).
-Last checked against build v3.4.1-3d03023 on 8/4/2026.
-AUTOMATION: READY
-</t>
+What you should see today: items 1 and 2 pass, but items 3 and 4 do not: ticking a technician in the technician filter sends a request to the server, and so does every click on a column heading. This is a known problem and it is already reported - see https://shopview.atlassian.net/browse/SV-8945
+· If you see exactly that, mark this test FAILED and do not raise anything new.
+· If it fails in a DIFFERENT way from what is described above, that is a NEW problem - please report it.
+· If it PASSES, the fix has shipped: tell the QA lead so the ticket can be closed and this note removed.
+---
+This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Technician Utilization report specification version 7 (S1-R5, S9-R3, S2-R13), read on 11 August 2026.
+Last checked against build v3.5-16cf83f on 8/6/2026.
+AUTOMATION: READY - EXPECT FAIL (SV-8945)</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">

--- a/testrail-import/Report-Suite_Technician-Utilization-Report_testrail-import.xlsx
+++ b/testrail-import/Report-Suite_Technician-Utilization-Report_testrail-import.xlsx
@@ -3498,7 +3498,7 @@
           <t>1. Find the column-selection button in the toolbar and hover it to read its tooltip.
 2. With the button focused, read the name assistive technology gives it — use the browser's accessibility inspector or a screen reader.
 3. Note its position relative to the three-dot download menu.
-4. Open it and read every toggle in the list, and which ones are on.
+4. Open it and read every toggle in the list, and which ones are on — including whether Location is among them.
 5. Turn Est. Lost Labor off, then turn Internal Hours off, watching the table each time.
 6. Turn both back on and check where each column lands.
 7. Reload the page, then close the browser, reopen it and return to the report.</t>
@@ -3508,14 +3508,14 @@
         <is>
           <t xml:space="preserve">1. The control is an icon button whose tooltip reads "Column Selection", sitting immediately after the three-dot download menu in the toolbar.
 2. Because the button shows an icon and no text, it still carries a name that assistive technology reads out — it is not left unnamed.
-3. The list offers five toggles — Total Hours, WO Hours, Internal Hours, Utilization % and Est. Lost Labor — and all five are on by default.
+3. The list offers a toggle for each data column — Total Hours, WO Hours, Internal Hours, Utilization % and Est. Lost Labor — and all five are on by default. If your login can reach more than one location, Location is listed as well and is also on by default.
 4. Technician is always shown and cannot be turned off (it is not offered as a toggle).
-5. The Location column is never listed here — it appears on its own whenever more than one location is in scope.
+5. Location is listed here for anyone whose login can reach more than one location; it is on by default and can be switched off like any other column. Someone whose login reaches only one location never sees the column and is never offered it in this list.
 6. Turning a toggle off hides that column (header and cells) immediately, with no reload; turning it back on returns it to its usual place in the fixed left-to-right order — the remaining columns never reorder.
 7. Est. Lost Labor can now be hidden like any other column (it used to be always on).
 8. Your column choice is remembered in this browser and is still applied when you come back.
 ---
-This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Technician Utilization report specification version 7 (S10-R1, S10-R2, S10-R3, S10-R4, S10-R5, S10-R6, S8-R16), read on 11 August 2026.
+This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Technician Utilization report specification version 7 (S10-R1, S10-R2, S10-R3, S10-R4, S10-R5, S10-R6, S9-R9, S8-R16), read on 11 August 2026.
 Last checked against build v3.5-16cf83f on 8/5/2026.
 AUTOMATION: READY
 </t>

--- a/testrail-import/Report-Suite_Technician-Utilization-Report_testrail-import.xlsx
+++ b/testrail-import/Report-Suite_Technician-Utilization-Report_testrail-import.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J61"/>
+  <dimension ref="A1:J62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
@@ -3184,31 +3184,84 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
+          <t>CSV export repeats the PDF header's technician and Locations filter lines</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>TU — Exports</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>1. You are signed in to the ShopView App on a desktop browser.
+2. The Technician Utilization report is open with at least one filter narrowed (for example a chosen date/scope and one or more locations) so the PDF header would show more than one filter line.</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t>1. Download the report as a PDF and read the filter-summary lines in its header area.
+2. Download the report as a CSV and open it in a plain text editor or spreadsheet.
+3. Compare the leading rows of the CSV (above the column-header row) with the PDF header lines.</t>
+        </is>
+      </c>
+      <c r="G52" s="2" t="inlineStr">
+        <is>
+          <t>1. The CSV carries the same filter-summary lines as the PDF header - the date range, the technician selection when it is narrowed, and the "Locations:" line - each as a leading metadata row above the column-header row.
+2. The lines appear verbatim (the same wording) and in the same order as in the PDF header.
+3. A CSV saved or forwarded later is never ambiguous about which filters produced it: every filter the PDF header names is present in the CSV.
+4. Note for the tester: this is the suite-wide rule that the CSV must name the same filters as the PDF. If your report shows no narrowed filters, widen or narrow one so at least one filter line appears, then compare again.
+---
+This is the expected behaviour as per epic SV-8582 and the Technician Utilization report specification version 9 (S7-R13a), both read on 17 August 2026. S7-R13a is the suite-wide rule (added 2026-08-12, SV-9283) that the CSV carries every filter-summary line the PDF header names.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026</t>
+        </is>
+      </c>
+      <c r="H52" s="2" t="inlineStr">
+        <is>
+          <t>SV-8654 (TU spec v9 2026-08-17 S7-R13a; suite-wide CSV filter-summary rule SV-9283)</t>
+        </is>
+      </c>
+      <c r="I52" s="2" t="inlineStr"/>
+      <c r="J52" s="2" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
+        <is>
           <t>The Location filter is the rightmost multi-select; All Locations = select-all</t>
         </is>
       </c>
-      <c r="B52" s="2" t="inlineStr">
+      <c r="B53" s="2" t="inlineStr">
         <is>
           <t>TU — Location Filter</t>
         </is>
       </c>
-      <c r="C52" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D52" s="2" t="inlineStr">
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E52" s="2" t="inlineStr">
+      <c r="E53" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in as a user with access to at least two locations.
 2. You are on the Technician Utilization report.</t>
         </is>
       </c>
-      <c r="F52" s="2" t="inlineStr">
+      <c r="F53" s="2" t="inlineStr">
         <is>
           <t>1. Look at the rightmost control in the toolbar and read its label.
 2. Open it and read the listed options.
@@ -3216,7 +3269,7 @@
 4. With every accessible location selected, look at how the report tells you which location the shown data belongs to.</t>
         </is>
       </c>
-      <c r="G52" s="2" t="inlineStr">
+      <c r="G53" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1. The toolbar has a location filter labeled "Location" - a multi-select and the RIGHTMOST control.
 2. It lists the locations the signed-in user has access to, plus an "All locations" option and a "Clear all" action. (If you only have access to one location, the "All locations" entry is not offered - you see "Clear all" and your one location.)
@@ -3229,42 +3282,42 @@
 </t>
         </is>
       </c>
-      <c r="H52" s="2" t="inlineStr">
+      <c r="H53" s="2" t="inlineStr">
         <is>
           <t>SV-8656 (TU spec v5 2026-07-29 S9-R1 — per-row location identifier in All-Locations view ADDED per kickoff video P10 40:58-41:20; user ruling 2026-07-28: video overrides spec (video newer; last-update-wins))</t>
         </is>
       </c>
-      <c r="I52" s="2" t="inlineStr"/>
-      <c r="J52" s="2" t="inlineStr"/>
-    </row>
-    <row r="53">
-      <c r="A53" s="2" t="inlineStr">
+      <c r="I53" s="2" t="inlineStr"/>
+      <c r="J53" s="2" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
         <is>
           <t>Location changes reload with hours pooled into one row per technician</t>
         </is>
       </c>
-      <c r="B53" s="2" t="inlineStr">
+      <c r="B54" s="2" t="inlineStr">
         <is>
           <t>TU — Location Filter</t>
         </is>
       </c>
-      <c r="C53" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D53" s="2" t="inlineStr">
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="E53" s="2" t="inlineStr">
+      <c r="E54" s="2" t="inlineStr">
         <is>
           <t>1. A technician has clocked time at TWO accessible locations in the range.
 2. You are on the Technician Utilization report.</t>
         </is>
       </c>
-      <c r="F53" s="2" t="inlineStr">
+      <c r="F54" s="2" t="inlineStr">
         <is>
           <t>1. Select only location A and read the technician's hours.
 2. Add location B to the selection and watch the report.
@@ -3272,7 +3325,7 @@
 4. Expand the technician and check the day rows on a day with time at both locations.</t>
         </is>
       </c>
-      <c r="G53" s="2" t="inlineStr">
+      <c r="G54" s="2" t="inlineStr">
         <is>
           <t>1. Selecting one, several, or all locations RELOADS the report scoped to that set (unlike the technician filter, which is on-screen only).
 2. All metrics (technician rows, per-day rows, and the Summary) reflect only clock records at the selected location(s).
@@ -3284,47 +3337,47 @@
 AUTOMATION: READY</t>
         </is>
       </c>
-      <c r="H53" s="2" t="inlineStr">
+      <c r="H54" s="2" t="inlineStr">
         <is>
           <t>SV-8656 (TU spec v5 2026-07-29 S9-R3; S9-R4; S9-R5 + on-screen location-scope indicator per Chris Ward group message 2026-07-29 (chris-update-2026-07-29/chris-message-2026-07-29.md; NEWEST source; last-update-wins))</t>
         </is>
       </c>
-      <c r="I53" s="2" t="inlineStr"/>
-      <c r="J53" s="2" t="inlineStr"/>
-    </row>
-    <row r="54">
-      <c r="A54" s="2" t="inlineStr">
+      <c r="I54" s="2" t="inlineStr"/>
+      <c r="J54" s="2" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
         <is>
           <t>The saved location selection restores defensively; bad ones are dropped</t>
         </is>
       </c>
-      <c r="B54" s="2" t="inlineStr">
+      <c r="B55" s="2" t="inlineStr">
         <is>
           <t>TU — Location Filter</t>
         </is>
       </c>
-      <c r="C54" s="2" t="inlineStr">
+      <c r="C55" s="2" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="D54" s="2" t="inlineStr">
+      <c r="D55" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E54" s="2" t="inlineStr">
+      <c r="E55" s="2" t="inlineStr">
         <is>
           <t>1. The user saved a location selection that includes a location their access to was later removed.</t>
         </is>
       </c>
-      <c r="F54" s="2" t="inlineStr">
+      <c r="F55" s="2" t="inlineStr">
         <is>
           <t>1. Return to the Technician Utilization report and read the restored location selection.
 2. Repeat with a saved selection consisting ONLY of now-inaccessible locations.</t>
         </is>
       </c>
-      <c r="G54" s="2" t="inlineStr">
+      <c r="G55" s="2" t="inlineStr">
         <is>
           <t>1. Any saved location the user can no longer access is DROPPED from the restored selection; the remaining accessible locations restore normally.
 2. If the remaining set is empty, the report falls back to the user's currently active location (the first-visit default).
@@ -3336,48 +3389,48 @@
 AUTOMATION: READY</t>
         </is>
       </c>
-      <c r="H54" s="2" t="inlineStr">
+      <c r="H55" s="2" t="inlineStr">
         <is>
           <t>SV-8656 (TU spec v5 2026-07-29 S9-R6; S1-R8; S9-R2; S9-R7)</t>
         </is>
       </c>
-      <c r="I54" s="2" t="inlineStr"/>
-      <c r="J54" s="2" t="inlineStr"/>
-    </row>
-    <row r="55">
-      <c r="A55" s="2" t="inlineStr">
+      <c r="I55" s="2" t="inlineStr"/>
+      <c r="J55" s="2" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
         <is>
           <t>Technician Utilization: Location filter hidden for a one-location user</t>
         </is>
       </c>
-      <c r="B55" s="2" t="inlineStr">
+      <c r="B56" s="2" t="inlineStr">
         <is>
           <t>TU — Location Filter</t>
         </is>
       </c>
-      <c r="C55" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D55" s="2" t="inlineStr">
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="E55" s="2" t="inlineStr">
+      <c r="E56" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in as a user with access to exactly one location.
 2. You are on the Technician Utilization report.</t>
         </is>
       </c>
-      <c r="F55" s="2" t="inlineStr">
+      <c r="F56" s="2" t="inlineStr">
         <is>
           <t>1. Look for the Location filter in the toolbar.
 2. Then sign in as a user with access to two or more locations and look again.</t>
         </is>
       </c>
-      <c r="G55" s="2" t="inlineStr">
+      <c r="G56" s="2" t="inlineStr">
         <is>
           <t>1. For the single-location user the Location filter is NOT shown at all — the report simply shows that one location's data.
 2. For the user with access to two or more locations the Location filter IS shown.
@@ -3387,43 +3440,43 @@
 AUTOMATION: HOLD - needs a second sign-in as a user who can reach only one location, and there is one shared sign-in on this environment</t>
         </is>
       </c>
-      <c r="H55" s="2" t="inlineStr">
+      <c r="H56" s="2" t="inlineStr">
         <is>
           <t>SV-8656 (TU spec S9-N1 — RULED HIDDEN by Chris Ward answer 2026-07-31 Q1=A "classic spec drift"; the S9-N1 "still sees the filter" note is stale; spec edit pending)</t>
         </is>
       </c>
-      <c r="I55" s="2" t="inlineStr"/>
-      <c r="J55" s="2" t="inlineStr"/>
-    </row>
-    <row r="56">
-      <c r="A56" s="2" t="inlineStr">
+      <c r="I56" s="2" t="inlineStr"/>
+      <c r="J56" s="2" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
         <is>
           <t>Location column: leftmost for a multi-location user; Summary row blank</t>
         </is>
       </c>
-      <c r="B56" s="2" t="inlineStr">
+      <c r="B57" s="2" t="inlineStr">
         <is>
           <t>TU — Location Filter</t>
         </is>
       </c>
-      <c r="C56" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D56" s="2" t="inlineStr">
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E56" s="2" t="inlineStr">
+      <c r="E57" s="2" t="inlineStr">
         <is>
           <t>1. You are on the Technician Utilization report as a user with access to two or more locations.
 2. One technician clocked time at a single location in the range and another clocked time at two different locations.
 3. One of those days has hours at two locations (for the per-day check).</t>
         </is>
       </c>
-      <c r="F56" s="2" t="inlineStr">
+      <c r="F57" s="2" t="inlineStr">
         <is>
           <t>1. Select two or more locations and read the column headers from the left.
 2. Read the Location cell on the single-location technician's row.
@@ -3435,7 +3488,7 @@
 8. With more than one location still selected, download both PDF views and the CSV and read their columns from the left.</t>
         </is>
       </c>
-      <c r="G56" s="2" t="inlineStr">
+      <c r="G57" s="2" t="inlineStr">
         <is>
           <t>1. Signed in as someone whose account can reach more than one location, a Location column is shown as the LEFTMOST column, before Technician, already switched on.
 2. A technician whose hours were all clocked at one location shows that location's name.
@@ -3457,43 +3510,43 @@
 AUTOMATION: READY - EXPECT FAIL (SV-8954)</t>
         </is>
       </c>
-      <c r="H56" s="2" t="inlineStr">
+      <c r="H57" s="2" t="inlineStr">
         <is>
           <t>SV-8656; SV-8654 (TU spec v5 2026-07-29 S9-R9; S9-R10; S8-R15; S10-R4; S7-R13 — per-row Location column; leftmost before Technician; "Multiple" on a spanning row; Summary row blank; not in the selector; S7-R13 = same column in every download)</t>
         </is>
       </c>
-      <c r="I56" s="2" t="inlineStr"/>
-      <c r="J56" s="2" t="inlineStr"/>
-    </row>
-    <row r="57">
-      <c r="A57" s="2" t="inlineStr">
+      <c r="I57" s="2" t="inlineStr"/>
+      <c r="J57" s="2" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
         <is>
           <t>Column Selection: Technician always on, the other five toggleable, remembered</t>
         </is>
       </c>
-      <c r="B57" s="2" t="inlineStr">
+      <c r="B58" s="2" t="inlineStr">
         <is>
           <t>TU — Visual &amp; Accessibility</t>
         </is>
       </c>
-      <c r="C57" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D57" s="2" t="inlineStr">
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E57" s="2" t="inlineStr">
+      <c r="E58" s="2" t="inlineStr">
         <is>
           <t>1. You are on the Technician Utilization report with rows loaded.
 2. This browser has never saved settings for this report (fresh visit), so every column is at its default.
 3. Part of this test checks what a blind user would hear, so you need a screen reader. On Windows install NVDA — it is free, from nvaccess.org. On a Mac use VoiceOver, which is already built in (Cmd+F5 turns it on and off). Alternatively the browser's developer tools (F12) have an "Accessibility" panel that shows the same names without you having to listen to anything.</t>
         </is>
       </c>
-      <c r="F57" s="2" t="inlineStr">
+      <c r="F58" s="2" t="inlineStr">
         <is>
           <t>1. Find the column-selection button in the toolbar and hover it to read its tooltip.
 2. With the button focused, read the name assistive technology gives it — use the browser's accessibility inspector or a screen reader.
@@ -3504,7 +3557,7 @@
 7. Reload the page, then close the browser, reopen it and return to the report.</t>
         </is>
       </c>
-      <c r="G57" s="2" t="inlineStr">
+      <c r="G58" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1. The control is an icon button whose tooltip reads "Column Selection", sitting immediately after the three-dot download menu in the toolbar.
 2. Because the button shows an icon and no text, it still carries a name that assistive technology reads out — it is not left unnamed.
@@ -3521,48 +3574,48 @@
 </t>
         </is>
       </c>
-      <c r="H57" s="2" t="inlineStr">
+      <c r="H58" s="2" t="inlineStr">
         <is>
           <t>SV-8655; SV-8582 (TU spec v5 2026-07-29 Story 10 S10-R1; S10-R2; S10-R3; S10-R4; S10-R5; S10-R6 column selector + Story 8 S8-R16 accessible name — Story 10 has NO owning Jira story so epic SV-8582 is used and FLAGGED; S8-R16 is owned by SV-8655)</t>
         </is>
       </c>
-      <c r="I57" s="2" t="inlineStr"/>
-      <c r="J57" s="2" t="inlineStr"/>
-    </row>
-    <row r="58">
-      <c r="A58" s="2" t="inlineStr">
+      <c r="I58" s="2" t="inlineStr"/>
+      <c r="J58" s="2" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
         <is>
           <t>All-white table with no row shading; toolbar controls in the fixed order</t>
         </is>
       </c>
-      <c r="B58" s="2" t="inlineStr">
+      <c r="B59" s="2" t="inlineStr">
         <is>
           <t>TU — Visual &amp; Accessibility</t>
         </is>
       </c>
-      <c r="C58" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D58" s="2" t="inlineStr">
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E58" s="2" t="inlineStr">
+      <c r="E59" s="2" t="inlineStr">
         <is>
           <t>1. You are on the Technician Utilization report with rows loaded, in light mode.</t>
         </is>
       </c>
-      <c r="F58" s="2" t="inlineStr">
+      <c r="F59" s="2" t="inlineStr">
         <is>
           <t>1. Look at the column headers and the data rows' backgrounds.
 2. Read the toolbar controls left to right.
 3. Look for the expand/collapse-all control's position.</t>
         </is>
       </c>
-      <c r="G58" s="2" t="inlineStr">
+      <c r="G59" s="2" t="inlineStr">
         <is>
           <t>1. The report uses an all-white table: white column headers and white data cells, with NO alternating row shading.
 2. The toolbar controls run, left to right: the three-dot download menu, the Column Selection control, the date-range picker, the technician filter, and the Location filter (rightmost).
@@ -3573,42 +3626,42 @@
 AUTOMATION: READY</t>
         </is>
       </c>
-      <c r="H58" s="2" t="inlineStr">
+      <c r="H59" s="2" t="inlineStr">
         <is>
           <t>SV-8655 (TU spec v5 2026-07-29 S8-R1; S8-R2; S8-R3 — toolbar order rewritten: Column Selection inserted after the three-dot menu; and the date-range picker now precedes the technician filter)</t>
         </is>
       </c>
-      <c r="I58" s="2" t="inlineStr"/>
-      <c r="J58" s="2" t="inlineStr"/>
-    </row>
-    <row r="59">
-      <c r="A59" s="2" t="inlineStr">
+      <c r="I59" s="2" t="inlineStr"/>
+      <c r="J59" s="2" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
         <is>
           <t>Dark mode keeps every report element legible</t>
         </is>
       </c>
-      <c r="B59" s="2" t="inlineStr">
+      <c r="B60" s="2" t="inlineStr">
         <is>
           <t>TU — Visual &amp; Accessibility</t>
         </is>
       </c>
-      <c r="C59" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D59" s="2" t="inlineStr">
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="E59" s="2" t="inlineStr">
+      <c r="E60" s="2" t="inlineStr">
         <is>
           <t>1. You are on the Technician Utilization report with rows loaded, including a "—" Est. Lost Labor cell.
 2. Dark mode is available in the application.</t>
         </is>
       </c>
-      <c r="F59" s="2" t="inlineStr">
+      <c r="F60" s="2" t="inlineStr">
         <is>
           <t>1. Switch the application to dark mode.
 2. Check each element: page background, toolbar, cells, the Total Hours link, the information icon, the sort indicator, and a "—" glyph.
@@ -3616,7 +3669,7 @@
 4. Check the Total Hours link's underline/affordance and focus indicator in both modes.</t>
         </is>
       </c>
-      <c r="G59" s="2" t="inlineStr">
+      <c r="G60" s="2" t="inlineStr">
         <is>
           <t>1. The report supports dark mode: page background, toolbar, cells, the Total Hours link, the information icon, the sort indicator, and the "—" glyph are all clearly legible in dark mode.
 2. In BOTH light mode and dark mode the information icon is clearly visible against the background behind it - you can see it at a glance and it does not disappear into the background.
@@ -3628,49 +3681,49 @@
 AUTOMATION: READY</t>
         </is>
       </c>
-      <c r="H59" s="2" t="inlineStr">
+      <c r="H60" s="2" t="inlineStr">
         <is>
           <t>SV-8655 (TU spec v5 2026-07-29 S8-R9; S8-R13; S8-R14 — dark-mode legibility of every named element; the info icon at ≥ 3:1 in both modes; the Total Hours link affordance/focus in both modes; the ratio is design-token-owned)</t>
         </is>
       </c>
-      <c r="I59" s="2" t="inlineStr"/>
-      <c r="J59" s="2" t="inlineStr"/>
-    </row>
-    <row r="60">
-      <c r="A60" s="2" t="inlineStr">
+      <c r="I60" s="2" t="inlineStr"/>
+      <c r="J60" s="2" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
         <is>
           <t>The per-day breakdown is fetched only when a technician row is expanded</t>
         </is>
       </c>
-      <c r="B60" s="2" t="inlineStr">
+      <c r="B61" s="2" t="inlineStr">
         <is>
           <t>TU — API</t>
         </is>
       </c>
-      <c r="C60" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D60" s="2" t="inlineStr">
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E60" s="2" t="inlineStr">
+      <c r="E61" s="2" t="inlineStr">
         <is>
           <t>1. You are on the Technician Utilization report with rows loaded and browser devtools (network tab) open.
 2. To see the information this test asks for you need the browser's own developer tools: press F12 (or Ctrl+Shift+I; on a Mac Cmd+Option+I) and open the "Network" tab, then reload the page. There is nothing to install — it is built into Chrome, Edge and Firefox.</t>
         </is>
       </c>
-      <c r="F60" s="2" t="inlineStr">
+      <c r="F61" s="2" t="inlineStr">
         <is>
           <t>1. Load the report and inspect the initial data response for per-day content.
 2. Expand a technician row and watch the network traffic.
 3. Collapse and re-expand after a data reload.</t>
         </is>
       </c>
-      <c r="G60" s="2" t="inlineStr">
+      <c r="G61" s="2" t="inlineStr">
         <is>
           <t>1. The initial report payload does NOT ship the day rows.
 2. Expanding a technician row issues an on-demand backend request that returns that technician's per-day breakdown.
@@ -3681,42 +3734,42 @@
 AUTOMATION: READY</t>
         </is>
       </c>
-      <c r="H60" s="2" t="inlineStr">
+      <c r="H61" s="2" t="inlineStr">
         <is>
           <t>SV-8651 (TU spec v5 2026-07-29 S4-R2; S4-R5)</t>
         </is>
       </c>
-      <c r="I60" s="2" t="inlineStr"/>
-      <c r="J60" s="2" t="inlineStr"/>
-    </row>
-    <row r="61">
-      <c r="A61" s="2" t="inlineStr">
+      <c r="I61" s="2" t="inlineStr"/>
+      <c r="J61" s="2" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
         <is>
           <t>Date-range and location changes trigger a fresh server load</t>
         </is>
       </c>
-      <c r="B61" s="2" t="inlineStr">
+      <c r="B62" s="2" t="inlineStr">
         <is>
           <t>TU — API</t>
         </is>
       </c>
-      <c r="C61" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D61" s="2" t="inlineStr">
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E61" s="2" t="inlineStr">
+      <c r="E62" s="2" t="inlineStr">
         <is>
           <t>1. You are on the Technician Utilization report with rows loaded and browser devtools (network tab) open.
 2. To see the information this test asks for you need the browser's own developer tools: press F12 (or Ctrl+Shift+I; on a Mac Cmd+Option+I) and open the "Network" tab, then reload the page. There is nothing to install — it is built into Chrome, Edge and Firefox.</t>
         </is>
       </c>
-      <c r="F61" s="2" t="inlineStr">
+      <c r="F62" s="2" t="inlineStr">
         <is>
           <t>1. Change the date range and watch the network traffic.
 2. Change the location selection and watch the traffic.
@@ -3724,7 +3777,7 @@
 4. Click several column headers to sort and watch the traffic.</t>
         </is>
       </c>
-      <c r="G61" s="2" t="inlineStr">
+      <c r="G62" s="2" t="inlineStr">
         <is>
           <t>1. A date-range change triggers a fresh server load of the rows.
 2. A location change triggers a fresh server load scoped to the selected set.
@@ -3740,13 +3793,13 @@
 AUTOMATION: READY - EXPECT FAIL (SV-8945)</t>
         </is>
       </c>
-      <c r="H61" s="2" t="inlineStr">
+      <c r="H62" s="2" t="inlineStr">
         <is>
           <t>SV-8648 (TU spec v5 2026-07-29 S1-R5; S9-R3; S5 context note; S2-R13; §3)</t>
         </is>
       </c>
-      <c r="I61" s="2" t="inlineStr"/>
-      <c r="J61" s="2" t="inlineStr"/>
+      <c r="I62" s="2" t="inlineStr"/>
+      <c r="J62" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/testrail-import/Report-Suite_Technician-Utilization-Report_testrail-import.xlsx
+++ b/testrail-import/Report-Suite_Technician-Utilization-Report_testrail-import.xlsx
@@ -527,14 +527,13 @@
 2. Clicking it opens the report.
 3. The entry sits BELOW the pre-existing report links — Sales, Technician Efficiency, Advisor Analysis, Shop Efficiency — the new reports are added below those items without moving or disturbing them.
 ---
-This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Technician Utilization report specification version 7 (S1-R1), read on 11 August 2026.
-Last checked against build v3.5-16cf83f on 8/6/2026.
-AUTOMATION: READY</t>
+This is the expected behaviour as per epic SV-8582, read on 17 August 2026, and the Technician Utilization report specification version 9 (S1-R1), read on 17 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>SV-8648 (TU spec S1-R1 — below the named anchor items [Sales; Technician Efficiency; Advisor Analysis; Shop Efficiency] per the PRD video 2026-07-30; access = the one ordinary reports permission per QA lead 2026-08-03)</t>
+          <t>SV-8648 (TU spec v9 2026-08-17 S1-R1 — below the named anchor items [Sales; Technician Efficiency; Advisor Analysis; Shop Efficiency] per the PRD video 2026-07-30; access = the one ordinary reports permission per QA lead 2026-08-03)</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr"/>
@@ -578,14 +577,13 @@
           <t>1. Technician A has exactly ONE row.
 2. Technician B has NO row - only technicians with clocked time in the selected range at the selected location(s) appear.
 ---
-This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Technician Utilization report specification version 7 (S1-R2), read on 11 August 2026.
-Last checked against build v3.5-16cf83f on 8/6/2026.
-AUTOMATION: READY</t>
+This is the expected behaviour as per epic SV-8582, read on 17 August 2026, and the Technician Utilization report specification version 9 (S1-R2), read on 17 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>SV-8648 (TU spec v5 2026-07-29 S1-R2)</t>
+          <t>SV-8648 (TU spec v9 2026-08-17 S1-R2)</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr"/>
@@ -633,14 +631,14 @@
 · If it fails in a DIFFERENT way from what is described above, that is a NEW problem - please report it.
 · If it PASSES, the fix has shipped: tell the QA lead so the ticket can be closed and this note removed.
 ---
-This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Technician Utilization report specification version 7 (S1-R3, S1-R6, S9-R2), read on 11 August 2026.
+This is the expected behaviour as per epic SV-8582, read on 17 August 2026, and the Technician Utilization report specification version 9 (S1-R3, S1-R6, S9-R2), read on 17 August 2026.
 Last checked against build v3.5-16cf83f on 8/6/2026.
 AUTOMATION: READY - EXPECT FAIL (SV-8943)</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>SV-8648 (TU spec v5 2026-07-29 S1-R3; S1-R6; S9-R2)</t>
+          <t>SV-8648 (TU spec v9 2026-08-17 S1-R3; S1-R6; S9-R2)</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr"/>
@@ -685,14 +683,13 @@
 2. A valid Custom range applies normally.
 3. A Custom span wider than 366 days (matching the largest preset) is rejected - it cannot be applied.
 ---
-This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Technician Utilization report specification version 7 (S1-R4, S1-R5), read on 11 August 2026.
-Last checked against build v3.5-16cf83f on 8/6/2026.
-AUTOMATION: READY</t>
+This is the expected behaviour as per epic SV-8582, read on 17 August 2026, and the Technician Utilization report specification version 9 (S1-R4, S1-R5), read on 17 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>SV-8648 (TU spec v5 2026-07-29 S1-R4; S1-R5)</t>
+          <t>SV-8648 (TU spec v9 2026-08-17 S1-R4; S1-R5)</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr"/>
@@ -737,14 +734,13 @@
 2. The existing rows are replaced only when the new data returns.
 3. The toolbar remains interactive during the load.
 ---
-This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Technician Utilization report specification version 7 (S1-R10), read on 11 August 2026.
-Last checked against build v3.5-16cf83f on 8/6/2026.
-AUTOMATION: READY</t>
+This is the expected behaviour as per epic SV-8582, read on 17 August 2026, and the Technician Utilization report specification version 9 (S1-R10), read on 17 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>SV-8648 (TU spec v5 2026-07-29 S1-R10)</t>
+          <t>SV-8648 (TU spec v9 2026-08-17 S1-R10)</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr"/>
@@ -792,14 +788,13 @@
 3. EVERY record is day-grouped and windowed in a SINGLE report-level time zone - the active workplace's - regardless of the location where it was clocked (a record's day, the current-month boundary, and the midnight split all use that one zone).
 4. This matches the Timesheet Activities report's single-time-zone grouping.
 ---
-This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Technician Utilization report specification version 7 (S1-R7), read on 11 August 2026.
-Last checked against build v3.5-16cf83f on 8/6/2026.
-AUTOMATION: READY</t>
+This is the expected behaviour as per epic SV-8582, read on 17 August 2026, and the Technician Utilization report specification version 9 (S1-R7), read on 17 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>SV-8648 (TU spec v5 2026-07-29 S1-R7; S1 context notes)</t>
+          <t>SV-8648 (TU spec v9 2026-08-17 S1-R7; S1 context notes)</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr"/>
@@ -841,14 +836,14 @@
         <is>
           <t>1. The Technician Utilization report does NOT appear in the navigation.
 ---
-This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Technician Utilization report specification version 7 (S1-N1), read on 11 August 2026.
+This is the expected behaviour as per epic SV-8582, read on 17 August 2026, and the Technician Utilization report specification version 9 (S1-N1), read on 17 August 2026.
 Last checked against build v3.5-16cf83f on 8/6/2026.
 AUTOMATION: HOLD - needs a second sign-in as a user without reports access, and there is one shared sign-in on this environment</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>SV-8648 (TU spec S1-N1 — the gate is the one ordinary reports access per Chris Ward Q2=A + QA lead 2026-08-03 "ONE permission FOR NOW"; the TU prerequisite still names the timesheet-reports permission — his spec edit owed)</t>
+          <t>SV-8648 (TU spec v9 2026-08-17 S1-N1 — the gate is the one ordinary reports access per Chris Ward Q2=A + QA lead 2026-08-03 "ONE permission FOR NOW"; Story 1 Prerequisites now states the single reports permission outright so his spec edit is DONE)</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr"/>
@@ -894,14 +889,13 @@
 2. The Summary row is hidden.
 3. Clearing every technician shows the SAME message and hides the Summary row — this version does not use distinct copy for genuinely-no-data vs a cleared filter.
 ---
-This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Technician Utilization report specification version 7 (S1-N2, S3-N1, S5-N1, S9-N2), read on 11 August 2026.
-Last checked against build v3.5-16cf83f on 8/6/2026.
-AUTOMATION: READY</t>
+This is the expected behaviour as per epic SV-8582, read on 17 August 2026, and the Technician Utilization report specification version 9 (S1-N2, S3-N1, S5-N1, S9-N2), read on 17 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>SV-8648 (TU spec v5 2026-07-29 S1-N2; S3-N1; S5-N1; S9-N2; §7 — §7 CLOSES the no-data string verbatim ("Empty bays" ... "Get Going!") as the standard reports no-data label; so the exact string IS the requirement)</t>
+          <t>SV-8648 (TU spec v9 2026-08-17 S1-N2; S3-N1; S5-N1; S9-N2; §7 — §7 CLOSES the no-data string verbatim ("Empty bays" ... "Get Going!") as the standard reports no-data label; so the exact string IS the requirement)</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr"/>
@@ -954,14 +948,13 @@
 Note for the tester: if the Location column does not behave this way on the build, mark this test Failed and report it - do not change the test.
 Location is one of the columns you can switch on and off in the column-selection control, but only if your own account can reach more than one location: for you it is already switched on when you arrive, and you can switch it off. Someone whose account can reach only one location never sees the column and it is not offered to them in that list.
 ---
-This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Technician Utilization report specification version 7 (S2-R1, S2-R2, S2-R3, S2-R4, S2-R5, S9-R9), read on 11 August 2026. Version 6 of that specification, published on 5 August 2026, is what settles the one point about the Location column: it now states in both of its own requirements that the column belongs to anyone whose account can reach more than one location and can be switched on and off in the column-selection control. Chris Ward asked for that change in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true, read on 11 August 2026
-Last checked against build v3.5-16cf83f on 8/6/2026.
-AUTOMATION: READY</t>
+This is the expected behaviour as per epic SV-8582, read on 17 August 2026, and the Technician Utilization report specification version 9 (S2-R1, S2-R2, S2-R3, S2-R4, S2-R5, S9-R9), read on 17 August 2026. Version 6 of that specification, published on 5 August 2026, is what settles the one point about the Location column: it now states in both of its own requirements that the column belongs to anyone whose account can reach more than one location and can be switched on and off in the column-selection control. Chris Ward asked for that change in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true, read on 17 August 2026
+AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>SV-8649; SV-8656 (TU spec v5 2026-07-29 S2-R1; S2-R2; S2-R3; S2-R4; S2-R5; §3 + Story 9 S9-R9 — header order and the hours columns; plus the automatic Location column leftmost when shown)</t>
+          <t>SV-8649; SV-8656 (TU spec v9 2026-08-17 S2-R1; S2-R2; S2-R3; S2-R4; S2-R5; §3 + Story 9 S9-R9 — header order and the hours columns; plus the automatic Location column leftmost when shown)</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr"/>
@@ -1004,14 +997,13 @@
           <t>1. Utilization % = work-order hours as a percentage of total clocked hours, computed from the unrounded hours (not from the already-rounded displays).
 2. It shows one decimal place followed by a percent sign, rounded round-half-up (66.65% → 66.7%).
 ---
-This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Technician Utilization report specification version 7 (S2-R6, S2-R7), read on 11 August 2026.
-Last checked against build v3.5-16cf83f on 8/6/2026.
-AUTOMATION: READY</t>
+This is the expected behaviour as per epic SV-8582, read on 17 August 2026, and the Technician Utilization report specification version 9 (S2-R6, S2-R7), read on 17 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>SV-8649 (TU spec v5 2026-07-29 S2-R6; S2-R7; §3)</t>
+          <t>SV-8649 (TU spec v9 2026-08-17 S2-R6; S2-R7; §3)</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr"/>
@@ -1056,14 +1048,13 @@
 2. No row shows more than 100% - work-order hours are always part of total clocked hours.
 3. The "—" (undefined, total = 0) state is unreachable on a rendered technician or day row, because only technicians with clocked time get rows.
 ---
-This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Technician Utilization report specification version 7 (S2-E1, S2-R7), read on 11 August 2026.
-Last checked against build v3.5-16cf83f on 8/6/2026.
-AUTOMATION: READY</t>
+This is the expected behaviour as per epic SV-8582, read on 17 August 2026, and the Technician Utilization report specification version 9 (S2-E1, S2-R7), read on 17 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>SV-8649 (TU spec v5 2026-07-29 S2-E1; S2-R7; S2 context note)</t>
+          <t>SV-8649 (TU spec v9 2026-08-17 S2-E1; S2-R7; S2 context note)</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr"/>
@@ -1110,14 +1101,13 @@
 2. In a single-location view it is simply that one location's rate × the technician's internal hours.
 3. The value shows as dollars with two decimals and commas between thousands (e.g. "$1,234.50").
 ---
-This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Technician Utilization report specification version 7 (S2-R8, S2-R9), read on 11 August 2026.
-Last checked against build v3.5-16cf83f on 8/6/2026.
-AUTOMATION: READY</t>
+This is the expected behaviour as per epic SV-8582, read on 17 August 2026, and the Technician Utilization report specification version 9 (S2-R8, S2-R9), read on 17 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>SV-8649 (TU spec v5 2026-07-29 S2-R8; S2-R9; §3)</t>
+          <t>SV-8649 (TU spec v9 2026-08-17 S2-R8; S2-R9; §3)</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr"/>
@@ -1165,14 +1155,13 @@
 3. NO column header other than Est. Lost Labor shows the information icon.
 4. Est. Lost Labor can be turned OFF in the Column Selection control; when it is off the column, its bold styling and its information icon are all absent, and the report still works normally.
 ---
-This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Technician Utilization report specification version 7 (S2-R10, S2-R11, S8-R4, S8-R6, S8-R7, S8-N1, S10-R3), read on 11 August 2026.
-Last checked against build v3.5-16cf83f on 8/6/2026.
-AUTOMATION: READY</t>
+This is the expected behaviour as per epic SV-8582, read on 17 August 2026, and the Technician Utilization report specification version 9 (S2-R10, S2-R11, S8-R4, S8-R6, S8-R7, S8-N1, S10-R3), read on 17 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>SV-8649 (TU spec v5 2026-07-29 S2-R10; S2-R11; S8-R4; S8-R6; S8-R7; S8-N1 — each re-worded "When shown" now that Est. Lost Labor is a hideable column; new Story 10 S10-R3)</t>
+          <t>SV-8649 (TU spec v9 2026-08-17 S2-R10; S2-R11; S8-R4; S8-R6; S8-R7; S8-N1 — each re-worded "When shown" now that Est. Lost Labor is a hideable column; new Story 10 S10-R3)</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr"/>
@@ -1217,14 +1206,13 @@
 2. Technician B also shows "$0.00" - a configured rate of exactly $0.00 is a KNOWN rate that values the hours at $0.00, not "—".
 3. "$0.00" means 'the rate is known and there is nothing (or $0) to value' - a different state from "—" ('the rate is unknown').
 ---
-This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Technician Utilization report specification version 7 (S2-E2), read on 11 August 2026.
-Last checked against build v3.5-16cf83f on 8/6/2026.
-AUTOMATION: READY</t>
+This is the expected behaviour as per epic SV-8582, read on 17 August 2026, and the Technician Utilization report specification version 9 (S2-E2), read on 17 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>SV-8649 (TU spec v5 2026-07-29 S2-E2; §5 Assumptions; S2 context note)</t>
+          <t>SV-8649 (TU spec v9 2026-08-17 S2-E2; §5 Assumptions; S2 context note)</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr"/>
@@ -1269,14 +1257,14 @@
 2. The "—" cell carries the assistive-technology label "No default labor rate configured" (distinguishing it from "$0.00", which reads as its dollar value).
 3. The technician's Internal Hours column still shows all the internal hours (they are counted even though they cannot be valued).
 ---
-This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Technician Utilization report specification version 7 (S2-E3, S8-R11, S2-R4), read on 11 August 2026.
+This is the expected behaviour as per epic SV-8582, read on 17 August 2026, and the Technician Utilization report specification version 9 (S2-E3, S8-R11, S2-R4), read on 17 August 2026.
 Last checked against build v3.5-16cf83f on 8/6/2026.
 AUTOMATION: HOLD - no location on this environment is set up without a default labor rate, so the em-dash state cannot be produced</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>SV-8649 (TU spec v5 2026-07-29 S2-E3; S8-R11; S2-R4)</t>
+          <t>SV-8649 (TU spec v9 2026-08-17 S2-E3; S8-R11; S2-R4)</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr"/>
@@ -1321,14 +1309,14 @@
 2. The amount shows as a normal "$X.XX" with NO partial-value indicator in this version - so the row's Est. Lost Labor values fewer hours than its Internal Hours column shows.
 3. This is a documented known limitation (a partial-value indicator is a possible follow-up) - expected behavior, not a defect.
 ---
-This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Technician Utilization report specification version 7 (S2-E4), read on 11 August 2026.
+This is the expected behaviour as per epic SV-8582, read on 17 August 2026, and the Technician Utilization report specification version 9 (S2-E4), read on 17 August 2026.
 Last checked against build v3.5-16cf83f on 8/6/2026.
 AUTOMATION: HOLD - no location on this environment is set up without a default labor rate, so a part-valued row cannot be produced</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>SV-8649 (TU spec v5 2026-07-29 S2-E4)</t>
+          <t>SV-8649 (TU spec v9 2026-08-17 S2-E4)</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr"/>
@@ -1374,14 +1362,13 @@
 2. The Technician header shows the ascending sort indicator.
 3. The active sort header exposes its state to assistive technology (aria-sort = ascending on the Technician header; none on the others).
 ---
-This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Technician Utilization report specification version 7 (S2-R12, S8-R8, S8-R10), read on 11 August 2026.
-Last checked against build v3.5-16cf83f on 8/6/2026.
-AUTOMATION: READY</t>
+This is the expected behaviour as per epic SV-8582, read on 17 August 2026, and the Technician Utilization report specification version 9 (S2-R12, S8-R8, S8-R10), read on 17 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>SV-8649 (TU spec v5 2026-07-29 S2-R12; S8-R8; S8-R10)</t>
+          <t>SV-8649 (TU spec v9 2026-08-17 S2-R12; S8-R8; S8-R10)</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr"/>
@@ -1430,14 +1417,13 @@
 4. Sorting is applied on screen to the loaded rows - NO reload/server request happens.
 5. Technicians tied in the sorted column are ordered by Technician name A to Z; two technicians sharing the same display name keep a stable order between renders.
 ---
-This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Technician Utilization report specification version 7 (S2-R13, S2-R14), read on 11 August 2026.
-Last checked against build v3.5-4795eee on 8/10/2026.
-AUTOMATION: READY</t>
+This is the expected behaviour as per epic SV-8582, read on 17 August 2026, and the Technician Utilization report specification version 9 (S2-R13, S2-R14), read on 17 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>SV-8649 (TU spec v5 2026-07-29 S2-R13; S2-R14)</t>
+          <t>SV-8649 (TU spec v9 2026-08-17 S2-R13; S2-R14)</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr"/>
@@ -1481,14 +1467,13 @@
           <t>1. After the reload, the rows are back to Technician name A to Z (the sort reset).
 2. On the return visit, the sort is again Technician A to Z - sort is NOT persisted (unlike the date range, technician selection, and location selection, which are).
 ---
-This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Technician Utilization report specification version 7 (S2-R15), read on 11 August 2026.
-Last checked against build v3.5-16cf83f on 8/6/2026.
-AUTOMATION: READY</t>
+This is the expected behaviour as per epic SV-8582, read on 17 August 2026, and the Technician Utilization report specification version 9 (S2-R15), read on 17 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>SV-8649 (TU spec v5 2026-07-29 S2-R15; §3)</t>
+          <t>SV-8649 (TU spec v9 2026-08-17 S2-R15; §3)</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr"/>
@@ -1533,14 +1518,13 @@
 2. The Summary row stays pinned at the bottom.
 3. Each technician's expanded day rows stay under that technician, still in date order (earliest to latest) - they do not re-sort by the clicked column.
 ---
-This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Technician Utilization report specification version 7 (S2-R16), read on 11 August 2026.
-Last checked against build v3.5-16cf83f on 8/6/2026.
-AUTOMATION: READY</t>
+This is the expected behaviour as per epic SV-8582, read on 17 August 2026, and the Technician Utilization report specification version 9 (S2-R16), read on 17 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>SV-8649 (TU spec v5 2026-07-29 S2-R16)</t>
+          <t>SV-8649 (TU spec v9 2026-08-17 S2-R16)</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr"/>
@@ -1585,14 +1569,14 @@
 2. Among themselves, the "—" rows are ordered by Technician name A to Z.
 3. A "$0.00" value is a number, not "—" - it sorts as zero (lowest ascending, above only the — group).
 ---
-This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Technician Utilization report specification version 7 (S2-R17), read on 11 August 2026.
+This is the expected behaviour as per epic SV-8582, read on 17 August 2026, and the Technician Utilization report specification version 9 (S2-R17), read on 17 August 2026.
 Last checked against build v3.5-16cf83f on 8/6/2026.
 AUTOMATION: HOLD - no technician on this environment has an em-dash in Est. Lost Labor, because both locations have a default labor rate</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>SV-8649 (TU spec v5 2026-07-29 S2-R17)</t>
+          <t>SV-8649 (TU spec v9 2026-08-17 S2-R17)</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr"/>
@@ -1638,14 +1622,13 @@
 3. It uses the same number formats as the technician rows.
 4. Its values carry NO label prefix such as "TOTAL:" or "AVG:".
 ---
-This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Technician Utilization report specification version 7 (S3-R1, S3-R2, S3-R6, S3-R7, S8-R5), read on 11 August 2026.
-Last checked against build v3.5-16cf83f on 8/6/2026.
-AUTOMATION: READY</t>
+This is the expected behaviour as per epic SV-8582, read on 17 August 2026, and the Technician Utilization report specification version 9 (S3-R1, S3-R2, S3-R6, S3-R7, S8-R5), read on 17 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>SV-8650 (TU spec v5 2026-07-29 S3-R1; S3-R2; S3-R6; S3-R7; S8-R5)</t>
+          <t>SV-8650 (TU spec v9 2026-08-17 S3-R1; S3-R2; S3-R6; S3-R7; S8-R5)</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr"/>
@@ -1690,14 +1673,13 @@
 2. Eye-summing the displayed rows MAY differ from the displayed Summary by 0.01 — one unit in the last decimal (these values are HOURS, not money) — expected in a compute-from-unrounded report, not a defect.
 3. With every technician selected, the Summary row equals the shop totals for the full date range at the selected location(s).
 ---
-This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Technician Utilization report specification version 7 (S3-R3, S5-E1), read on 11 August 2026.
-Last checked against build v3.5-16cf83f on 8/6/2026.
-AUTOMATION: READY</t>
+This is the expected behaviour as per epic SV-8582, read on 17 August 2026, and the Technician Utilization report specification version 9 (S3-R3, S5-E1), read on 17 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>SV-8650 (TU spec v5 2026-07-29 S3-R3; §3 context note; S5-E1)</t>
+          <t>SV-8650 (TU spec v9 2026-08-17 S3-R3; §3 context note; S5-E1)</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr"/>
@@ -1741,14 +1723,13 @@
           <t>1. The Summary Utilization % shows the WEIGHTED rate - the visible technicians' total work-order hours as a percentage of their total clocked hours, from unrounded hours (10.0% in the example).
 2. It is NOT the average of the per-technician percentages (not 50.0%).
 ---
-This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Technician Utilization report specification version 7 (S3-R4), read on 11 August 2026.
-Last checked against build v3.5-16cf83f on 8/6/2026.
-AUTOMATION: READY</t>
+This is the expected behaviour as per epic SV-8582, read on 17 August 2026, and the Technician Utilization report specification version 9 (S3-R4), read on 17 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>SV-8650 (TU spec v5 2026-07-29 S3-R4)</t>
+          <t>SV-8650 (TU spec v9 2026-08-17 S3-R4)</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr"/>
@@ -1792,14 +1773,13 @@
 2. A visible technician whose value is "—" contributes NOTHING to the sum - so the Summary understates true lost labor whenever any visible technician is "—" or partially valued (documented, expected).
 3. The Summary shows "—" only when EVERY visible technician's Est. Lost Labor is "—".
 ---
-This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Technician Utilization report specification version 7 (S3-R5), read on 11 August 2026.
-Last checked against build v3.5-16cf83f on 8/6/2026.
-AUTOMATION: READY</t>
+This is the expected behaviour as per epic SV-8582, read on 17 August 2026, and the Technician Utilization report specification version 9 (S3-R5), read on 17 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>SV-8650 (TU spec v5 2026-07-29 S3-R5)</t>
+          <t>SV-8650 (TU spec v9 2026-08-17 S3-R5)</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr"/>
@@ -1849,14 +1829,14 @@
 · If it fails in a DIFFERENT way from what is described above, that is a NEW problem - please report it.
 · If it PASSES, the fix has shipped: tell the QA lead so the ticket can be closed and this note removed.
 ---
-This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Technician Utilization report specification version 7 (S4-R1, S8-R12), read on 11 August 2026.
+This is the expected behaviour as per epic SV-8582, read on 17 August 2026, and the Technician Utilization report specification version 9 (S4-R1, S8-R12), read on 17 August 2026.
 Last checked against build v3.5-4795eee on 8/10/2026.
 AUTOMATION: READY - EXPECT FAIL (SV-8953)</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>SV-8651 (TU spec v5 2026-07-29 S4-R1; S8-R12)</t>
+          <t>SV-8651 (TU spec v9 2026-08-17 S4-R1; S8-R12)</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr"/>
@@ -1905,14 +1885,13 @@
 4. With several locations selected, a day's row POOLS that day's hours across the selected locations - one day row per date, not one per location.
 5. Note for the tester: you do not need developer tools for this test - just watch the screen.
 ---
-This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Technician Utilization report specification version 7 (S4-R2, S4-N1, S9-R4), read on 11 August 2026.
-Last checked against build v3.5-16cf83f on 8/6/2026.
-AUTOMATION: READY</t>
+This is the expected behaviour as per epic SV-8582, read on 17 August 2026, and the Technician Utilization report specification version 9 (S4-R2, S4-N1, S9-R4), read on 17 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>SV-8651 (TU spec v5 2026-07-29 S4-R2; S4-N1; S9-R4 — one row per clocked day in date order; load-on-expand; no row for an unclocked day; per-day pooling across selected locations; the back-end half is covered by C30449 in "TU - API")</t>
+          <t>SV-8651 (TU spec v9 2026-08-17 S4-R2; S4-N1; S9-R4 — one row per clocked day in date order; load-on-expand; no row for an unclocked day; per-day pooling across selected locations; the back-end half is covered by C30449 in "TU - API")</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr"/>
@@ -1957,14 +1936,13 @@
 2. The day's Est. Lost Labor is valued per location exactly like a technician row (that location's default labor rate × that day's internal hours there).
 3. Hours 2dp / Utilization one decimal + % / dollars with commas - all identical to the row formats, computed from unrounded values and rounded once.
 ---
-This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Technician Utilization report specification version 7 (S4-R3, S2-R8), read on 11 August 2026.
-Last checked against build v3.5-16cf83f on 8/6/2026.
-AUTOMATION: READY</t>
+This is the expected behaviour as per epic SV-8582, read on 17 August 2026, and the Technician Utilization report specification version 9 (S4-R3, S2-R8), read on 17 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>SV-8651 (TU spec v5 2026-07-29 S4-R3; S2-R8; §3)</t>
+          <t>SV-8651 (TU spec v9 2026-08-17 S4-R3; S2-R8; §3)</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr"/>
@@ -2016,14 +1994,14 @@
 · If it fails in a DIFFERENT way from what is described above, that is a NEW problem - please report it.
 · If it PASSES, the fix has shipped: tell the QA lead so the ticket can be closed and this note removed.
 ---
-This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Technician Utilization report specification version 7 (S4-R4, S8-R12, S8-R3), read on 11 August 2026.
+This is the expected behaviour as per epic SV-8582, read on 17 August 2026, and the Technician Utilization report specification version 9 (S4-R4, S8-R12, S8-R3), read on 17 August 2026.
 Last checked against build v3.5-16cf83f on 8/6/2026.
 AUTOMATION: READY - EXPECT FAIL (SV-8953)</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>SV-8651 (TU spec v5 2026-07-29 S4-R4; S8-R12; S8-R3)</t>
+          <t>SV-8651 (TU spec v9 2026-08-17 S4-R4; S8-R12; S8-R3)</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr"/>
@@ -2068,14 +2046,13 @@
 2. On a fresh visit, all rows start collapsed - expansion is never persisted.
 3. Deselecting and re-selecting a technician (an on-screen operation) does NOT change the expansion state of the other rows - the expanded row stays expanded.
 ---
-This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Technician Utilization report specification version 7 (S4-R5), read on 11 August 2026.
-Last checked against build v3.5-16cf83f on 8/6/2026.
-AUTOMATION: READY</t>
+This is the expected behaviour as per epic SV-8582, read on 17 August 2026, and the Technician Utilization report specification version 9 (S4-R5), read on 17 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>SV-8651 (TU spec v5 2026-07-29 S4-R5)</t>
+          <t>SV-8651 (TU spec v9 2026-08-17 S4-R5)</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr"/>
@@ -2120,14 +2097,13 @@
 2. On the first visit, EVERY technician is selected.
 3. All technicians' rows are shown.
 ---
-This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Technician Utilization report specification version 7 (S5-R1, S5-R2), read on 11 August 2026.
-Last checked against build v3.5-4795eee on 8/10/2026.
-AUTOMATION: READY</t>
+This is the expected behaviour as per epic SV-8582, read on 17 August 2026, and the Technician Utilization report specification version 9 (S5-R1, S5-R2), read on 17 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>SV-8652 (TU spec v5 2026-07-29 S5-R1; S5-R2)</t>
+          <t>SV-8652 (TU spec v9 2026-08-17 S5-R1; S5-R2)</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr"/>
@@ -2179,14 +2155,14 @@
 · If it fails in a DIFFERENT way from what is described above, that is a NEW problem - please report it.
 · If it PASSES, the fix has shipped: tell the QA lead so the ticket can be closed and this note removed.
 ---
-This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Technician Utilization report specification version 7 (S5-R3, S5-R4, S5-R5), read on 11 August 2026.
+This is the expected behaviour as per epic SV-8582, read on 17 August 2026, and the Technician Utilization report specification version 9 (S5-R3, S5-R4, S5-R5), read on 17 August 2026.
 Last checked against build v3.5-4795eee on 8/10/2026.
 AUTOMATION: READY - EXPECT FAIL (SV-8946)</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>SV-8652 (TU spec v5 2026-07-29 S5-R3; S5-R4; S5-R5 + §3 Key Decisions ("the technician filter works on screen only and does not reload the report"); S5 context note — the server half is covered by C30450 in "TU - API")</t>
+          <t>SV-8652 (TU spec v9 2026-08-17 S5-R3; S5-R4; S5-R5 + §3 Key Decisions ("the technician filter works on screen only and does not reload the report"); S5 context note — the server half is covered by C30450 in "TU - API")</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr"/>
@@ -2237,14 +2213,14 @@
 · If it fails in a DIFFERENT way from what is described above, that is a NEW problem - please report it.
 · If it PASSES, the fix has shipped: tell the QA lead so the ticket can be closed and this note removed.
 ---
-This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Technician Utilization report specification version 7 (S5-R6, S5-R7, S5-R8, S5-R9), read on 11 August 2026.
+This is the expected behaviour as per epic SV-8582, read on 17 August 2026, and the Technician Utilization report specification version 9 (S5-R6, S5-R7, S5-R8, S5-R9), read on 17 August 2026.
 Last checked against build v3.5-16cf83f on 8/6/2026.
 AUTOMATION: READY - EXPECT FAIL (SV-8947)</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>SV-8652 (TU spec v5 2026-07-29 S5-R6; S5-R7; S5-R8; S5-R9)</t>
+          <t>SV-8652 (TU spec v9 2026-08-17 S5-R6; S5-R7; S5-R8; S5-R9)</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr"/>
@@ -2289,14 +2265,13 @@
 2. All other technicians - including any who appear for the first time - are selected.
 3. The saved date range and location selection are restored alongside.
 ---
-This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Technician Utilization report specification version 7 (S5-R10, S1-R8), read on 11 August 2026.
-Last checked against build v3.5-16cf83f on 8/6/2026.
-AUTOMATION: READY</t>
+This is the expected behaviour as per epic SV-8582, read on 17 August 2026, and the Technician Utilization report specification version 9 (S5-R10, S1-R8), read on 17 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>SV-8652 (TU spec v5 2026-07-29 S5-R10; S1-R8; §3)</t>
+          <t>SV-8652 (TU spec v9 2026-08-17 S5-R10; S1-R8; §3)</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr"/>
@@ -2337,18 +2312,18 @@
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>1. Every technician row's Total Hours is rendered as a link (every rendered row has clocked time &gt; 0, so the link always applies).
+          <t>1. A technician row's Total Hours is rendered as a link ONLY when the report's location scope is exactly your active shop (the default view). Under any other scope — a different single location, or multiple locations — the value renders as plain text, styled like the other hour columns (no link).
 2. The link is distinguished by more than color - it carries an underline (or equivalent non-color affordance), is keyboard-focusable with a visible focus indicator, and activates on Enter.
 3. The Summary row's Total Hours value is NOT a link.
----
-This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Technician Utilization report specification version 7 (S6-R1, S6-N1, S8-R14), read on 11 August 2026.
-Last checked against build v3.5-16cf83f on 8/6/2026.
-AUTOMATION: READY</t>
+Note for the tester: an earlier version of this report showed Total Hours as a link in every scope. The current Technician Utilization report specification (version 9, S6-R1/S6-R6, per SV-9064) makes it a link ONLY in the default view where the location scope is your active shop; in any other scope it is plain text. Follow the current specification.
+---
+This is the expected behaviour as per epic SV-8582, read on 17 August 2026, and the Technician Utilization report specification version 9 (S6-R1, S6-N1, S8-R14), read on 17 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>SV-8653 (TU spec v5 2026-07-29 S6-R1; S6-N1; S8-R14)</t>
+          <t>SV-8653 (TU spec v9 2026-08-17 S6-R1; S6-N1; S8-R14)</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr"/>
@@ -2393,14 +2368,13 @@
 2. It is already filtered to that technician.
 3. It uses the same date range that was active on the Technician Utilization report.
 ---
-This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Technician Utilization report specification version 7 (S6-R2, S6-R3, S6-R4), read on 11 August 2026.
-Last checked against build v3.5-16cf83f on 8/6/2026.
-AUTOMATION: READY</t>
+This is the expected behaviour as per epic SV-8582, read on 17 August 2026, and the Technician Utilization report specification version 9 (S6-R2, S6-R3, S6-R4), read on 17 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>SV-8653 (TU spec v5 2026-07-29 S6-R2; S6-R3; S6-R4)</t>
+          <t>SV-8653 (TU spec v9 2026-08-17 S6-R2; S6-R3; S6-R4)</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr"/>
@@ -2450,14 +2424,14 @@
 · If it fails in a DIFFERENT way from what is described above, that is a NEW problem - please report it.
 · If it PASSES, the fix has shipped: tell the QA lead so the ticket can be closed and this note removed.
 ---
-This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Technician Utilization report specification version 7 (S1-R9), read on 11 August 2026.
+This is the expected behaviour as per epic SV-8582, read on 17 August 2026, and the Technician Utilization report specification version 9 (S1-R9), read on 17 August 2026.
 Last checked against build v3.5-16cf83f on 8/6/2026.
 AUTOMATION: READY - EXPECT FAIL (SV-8944)</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>SV-8648 (TU spec v5 2026-07-29 S1-R9; §2; §5 Assumptions)</t>
+          <t>SV-8648 (TU spec v9 2026-08-17 S1-R9; §2; §5 Assumptions)</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr"/>
@@ -2502,14 +2476,14 @@
 2. The two reports, loaded at different moments, MAY differ by the elapsed open time - this is a deliberate scope difference of the reconciliation guarantee, EXPECTED and NOT a defect.
 3. Reloading the Technician Utilization report takes a fresh snapshot (the value grows by the elapsed time).
 ---
-This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Technician Utilization report specification version 7 (S1-R9, S1-E1), read on 11 August 2026.
+This is the expected behaviour as per epic SV-8582, read on 17 August 2026, and the Technician Utilization report specification version 9 (S1-R9, S1-E1), read on 17 August 2026.
 Last checked against build v3.5-16cf83f on 8/6/2026.
 AUTOMATION: HOLD - needs a technician clocked in at the moment of the test, and no technician on this environment is currently clocked in</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>SV-8648 (TU spec v5 2026-07-29 S1-R9(a); S1-E1)</t>
+          <t>SV-8648 (TU spec v9 2026-08-17 S1-R9(a); S1-E1)</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr"/>
@@ -2551,18 +2525,18 @@
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>1. The link passes the technician and the date range ONLY - it does NOT pass the location selection.
-2. Timesheet Activities opens for the user's currently active shop, so it shows one location's portion - it will differ from (or be disjoint with) the multi-location row value.
-3. This is a KNOWN drill-through limitation, EXPECTED and NOT a data defect (the same applies when the single selected location is not the active shop).
----
-This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Technician Utilization report specification version 7 (S6-R6, S1-R9), read on 11 August 2026.
-Last checked against build v3.5-16cf83f on 8/6/2026.
-AUTOMATION: READY</t>
+          <t>1. Total Hours is a link ONLY in the default view where the location scope is your active shop; under that scope the drill-through reconciles to the cent.
+2. In any other scope — a single location that is not your active shop, or multiple locations — Total Hours is plain text, not a link, so there is no drill-through and no reconciliation mismatch to worry about.
+3. This resolves the earlier "reconciliation exception (b)": because the link no longer appears outside the active-shop scope, the mismatch it described can no longer occur (per SV-9064).
+Note for the tester: an earlier version of this report showed Total Hours as a link in every scope. The current Technician Utilization report specification (version 9, S6-R1/S6-R6, per SV-9064) makes it a link ONLY in the default view where the location scope is your active shop; in any other scope it is plain text. Follow the current specification.
+---
+This is the expected behaviour as per epic SV-8582, read on 17 August 2026, and the Technician Utilization report specification version 9 (S6-R6, S1-R9), read on 17 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>SV-8653 (TU spec v5 2026-07-29 S6-R6; S1-R9(b))</t>
+          <t>SV-8653 (TU spec v9 2026-08-17 S6-R6; S1-R9(b))</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr"/>
@@ -2604,15 +2578,16 @@
         <is>
           <t>1. Timesheet Activities opens filtered to that technician.
 2. The date range covers ONLY that single day.
----
-This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Technician Utilization report specification version 7 (S6-R5), read on 11 August 2026.
-Last checked against build v3.5-16cf83f on 8/6/2026.
-AUTOMATION: READY</t>
+3. This day-row link appears only under the default active-shop scope (the same scope gate as the technician row, per SV-9064); under any other scope the day row's Total Hours is plain text, not a link.
+Note for the tester: an earlier version of this report showed Total Hours as a link in every scope. The current Technician Utilization report specification (version 9, S6-R1/S6-R6, per SV-9064) makes it a link ONLY in the default view where the location scope is your active shop; in any other scope it is plain text. Follow the current specification.
+---
+This is the expected behaviour as per epic SV-8582, read on 17 August 2026, and the Technician Utilization report specification version 9 (S6-R5), read on 17 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>SV-8653 (TU spec v5 2026-07-29 S6-R5)</t>
+          <t>SV-8653 (TU spec v9 2026-08-17 S6-R5)</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr"/>
@@ -2656,14 +2631,13 @@
 2. The menu holds four download options, labeled exactly: "Download Summary (PDF)", "Download Expanded View (PDF)", "Download Summary (CSV)" and "Download Expanded View (CSV)".
 3. The order these four options appear in is NOT part of this check. The specification requires each option to be present with that exact label; it does not fix the order they are listed in. Do not fail this test on the order alone.
 ---
-This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and its story SV-8654, read on 11 August 2026, and the Technician Utilization report specification version 7 (S7-R1, S7-R2, S7-R3, S7-R4, S7-R4a, S8-R2), read on 11 August 2026. Chris Ward asked for this menu wording in his answers of 5 August 2026 in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true, read on 11 August 2026; the specification now carries the same wording, so the two agree.
-Last checked against build v3.5-16cf83f on 8/6/2026.
-AUTOMATION: READY</t>
+This is the expected behaviour as per epic SV-8582, read on 17 August 2026, and its story SV-8654, read on 17 August 2026, and the Technician Utilization report specification version 9 (S7-R1, S7-R2, S7-R3, S7-R4, S7-R4a, S8-R2), read on 17 August 2026. Chris Ward asked for this menu wording in his answers of 5 August 2026 in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true, read on 17 August 2026; the specification now carries the same wording, so the two agree.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>SV-8654 (TU spec v5 2026-07-29 S7-R1; S7-R2; S7-R3; S7-R4; S8-R2 — S8-R2 now adds "followed by the Column Selection control")</t>
+          <t>SV-8654 (TU spec v9 2026-08-17 S7-R1; S7-R2; S7-R3; S7-R4; S7-R4a; S8-R2 — the spec requires each of the four options by exact label and pins no menu order; S8-R2 gives the three-dot menu leftmost followed by Column Selection)</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr"/>
@@ -2711,14 +2685,14 @@
 · If it fails in a DIFFERENT way from what is described above, that is a NEW problem - please report it.
 · If it PASSES, the fix has shipped: tell the QA lead so the ticket can be closed and this note removed.
 ---
-This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Technician Utilization report specification version 7 (S7-R5, S7-R6, S7-R12), read on 11 August 2026.
+This is the expected behaviour as per epic SV-8582, read on 17 August 2026, and the Technician Utilization report specification version 9 (S7-R5, S7-R6, S7-R12), read on 17 August 2026.
 Last checked against build v3.5-16cf83f on 8/6/2026.
 AUTOMATION: READY - EXPECT FAIL (SV-8950)</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>SV-8654 (TU spec v5 2026-07-29 S7-R5; S7-R6; S7-R12)</t>
+          <t>SV-8654 (TU spec v9 2026-08-17 S7-R5; S7-R6; S7-R12)</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr"/>
@@ -2767,14 +2741,14 @@
 · If it fails in a DIFFERENT way from what is described above, that is a NEW problem - please report it.
 · If it PASSES, the fix has shipped: tell the QA lead so the ticket can be closed and this note removed.
 ---
-This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Technician Utilization report specification version 7 (S7-R7, S7-R10, S7-R12), read on 11 August 2026.
+This is the expected behaviour as per epic SV-8582, read on 17 August 2026, and the Technician Utilization report specification version 9 (S7-R7, S7-R10, S7-R12), read on 17 August 2026.
 Last checked against build v3.5-16cf83f on 8/6/2026.
 AUTOMATION: READY - EXPECT FAIL (SV-8951)</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>SV-8654 (TU spec v5 2026-07-29 S7-R7; S7-R10; S7-R12)</t>
+          <t>SV-8654 (TU spec v9 2026-08-17 S7-R7; S7-R10; S7-R12)</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr"/>
@@ -2831,14 +2805,14 @@
 Note for the tester: if the Location column does not behave this way on the build, mark this test Failed and report it - do not change the test.
 Location is one of the columns you can switch on and off in the column-selection control, but only if your own account can reach more than one location: for you it is already switched on when you arrive, and you can switch it off. Someone whose account can reach only one location never sees the column and it is not offered to them in that list.
 ---
-This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Technician Utilization report specification version 7 (S7-R8, S7-R9, S7-R10, S7-R13, S7-E1, S9-R8), read on 11 August 2026. Version 6 of that specification, published on 5 August 2026, is what settles the one point about the Location column: it now states in both of its own requirements that the column belongs to anyone whose account can reach more than one location and can be switched on and off in the column-selection control. Chris Ward asked for that change in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true, read on 11 August 2026
+This is the expected behaviour as per epic SV-8582, read on 17 August 2026, and the Technician Utilization report specification version 9 (S7-R8, S7-R9, S7-R10, S7-R13, S7-E1, S9-R8), read on 17 August 2026. Version 6 of that specification, published on 5 August 2026, is what settles the one point about the Location column: it now states in both of its own requirements that the column belongs to anyone whose account can reach more than one location and can be switched on and off in the column-selection control. Chris Ward asked for that change in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true, read on 17 August 2026
 Last checked against build v3.5-16cf83f on 8/6/2026.
 AUTOMATION: READY - EXPECT FAIL (SV-8948)</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>SV-8654 (TU spec v5 2026-07-29 S7-R8; S7-R9; S7-R10; S7-R13; S7-E1; S9-R8 — downloads mirror the shown columns and the technician/location/date scope; S7-R13 = the "Locations:" line and the automatic Location column)</t>
+          <t>SV-8654 (TU spec v9 2026-08-17 S7-R8; S7-R9; S7-R10; S7-R13; S7-E1; S9-R8 — downloads mirror the shown columns and the technician/location/date scope; S7-R13 = the "Locations:" line and the automatic Location column)</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr"/>
@@ -2887,14 +2861,14 @@
 · If it fails in a DIFFERENT way from what is described above, that is a NEW problem - please report it.
 · If it PASSES, the fix has shipped: tell the QA lead so the ticket can be closed and this note removed.
 ---
-This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Technician Utilization report specification version 7 (S7-R10, S7-R10a), read on 11 August 2026.
+This is the expected behaviour as per epic SV-8582, read on 17 August 2026, and the Technician Utilization report specification version 9 (S7-R10, S7-R10a), read on 17 August 2026.
 Last checked against build v3.5-16cf83f on 8/6/2026.
 AUTOMATION: READY - EXPECT FAIL (SV-8949)</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>SV-8654 (TU spec v5 2026-07-29 S7-R10; S7-R10a)</t>
+          <t>SV-8654 (TU spec v9 2026-08-17 S7-R10; S7-R10a)</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr"/>
@@ -2940,14 +2914,13 @@
 3. With a logo uploaded, that logo appears. If a logo is set but fails to load, the built-in ShopView logo is used instead. If no logo is uploaded at all, NO logo is printed and the text fills the space.
 Note for the tester: on this build a report with no uploaded logo still prints the built-in ShopView logo. The product owner has decided it should print no logo at all, so record what you see; the change is with the developers.
 ---
-This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and Chris Ward's decision of 8/5/2026, recorded in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true, read on 11 August 2026; where the Technician Utilization report specification version 7 (S7-R11, S7-N2, S7-N3), read on 11 August 2026, differs, his decision is the authority.
-Last checked against build v3.5-16cf83f on 8/6/2026.
-AUTOMATION: READY</t>
+This is the expected behaviour as per epic SV-8582, read on 17 August 2026, and Chris Ward's decision of 8/5/2026, recorded in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true, read on 17 August 2026; where the Technician Utilization report specification version 9 (S7-R11, S7-N2, S7-N3), read on 17 August 2026, differs, his decision is the authority.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>SV-8654 (TU spec v5 2026-07-29 S7-R11; S7-N2; S7-N3 — logo now resolved by the shared resolver: the organization's uploaded logo; else the bundled ShopView default)</t>
+          <t>SV-8654 (TU spec v9 2026-08-17 S7-R11; S7-N2; S7-N3 — logo now resolved by the shared resolver: the organization's uploaded logo; else the bundled ShopView default)</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr"/>
@@ -2995,14 +2968,14 @@
 · If it fails in a DIFFERENT way from what is described above, that is a NEW problem - please report it.
 · If it PASSES, the fix has shipped: tell the QA lead so the ticket can be closed and this note removed.
 ---
-This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Technician Utilization report specification version 7 (S7-N1), read on 11 August 2026.
+This is the expected behaviour as per epic SV-8582, read on 17 August 2026, and the Technician Utilization report specification version 9 (S7-N1), read on 17 August 2026.
 Last checked against build v3.5-16cf83f on 8/6/2026.
 AUTOMATION: READY - EXPECT FAIL (SV-8948)</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>SV-8654 (TU spec v5 2026-07-29 S7-N1; §7 context note)</t>
+          <t>SV-8654 (TU spec v9 2026-08-17 S7-N1; §7 context note)</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr"/>
@@ -3050,14 +3023,14 @@
 · If it fails in a DIFFERENT way from what is described above, that is a NEW problem - please report it.
 · If it PASSES, the fix has shipped: tell the QA lead so the ticket can be closed and this note removed.
 ---
-This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Technician Utilization report specification version 7 (§7 notifications table, Story 7 has no S, §7 is the closing reference), read on 11 August 2026.
+This is the expected behaviour as per epic SV-8582, read on 17 August 2026, and the Technician Utilization report specification version 9 (§7 notifications table, Story 7 has no S, §7 is the closing reference), read on 17 August 2026.
 Last checked against build v3.5-16cf83f on 8/6/2026.
 AUTOMATION: READY - EXPECT FAIL (SV-8952)</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>SV-8654 (TU spec v5 2026-07-29 Story 7 Error Handling + §7 notifications table — these CLOSE both strings verbatim ("Download started" / "Failed to download report"); Story 7 has no S-anchor for them so §7 is the closing reference)</t>
+          <t>SV-8654 (TU spec v9 2026-08-17 Story 7 Error Handling + §7 notifications table — these CLOSE both strings verbatim ("Download started" / "Failed to download report"); Story 7 has no S-anchor for them so §7 is the closing reference)</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr"/>
@@ -3108,14 +3081,14 @@
 - If it fails in a DIFFERENT way from what is described above, that is a NEW problem - please report it.
 - If it PASSES, the fix has shipped: tell the QA lead so the ticket can be closed and this note removed.
 ---
-This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Technician Utilization report specification version 7 (S7-R14), read on 11 August 2026, which was added to that specification on 2026-08-06 and states this row limit and its exact message. Before that the specification said nothing about a limit and this expectation came from the engineering plan of 2026-07-29; the written description now says the same thing, so the two agree.
+This is the expected behaviour as per epic SV-8582, read on 17 August 2026, and the Technician Utilization report specification version 9 (S7-R14), read on 17 August 2026, which was added to that specification on 2026-08-06 and states this row limit and its exact message. Before that the specification said nothing about a limit and this expectation came from the engineering plan of 2026-07-29; the written description now says the same thing, so the two agree.
 Last checked against build v3.5-16cf83f on 8/6/2026.
 AUTOMATION: READY - EXPECT FAIL (SV-8818)</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>SV-8654 (TU spec v5 2026-07-29 Story 7 exports — spec silent on a cap; tech-plan-2026-07-29 A3/FR-F4: suite-wide 10; 000-row export cap; locked by Chris 2026-07-21)</t>
+          <t>SV-8654 (TU spec v9 2026-08-17 S7-R14 — the 10;000-row export cap and its verbatim message are now IN the TU spec; previously spec-silent and sourced from tech-plan-2026-07-29 A3/FR-F4; locked by Chris 2026-07-21)</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr"/>
@@ -3168,14 +3141,14 @@
 · If it fails in a DIFFERENT way from what is described above, that is a NEW problem - please report it.
 · If it PASSES, the fix has shipped: tell the QA lead so the ticket can be closed and this note removed.
 ---
-This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Technician Utilization report specification version 7 (S7-R7), read on 11 August 2026, which says the spreadsheet always holds the technician rows and the Summary row and does not change with the Summary or Expanded choice. The test exists at all because of Chris Ward's decision of 8/5/2026, recorded in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true, read on 11 August 2026, - he asked this report's download menu to match Sales By Customer and Sales By Representative, which each offer a spreadsheet for both views, whereas that written description covers only one spreadsheet download. That his answer leaves the menu with four options is our reading of his words and he has not confirmed it.
+This is the expected behaviour as per epic SV-8582, read on 17 August 2026, and the Technician Utilization report specification version 9 (S7-R7), read on 17 August 2026, which says the spreadsheet always holds the technician rows and the Summary row and does not change with the Summary or Expanded choice. The test exists at all because of Chris Ward's decision of 8/5/2026, recorded in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true, read on 17 August 2026, - he asked this report's download menu to match Sales By Customer and Sales By Representative, which each offer a spreadsheet for both views, whereas that written description covers only one spreadsheet download. That his answer leaves the menu with four options is our reading of his words and he has not confirmed it.
 Last checked against build v3.5-16cf83f on 8/6/2026.
 AUTOMATION: READY - EXPECT FAIL (SV-8951)</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>SV-8654 (TU spec v5 2026-07-29 S7-R7 - the spreadsheet is always summary-level; a SECOND spreadsheet option exists only because of Chris Ward's answer T2-6 option B of 2026-08-05)</t>
+          <t>SV-8654 (TU spec v9 2026-08-17 S7-R7 - the spreadsheet is always summary-level; a SECOND spreadsheet option exists only because of Chris Ward's answer T2-6 option B of 2026-08-05)</t>
         </is>
       </c>
       <c r="I51" s="2" t="inlineStr"/>
@@ -3271,20 +3244,18 @@
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. The toolbar has a location filter labeled "Location" - a multi-select and the RIGHTMOST control.
+          <t>1. The toolbar has a location filter labeled "Location" - a multi-select and the RIGHTMOST control.
 2. It lists the locations the signed-in user has access to, plus an "All locations" option and a "Clear all" action. (If you only have access to one location, the "All locations" entry is not offered - you see "Clear all" and your one location.)
 3. "All locations" acts as a select-all shortcut: choosing it selects every accessible location; unchecking one location leaves the remaining specific locations selected - the selection is always the concrete set of checked locations.
 4. With more than one location selected, a Location column appears in the table and each row names its location - or reads "Multiple" for a technician whose hours span more than one of them. (Where that column sits on screen is checked by its own test.)
 ---
-This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Technician Utilization report specification version 7 (S9-R1), read on 11 August 2026.
-Last checked against build v3.5-16cf83f on 8/5/2026.
-AUTOMATION: READY
-</t>
+This is the expected behaviour as per epic SV-8582, read on 17 August 2026, and the Technician Utilization report specification version 9 (S9-R1), read on 17 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>SV-8656 (TU spec v5 2026-07-29 S9-R1 — per-row location identifier in All-Locations view ADDED per kickoff video P10 40:58-41:20; user ruling 2026-07-28: video overrides spec (video newer; last-update-wins))</t>
+          <t>SV-8656 (TU spec v9 2026-08-17 S9-R1 — per-row location identifier in All-Locations view ADDED per kickoff video P10 40:58-41:20; user ruling 2026-07-28: video overrides spec (video newer; last-update-wins))</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr"/>
@@ -3332,14 +3303,13 @@
 3. The technician's hours are POOLED across the selected locations into ONE row (one row per technician, not one per location); per-day rows pool the same way.
 4. Scoping never goes beyond the user's accessible locations - a location the user cannot access is never included.
 ---
-This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Technician Utilization report specification version 7 (S9-R3, S9-R4, S9-R5), read on 11 August 2026.
-Last checked against build v3.5-16cf83f on 8/6/2026.
-AUTOMATION: READY</t>
+This is the expected behaviour as per epic SV-8582, read on 17 August 2026, and the Technician Utilization report specification version 9 (S9-R3, S9-R4, S9-R5), read on 17 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>SV-8656 (TU spec v5 2026-07-29 S9-R3; S9-R4; S9-R5 + on-screen location-scope indicator per Chris Ward group message 2026-07-29 (chris-update-2026-07-29/chris-message-2026-07-29.md; NEWEST source; last-update-wins))</t>
+          <t>SV-8656 (TU spec v9 2026-08-17 S9-R3; S9-R4; S9-R5 + on-screen location-scope indicator per Chris Ward group message 2026-07-29 (chris-update-2026-07-29/chris-message-2026-07-29.md; NEWEST source; last-update-wins))</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr"/>
@@ -3384,14 +3354,13 @@
 3. The report loads without an error in both cases.
 4. The same fallback happens when you deselect every location by hand in the Location filter — the report loads the currently active location's rows rather than showing nothing.
 ---
-This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Technician Utilization report specification version 7 (S9-R6, S1-R8, S9-R2, S9-R7), read on 11 August 2026.
-Last checked against build v3.5-16cf83f on 8/6/2026.
-AUTOMATION: READY</t>
+This is the expected behaviour as per epic SV-8582, read on 17 August 2026, and the Technician Utilization report specification version 9 (S9-R6, S1-R8, S9-R2, S9-R7), read on 17 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>SV-8656 (TU spec v5 2026-07-29 S9-R6; S1-R8; S9-R2; S9-R7)</t>
+          <t>SV-8656 (TU spec v9 2026-08-17 S9-R6; S1-R8; S9-R2; S9-R7)</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr"/>
@@ -3435,14 +3404,14 @@
           <t>1. For the single-location user the Location filter is NOT shown at all — the report simply shows that one location's data.
 2. For the user with access to two or more locations the Location filter IS shown.
 ---
-This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Technician Utilization report specification version 7 (S9-N1), read on 11 August 2026. Chris Ward confirmed this on 8/5/2026 in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true, read on 11 August 2026
+This is the expected behaviour as per epic SV-8582, read on 17 August 2026, and the Technician Utilization report specification version 9 (S9-N1), read on 17 August 2026. Chris Ward confirmed this on 8/5/2026 in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true, read on 17 August 2026
 Last checked against build v3.5-16cf83f on 8/6/2026.
 AUTOMATION: HOLD - needs a second sign-in as a user who can reach only one location, and there is one shared sign-in on this environment</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>SV-8656 (TU spec S9-N1 — RULED HIDDEN by Chris Ward answer 2026-07-31 Q1=A "classic spec drift"; the S9-N1 "still sees the filter" note is stale; spec edit pending)</t>
+          <t>SV-8656 (TU spec v9 2026-08-17 S9-N1 — RULED HIDDEN by Chris Ward answer 2026-07-31 Q1=A; S9-N1 now reads "A user with access to only one location does not see the filter; it is hidden"; so his spec edit is DONE and the note is no longer stale)</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr"/>
@@ -3505,14 +3474,14 @@
 - If it PASSES, the fix has shipped: tell the QA lead so this note can be removed.
 Also today: the column is drawn SECOND, after Technician, not leftmost as item 1 requires - count that as part of the same failure. Item 3 CAN now be checked on this environment: a technician with hours at more than one location does show "Multiple" (seen on 8/10/2026). Item 6 still needs a second sign-in as a one-location user.
 ---
-This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Technician Utilization report specification version 7 (S9-R9, S9-R10, S8-R15, S10-R4, S7-R13, S2-R1), read on 11 August 2026. Chris Ward confirmed this same access-gated, switchable rule in his answers of 8/10/2026, in this file: build/report-suite/chris-answers-2026-08-10/ - his answer and the specification agree.
+This is the expected behaviour as per epic SV-8582, read on 17 August 2026, and the Technician Utilization report specification version 9 (S9-R9, S9-R10, S8-R15, S10-R4, S7-R13, S2-R1), read on 17 August 2026. Chris Ward confirmed this same access-gated, switchable rule in his answers of 8/10/2026, in this file: build/report-suite/chris-answers-2026-08-10/ - his answer and the specification agree.
 Last checked against build v3.5-4795eee on 8/10/2026.
 AUTOMATION: READY - EXPECT FAIL (SV-8954)</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>SV-8656; SV-8654 (TU spec v5 2026-07-29 S9-R9; S9-R10; S8-R15; S10-R4; S7-R13 — per-row Location column; leftmost before Technician; "Multiple" on a spanning row; Summary row blank; not in the selector; S7-R13 = same column in every download)</t>
+          <t>SV-8620; SV-8637 (TU spec v9 2026-08-17 S9-R9; S9-R10; S8-R15; S10-R4; S7-R13; S2-R1 - access-gated toggleable Location column; leftmost before Technician; "Multiple" on a multi-location row; blank on Summary; present in every export)</t>
         </is>
       </c>
       <c r="I57" s="2" t="inlineStr"/>
@@ -3559,7 +3528,7 @@
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. The control is an icon button whose tooltip reads "Column Selection", sitting immediately after the three-dot download menu in the toolbar.
+          <t>1. The control is an icon button whose tooltip reads "Column Selection", sitting immediately after the three-dot download menu in the toolbar.
 2. Because the button shows an icon and no text, it still carries a name that assistive technology reads out — it is not left unnamed.
 3. The list offers a toggle for each data column — Total Hours, WO Hours, Internal Hours, Utilization % and Est. Lost Labor — and all five are on by default. If your login can reach more than one location, Location is listed as well and is also on by default.
 4. Technician is always shown and cannot be turned off (it is not offered as a toggle).
@@ -3568,15 +3537,13 @@
 7. Est. Lost Labor can now be hidden like any other column (it used to be always on).
 8. Your column choice is remembered in this browser and is still applied when you come back.
 ---
-This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Technician Utilization report specification version 7 (S10-R1, S10-R2, S10-R3, S10-R4, S10-R5, S10-R6, S9-R9, S8-R16), read on 11 August 2026.
-Last checked against build v3.5-16cf83f on 8/5/2026.
-AUTOMATION: READY
-</t>
+This is the expected behaviour as per epic SV-8582, read on 17 August 2026, and the Technician Utilization report specification version 9 (S10-R1, S10-R2, S10-R3, S10-R4, S10-R5, S10-R6, S9-R9, S8-R16), read on 17 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>SV-8655; SV-8582 (TU spec v5 2026-07-29 Story 10 S10-R1; S10-R2; S10-R3; S10-R4; S10-R5; S10-R6 column selector + Story 8 S8-R16 accessible name — Story 10 has NO owning Jira story so epic SV-8582 is used and FLAGGED; S8-R16 is owned by SV-8655)</t>
+          <t>SV-8655; SV-8582 (TU spec v9 2026-08-17 S10-R1; S10-R2; S10-R3; S10-R4; S10-R5; S10-R6 column selector incl. the toggleable Location column per S9-R9 + S8-R16 accessible name — Story 10 has NO owning Jira story so epic SV-8582 is used and FLAGGED)</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr"/>
@@ -3621,14 +3588,13 @@
 2. The toolbar controls run, left to right: the three-dot download menu, the Column Selection control, the date-range picker, the technician filter, and the Location filter (rightmost).
 3. The expand/collapse-all control is NOT a toolbar control - it lives in the table header (in the Technician column).
 ---
-This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Technician Utilization report specification version 7 (S8-R1, S8-R2, S8-R3), read on 11 August 2026.
-Last checked against build v3.5-16cf83f on 8/6/2026.
-AUTOMATION: READY</t>
+This is the expected behaviour as per epic SV-8582, read on 17 August 2026, and the Technician Utilization report specification version 9 (S8-R1, S8-R2, S8-R3), read on 17 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t>SV-8655 (TU spec v5 2026-07-29 S8-R1; S8-R2; S8-R3 — toolbar order rewritten: Column Selection inserted after the three-dot menu; and the date-range picker now precedes the technician filter)</t>
+          <t>SV-8655 (TU spec v9 2026-08-17 S8-R1; S8-R2; S8-R3 — toolbar order rewritten: Column Selection inserted after the three-dot menu; and the date-range picker now precedes the technician filter)</t>
         </is>
       </c>
       <c r="I59" s="2" t="inlineStr"/>
@@ -3676,14 +3642,13 @@
 3. The Total Hours link's non-color affordance and focus indicator apply in both modes.
 4. Note for the tester: you do not need to measure anything and you do not need any tool. Just say whether you can see the icon easily in both modes, and only report it if you cannot. (The design rule behind this is a minimum 3:1 contrast ratio, which the design and engineering team check with a contrast tool - not by hand.)
 ---
-This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Technician Utilization report specification version 7 (S8-R9, S8-R13, S8-R14), read on 11 August 2026.
-Last checked against build v3.5-16cf83f on 8/6/2026.
-AUTOMATION: READY</t>
+This is the expected behaviour as per epic SV-8582, read on 17 August 2026, and the Technician Utilization report specification version 9 (S8-R9, S8-R13, S8-R14), read on 17 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>SV-8655 (TU spec v5 2026-07-29 S8-R9; S8-R13; S8-R14 — dark-mode legibility of every named element; the info icon at ≥ 3:1 in both modes; the Total Hours link affordance/focus in both modes; the ratio is design-token-owned)</t>
+          <t>SV-8655 (TU spec v9 2026-08-17 S8-R9; S8-R13; S8-R14 — dark-mode legibility of every named element; the info icon at ≥ 3:1 in both modes; the Total Hours link affordance/focus in both modes; the ratio is design-token-owned)</t>
         </is>
       </c>
       <c r="I60" s="2" t="inlineStr"/>
@@ -3729,14 +3694,13 @@
 2. Expanding a technician row issues an on-demand backend request that returns that technician's per-day breakdown.
 3. Because expansion state resets (all collapsed) on any data reload, nothing is lost by the lazy loading - re-expanding fetches fresh day data.
 ---
-This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Technician Utilization report specification version 7 (S4-R2, S4-R5), read on 11 August 2026.
-Last checked against build v3.5-16cf83f on 8/6/2026.
-AUTOMATION: READY</t>
+This is the expected behaviour as per epic SV-8582, read on 17 August 2026, and the Technician Utilization report specification version 9 (S4-R2, S4-R5), read on 17 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>SV-8651 (TU spec v5 2026-07-29 S4-R2; S4-R5)</t>
+          <t>SV-8651 (TU spec v9 2026-08-17 S4-R2; S4-R5)</t>
         </is>
       </c>
       <c r="I61" s="2" t="inlineStr"/>
@@ -3788,14 +3752,14 @@
 · If it fails in a DIFFERENT way from what is described above, that is a NEW problem - please report it.
 · If it PASSES, the fix has shipped: tell the QA lead so the ticket can be closed and this note removed.
 ---
-This is the expected behaviour as per epic SV-8582, read on 11 August 2026, and the Technician Utilization report specification version 7 (S1-R5, S9-R3, S2-R13), read on 11 August 2026.
+This is the expected behaviour as per epic SV-8582, read on 17 August 2026, and the Technician Utilization report specification version 9 (S1-R5, S9-R3, S2-R13), read on 17 August 2026.
 Last checked against build v3.5-16cf83f on 8/6/2026.
 AUTOMATION: READY - EXPECT FAIL (SV-8945)</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>SV-8648 (TU spec v5 2026-07-29 S1-R5; S9-R3; S5 context note; S2-R13; §3)</t>
+          <t>SV-8648 (TU spec v9 2026-08-17 S1-R5; S9-R3; S5 context note; S2-R13; §3)</t>
         </is>
       </c>
       <c r="I62" s="2" t="inlineStr"/>

--- a/testrail-import/Report-Suite_Technician-Utilization-Report_testrail-import.xlsx
+++ b/testrail-import/Report-Suite_Technician-Utilization-Report_testrail-import.xlsx
@@ -528,7 +528,7 @@
 3. The entry sits BELOW the pre-existing report links — Sales, Technician Efficiency, Advisor Analysis, Shop Efficiency — the new reports are added below those items without moving or disturbing them.
 ---
 This is the expected behaviour as per epic SV-8582, read on 17 August 2026, and the Technician Utilization report specification version 9 (S1-R1), read on 17 August 2026.
-AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026</t>
+AUTOMATION: READY</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
@@ -578,7 +578,7 @@
 2. Technician B has NO row - only technicians with clocked time in the selected range at the selected location(s) appear.
 ---
 This is the expected behaviour as per epic SV-8582, read on 17 August 2026, and the Technician Utilization report specification version 9 (S1-R2), read on 17 August 2026.
-AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026</t>
+AUTOMATION: READY</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
 3. A Custom span wider than 366 days (matching the largest preset) is rejected - it cannot be applied.
 ---
 This is the expected behaviour as per epic SV-8582, read on 17 August 2026, and the Technician Utilization report specification version 9 (S1-R4, S1-R5), read on 17 August 2026.
-AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026</t>
+AUTOMATION: READY</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -735,7 +735,7 @@
 3. The toolbar remains interactive during the load.
 ---
 This is the expected behaviour as per epic SV-8582, read on 17 August 2026, and the Technician Utilization report specification version 9 (S1-R10), read on 17 August 2026.
-AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026</t>
+AUTOMATION: READY</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -789,7 +789,7 @@
 4. This matches the Timesheet Activities report's single-time-zone grouping.
 ---
 This is the expected behaviour as per epic SV-8582, read on 17 August 2026, and the Technician Utilization report specification version 9 (S1-R7), read on 17 August 2026.
-AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026</t>
+AUTOMATION: READY</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -890,7 +890,7 @@
 3. Clearing every technician shows the SAME message and hides the Summary row — this version does not use distinct copy for genuinely-no-data vs a cleared filter.
 ---
 This is the expected behaviour as per epic SV-8582, read on 17 August 2026, and the Technician Utilization report specification version 9 (S1-N2, S3-N1, S5-N1, S9-N2), read on 17 August 2026.
-AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026</t>
+AUTOMATION: READY</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -949,7 +949,7 @@
 Location is one of the columns you can switch on and off in the column-selection control, but only if your own account can reach more than one location: for you it is already switched on when you arrive, and you can switch it off. Someone whose account can reach only one location never sees the column and it is not offered to them in that list.
 ---
 This is the expected behaviour as per epic SV-8582, read on 17 August 2026, and the Technician Utilization report specification version 9 (S2-R1, S2-R2, S2-R3, S2-R4, S2-R5, S9-R9), read on 17 August 2026. Version 6 of that specification, published on 5 August 2026, is what settles the one point about the Location column: it now states in both of its own requirements that the column belongs to anyone whose account can reach more than one location and can be switched on and off in the column-selection control. Chris Ward asked for that change in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true, read on 17 August 2026
-AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026</t>
+AUTOMATION: READY</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
@@ -998,7 +998,7 @@
 2. It shows one decimal place followed by a percent sign, rounded round-half-up (66.65% → 66.7%).
 ---
 This is the expected behaviour as per epic SV-8582, read on 17 August 2026, and the Technician Utilization report specification version 9 (S2-R6, S2-R7), read on 17 August 2026.
-AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026</t>
+AUTOMATION: READY</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -1049,7 +1049,7 @@
 3. The "—" (undefined, total = 0) state is unreachable on a rendered technician or day row, because only technicians with clocked time get rows.
 ---
 This is the expected behaviour as per epic SV-8582, read on 17 August 2026, and the Technician Utilization report specification version 9 (S2-E1, S2-R7), read on 17 August 2026.
-AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026</t>
+AUTOMATION: READY</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
@@ -1102,7 +1102,7 @@
 3. The value shows as dollars with two decimals and commas between thousands (e.g. "$1,234.50").
 ---
 This is the expected behaviour as per epic SV-8582, read on 17 August 2026, and the Technician Utilization report specification version 9 (S2-R8, S2-R9), read on 17 August 2026.
-AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026</t>
+AUTOMATION: READY</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1156,7 +1156,7 @@
 4. Est. Lost Labor can be turned OFF in the Column Selection control; when it is off the column, its bold styling and its information icon are all absent, and the report still works normally.
 ---
 This is the expected behaviour as per epic SV-8582, read on 17 August 2026, and the Technician Utilization report specification version 9 (S2-R10, S2-R11, S8-R4, S8-R6, S8-R7, S8-N1, S10-R3), read on 17 August 2026.
-AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026</t>
+AUTOMATION: READY</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
@@ -1207,7 +1207,7 @@
 3. "$0.00" means 'the rate is known and there is nothing (or $0) to value' - a different state from "—" ('the rate is unknown').
 ---
 This is the expected behaviour as per epic SV-8582, read on 17 August 2026, and the Technician Utilization report specification version 9 (S2-E2), read on 17 August 2026.
-AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026</t>
+AUTOMATION: READY</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -1363,7 +1363,7 @@
 3. The active sort header exposes its state to assistive technology (aria-sort = ascending on the Technician header; none on the others).
 ---
 This is the expected behaviour as per epic SV-8582, read on 17 August 2026, and the Technician Utilization report specification version 9 (S2-R12, S8-R8, S8-R10), read on 17 August 2026.
-AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026</t>
+AUTOMATION: READY</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
 5. Technicians tied in the sorted column are ordered by Technician name A to Z; two technicians sharing the same display name keep a stable order between renders.
 ---
 This is the expected behaviour as per epic SV-8582, read on 17 August 2026, and the Technician Utilization report specification version 9 (S2-R13, S2-R14), read on 17 August 2026.
-AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026</t>
+AUTOMATION: READY</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
@@ -1468,7 +1468,7 @@
 2. On the return visit, the sort is again Technician A to Z - sort is NOT persisted (unlike the date range, technician selection, and location selection, which are).
 ---
 This is the expected behaviour as per epic SV-8582, read on 17 August 2026, and the Technician Utilization report specification version 9 (S2-R15), read on 17 August 2026.
-AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026</t>
+AUTOMATION: READY</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
@@ -1519,7 +1519,7 @@
 3. Each technician's expanded day rows stay under that technician, still in date order (earliest to latest) - they do not re-sort by the clicked column.
 ---
 This is the expected behaviour as per epic SV-8582, read on 17 August 2026, and the Technician Utilization report specification version 9 (S2-R16), read on 17 August 2026.
-AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026</t>
+AUTOMATION: READY</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
@@ -1623,7 +1623,7 @@
 4. Its values carry NO label prefix such as "TOTAL:" or "AVG:".
 ---
 This is the expected behaviour as per epic SV-8582, read on 17 August 2026, and the Technician Utilization report specification version 9 (S3-R1, S3-R2, S3-R6, S3-R7, S8-R5), read on 17 August 2026.
-AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026</t>
+AUTOMATION: READY</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
@@ -1674,7 +1674,7 @@
 3. With every technician selected, the Summary row equals the shop totals for the full date range at the selected location(s).
 ---
 This is the expected behaviour as per epic SV-8582, read on 17 August 2026, and the Technician Utilization report specification version 9 (S3-R3, S5-E1), read on 17 August 2026.
-AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026</t>
+AUTOMATION: READY</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
@@ -1724,7 +1724,7 @@
 2. It is NOT the average of the per-technician percentages (not 50.0%).
 ---
 This is the expected behaviour as per epic SV-8582, read on 17 August 2026, and the Technician Utilization report specification version 9 (S3-R4), read on 17 August 2026.
-AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026</t>
+AUTOMATION: READY</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
@@ -1774,7 +1774,7 @@
 3. The Summary shows "—" only when EVERY visible technician's Est. Lost Labor is "—".
 ---
 This is the expected behaviour as per epic SV-8582, read on 17 August 2026, and the Technician Utilization report specification version 9 (S3-R5), read on 17 August 2026.
-AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026</t>
+AUTOMATION: READY</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
@@ -1886,7 +1886,7 @@
 5. Note for the tester: you do not need developer tools for this test - just watch the screen.
 ---
 This is the expected behaviour as per epic SV-8582, read on 17 August 2026, and the Technician Utilization report specification version 9 (S4-R2, S4-N1, S9-R4), read on 17 August 2026.
-AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026</t>
+AUTOMATION: READY</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
@@ -1937,7 +1937,7 @@
 3. Hours 2dp / Utilization one decimal + % / dollars with commas - all identical to the row formats, computed from unrounded values and rounded once.
 ---
 This is the expected behaviour as per epic SV-8582, read on 17 August 2026, and the Technician Utilization report specification version 9 (S4-R3, S2-R8), read on 17 August 2026.
-AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026</t>
+AUTOMATION: READY</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
@@ -2047,7 +2047,7 @@
 3. Deselecting and re-selecting a technician (an on-screen operation) does NOT change the expansion state of the other rows - the expanded row stays expanded.
 ---
 This is the expected behaviour as per epic SV-8582, read on 17 August 2026, and the Technician Utilization report specification version 9 (S4-R5), read on 17 August 2026.
-AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026</t>
+AUTOMATION: READY</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
@@ -2098,7 +2098,7 @@
 3. All technicians' rows are shown.
 ---
 This is the expected behaviour as per epic SV-8582, read on 17 August 2026, and the Technician Utilization report specification version 9 (S5-R1, S5-R2), read on 17 August 2026.
-AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026</t>
+AUTOMATION: READY</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
@@ -2266,7 +2266,7 @@
 3. The saved date range and location selection are restored alongside.
 ---
 This is the expected behaviour as per epic SV-8582, read on 17 August 2026, and the Technician Utilization report specification version 9 (S5-R10, S1-R8), read on 17 August 2026.
-AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026</t>
+AUTOMATION: READY</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
@@ -2369,7 +2369,7 @@
 3. It uses the same date range that was active on the Technician Utilization report.
 ---
 This is the expected behaviour as per epic SV-8582, read on 17 August 2026, and the Technician Utilization report specification version 9 (S6-R2, S6-R3, S6-R4), read on 17 August 2026.
-AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026</t>
+AUTOMATION: READY</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
@@ -2632,7 +2632,7 @@
 3. The order these four options appear in is NOT part of this check. The specification requires each option to be present with that exact label; it does not fix the order they are listed in. Do not fail this test on the order alone.
 ---
 This is the expected behaviour as per epic SV-8582, read on 17 August 2026, and its story SV-8654, read on 17 August 2026, and the Technician Utilization report specification version 9 (S7-R1, S7-R2, S7-R3, S7-R4, S7-R4a, S8-R2), read on 17 August 2026. Chris Ward asked for this menu wording in his answers of 5 August 2026 in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true, read on 17 August 2026; the specification now carries the same wording, so the two agree.
-AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026</t>
+AUTOMATION: READY</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
@@ -2915,7 +2915,7 @@
 Note for the tester: on this build a report with no uploaded logo still prints the built-in ShopView logo. The product owner has decided it should print no logo at all, so record what you see; the change is with the developers.
 ---
 This is the expected behaviour as per epic SV-8582, read on 17 August 2026, and Chris Ward's decision of 8/5/2026, recorded in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true, read on 17 August 2026; where the Technician Utilization report specification version 9 (S7-R11, S7-N2, S7-N3), read on 17 August 2026, differs, his decision is the authority.
-AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026</t>
+AUTOMATION: READY</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
@@ -3250,7 +3250,7 @@
 4. With more than one location selected, a Location column appears in the table and each row names its location - or reads "Multiple" for a technician whose hours span more than one of them. (Where that column sits on screen is checked by its own test.)
 ---
 This is the expected behaviour as per epic SV-8582, read on 17 August 2026, and the Technician Utilization report specification version 9 (S9-R1), read on 17 August 2026.
-AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026</t>
+AUTOMATION: READY</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
@@ -3304,7 +3304,7 @@
 4. Scoping never goes beyond the user's accessible locations - a location the user cannot access is never included.
 ---
 This is the expected behaviour as per epic SV-8582, read on 17 August 2026, and the Technician Utilization report specification version 9 (S9-R3, S9-R4, S9-R5), read on 17 August 2026.
-AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026</t>
+AUTOMATION: READY</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
@@ -3355,7 +3355,7 @@
 4. The same fallback happens when you deselect every location by hand in the Location filter — the report loads the currently active location's rows rather than showing nothing.
 ---
 This is the expected behaviour as per epic SV-8582, read on 17 August 2026, and the Technician Utilization report specification version 9 (S9-R6, S1-R8, S9-R2, S9-R7), read on 17 August 2026.
-AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026</t>
+AUTOMATION: READY</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
@@ -3538,7 +3538,7 @@
 8. Your column choice is remembered in this browser and is still applied when you come back.
 ---
 This is the expected behaviour as per epic SV-8582, read on 17 August 2026, and the Technician Utilization report specification version 9 (S10-R1, S10-R2, S10-R3, S10-R4, S10-R5, S10-R6, S9-R9, S8-R16), read on 17 August 2026.
-AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026</t>
+AUTOMATION: READY</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
@@ -3589,7 +3589,7 @@
 3. The expand/collapse-all control is NOT a toolbar control - it lives in the table header (in the Technician column).
 ---
 This is the expected behaviour as per epic SV-8582, read on 17 August 2026, and the Technician Utilization report specification version 9 (S8-R1, S8-R2, S8-R3), read on 17 August 2026.
-AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026</t>
+AUTOMATION: READY</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
@@ -3643,7 +3643,7 @@
 4. Note for the tester: you do not need to measure anything and you do not need any tool. Just say whether you can see the icon easily in both modes, and only report it if you cannot. (The design rule behind this is a minimum 3:1 contrast ratio, which the design and engineering team check with a contrast tool - not by hand.)
 ---
 This is the expected behaviour as per epic SV-8582, read on 17 August 2026, and the Technician Utilization report specification version 9 (S8-R9, S8-R13, S8-R14), read on 17 August 2026.
-AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026</t>
+AUTOMATION: READY</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
@@ -3695,7 +3695,7 @@
 3. Because expansion state resets (all collapsed) on any data reload, nothing is lost by the lazy loading - re-expanding fetches fresh day data.
 ---
 This is the expected behaviour as per epic SV-8582, read on 17 August 2026, and the Technician Utilization report specification version 9 (S4-R2, S4-R5), read on 17 August 2026.
-AUTOMATION: Not available on Build to test Yet - Last checked 8/17/2026</t>
+AUTOMATION: READY</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
